--- a/resources/tenable/TenableWAS_JuiceShop.xlsx
+++ b/resources/tenable/TenableWAS_JuiceShop.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Vulnerabilities" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,99 +417,99 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>solution</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>impact</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>references</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>severity</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>host</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>port</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>protocol</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
         <is>
           <t>cvss</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>plugin</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>plugin_details</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>instances</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
         <is>
           <t>detection_method</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>detection_result</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>http_info</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>identification</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>impact</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>insight</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>log_method</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>port</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>product_detection_result</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>protocol</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>references</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>severity</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>plugin</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>solution</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>instances</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>source</t>
         </is>
       </c>
     </row>
@@ -533,12 +521,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>['10.0', 'CVSS:3.0/AV:N/AC:L/PR:N/UI:N/S:C/C:H/I:H/A:H', '10.0', 'CVSS2#AV:N/AC:L/Au:N/C:C/I:C/A:C']</t>
+          <t>['The installation of PHP detected on the remote host is no longer supported. Lack of support implies that no new security patches for the product will be released by the vendor. As a result, it is likely to contain security vulnerabilities.']</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>['The installation of PHP detected on the remote host is no longer supported. Lack of support implies that no new security patches for the product will be released by the vendor. As a result, it is likely to contain security vulnerabilities.']</t>
+          <t>['Upgrade to a supported version of PHP.']</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -548,67 +536,68 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['CWE 16', 'WASC Application Misconfiguration', 'OWASP 2021-A5', 'OWASP 2013-A5', 'OWASP 2013-A9', 'OWASP 2017-A9', 'OWASP 2017-A6', 'OWASP 2021-A6', 'OWASP 2010-A6', 'OWASP 2023-API8', 'OWASP 2019-API7']</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>['CVSSV3 BASE SCORE 10.0', 'CVSSV3 VECTOR CVSS:3.0/AV:N/AC:L/PR:N/UI:N/S:C/C:H/I:H/A:H', 'CVSS BASE SCORE 10.0', 'CVSS VECTOR CVSS2#AV:N/AC:L/Au:N/C:C/I:C/A:C']</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>98230</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"publication_date": "2018-08-09T00:00:00+00:00",
+"modification_date": "2024-01-11T00:00:00+00:00",
+"family": "Component Vulnerability",
+"severity": "Critical",
+"plugin_id": 98230}
+</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>['CWE 16', 'WASC Application Misconfiguration', 'OWASP 2021-A5, 2013-A5, 2013-A9, 2017-A9, 2017-A6, 2021-A6, 2010-A6, 2023-API8, 2019-API7', 'CVE -', 'BID -']</t>
+          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/#/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Technology PHP version 5.5.9 has been detected. Upgrade to the last supported version of PHP: 8.1', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/info_install.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Technology PHP version 5.5.9 has been detected. Upgrade to the last supported version of PHP: 8.1', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/soap/nusoap.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Technology PHP version 5.5.9 has been detected. Upgrade to the last supported version of PHP: 8.1', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/user_new.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Technology PHP version 5.5.9 has been detected. Upgrade to the last supported version of PHP: 8.1', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/phpinfo.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Technology PHP version 5.5.9 has been detected. Upgrade to the last supported version of PHP: 8.1', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/soap/class.wsdlcache.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Technology PHP version 5.5.9 has been detected. Upgrade to the last supported version of PHP: 8.1', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/portal.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Technology PHP version 5.5.9 has been detected. Upgrade to the last supported version of PHP: 8.1', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/install.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Technology PHP version 5.5.9 has been detected. Upgrade to the last supported version of PHP: 8.1', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/soap/class.nusoap_base.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Technology PHP version 5.5.9 has been detected. Upgrade to the last supported version of PHP: 8.1', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/soap/class.soap_fault.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Technology PHP version 5.5.9 has been detected. Upgrade to the last supported version of PHP: 8.1', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/info.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Technology PHP version 5.5.9 has been detected. Upgrade to the last supported version of PHP: 8.1', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/login.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Technology PHP version 5.5.9 has been detected. Upgrade to the last supported version of PHP: 8.1', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/training_install.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Technology PHP version 5.5.9 has been detected. Upgrade to the last supported version of PHP: 8.1', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/training.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Technology PHP version 5.5.9 has been detected. Upgrade to the last supported version of PHP: 8.1', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>CRITICAL</t>
-        </is>
-      </c>
-      <c r="P2" t="n">
-        <v>98230</v>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>['Upgrade to a supported version of PHP.']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/#/', 'input_type': 'link', 'input_name': None, 'payload': None, 'proof': 'Technology PHP version 5.5.9 has been detected.', 'output': 'Upgrade to the last supported version of PHP: 8.1', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/info_install.php', 'input_type': 'link', 'input_name': None, 'payload': None, 'proof': 'Technology PHP version 5.5.9 has been detected.', 'output': 'Upgrade to the last supported version of PHP: 8.1', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/soap/nusoap.php', 'input_type': 'link', 'input_name': None, 'payload': None, 'proof': 'Technology PHP version 5.5.9 has been detected.', 'output': 'Upgrade to the last supported version of PHP: 8.1', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/user_new.php', 'input_type': 'link', 'input_name': None, 'payload': None, 'proof': 'Technology PHP version 5.5.9 has been detected.', 'output': 'Upgrade to the last supported version of PHP: 8.1', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/phpinfo.php', 'input_type': 'link', 'input_name': None, 'payload': None, 'proof': 'Technology PHP version 5.5.9 has been detected.', 'output': 'Upgrade to the last supported version of PHP: 8.1', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -620,12 +609,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>['9.1', 'CVSS:3.0/AV:N/AC:L/PR:N/UI:N/S:U/C:H/I:N/A:H', '7.8', 'CVSS2#AV:N/AC:L/Au:N/C:N/I:N/A:C']</t>
+          <t>['According to its banner, the version of Apache running on the remote host is 2.4.x prior to 2.4.41. It is, therefore, affected by multiple vulnerabilities:', '- A cross-site scripting (XSS) vulnerability exists in mod_proxy when proxying is enabled and Proxy Error page is displayed. (CVE-2019-10092)', '- An open redirect vulnerability exists in mod_rewrite when using self-referential redirects. (CVE-2019-10098)', '- A read-after-free vulnerability exists in mod_http2 during connection shutdown. (CVE-2019-10082)', '- A memory corruption vulnerability exists in mod_http2 on early pushes. (CVE-2019-10081)', '- A denial of service (DoS) vulnerability exists in mod_http2 by exhausting h2 workers. (CVE-2019-9517)', '- A stack buffer overflow and NULL pointer dereference vulnerabilities exist in mod_remoteip when using a specially crafted PROXY header. (CVE-2019-10097)', ""Note that the scanner has not tested for these issues but has instead relied only on the application's self-reported version number."", 'According to its banner, the version of Apache running on the remote host is 2.4.x prior to 2.4.41. It is, therefore, affected by multiple vulnerabilities.']</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>['According to its banner, the version of Apache running on the remote host is 2.4.x prior to 2.4.41. It is, therefore, affected by multiple vulnerabilities:', '- A cross-site scripting (XSS) vulnerability exists in mod_proxy when proxying is enabled and Proxy Error page is displayed. (CVE-2019-10092)', '- An open redirect vulnerability exists in mod_rewrite when using self-referential redirects. (CVE-2019-10098)', '- A read-after-free vulnerability exists in mod_http2 during connection shutdown. (CVE-2019-10082)', '- A memory corruption vulnerability exists in mod_http2 on early pushes. (CVE-2019-10081)', '- A denial of service (DoS) vulnerability exists in mod_http2 by exhausting h2 workers. (CVE-2019-9517)', '- A stack buffer overflow and NULL pointer dereference vulnerabilities exist in mod_remoteip when using a specially crafted PROXY header. (CVE-2019-10097)', ""Note that the scanner has not tested for these issues but has instead relied only on the application's self-reported version number."", 'According to its banner, the version of Apache running on the remote host is 2.4.x prior to 2.4.41. It is, therefore, affected by multiple vulnerabilities.']</t>
+          <t>['Upgrade to Apache version 2.4.41 or later.']</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -635,67 +624,68 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['CWE 125', 'CWE 476', 'CWE 601', 'CWE 787', 'CWE 770', 'CWE 416', 'CWE 79', 'CWE 400', 'WASC Buffer Overflow', 'WASC Cross-Site Scripting', 'WASC Denial of Service', 'WASC URL Redirector Abuse', 'OWASP 2021-A3', 'OWASP 2021-A6', 'OWASP 2010-A2', 'OWASP 2021-A1', 'OWASP 2010-A10', 'OWASP 2013-A9', 'OWASP 2017-A7', 'OWASP 2017-A9', 'OWASP 2013-A10', 'OWASP 2013-A3', 'OWASP 2019-API7', 'OWASP 2023-API8', 'CVE-2019-10082', 'CVE-2019-10098', 'CVE-2019-9517', 'CVE-2019-10092', 'CVE-2019-10081', 'CVE-2019-10097']</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>['CVSSV3 BASE SCORE 9.1', 'CVSSV3 VECTOR CVSS:3.0/AV:N/AC:L/PR:N/UI:N/S:U/C:H/I:N/A:H', 'CVSS BASE SCORE 7.8', 'CVSS VECTOR CVSS2#AV:N/AC:L/Au:N/C:N/I:N/A:C']</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>98669</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"publication_date": "2019-08-20T00:00:00+00:00",
+"modification_date": "2023-03-14T00:00:00+00:00",
+"family": "Component Vulnerability",
+"severity": "Critical",
+"plugin_id": 98669}
+</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>['CWE 125, 476, 601, 787, 770, 416, 79, 400', 'WASC Buffer Overflow, Cross-Site Scripting, Denial of Service, URL Redirector Abuse', 'OWASP 2021-A3, 2021-A6, 2010-A2, 2021-A1, 2010-A10, 2013-A9, 2017']</t>
+          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Current Version: 2.4.7 Fixed Version: 2.4.41 Detected technology URL: https://juice-shop-388277804329.us-west1.run.app/apps/', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>CRITICAL</t>
-        </is>
-      </c>
-      <c r="P3" t="n">
-        <v>98669</v>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>['Upgrade to Apache version 2.4.41 or later.']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/', 'input_type': 'link', 'input_name': None, 'payload': None, 'proof': 'Current Version: 2.4.7', 'output': 'Fixed Version: 2.4.41', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -707,12 +697,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>['9.8', 'CVSS:3.0/AV:N/AC:L/PR:N/UI:N/S:U/C:H/I:H/A:H', '7.5', 'CVSS2#AV:N/AC:L/Au:N/C:P/I:P/A:P']</t>
+          <t>['According to its banner, the version of Apache running on the remote host is 2.4.x prior to 2.4.26. It is, therefore, affected by the following vulnerabilities :', '- An authentication bypass vulnerability exists due to third-party modules using the ap_get_basic_auth_pw() function outside of the authentication phase. An unauthenticated, remote attacker can exploit this to bypass authentication requirements. (CVE-2017-3167)', '- A NULL pointer dereference flaw exists due to third-party module calls to the mod_ssl ap_hook_process_connection() function during an HTTP request to an HTTPS port. An unauthenticated, remote attacker can exploit this to cause a denial of service condition. (CVE-2017-3169)', '- A NULL pointer dereference flaw exists in mod_http2 that is triggered when handling a specially crafted HTTP/2 request. An unauthenticated, remote attacker can exploit this to cause a denial of service condition. Note that this vulnerability does not affect 2.2.x. (CVE-2017-7659)', '- An out-of-bounds read error exists in the ap_find_token() function due to improper handling of header sequences. An unauthenticated, remote attacker can exploit this, via a specially crafted header sequence, to cause a denial of service condition. (CVE-2017-7668)', '- An out-of-bounds read error exists in mod_mime due to improper handling of Content-Type response headers. An unauthenticated, remote attacker can exploit this, via a specially crafted Content-Type response header, to cause a denial of service condition or the disclosure of sensitive information. (CVE-2017-7679)', ""Note that the scanner has not tested for these issues but has instead relied only on the application's self-reported version number.""]</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>['According to its banner, the version of Apache running on the remote host is 2.4.x prior to 2.4.26. It is, therefore, affected by the following vulnerabilities :', '- An authentication bypass vulnerability exists due to third-party modules using the ap_get_basic_auth_pw() function outside of the authentication phase. An unauthenticated, remote attacker can exploit this to bypass authentication requirements. (CVE-2017-3167)', '- A NULL pointer dereference flaw exists due to third-party module calls to the mod_ssl ap_hook_process_connection() function during an HTTP request to an HTTPS port. An unauthenticated, remote attacker can exploit this to cause a denial of service condition. (CVE-2017-3169)', '- A NULL pointer dereference flaw exists in mod_http2 that is triggered when handling a specially crafted HTTP/2 request. An unauthenticated, remote attacker can exploit this to cause a denial of service condition. Note that this vulnerability does not affect 2.2.x. (CVE-2017-7659)', '- An out-of-bounds read error exists in the ap_find_token() function due to improper handling of header sequences. An unauthenticated, remote attacker can exploit this, via a specially crafted header sequence, to cause a denial of service condition. (CVE-2017-7668)', '- An out-of-bounds read error exists in mod_mime due to improper handling of Content-Type response headers. An unauthenticated, remote attacker can exploit this, via a specially crafted Content-Type response header, to cause a denial of service condition or the disclosure of sensitive information. (CVE-2017-7679)', ""Note that the scanner has not tested for these issues but has instead relied only on the application's self-reported version number.""]</t>
+          <t>['Upgrade to Apache version 2.4.26 or later.']</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -722,67 +712,68 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['CWE 125', 'CWE 20', 'CWE 476', 'CWE 126', 'CWE 122', 'CWE 119', 'CWE 287', 'WASC Buffer Overflow', 'WASC Improper Input Handling', 'WASC Insufficient Authentication', 'OWASP 2010-A4', 'OWASP 2021-A3', 'OWASP 2013-A4', 'OWASP 2010-A3', 'OWASP 2021-A7', 'OWASP 2017-A9', 'OWASP 2017-A5', 'OWASP 2013-A2', 'OWASP 2021-A6', 'OWASP 2017-A2', 'OWASP 2013-A9', 'OWASP 2019-API7', 'OWASP 2023-API8', 'CVE-2017-7679', 'CVE-2017-7668', 'CVE-2017-7659', 'CVE-2017-3169', 'CVE-2017-3167', 'BID 99132', 'BID 99135', 'BID 99137', 'BID 99134', 'BID 99170']</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>['CVSSV3 BASE SCORE 9.8', 'CVSSV3 VECTOR CVSS:3.0/AV:N/AC:L/PR:N/UI:N/S:U/C:H/I:H/A:H', 'CVSS BASE SCORE 7.5', 'CVSS VECTOR CVSS2#AV:N/AC:L/Au:N/C:P/I:P/A:P']</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>98911</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"publication_date": "2019-01-09T00:00:00+00:00",
+"modification_date": "2023-03-14T00:00:00+00:00",
+"family": "Component Vulnerability",
+"severity": "Critical",
+"plugin_id": 98911}
+</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>['CWE 125, 20, 476, 126, 122, 119, 287', 'WASC Buffer Overflow, Improper Input Handling, Insufficient Authentication', 'OWASP 2010-A4, 2021-A3, 2013-A4, 2010-A3, 2021-A7, 2017-A9, 2017-A5, 2013-A2, 2021-A6, 2017-A2, 2013-A9, 2019-API7, 2023-API8', 'CVE CVE-2017-7679, CVE-2017-7668, CVE-2017-7659, CVE-2017-3169, CVE-2017-3167', 'BID 99132, 99135, 99137, 99134, 99170']</t>
+          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Current Version: 2.4.7 Fixed Version: 2.4.26 Detected technology URL: https://juice-shop-388277804329.us-west1.run.app/apps/', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>CRITICAL</t>
-        </is>
-      </c>
-      <c r="P4" t="n">
-        <v>98911</v>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>['Upgrade to Apache version 2.4.26 or later.']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/', 'input_type': 'link', 'input_name': None, 'payload': None, 'proof': 'Current Version: 2.4.7', 'output': 'Fixed Version: 2.4.26', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -794,12 +785,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>['9.1', 'CVSS:3.0/AV:N/AC:L/PR:N/UI:N/S:U/C:H/I:N/A:H', '6.4', 'CVSS2#AV:N/AC:L/Au:N/C:P/I:N/A:P']</t>
+          <t>['According to its banner, the version of Apache running on the remote host is 2.4.x prior to 2.4.27. It is, therefore, affected by the following vulnerabilities :', ""- A denial of service vulnerability exists in httpd due to a failure to initialize or reset the value placeholder in [Proxy-] Authorization headers of type 'Digest' before or between successive key=value assignments by mod_auth_digest. An unauthenticated, remote attacker can exploit this, by providing an initial key with no '=' assignment, to disclose sensitive information or cause a denial of service condition. (CVE-2017-9788)"", '- A read-after-free error exists in httpd that is triggered when closing a large number of connections. An unauthenticated, remote attacker can exploit this to have an unspecified impact. (CVE-2017-9789)', ""Note that the scanner has not tested for these issues but has instead relied only on the application's self-reported version number.""]</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>['According to its banner, the version of Apache running on the remote host is 2.4.x prior to 2.4.27. It is, therefore, affected by the following vulnerabilities :', ""- A denial of service vulnerability exists in httpd due to a failure to initialize or reset the value placeholder in [Proxy-] Authorization headers of type 'Digest' before or between successive key=value assignments by mod_auth_digest. An unauthenticated, remote attacker can exploit this, by providing an initial key with no '=' assignment, to disclose sensitive information or cause a denial of service condition. (CVE-2017-9788)"", '- A read-after-free error exists in httpd that is triggered when closing a large number of connections. An unauthenticated, remote attacker can exploit this to have an unspecified impact. (CVE-2017-9789)', ""Note that the scanner has not tested for these issues but has instead relied only on the application's self-reported version number.""]</t>
+          <t>['Upgrade to Apache version 2.4.27 or later.']</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -809,67 +800,68 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['CWE 20', 'CWE 200', 'CWE 416', 'CWE 456', 'WASC Improper Input Handling', 'WASC Information Leakage', 'OWASP 2010-A4', 'OWASP 2021-A3', 'OWASP 2021-A1', 'OWASP 2013-A5', 'OWASP 2013-A9', 'OWASP 2013-A4', 'OWASP 2017-A9', 'OWASP 2017-A5', 'OWASP 2017-A6', 'OWASP 2021-A6', 'OWASP 2010-A6', 'OWASP 2023-API8', 'OWASP 2019-API7', 'CVE-2017-9788', 'CVE-2017-9789', 'BID 99569', 'BID 99568']</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>['CVSSV3 BASE SCORE 9.1', 'CVSSV3 VECTOR CVSS:3.0/AV:N/AC:L/PR:N/UI:N/S:U/C:H/I:N/A:H', 'CVSS BASE SCORE 6.4', 'CVSS VECTOR CVSS2#AV:N/AC:L/Au:N/C:P/I:N/A:P']</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>98912</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"publication_date": "2019-01-09T00:00:00+00:00",
+"modification_date": "2023-03-14T00:00:00+00:00",
+"family": "Component Vulnerability",
+"severity": "Critical",
+"plugin_id": 98912}
+</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>['CWE 20, 200, 416, 456', 'WASC Improper Input Handling, Information Leakage', 'OWASP 2010-A4, 2021-A3, 2021-A1, 2013-A5, 2013-A9, 2013-A4, 2017-A9, 2017-A5, 2017-A6, 2021-A6, 2010-A6, 2023-API8, 2019-API7', 'CVE CVE-2017-9788, CVE-2017-9789', 'BID 99569, 99568']</t>
+          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Current Version: 2.4.7 Fixed Version: 2.4.27 Detected technology URL: https://juice-shop-388277804329.us-west1.run.app/apps/', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>CRITICAL</t>
-        </is>
-      </c>
-      <c r="P5" t="n">
-        <v>98912</v>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>['Upgrade to Apache version 2.4.27 or later.']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/', 'input_type': 'link', 'input_name': None, 'payload': None, 'proof': 'Current Version: 2.4.7', 'output': 'Fixed Version: 2.4.27', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -881,12 +873,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>['9.8', 'CVSS:3.0/AV:N/AC:L/PR:N/UI:N/S:U/C:H/I:H/A:H', '6.8', 'CVSS2#AV:N/AC:M/Au:N/C:P/I:P/A:P']</t>
+          <t>['According to its banner, the version of Apache running on the remote host is 2.4.x prior to 2.4.33. It is, therefore, affected by the following vulnerabilities:', ""- An out-of-bounds write flaw exists within the derive_codepage_from_lang() function of the modules/aaa/mod_authnz_ldap.c script due to improper handling of 'Accept-Language' header values that are less than two-bytes. A remote attacker, with a specially crafted request, could potentially crash the process. (CVE-2017-15710)"", '- A ACL bypass flaw exists within the ap_rgetline_core() function of the server/protocol.c script due to improper handling of &lt;FilesMatch&gt; expressions. A remote attacker could potentially bypass restrictions an upload a file. (CVE-2017-15715)', '- A data tampering flaw exists in the session_fixups() function of the modules/session/mod_session.c script when forwarding mod_session data to CGI applications. A remote attacker, with a specially crafted request, could potentially tamper with the mod_session data of the CGI application. (CVE-2018-1283)', '- An out-of-bound read flaw exists when hitting a size limit while handling HTTP headers. A remote attacker, with a specially crafted request, could crash the process. (CVE-2018-1301)', '- A use-after-free flaw exists when handling the HTTP/2 stream shutdown. A remote attacker could potentially write to already freed memory and crash the process. (CVE-2018-1302)', '- An out-of-bounds read flaw exists in the read_table() function of the modules/cache/mod_cache_socache.c script when handling empty headers. A remote attacker, with a specially crafted request, could potentially crash the process. (CVE-2018-1303)', '- A flaw exists within the modules/aaa/mod_auth_digest.c script due to improperly generating nonce when sending HTTP Digest Authentication challenges. A remote attacker could potentially conduct replay attacks against the server. (CVE-2018-1312)', ""Note that the scanner has not tested for these issues but has instead relied only on the application's self-reported version number.""]</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>['According to its banner, the version of Apache running on the remote host is 2.4.x prior to 2.4.33. It is, therefore, affected by the following vulnerabilities:', ""- An out-of-bounds write flaw exists within the derive_codepage_from_lang() function of the modules/aaa/mod_authnz_ldap.c script due to improper handling of 'Accept-Language' header values that are less than two-bytes. A remote attacker, with a specially crafted request, could potentially crash the process. (CVE-2017-15710)"", '- A ACL bypass flaw exists within the ap_rgetline_core() function of the server/protocol.c script due to improper handling of &lt;FilesMatch&gt; expressions. A remote attacker could potentially bypass restrictions an upload a file. (CVE-2017-15715)', '- A data tampering flaw exists in the session_fixups() function of the modules/session/mod_session.c script when forwarding mod_session data to CGI applications. A remote attacker, with a specially crafted request, could potentially tamper with the mod_session data of the CGI application. (CVE-2018-1283)', '- An out-of-bound read flaw exists when hitting a size limit while handling HTTP headers. A remote attacker, with a specially crafted request, could crash the process. (CVE-2018-1301)', '- A use-after-free flaw exists when handling the HTTP/2 stream shutdown. A remote attacker could potentially write to already freed memory and crash the process. (CVE-2018-1302)', '- An out-of-bounds read flaw exists in the read_table() function of the modules/cache/mod_cache_socache.c script when handling empty headers. A remote attacker, with a specially crafted request, could potentially crash the process. (CVE-2018-1303)', '- A flaw exists within the modules/aaa/mod_auth_digest.c script due to improperly generating nonce when sending HTTP Digest Authentication challenges. A remote attacker could potentially conduct replay attacks against the server. (CVE-2018-1312)', ""Note that the scanner has not tested for these issues but has instead relied only on the application's self-reported version number.""]</t>
+          <t>['Upgrade to Apache version 2.4.33 or later.']</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -896,67 +888,68 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['CWE 125', 'CWE 20', 'CWE 476', 'CWE 787', 'CWE 305', 'CWE 119', 'CWE 287', 'WASC Buffer Overflow', 'WASC Improper Input Handling', 'WASC Insufficient Authentication', 'OWASP 2010-A4', 'OWASP 2021-A3', 'OWASP 2013-A4', 'OWASP 2010-A3', 'OWASP 2021-A7', 'OWASP 2017-A9', 'OWASP 2017-A5', 'OWASP 2013-A2', 'OWASP 2021-A6', 'OWASP 2017-A2', 'OWASP 2013-A9', 'OWASP 2019-API7', 'OWASP 2023-API8', 'CVE-2017-15715', 'CVE-2018-1303', 'CVE-2018-1302', 'CVE-2018-1301', 'CVE-2018-1312', 'CVE-2017-15710', 'CVE-2018-1283', 'BID 103525', 'BID 103515', 'BID 103524', 'BID 103528', 'BID 103520', 'BID 103522', 'BID 103512']</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>['CVSSV3 BASE SCORE 9.8', 'CVSSV3 VECTOR CVSS:3.0/AV:N/AC:L/PR:N/UI:N/S:U/C:H/I:H/A:H', 'CVSS BASE SCORE 6.8', 'CVSS VECTOR CVSS2#AV:N/AC:M/Au:N/C:P/I:P/A:P']</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>98914</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"publication_date": "2019-01-09T00:00:00+00:00",
+"modification_date": "2023-03-14T00:00:00+00:00",
+"family": "Component Vulnerability",
+"severity": "Critical",
+"plugin_id": 98914}
+</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>['CWE 125, 20, 476, 787, 305, 119, 287', 'WASC Buffer Overflow, Improper Input Handling, Insufficient Authentication', 'OWASP 2010-A4, 2021-A3, 2013-A4, 2010-A3, 2021-A7, 2017-A9, 2017-A5, 2013-A2, 2021-A6, 2017-A2, 2013-A9, 2019-API7, 2023-API8', 'CVE CVE-2017-15715, CVE-2018-1303, CVE-2018-1302, CVE-2018-1301, CVE-2018-1312, CVE-2017-15710, CVE-2018-1283', 'BID 103525, 103515, 103524, 103528, 103520, 103522, 103512']</t>
+          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Current Version: 2.4.7 Fixed Version: 2.4.33 Detected technology URL: https://juice-shop-388277804329.us-west1.run.app/apps/', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>CRITICAL</t>
-        </is>
-      </c>
-      <c r="P6" t="n">
-        <v>98914</v>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>['Upgrade to Apache version 2.4.33 or later.']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/', 'input_type': 'link', 'input_name': None, 'payload': None, 'proof': 'Current Version: 2.4.7', 'output': 'Fixed Version: 2.4.33', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -968,12 +961,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>['9.8', 'CVSS:3.0/AV:N/AC:L/PR:N/UI:N/S:U/C:H/I:H/A:H', '7.5', 'CVSCVSS2#AV:N/AC:L/Au:N/C:P/I:P/A:P']</t>
+          <t>['According to its banner, the version of Apache running on the remote host is 2.4.x prior to 2.4.48. It is, therefore, affected by multiple vulnerabilities:', ""- Unexpected &lt;Location&gt; section matching with 'MergeSlashes OFF'. (CVE-2021-30641)"", '- mod_auth_digest: possible stack overflow by one nul byte while validating the Digest nonce. (CVE-2020-35452)', '- mod_session: Fix possible crash due to NULL pointer dereference, which could be used to cause a Denial of Service with a malicious backend server and SessionHeader. (CVE-2021-26691)', '- mod_session: Fix possible crash due to NULL pointer dereference, which could be used to cause a Denial of Service. (CVE-2021-26690)', '- mod_proxy_http: Fix possible crash due to NULL pointer dereference, which could be used to cause a Denial of Service. (CVE-2020-13950)', '- Windows: Prevent local users from stopping the httpd process (CVE-2020-13938)', '- mod_proxy_wstunnel, mod_proxy_http: Handle Upgradable protocols end-to-end negotiation. (CVE-2019-17567)', '- mod_http2: Fix a potential NULL pointer dereference. (CVE-2021-31618)', ""Note that the scanner has not tested for these issues but has instead relied only on the application's self-reported version number."", 'The remote Apache HTTP Server 2.4.x is prior to 2.4.48 and is affected by multiple vulnerabilities.']</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>['According to its banner, the version of Apache running on the remote host is 2.4.x prior to 2.4.48. It is, therefore, affected by multiple vulnerabilities:', ""- Unexpected &lt;Location&gt; section matching with 'MergeSlashes OFF'. (CVE-2021-30641)"", '- mod_auth_digest: possible stack overflow by one nul byte while validating the Digest nonce. (CVE-2020-35452)', '- mod_session: Fix possible crash due to NULL pointer dereference, which could be used to cause a Denial of Service with a malicious backend server and SessionHeader. (CVE-2021-26691)', '- mod_session: Fix possible crash due to NULL pointer dereference, which could be used to cause a Denial of Service. (CVE-2021-26690)', '- mod_proxy_http: Fix possible crash due to NULL pointer dereference, which could be used to cause a Denial of Service. (CVE-2020-13950)', '- Windows: Prevent local users from stopping the httpd process (CVE-2020-13938)', '- mod_proxy_wstunnel, mod_proxy_http: Handle Upgradable protocols end-to-end negotiation. (CVE-2019-17567)', '- mod_http2: Fix a potential NULL pointer dereference. (CVE-2021-31618)', ""Note that the scanner has not tested for these issues but has instead relied only on the application's self-reported version number."", 'The remote Apache HTTP Server 2.4.x is prior to 2.4.48 and is affected by multiple vulnerabilities.']</t>
+          <t>['Upgrade to Apache version 2.4.48 or later.']</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -983,67 +976,68 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['CWE 120', 'CWE 20', 'CWE 862', 'CWE 476', 'CWE 444', 'CWE 787', 'CWE 122', 'CWE 119', 'CWE 287', 'WASC Insufficient Authentication', 'WASC Buffer Overflow', 'WASC HTTP Request Smuggling', 'WASC Improper Input Handling', 'WASC Insufficient Authorization', 'OWASP 2013-A7', 'OWASP 2010-A4', 'OWASP 2021-A3', 'OWASP 2021-A1', 'OWASP 2021-A4', 'OWASP 2013-A4', 'OWASP 2010-A3', 'OWASP 2021-A7', 'OWASP 2017-A9', 'OWASP 2017-A5', 'OWASP 2013-A2', 'OWASP 2021-A6', 'OWASP 2017A2', 'OWASP 2013-A9', 'OWASP 2010-A8', 'OWASP 2019-API7', 'OWASP 2023-API8', 'CVE-2021-30641', 'CVE-2021-26690', 'CVE-2021-31618', 'CVE-2019-17567', 'CVE-2021-26691', 'CVE-2020-35452', 'CVE\ufffe2020-13950', 'CVE-2020-13938']</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>['CVSSV3 BASE SCORE 9.8', 'CVSSV3 VECTOR CVSS:3.0/AV:N/AC:L/PR:N/UI:N/S:U/C:H/I:H/A:H', 'CVSS BASE SCORE 7.5', 'CVSS VECTOR CVSS2#AV:N/AC:L/Au:N/C:P/I:P/A:P']</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>112806</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"publication_date": "2021-06-15T00:00:00+00:00",
+"modification_date": "2023-03-14T00:00:00+00:00",
+"family": "Component Vulnerability",
+"severity": "Critical",
+"plugin_id": 112806}
+</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>['CWE 120, 20, 862, 476, 444, 787, 122, 119, 287', 'WASC Insufficient Authentication, Buffer Overflow, HTTP Request Smuggling, Improper Input Handling, Insufficient Authorization', 'OWASP 2013-A7, 2010-A4, 2021-A3, 2021-A1, 2021-A4, 2013-A4, 2010-A3, 2021-A7, 2017-A9, 2017-A5, 2013-A2, 2021-A6, 2017-A2, 2013-A9, 2010-A8, 2019-API7, 2023-API8', 'CVE CVE-2021-30641, CVE-2021-26690, CVE-2021-31618, CVE-2019-17567, CVE-2021-26691, CVE-2020-35452, CVE-2020-13950, CVE-2020-13938', 'BID -']</t>
+          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Current Version: 2.4.7 Fixed Version: 2.4.48 Detected technology URL: https://juice-shop-388277804329.us-west1.run.app/apps/', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>CRITICAL</t>
-        </is>
-      </c>
-      <c r="P7" t="n">
-        <v>112806</v>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>['Upgrade to Apache version 2.4.48 or later.']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/', 'input_type': 'link', 'input_name': None, 'payload': None, 'proof': 'Current Version: 2.4.7', 'output': 'Fixed Version: 2.4.48', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -1055,12 +1049,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>['9.8', 'CVSS:3.0/AV:N/AC:L/PR:N/UI:N/S:U/C:H/I:H/A:H', '7.5', 'CVSS2#AV:N/AC:L/Au:N/C:P/I:P/A:P']</t>
+          <t>['According to its banner, the version of Apache running on the remote host is 2.4.x prior to 2.4.49. It is, therefore, affected by multiple vulnerabilities:', '- A crafted method sent through HTTP/2 will bypass validation and be forwarded by mod_proxy, which can lead to request splitting or cache poisoning. (CVE-2021-33193)', '- Malformed requests may cause the server to dereference a NULL pointer. (CVE-2021-34798)', '- A carefully crafted request uri-path can cause mod_proxy_uwsgi to read above the allocated memory and crash (DoS). (CVE-2021-36160)', '- ap_escape_quotes() may write beyond the end of a buffer when given malicious input. (CVE-2021-39275)', '- A crafted request uri-path can cause mod_proxy to forward the request to an origin server choosen by the remote user. (CVE-2021-40438)', ""Note that the scanner has not tested for these issues but has instead relied only on the application's self-reported version number.""]</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>['According to its banner, the version of Apache running on the remote host is 2.4.x prior to 2.4.49. It is, therefore, affected by multiple vulnerabilities:', '- A crafted method sent through HTTP/2 will bypass validation and be forwarded by mod_proxy, which can lead to request splitting or cache poisoning. (CVE-2021-33193)', '- Malformed requests may cause the server to dereference a NULL pointer. (CVE-2021-34798)', '- A carefully crafted request uri-path can cause mod_proxy_uwsgi to read above the allocated memory and crash (DoS). (CVE-2021-36160)', '- ap_escape_quotes() may write beyond the end of a buffer when given malicious input. (CVE-2021-39275)', '- A crafted request uri-path can cause mod_proxy to forward the request to an origin server choosen by the remote user. (CVE-2021-40438)', ""Note that the scanner has not tested for these issues but has instead relied only on the application's self-reported version number.""]</t>
+          <t>['Upgrade to Apache version 2.4.49 or later.']</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1070,67 +1064,68 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['CWE 125', 'CWE 476', 'CWE 444', 'CWE 787', 'CWE 119', 'CWE 918', 'WASC Application Misconfiguration', 'WASC Buffer Overflow', 'WASC HTTP Request Smuggling', 'OWASP 2021-A4', 'OWASP 2021-A10', 'OWASP 2013-A5', 'OWASP 2013-A9', 'OWASP 2017-A9', 'OWASP 2017-A6', 'OWASP 2021-A6', 'OWASP 2010-A6', 'OWASP 2023-API7', 'OWASP 2023-API8', 'OWASP 2019-API7', 'CVE-2021-33193', 'CVE-2021-40438', 'CVE-2021-39275', 'CVE-2021-36160', 'CVE-2021-34798']</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>['CVSSV3 BASE SCORE 9.8', 'CVSSV3 VECTOR CVSS:3.0/AV:N/AC:L/PR:N/UI:N/S:U/C:H/I:H/A:H', 'CVSS BASE SCORE 7.5', 'CVSS VECTOR CVSS2#AV:N/AC:L/Au:N/C:P/I:P/A:P']</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>112981</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"publication_date": "2021-09-17T00:00:00+00:00",
+"modification_date": "2023-03-14T00:00:00+00:00",
+"family": "Component Vulnerability",
+"severity": "Critical",
+"plugin_id": 112981}
+</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>['CWE 125, 476, 444, 787, 119, 918', 'WASC Application Misconfiguration, Buffer Overflow, HTTP Request Smuggling', 'OWASP 2021-A4, 2021-A10, 2013-A5, 2013-A9, 2017-A9, 2017-A6, 2021-A6, 2010-A6, 2023-API7, 2023-API8, 2019-API7', 'CVE CVE-2021-33193, CVE-2021-40438, CVE-2021-39275, CVE-2021-36160, CVE-2021-34798', 'BID -']</t>
+          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Current Version: 2.4.7 Fixed Version: 2.4.49 Detected technology URL: https://juice-shop-388277804329.us-west1.run.app/apps/', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>CRITICAL</t>
-        </is>
-      </c>
-      <c r="P8" t="n">
-        <v>112981</v>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>['Upgrade to Apache version 2.4.49 or later.']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/', 'input_type': 'link', 'input_name': None, 'payload': None, 'proof': 'Current Version: 2.4.7', 'output': 'Fixed Version: 2.4.49', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -1142,12 +1137,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>['9.8', 'CVSS:3.0/AV:N/AC:L/PR:N/UI:N/S:U/C:H/I:H/A:H', '7.5', 'CVSS2#AV:N/AC:L/Au:N/C:P/I:P/A:P']</t>
+          <t>['The version of Apache httpd installed on the remote host is prior to 2.4.52. It is, therefore, affected by multiple vulnerabilities as referenced in the 2.4.52 advisory.', '- A crafted URI sent to httpd configured as a forward proxy (ProxyRequests on) can cause a crash (NULL pointer dereference) or, for configurations mixing forward and reverse proxy declarations, can allow for requests to be directed to a declared Unix Domain Socket endpoint (Server Side Request Forgery). This issue affects Apache HTTP Server 2.4.7 up to 2.4.51 (included). (CVE-2021-44224)', '- A carefully crafted request body can cause a buffer overflow in the mod_lua multipart parser (r:parsebody() called from Lua scripts). The Apache httpd team is not aware of an exploit for the vulnerabilty though it might be possible to craft one. This issue affects Apache HTTP Server 2.4.51 and earlier. (CVE-2021-44790)', ""Note that the scanner has not tested for these issues but has instead relied only on the application's self-reported version number.""]</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>['The version of Apache httpd installed on the remote host is prior to 2.4.52. It is, therefore, affected by multiple vulnerabilities as referenced in the 2.4.52 advisory.', '- A crafted URI sent to httpd configured as a forward proxy (ProxyRequests on) can cause a crash (NULL pointer dereference) or, for configurations mixing forward and reverse proxy declarations, can allow for requests to be directed to a declared Unix Domain Socket endpoint (Server Side Request Forgery). This issue affects Apache HTTP Server 2.4.7 up to 2.4.51 (included). (CVE-2021-44224)', '- A carefully crafted request body can cause a buffer overflow in the mod_lua multipart parser (r:parsebody() called from Lua scripts). The Apache httpd team is not aware of an exploit for the vulnerabilty though it might be possible to craft one. This issue affects Apache HTTP Server 2.4.51 and earlier. (CVE-2021-44790)', ""Note that the scanner has not tested for these issues but has instead relied only on the application's self-reported version number.""]</t>
+          <t>['Upgrade to Apache version 2.4.52 or later.']</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1157,67 +1152,68 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['CWE 476', 'CWE 787', 'CWE 918', 'WASC Application Misconfiguration', 'WASC Buffer Overflow', 'OWASP 2021-A10', 'OWASP 2013-A5', 'OWASP 2013-A9', 'OWASP 2017-A9', 'OWASP 2017-A6', 'OWASP 2021-A6', 'OWASP 2010-A6', 'OWASP 2023-API7', 'OWASP 2023-API8', 'OWASP 2019-API7', 'CVE-2021-44224', 'CVE-2021-44790']</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>['CVSSV3 BASE SCORE 9.8', 'CVSSV3 VECTOR CVSS:3.0/AV:N/AC:L/PR:N/UI:N/S:U/C:H/I:H/A:H', 'CVSS BASE SCORE 7.5', 'CVSS VECTOR CVSS2#AV:N/AC:L/Au:N/C:P/I:P/A:P']</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>113079</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"publication_date": "2021-12-21T00:00:00+00:00",
+"modification_date": "2023-03-14T00:00:00+00:00",
+"family": "Component Vulnerability",
+"severity": "Critical",
+"plugin_id": 113079}
+</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>['CWE 476, 787, 918', 'WASC Application Misconfiguration, Buffer Overflow', 'OWASP 2021-A10, 2013-A5, 2013-A9, 2017-A9, 2017-A6, 2021-A6, 2010-A6, 2023-API7, 2023-API8, 2019-API7', 'CVE CVE-2021-44224, CVE-2021-44790', 'BID -']</t>
+          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Current Version: 2.4.7 Fixed Version: 2.4.52 Detected technology URL: https://juice-shop-388277804329.us-west1.run.app/apps/', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>CRITICAL</t>
-        </is>
-      </c>
-      <c r="P9" t="n">
-        <v>113079</v>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>['Upgrade to Apache version 2.4.52 or later.']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/', 'input_type': 'link', 'input_name': None, 'payload': None, 'proof': 'Current Version: 2.4.7', 'output': 'Fixed Version: 2.4.52', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -1229,12 +1225,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>['9.8', 'CVSS:3.0/AV:N/AC:L/PR:N/UI:N/S:U/C:H/I:H/A:H', '7.5', 'CVSS2#AV:N/AC:L/Au:N/C:P/I:P/A:P']</t>
+          <t>['According to its banner, the version of Apache running on the remote host is 2.4.x prior to 2.4.53. It is, therefore, affected by multiple vulnerabilities:', '- A carefully crafted request body can cause a read to a random memory area which could cause the process to crash. (CVE-2022-22719)', '- A HTTP Request Smuggling vulnerability exists due earlier fails to close inbound connection when errors are encountered discarding the request body. (CVE-2022-22720)', '- If LimitXMLRequestBody is set to allow request bodies larger than 350MB (defaults to 1M) on 32 bit systems an integer overflow happens which later causes out of bounds writes. (CVE-2022-22721)', '- An out-of-bounds Write vulnerability in mod_sed of Apache HTTP Server allows an attacker to overwrite heap memory with possibly attacker provided data. (CVE-2022-23943)', ""Note that the scanner has not tested for these issues but has instead relied only on the application's self-reported version number.""]</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>['According to its banner, the version of Apache running on the remote host is 2.4.x prior to 2.4.53. It is, therefore, affected by multiple vulnerabilities:', '- A carefully crafted request body can cause a read to a random memory area which could cause the process to crash. (CVE-2022-22719)', '- A HTTP Request Smuggling vulnerability exists due earlier fails to close inbound connection when errors are encountered discarding the request body. (CVE-2022-22720)', '- If LimitXMLRequestBody is set to allow request bodies larger than 350MB (defaults to 1M) on 32 bit systems an integer overflow happens which later causes out of bounds writes. (CVE-2022-22721)', '- An out-of-bounds Write vulnerability in mod_sed of Apache HTTP Server allows an attacker to overwrite heap memory with possibly attacker provided data. (CVE-2022-23943)', ""Note that the scanner has not tested for these issues but has instead relied only on the application's self-reported version number.""]</t>
+          <t>['Upgrade to Apache version 2.4.53 or later.']</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1244,67 +1240,68 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['CWE 125', 'CWE 665', 'CWE 444', 'CWE 787', 'CWE 190', 'CWE 908', 'WASC Buffer Overflow', 'WASC HTTP Request Smuggling', 'WASC Integer Overflows', 'OWASP 2021-A6', 'OWASP 2021-A4', 'OWASP 2013-A9', 'OWASP 2017-A9', 'OWASP 2019-API7', 'OWASP 2023-API8', 'CVE-2022-22719', 'CVE-2022-22720', 'CVE-2022-22721', 'CVE-2022-23943']</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>['CVSSV3 BASE SCORE 9.8', 'CVSSV3 VECTOR CVSS:3.0/AV:N/AC:L/PR:N/UI:N/S:U/C:H/I:H/A:H', 'CVSS BASE SCORE 7.5', 'CVSS VECTOR CVSS2#AV:N/AC:L/Au:N/C:P/I:P/A:P']</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>113194</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"publication_date": "2022-03-14T00:00:00+00:00",
+"modification_date": "2023-03-14T00:00:00+00:00",
+"family": "Component Vulnerability",
+"severity": "Critical",
+"plugin_id": 113194}
+</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>['CWE 125, 665, 444, 787, 190, 908', 'WASC Buffer Overflow, HTTP Request Smuggling, Integer Overflows', 'OWASP 2021-A6, 2021-A4, 2013-A9, 2017-A9, 2019-API7, 2023-API8', 'CVE CVE-2022-22719, CVE-2022-22720, CVE-2022-22721, CVE-2022-23943', 'BID -']</t>
+          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Current Version: 2.4.7 Fixed Version: 2.4.53 Detected technology URL: https://juice-shop-388277804329.us-west1.run.app/apps/', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>CRITICAL</t>
-        </is>
-      </c>
-      <c r="P10" t="n">
-        <v>113194</v>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>['Upgrade to Apache version 2.4.53 or later.']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/', 'input_type': 'link', 'input_name': None, 'payload': None, 'proof': 'Current Version: 2.4.7', 'output': 'Fixed Version: 2.4.53', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -1316,12 +1313,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>['9.8', 'CVSS:3.0/AV:N/AC:L/PR:N/UI:N/S:U/C:H/I:H/A:H', '7.5', 'CVSS2#AV:N/AC:L/Au:N/C:P/I:P/A:P']</t>
+          <t>['According to its banner, the version of Apache running on the remote host is 2.4.x prior to 2.4.54. It is, therefore, affected by multiple vulnerabilities:', ""- Inconsistent Interpretation of HTTP Requests ('HTTP Request Smuggling') vulnerability in mod_proxy_ajp of Apache HTTP Server allows an attacker to smuggle requests to the AJP server it forwards requests to. (CVE-2022-26377)"", '- Apache HTTP Server 2.4.53 and earlier on Windows may read beyond bounds when configured to process requests with the mod_isapi module. (CVE-2022-28330)', '- The ap_rwrite() function in Apache HTTP Server 2.4.53 and earlier may read unintended memory if an attacker can cause the server to reflect very large input using ap_rwrite() or ap_rputs(), such as with mod_luas r:puts() function. (CVE-2022-28614)', '- Apache HTTP Server 2.4.53 and earlier may crash or disclose information due to a read beyond bounds in ap_strcmp_match() when provided with an extremely large input buffer. While no code distributed with the server can be coerced into such a call, third-party modules or lua scripts that use ap_strcmp_match() may hypothetically be affected. (CVE-2022-28615)', '- In Apache HTTP Server 2.4.53 and earlier, a malicious request to a lua script that calls r:parsebody(0) may cause a denial of service due to no default limit on possible input size. (CVE-2022-29404)', '- If Apache HTTP Server 2.4.53 is configured to do transformations with mod_sed in contexts where the input to mod_sed may be very large, mod_sed may make excessively large memory allocations and trigger an abort. (CVE-2022-30522)', '- Apache HTTP Server 2.4.53 and earlier may return lengths to applications calling r:wsread() that point past the end of the storage allocated for the buffer. (CVE-2022-30556)', '- Apache HTTP Server 2.4.53 and earlier may not send the X-Forwarded-* headers to the origin server based on client side Connection header hop-by-hop mechanism. This may be used to bypass IP based authentication on the origin server /application. (CVE-2022-31813)', ""Note that the scanner has not tested for these issues but has instead relied only on the application's self-reported version number.""]</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>['According to its banner, the version of Apache running on the remote host is 2.4.x prior to 2.4.54. It is, therefore, affected by multiple vulnerabilities:', ""- Inconsistent Interpretation of HTTP Requests ('HTTP Request Smuggling') vulnerability in mod_proxy_ajp of Apache HTTP Server allows an attacker to smuggle requests to the AJP server it forwards requests to. (CVE-2022-26377)"", '- Apache HTTP Server 2.4.53 and earlier on Windows may read beyond bounds when configured to process requests with the mod_isapi module. (CVE-2022-28330)', '- The ap_rwrite() function in Apache HTTP Server 2.4.53 and earlier may read unintended memory if an attacker can cause the server to reflect very large input using ap_rwrite() or ap_rputs(), such as with mod_luas r:puts() function. (CVE-2022-28614)', '- Apache HTTP Server 2.4.53 and earlier may crash or disclose information due to a read beyond bounds in ap_strcmp_match() when provided with an extremely large input buffer. While no code distributed with the server can be coerced into such a call, third-party modules or lua scripts that use ap_strcmp_match() may hypothetically be affected. (CVE-2022-28615)', '- In Apache HTTP Server 2.4.53 and earlier, a malicious request to a lua script that calls r:parsebody(0) may cause a denial of service due to no default limit on possible input size. (CVE-2022-29404)', '- If Apache HTTP Server 2.4.53 is configured to do transformations with mod_sed in contexts where the input to mod_sed may be very large, mod_sed may make excessively large memory allocations and trigger an abort. (CVE-2022-30522)', '- Apache HTTP Server 2.4.53 and earlier may return lengths to applications calling r:wsread() that point past the end of the storage allocated for the buffer. (CVE-2022-30556)', '- Apache HTTP Server 2.4.53 and earlier may not send the X-Forwarded-* headers to the origin server based on client side Connection header hop-by-hop mechanism. This may be used to bypass IP based authentication on the origin server /application. (CVE-2022-31813)', ""Note that the scanner has not tested for these issues but has instead relied only on the application's self-reported version number.""]</t>
+          <t>['Upgrade to Apache version 2.4.54 or later.']</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1331,67 +1328,68 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['CWE 125', 'CWE 770', 'CWE 444', 'CWE 345', 'CWE 190', 'CWE 200', 'CWE 789', 'CWE 348', 'WASC Insufficient Authentication', 'WASC Integer Overflows', 'WASC Information Leakage', 'WASC Denial of Service', 'WASC HTTP Request Smuggling', 'OWASP 2010-A3', 'OWASP 2021-A1', 'OWASP 2021-A4', 'OWASP 2017-A9', 'OWASP 2013-A2', 'OWASP 2017-A6', 'OWASP 2021-A6', 'OWASP 2010-A6', 'OWASP 2013-A5', 'OWASP 2021-A8', 'OWASP 2017-A2', 'OWASP 2013-A9', 'OWASP 2023-API8', 'OWASP 2019-API7', 'CVE-2022-30522', 'CVE-2022-28614', 'CVE-2022-31813', 'CVE-2022-29404', 'CVE-2022-26377', 'CVE-2022-30556', 'CVE\ufffe2022-28330', 'CVE-2022-28615']</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>['CVSSV3 BASE SCORE 9.8', 'CVSSV3 VECTOR CVSS:3.0/AV:N/AC:L/PR:N/UI:N/S:U/C:H/I:H/A:H', 'CVSS BASE SCORE 7.5', 'CVSS VECTOR CVSS2#AV:N/AC:L/Au:N/C:P/I:P/A:P']</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>113254</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"publication_date": "2022-06-13T00:00:00+00:00",
+"modification_date": "2023-03-14T00:00:00+00:00",
+"family": "Component Vulnerability",
+"severity": "Critical",
+"plugin_id": 113254}
+</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>['CWE 125, 770, 444, 345, 190, 200, 789, 348', 'WASC Insufficient Authentication, Integer Overflows, Information Leakage, Denial of Service, HTTP Request Smuggling', 'OWASP 2010-A3, 2021-A1, 2021-A4, 2017-A9, 2013-A2, 2017-A6, 2021-A6, 2010-A6, 2013-A5, 2021-A8, 2017-A2, 2013-A9, 2023-API8, 2019-API7', 'CVE CVE-2022-30522, CVE-2022-28614, CVE-2022-31813, CVE-2022-29404, CVE-2022-26377, CVE-2022-30556, CVE-2022-28330, CVE-2022-28615', 'BID -']</t>
+          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Current Version: 2.4.7 Fixed Version: 2.4.54 Detected technology URL: https://juice-shop-388277804329.us-west1.run.app/apps/', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>CRITICAL</t>
-        </is>
-      </c>
-      <c r="P11" t="n">
-        <v>113254</v>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>['Upgrade to Apache version 2.4.54 or later.']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/', 'input_type': 'link', 'input_name': None, 'payload': None, 'proof': 'Current Version: 2.4.7', 'output': 'Fixed Version: 2.4.53', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/', 'input_type': 'link', 'input_name': None, 'payload': None, 'proof': 'Current Version: 2.4.7', 'output': 'Fixed Version: 2.4.54', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1401,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>['9.0', 'CVSS:3.0/AV:N/AC:H/PR:N/UI:N/S:C/C:H/I:H/A:H', '7.8', 'CVSS2#AV:N/AC:L/Au:N/C:N/I:N/A:C']</t>
+          <t>[""The scanner has not tested for these issues but has instead relied only on the application's self-reported version number.""]</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>[""The scanner has not tested for these issues but has instead relied only on the application's self-reported version number.""]</t>
+          <t>['Upgrade to Apache version 2.4.55 or later.']</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1418,67 +1416,68 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['CWE 444', 'CWE 787', 'WASC Buffer Overflow', 'WASC HTTP Request Smuggling', 'OWASP 2021-A6', 'OWASP 2021-A4', 'OWASP 2013-A9', 'OWASP 2017-A9', 'OWASP 2019-API7', 'OWASP 2023-API8', 'CVE-2006-20001', 'CVE-2022-26377', 'CVE-2022-36760']</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>['CVSSV3 BASE SCORE 9.0', 'CVSSV3 VECTOR CVSS:3.0/AV:N/AC:H/PR:N/UI:N/S:C/C:H/I:H/A:H', 'CVSS BASE SCORE 7.8', 'CVSS VECTOR CVSS2#AV:N/AC:L/Au:N/C:N/I:N/A:C']</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>113545</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"publication_date": "2023-01-18T00:00:00+00:00",
+"modification_date": "2024-01-03T00:00:00+00:00",
+"family": "Component Vulnerability",
+"severity": "Critical",
+"plugin_id": 113545}
+</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>['CWE 444, 787', 'WASC Buffer Overflow, HTTP Request Smuggling', 'OWASP 2021-A6, 2021-A4, 2013-A9, 2017-A9, 2019-API7, 2023-API8', 'CVE CVE-2006-20001, CVE-2022-26377, CVE-2022-36760', 'BID -']</t>
+          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Current Version: 2.4.7 Fixed Version: 2.4.55 Detected technology URL: https://juice-shop-388277804329.us-west1.run.app/apps/', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>CRITICAL</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>113545</v>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>['Upgrade to Apache version 2.4.55 or later.']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/', 'input_type': 'link', 'input_name': None, 'payload': None, 'proof': 'Current Version: 2.4.7', 'output': 'Fixed Version: 2.4.55', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -1490,12 +1489,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>['9.8', 'CVSS:3.0/AV:N/AC:L/PR:N/UI:N/S:U/C:H/I:H/A:H', '10.0', 'CVSS2#AV:N/AC:L/Au:N/C:C/I:C/A:C']</t>
+          <t>['According to its banner, the version of Apache running on the remote host is 2.4.x prior to 2.4.56. It is, therefore, affected by multiple vulnerabilities:', '- Some mod_proxy configurations allow a HTTP Request Smuggling attack. (CVE-2023-25690)', '- HTTP Response Smuggling vulnerability via mod_proxy_uwsgi. (CVE-2023-27522)', ""Note that the scanner has not tested for these issues but has instead relied only on the application's self-reported version number.""]</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>['According to its banner, the version of Apache running on the remote host is 2.4.x prior to 2.4.56. It is, therefore, affected by multiple vulnerabilities:', '- Some mod_proxy configurations allow a HTTP Request Smuggling attack. (CVE-2023-25690)', '- HTTP Response Smuggling vulnerability via mod_proxy_uwsgi. (CVE-2023-27522)', ""Note that the scanner has not tested for these issues but has instead relied only on the application's self-reported version number.""]</t>
+          <t>['Upgrade to Apache version 2.4.56 or later.']</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1505,67 +1504,68 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['CWE 113', 'CWE 444', 'WASC HTTP Request Smuggling', 'WASC HTTP Response Splitting', 'OWASP 2013-A1', 'OWASP 2021-A3', 'OWASP 2021-A6', 'OWASP 2021-A4', 'OWASP 2017-A1', 'OWASP 2013-A9', 'OWASP 2017-A9', 'OWASP 2010-A1', 'OWASP 2019-API8', 'OWASP 2023-API8', 'OWASP 2019-API7', 'CVE-2023-25690', 'CVE-2023-27522']</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr"/>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>['CVSSV3 BASE SCORE 9.8', 'CVSSV3 VECTOR CVSS:3.0/AV:N/AC:L/PR:N/UI:N/S:U/C:H/I:H/A:H', 'CVSS BASE SCORE 10.0', 'CVSS VECTOR CVSS2#AV:N/AC:L/Au:N/C:C/I:C/A:C']</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>113673</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"publication_date": "2023-03-08T00:00:00+00:00",
+"modification_date": "2023-03-16T00:00:00+00:00",
+"family": "Component Vulnerability",
+"severity": "Critical",
+"plugin_id": 113673}
+</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>['CWE 113, 444', 'WASC HTTP Request Smuggling, HTTP Response Splitting', 'OWASP 2013-A1, 2021-A3, 2021-A6, 2021-A4, 2017-A1, 2013-A9, 2017-A9, 2010-A1, 2019-API8, 2023-API8, 2019-API7', 'CVE CVE-2023-25690, CVE-2023-27522', 'BID -']</t>
+          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Current Version: 2.4.7 Fixed Version: 2.4.56 Detected technology URL: https://juice-shop-388277804329.us-west1.run.app/apps/', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>CRITICAL</t>
-        </is>
-      </c>
-      <c r="P13" t="n">
-        <v>113673</v>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>['Upgrade to Apache version 2.4.56 or later.']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/', 'input_type': 'link', 'input_name': None, 'payload': None, 'proof': 'Current Version: 2.4.7', 'output': 'Fixed Version: 2.4.56', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -1577,12 +1577,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>['9.8', 'CVSS:3.0/AV:N/AC:L/PR:N/UI:N/S:U/C:H/I:H/A:H', '10.0', 'CVSS2#AV:N/AC:L/Au:N/C:C/I:C/A:C']</t>
+          <t>['According to its banner, the version of Apache running on the remote host is 2.4.x prior to 2.4.60. It is, therefore, affected by multiple vulnerabilities:', '- Serving WebSocket protocol upgrades over a HTTP/2 connection could result in a Null Pointer dereference, leading to a crash of the server process, degrading performance. (CVE-2024-36387)', '- SSRF in Apache HTTP Server on Windows allows to potentially leak NTML hashes to a malicious server via SSRF and malicious requests or content. (CVE-2024-38472)', '- Encoding problem in mod_proxy in Apache HTTP Server 2.4.59 and earlier allows request URLs with incorrect encoding to be sent to backend services, potentially bypassing authentication via crafted requests. (CVE-2024-38473)', '- Substitution encoding issue in mod_rewrite in Apache HTTP Server 2.4.59 and earlier allows attacker to execute scripts in directories permitted by the configuration but not directly reachable by any URL or source disclosure of scripts meant to only to be executed as CGI. (CVE-2024-38474)', '- Improper escaping of output in mod_rewrite in Apache HTTP Server 2.4.59 and earlier allows an attacker to map URLs to filesystem locations that are permitted to be served by the server but are not intentionally/directly reachable by any URL, resulting in code execution or source code disclosure. (CVE-2024-38475)', '- Vulnerability in core of Apache HTTP Server 2.4.59 and earlier are vulnerably to information disclosure, SSRF or local script execution via backend applications whose response headers are malicious or exploitable. (CVE-2024-38476)', '- Null pointer dereference in mod_proxy in Apache HTTP Server 2.4.59 and earlier allows an attacker to crash the server via a malicious request. (CVE-2024-38477)', ""- Potential SSRF in mod_rewrite in Apache HTTP Server 2.4.59 and earlier allows an attacker to cause unsafe RewriteRules to unexpectedly setup URL's to be handled by mod_proxy. (CVE-2024-39573)"", ""Note that the scanner has not tested for these issues but has instead relied only on the application's self-reported version number.""]</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>['According to its banner, the version of Apache running on the remote host is 2.4.x prior to 2.4.60. It is, therefore, affected by multiple vulnerabilities:', '- Serving WebSocket protocol upgrades over a HTTP/2 connection could result in a Null Pointer dereference, leading to a crash of the server process, degrading performance. (CVE-2024-36387)', '- SSRF in Apache HTTP Server on Windows allows to potentially leak NTML hashes to a malicious server via SSRF and malicious requests or content. (CVE-2024-38472)', '- Encoding problem in mod_proxy in Apache HTTP Server 2.4.59 and earlier allows request URLs with incorrect encoding to be sent to backend services, potentially bypassing authentication via crafted requests. (CVE-2024-38473)', '- Substitution encoding issue in mod_rewrite in Apache HTTP Server 2.4.59 and earlier allows attacker to execute scripts in directories permitted by the configuration but not directly reachable by any URL or source disclosure of scripts meant to only to be executed as CGI. (CVE-2024-38474)', '- Improper escaping of output in mod_rewrite in Apache HTTP Server 2.4.59 and earlier allows an attacker to map URLs to filesystem locations that are permitted to be served by the server but are not intentionally/directly reachable by any URL, resulting in code execution or source code disclosure. (CVE-2024-38475)', '- Vulnerability in core of Apache HTTP Server 2.4.59 and earlier are vulnerably to information disclosure, SSRF or local script execution via backend applications whose response headers are malicious or exploitable. (CVE-2024-38476)', '- Null pointer dereference in mod_proxy in Apache HTTP Server 2.4.59 and earlier allows an attacker to crash the server via a malicious request. (CVE-2024-38477)', ""- Potential SSRF in mod_rewrite in Apache HTTP Server 2.4.59 and earlier allows an attacker to cause unsafe RewriteRules to unexpectedly setup URL's to be handled by mod_proxy. (CVE-2024-39573)"", ""Note that the scanner has not tested for these issues but has instead relied only on the application's self-reported version number.""]</t>
+          <t>['Upgrade to Apache version 2.4.60 or later.']</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1592,67 +1592,68 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['CWE 829', 'CWE 20', 'CWE 116', 'CWE 476', 'CWE 918', 'WASC Application Misconfiguration', 'WASC Improper Input Handling', 'WASC Improper Output Handling', 'OWASP 2010-A4', 'OWASP 2021-A3', 'OWASP 2013-A9', 'OWASP 2013-A4', 'OWASP 2017-A9', 'OWASP 2017-A5', 'OWASP 2017-A6', 'OWASP 2021-A6', 'OWASP 2010-A6', 'OWASP 2021-A10', 'OWASP 2013-A5', 'OWASP 2021-A8', 'OWASP 2023-API7', 'OWASP 2023-API8', 'OWASP 2019-API7', 'OWASP 2019-API8', 'CVE-2024-38473', 'CVE-2024-38476', 'CVE-2024-38475', 'CVE-2024-39573', 'CVE-2024-36387', 'CVE-2024-38474', 'CVE\ufffe2024-38472', 'CVE-2024-38477']</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr"/>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>['CVSSV3 BASE SCORE 9.8', 'CVSSV3 VECTOR CVSS:3.0/AV:N/AC:L/PR:N/UI:N/S:U/C:H/I:H/A:H', 'CVSS BASE SCORE 10.0', 'CVSS VECTOR CVSS2#AV:N/AC:L/Au:N/C:C/I:C/A:C']</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>114360</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"publication_date": "2024-07-03T00:00:00+00:00",
+"modification_date": "2024-07-22T00:00:00+00:00",
+"family": "Component Vulnerability",
+"severity": "Critical",
+"plugin_id": 114360}
+</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>['CWE 829, 20, 116, 476, 918', 'WASC Application Misconfiguration, Improper Input Handling, Improper Output Handling', 'OWASP 2010-A4, 2021-A3, 2013-A9, 2013-A4, 2017-A9, 2017-A5, 2017-A6, 2021-A6, 2010-A6, 2021-A10, 2013-A5, 2021-A8, 2023-API7, 2023-API8, 2019-API7, 2019-API8', 'CVE CVE-2024-38473, CVE-2024-38476, CVE-2024-38475, CVE-2024-39573, CVE-2024-36387, CVE-2024-38474, CVE-2024-38472, CVE-2024-38477', 'BID -']</t>
+          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Current Version: 2.4.7 Fixed Version: 2.4.60 Detected technology URL: https://juice-shop-388277804329.us-west1.run.app/apps/', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>CRITICAL</t>
-        </is>
-      </c>
-      <c r="P14" t="n">
-        <v>114360</v>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>['Upgrade to Apache version 2.4.60 or later.']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/', 'input_type': 'link', 'input_name': None, 'payload': None, 'proof': 'Current Version: 2.4.7', 'output': 'Fixed Version: 2.4.60', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -1664,12 +1665,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>['7.8', 'CVSS:3.0/AV:L/AC:L/PR:L/UI:N/S:U/C:H/I:H/A:H', '7.2', 'CVSS2#AV:L/AC:L/Au:N/C:C/I:C/A:C']</t>
+          <t>['According to its banner, the version of Apache running on the remote host is 2.4.x prior to 2.4.39. It is, therefore, affected by multiple vulnerabilities:', '- A privilege escalation vulnerability exists in module scripts due to an ability to execute arbitrary code as the parent process by manipulating the scoreboard. (CVE-2019-0211)', '- An access control bypass vulnerability exists in mod_auth_digest due to a race condition when running in a threaded server. An attacker with valid credentials could authenticate using another username. (CVE-2019-0217)', '- An access control bypass vulnerability exists in mod_ssl when using per-location client certificate verification with TLSv1.3. (CVE-2019-0215)', 'In addition, Apache httpd is also affected by several additional vulnerabilities including a denial of service, read-after-free and URL path normalization inconsistencies.', ""Note that the scanner has not tested for these issues but has instead relied only on the application's self-reported version number.""]</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>['According to its banner, the version of Apache running on the remote host is 2.4.x prior to 2.4.39. It is, therefore, affected by multiple vulnerabilities:', '- A privilege escalation vulnerability exists in module scripts due to an ability to execute arbitrary code as the parent process by manipulating the scoreboard. (CVE-2019-0211)', '- An access control bypass vulnerability exists in mod_auth_digest due to a race condition when running in a threaded server. An attacker with valid credentials could authenticate using another username. (CVE-2019-0217)', '- An access control bypass vulnerability exists in mod_ssl when using per-location client certificate verification with TLSv1.3. (CVE-2019-0215)', 'In addition, Apache httpd is also affected by several additional vulnerabilities including a denial of service, read-after-free and URL path normalization inconsistencies.', ""Note that the scanner has not tested for these issues but has instead relied only on the application's self-reported version number.""]</t>
+          <t>['Upgrade to Apache version 2.4.39 or later.']</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1679,67 +1680,68 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['CWE 706', 'CWE 41', 'CWE 362', 'CWE 250', 'CWE 400', 'CWE 284', 'CWE 416', 'CWE 264', 'CWE 444', 'WASC Application Misconfiguration', 'WASC Denial of Service', 'WASC HTTP Request Smuggling', 'WASC Improper Input Handling', 'WASC Insufficient Authorization', 'OWASP 2010-A8', 'OWASP 2013-A7', 'OWASP 2021-A1', 'OWASP 2021-A4', 'OWASP 2013-A5', 'OWASP 2013-A9', 'OWASP 2013-A4', 'OWASP 2010-A4', 'OWASP 2021-A5', 'OWASP 2017-A9', 'OWASP 2017-A5', 'OWASP 2017-A6', 'OWASP 2021A6', 'OWASP 2010-A6', 'OWASP 2023-API8', 'OWASP 2019-API7', 'CVE-2019-0215', 'CVE-2019-0220', 'CVE-2019-0197', 'CVE-2019-0217', 'CVE-2019-0196', 'CVE-2019-0211', 'BID 107666', 'BID 107669', 'BID 107667', 'BID 107670', 'BID 107668', 'BID 107665']</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr"/>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>['CVSSV3 BASE SCORE 7.8', 'CVSSV3 VECTOR CVSS:3.0/AV:L/AC:L/PR:L/UI:N/S:U/C:H/I:H/A:H', 'CVSS BASE SCORE 7.2', 'CVSS VECTOR CVSS2#AV:L/AC:L/Au:N/C:C/I:C/A:C']</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>98530</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"publication_date": "2019-04-08T00:00:00+00:00",
+"modification_date": "2023-03-14T00:00:00+00:00",
+"family": "Component Vulnerability",
+"severity": "High",
+"plugin_id": 98530}
+</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>['CWE 706, 41, 362, 250, 400, 284, 416, 264, 444', 'WASC Application Misconfiguration, Denial of Service, HTTP Request Smuggling, Improper Input Handling, Insufficient Authorization', 'OWASP 2010-A8, 2013-A7, 2021-A1, 2021-A4, 2013-A5, 2013-A9, 2013-A4, 2010-A4, 2021-A5, 2017-A9, 2017-A5, 2017-A6, 2021-A6, 2010-A6, 2023-API8, 2019-API7', 'CVE CVE-2019-0215, CVE-2019-0220, CVE-2019-0197, CVE-2019-0217, CVE-2019-0196, CVE-2019-0211', 'BID 107666, 107669, 107667, 107670, 107668, 107665']</t>
+          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Current Version: 2.4.7 Fixed Version: 2.4.39 Detected technology URL: https://juice-shop-388277804329.us-west1.run.app/apps/', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="P15" t="n">
-        <v>98530</v>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>['Upgrade to Apache version 2.4.39 or later.']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/', 'Identification': {'OUTPUT': {'Current Version': '2.4.7', 'Fixed Version': '2.4.60', 'Detected technology URL': 'https://juice-shop-388277804329.us-west1.run.app/apps/'}}, 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1753,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>['7.5', 'CVSS:3.0/AV:N/AC:L/PR:N/UI:N/S:U/C:N/I:H/A:N', '5.0', 'CVSS2#AV:N/AC:L/Au:N/C:N/I:N/A:P']</t>
+          <t>['According to its banner, the version of Apache running on the remote host is 2.4.x prior to 2.4.38. It is, therefore, affected by multiple vulnerabilities:', '- A denial of service (DoS) vulnerability exists in HTTP/2 steam handling. An unauthenticated, remote attacker can exploit this issue, via sending request bodies in a slow loris way to plain resources, to occupy a server thread. (CVE-2018-17189)', '- A vulnerability exists in mod_sesion_cookie, as it does not properly check the expiry time of cookies. (CVE-2018-17199)', '- A denial of service (DoS) vulnerability exists in mod_ssl when used with OpenSSL 1.1.1 due to an interaction in changes to handling of renegotiation attempts. An unauthenticated, remote attacker can exploit this issue to cause mod_ssl to stop responding. (CVE-2019-0190)', ""Note that the scanner has not tested for these issues but has instead relied only on the application's self-reported version number.""]</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>['According to its banner, the version of Apache running on the remote host is 2.4.x prior to 2.4.38. It is, therefore, affected by multiple vulnerabilities:', '- A denial of service (DoS) vulnerability exists in HTTP/2 steam handling. An unauthenticated, remote attacker can exploit this issue, via sending request bodies in a slow loris way to plain resources, to occupy a server thread. (CVE-2018-17189)', '- A vulnerability exists in mod_sesion_cookie, as it does not properly check the expiry time of cookies. (CVE-2018-17199)', '- A denial of service (DoS) vulnerability exists in mod_ssl when used with OpenSSL 1.1.1 due to an interaction in changes to handling of renegotiation attempts. An unauthenticated, remote attacker can exploit this issue to cause mod_ssl to stop responding. (CVE-2019-0190)', ""Note that the scanner has not tested for these issues but has instead relied only on the application's self-reported version number.""]</t>
+          <t>['Upgrade to Apache version 2.4.38 or later.']</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1766,67 +1768,68 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['CWE 384', 'CWE 400', 'CWE 613', 'WASC Denial of Service', 'WASC Insufficient Session Expiration', 'WASC Session Fixation', 'OWASP 2010-A3', 'OWASP 2021-A7', 'OWASP 2017-A9', 'OWASP 2013-A2', 'OWASP 2021-A6', 'OWASP 2017-A2', 'OWASP 2013-A9', 'OWASP 2023-API2', 'OWASP 2019-API2', 'OWASP 2019-API7', 'OWASP 2023-API8', 'CVE-2018-17189', 'CVE-2018-17199', 'CVE-2019-0190', 'BID 106685', 'BID 106742', 'BID 106743']</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr"/>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>['CVSSV3 BASE SCORE 7.5', 'CVSSV3 VECTOR CVSS:3.0/AV:N/AC:L/PR:N/UI:N/S:U/C:N/I:H/A:N', 'CVSS BASE SCORE 5.0', 'CVSS VECTOR CVSS2#AV:N/AC:L/Au:N/C:N/I:N/A:P']</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>98537</v>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"publication_date": "2019-04-12T00:00:00+00:00",
+"modification_date": "2023-03-14T00:00:00+00:00",
+"family": "Component Vulnerability",
+"severity": "High",
+"plugin_id": 98537}
+</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>['CWE 384, 400, 613', 'WASC Denial of Service, Insufficient Session Expiration, Session Fixation', 'OWASP 2010-A3, 2021-A7, 2017-A9, 2013-A2, 2021-A6, 2017-A2, 2013-A9, 2023-API2, 2019-API2, 2019-API7, 2023-API8', 'CVE CVE-2018-17189, CVE-2018-17199, CVE-2019-0190', 'BID 106685, 106742, 106743']</t>
+          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Current Version: 2.4.7 Fixed Version: 2.4.38 Detected technology URL: https://juice-shop-388277804329.us-west1.run.app/apps/', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="P16" t="n">
-        <v>98537</v>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>['Upgrade to Apache version 2.4.38 or later.']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/', 'input_type': 'link', 'input_name': None, 'payload': None, 'proof': 'Current Version: 2.4.7', 'output': 'Fixed Version: 2.4.38', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -1838,12 +1841,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>['7.5', 'CVSS:3.0/AV:N/AC:L/PR:N/UI:N/S:U/C:N/I:N/A:H', '5.0', 'CVSS2#AV:N/AC:L/Au:N/C:N/I:N/A:P']</t>
+          <t>['According to its banner, the version of Apache 2.4.x running on the remote host is a version prior to 2.4.9. It is, therefore, affected by the following vulnerabilities :', ""- A flaw exists with the 'mod_dav' module that is caused when tracking the length of CDATA that has leading white space. A remote attacker with a specially crafted DAV WRITE request can cause the service to stop responding. (CVE-2013-6438)"", ""- A flaw exists in 'mod_log_config' module that is caused when logging a cookie that has an unassigned value. A remote attacker with a specially crafted request can cause the service to crash. (CVE-2014-0098)"", ""Note that the scanner did not actually test for these issues, but instead has relied on the version in the server's banner.""]</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>['According to its banner, the version of Apache 2.4.x running on the remote host is a version prior to 2.4.9. It is, therefore, affected by the following vulnerabilities :', ""- A flaw exists with the 'mod_dav' module that is caused when tracking the length of CDATA that has leading white space. A remote attacker with a specially crafted DAV WRITE request can cause the service to stop responding. (CVE-2013-6438)"", ""- A flaw exists in 'mod_log_config' module that is caused when logging a cookie that has an unassigned value. A remote attacker with a specially crafted request can cause the service to crash. (CVE-2014-0098)"", ""Note that the scanner did not actually test for these issues, but instead has relied on the version in the server's banner.""]</t>
+          <t>['Upgrade to Apache version 2.4.9 or later. Alternatively, ensure that the affected modules are not in use.']</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1853,67 +1856,68 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['CWE 119', 'CWE 125', 'CWE 20', 'WASC Buffer Overflow', 'WASC Improper Input Handling', 'OWASP 2010-A4', 'OWASP 2021-A3', 'OWASP 2021-A6', 'OWASP 2013-A9', 'OWASP 2013-A4', 'OWASP 2017-A9', 'OWASP 2017-A5', 'OWASP 2019-API7', 'OWASP 2023-API8', 'CVE-2013-6438', 'CVE-2014-0098', 'BID 66303']</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr"/>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>['CVSSV3 BASE SCORE 7.5', 'CVSSV3 VECTOR CVSS:3.0/AV:N/AC:L/PR:N/UI:N/S:U/C:N/I:N/A:H', 'CVSS BASE SCORE 5.0', 'CVSS VECTOR CVSS2#AV:N/AC:L/Au:N/C:N/I:N/A:P']</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>98905</v>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"publication_date": "2019-01-09T00:00:00+00:00",
+"modification_date": "2023-03-14T00:00:00+00:00",
+"family": "Component Vulnerability",
+"severity": "High",
+"plugin_id": 98905}
+</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>['CWE 119, 125, 20', 'WASC Buffer Overflow, Improper Input Handling', 'OWASP 2010-A4, 2021-A3, 2021-A6, 2013-A9, 2013-A4, 2017-A9, 2017-A5, 2019-API7, 2023-API8', 'CVE CVE-2013-6438, CVE-2014-0098', 'BID 66303']</t>
+          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Current Version: 2.4.7 Fixed Version: 2.4.9 Detected technology URL: https://juice-shop-388277804329.us-west1.run.app/apps/', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="P17" t="n">
-        <v>98905</v>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>['Upgrade to Apache version 2.4.9 or later. Alternatively, ensure that the affected modules are not in use.']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/', 'input_type': 'link', 'input_name': None, 'payload': None, 'proof': 'Current Version: 2.4.7', 'output': 'Fixed Version: 2.4.9', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -1925,12 +1929,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>['7.5', 'CVSS:3.0/AV:N/AC:L/PR:N/UI:N/S:U/C:N/I:N/A:H', '6.8', 'CVSS2#AV:N/AC:M/Au:N/C:P/I:P/A:P']</t>
+          <t>['According to its banner, the version of Apache 2.4.x running on the remote host is prior to 2.4.10. It is, therefore, affected by the following vulnerabilities :', ""- A flaw exists in the 'mod_proxy' module that may allow an attacker to send a specially crafted request to a server configured as a reverse proxy that may cause the child process to crash. This could potentially lead to a denial of service attack. (CVE-2014-0117)"", ""- A flaw exists in the 'mod_deflate' module when request body decompression is configured. This could allow a remote attacker to cause the server to consume significant resources. (CVE-2014-0118)"", ""- A flaw exists in the 'mod_status' module when a publicly accessible server status page is in place. This could allow an attacker to send a specially crafted request designed to cause a heap buffer overflow. (CVE-2014-0226)"", ""- A flaw exists in the 'mod_cgid' module in which CGI scripts that did not consume standard input may be manipulated in order to cause child processes to hang. A remote attacker may be able to abuse this in order to cause a denial of service. (CVE-2014-0231)"", '- A flaw exists in WinNT MPM versions 2.4.1 to 2.4.9 when using the default AcceptFilter. An attacker may be able to specially craft requests that create a memory leak in the application and may eventually lead to a denial of service attack. (CVE-2014-3523)', ""Note that the scanner has not tested for these issues but has instead relied only on the application's self-reported version number.""]</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>['According to its banner, the version of Apache 2.4.x running on the remote host is prior to 2.4.10. It is, therefore, affected by the following vulnerabilities :', ""- A flaw exists in the 'mod_proxy' module that may allow an attacker to send a specially crafted request to a server configured as a reverse proxy that may cause the child process to crash. This could potentially lead to a denial of service attack. (CVE-2014-0117)"", ""- A flaw exists in the 'mod_deflate' module when request body decompression is configured. This could allow a remote attacker to cause the server to consume significant resources. (CVE-2014-0118)"", ""- A flaw exists in the 'mod_status' module when a publicly accessible server status page is in place. This could allow an attacker to send a specially crafted request designed to cause a heap buffer overflow. (CVE-2014-0226)"", ""- A flaw exists in the 'mod_cgid' module in which CGI scripts that did not consume standard input may be manipulated in order to cause child processes to hang. A remote attacker may be able to abuse this in order to cause a denial of service. (CVE-2014-0231)"", '- A flaw exists in WinNT MPM versions 2.4.1 to 2.4.9 when using the default AcceptFilter. An attacker may be able to specially craft requests that create a memory leak in the application and may eventually lead to a denial of service attack. (CVE-2014-3523)', ""Note that the scanner has not tested for these issues but has instead relied only on the application's self-reported version number.""]</t>
+          <t>['Upgrade to Apache version 2.4.10 or later. Alternatively, ensure that the affected modules are not in use.']</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1940,67 +1944,68 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['CWE 20', 'CWE 362', 'CWE 399', 'CWE 400', 'CWE 122', 'WASC Buffer Overflow', 'WASC Denial of Service', 'WASC Improper Input Handling', 'OWASP 2010-A4', 'OWASP 2021-A3', 'OWASP 2021-A6', 'OWASP 2013-A9', 'OWASP 2013-A4', 'OWASP 2017-A9', 'OWASP 2017-A5', 'OWASP 2019-API7', 'OWASP 2023-API8', 'CVE-2014-0226', 'CVE-2014-3523', 'CVE-2014-0118', 'CVE-2014-0117', 'CVE-2014-0231', 'BID 68747', 'BID 68678', 'BID 68742', 'BID 68745', 'BID 68740']</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr"/>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>['CVSSV3 BASE SCORE 7.5', 'CVSSV3 VECTOR CVSS:3.0/AV:N/AC:L/PR:N/UI:N/S:U/C:N/I:N/A:H', 'CVSS BASE SCORE 6.8', 'CVSS VECTOR CVSS2#AV:N/AC:M/Au:N/C:P/I:P/A:P']</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>98906</v>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"publication_date": "2019-01-09T00:00:00+00:00",
+"modification_date": "2023-03-14T00:00:00+00:00",
+"family": "Component Vulnerability",
+"severity": "High",
+"plugin_id": 98906}
+</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>['CWE 20, 362, 399, 400, 122', 'WASC Buffer Overflow, Denial of Service, Improper Input Handling', 'OWASP 2010-A4, 2021-A3, 2021-A6, 2013-A9, 2013-A4, 2017-A9, 2017-A5, 2019-API7, 2023-API8', 'CVE CVE-2014-0226, CVE-2014-3523, CVE-2014-0118, CVE-2014-0117, CVE-2014-0231', 'BID 68747, 68678, 68742, 68745, 68740']</t>
+          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Current Version: 2.4.7 Fixed Version: 2.4.10 Detected technology URL: https://juice-shop-388277804329.us-west1.run.app/apps/', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="P18" t="n">
-        <v>98906</v>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>['Upgrade to Apache version 2.4.10 or later. Alternatively, ensure that the affected modules are not in use.']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/', 'input_type': 'link', 'input_name': None, 'payload': None, 'proof': 'Current Version: 2.4.7', 'output': 'Fixed Version: 2.4.10', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -2012,12 +2017,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>['7.5', 'CVSS:3.0/AV:N/AC:L/PR:N/UI:N/S:U/C:N/I:N/A:H', '5.0']</t>
+          <t>['According to its banner, the version of Apache 2.4.x running on the remote host is prior to 2.4.12. It is, therefore, affected by the following vulnerabilities :', '- A flaw exists in module mod_headers that can allow HTTP trailers to replace HTTP headers late during request processing, which a remote attacker can exploit to inject arbitrary headers. This can also cause some modules to function incorrectly or appear to function incorrectly. (CVE-2013-5704)', '- A NULL pointer dereference flaw exists in module mod_cache. A remote attacker, using an empty HTTP Content-Type header, can exploit this vulnerability to crash a caching forward proxy configuration, resulting in a denial of service if using a threaded MPM. (CVE-2014-3581)', '- A out-of-bounds memory read flaw exists in module mod_proxy_fcgi. An attacker, using a remote FastCGI server to send long response headers, can exploit this vulnerability to cause a denial of service by causing a buffer over-read. (CVE-2014-3583)', '- A flaw exists in module mod_lua when handling a LuaAuthzProvider used in multiple Require directives with different arguments. An attacker can exploit this vulnerability to bypass intended access restrictions. (CVE-2014-8109)', ""Note that the scanner has not tested for these issues but has instead relied only on the application's self-reported version number.""]</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>['According to its banner, the version of Apache 2.4.x running on the remote host is prior to 2.4.12. It is, therefore, affected by the following vulnerabilities :', '- A flaw exists in module mod_headers that can allow HTTP trailers to replace HTTP headers late during request processing, which a remote attacker can exploit to inject arbitrary headers. This can also cause some modules to function incorrectly or appear to function incorrectly. (CVE-2013-5704)', '- A NULL pointer dereference flaw exists in module mod_cache. A remote attacker, using an empty HTTP Content-Type header, can exploit this vulnerability to crash a caching forward proxy configuration, resulting in a denial of service if using a threaded MPM. (CVE-2014-3581)', '- A out-of-bounds memory read flaw exists in module mod_proxy_fcgi. An attacker, using a remote FastCGI server to send long response headers, can exploit this vulnerability to cause a denial of service by causing a buffer over-read. (CVE-2014-3583)', '- A flaw exists in module mod_lua when handling a LuaAuthzProvider used in multiple Require directives with different arguments. An attacker can exploit this vulnerability to bypass intended access restrictions. (CVE-2014-8109)', ""Note that the scanner has not tested for these issues but has instead relied only on the application's self-reported version number.""]</t>
+          <t>['Upgrade to Apache version 2.4.12 or later. Alternatively, ensure that the affected modules are not in use.']</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2027,67 +2032,68 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['CWE 125', 'CWE 476', 'CWE 264', 'CWE 863', 'CWE 399', 'CWE 119', 'CWE 287', 'WASC Buffer Overflow', 'WASC Insufficient Authentication', 'WASC Insufficient Authorization', 'OWASP 2010-A8', 'OWASP 2013-A7', 'OWASP 2021-A1', 'OWASP 2010-A3', 'OWASP 2021-A7', 'OWASP 2017-A9', 'OWASP 2017-A5', 'OWASP 2013-A2', 'OWASP 2021-A6', 'OWASP 2017-A2', 'OWASP 2013-A9', 'OWASP 2019-API7', 'OWASP 2023-API8', 'CVE-2013-5704', 'CVE-2014-3581', 'CVE-2014-3583', 'CVE-2014-8109', 'BID 66550', 'BID 71656', 'BID 71657', 'BID 73040']</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr"/>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>['CVSSV3 BASE SCORE 7.5', 'CVSSV3 VECTOR CVSS:3.0/AV:N/AC:L/PR:N/UI:N/S:U/C:N/I:N/A:H', 'CVSS BASE SCORE 5.0', 'CVSS VECTOR CVSS2#AV:N/AC:L/Au:N/C:N/I:P/A:N']</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
+        <v>98907</v>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"publication_date": "2019-01-09T00:00:00+00:00",
+"modification_date": "2023-03-14T00:00:00+00:00",
+"family": "Component Vulnerability",
+"severity": "High",
+"plugin_id": 98907}
+</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>['CWE 125, 476, 264, 863, 399, 119, 287', 'WASC Buffer Overflow, Insufficient Authentication, Insufficient Authorization', 'OWASP 2010-A8, 2013-A7, 2021-A1, 2010-A3, 2021-A7, 2017-A9, 2017-A5, 2013-A2, 2021-A6, 2017-A2, 2013-A9, 2019-API7, 2023-API8', 'CVE CVE-2013-5704, CVE-2014-3581, CVE-2014-3583, CVE-2014-8109', 'BID 66550, 71656, 71657, 73040']</t>
+          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Current Version: 2.4.7 Fixed Version: 2.4.12 Detected technology URL: https://juice-shop-388277804329.us-west1.run.app/apps/', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="P19" t="n">
-        <v>98907</v>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>['Upgrade to Apache version 2.4.12 or later. Alternatively, ensure that the affected modules are not in use.']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/', 'input_type': 'link', 'input_name': None, 'payload': None, 'proof': 'Current Version: 2.4.7', 'output': 'Fixed Version: 2.4.12', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -2099,12 +2105,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>['7.5', 'CVSS:3.0/AV:N/AC:L/PR:N/UI:N/S:U/C:N/I:N/A:H', '5.0', 'CVSS2#AV:N/AC:L/Au:N/C:N/I:N/A:P']</t>
+          <t>['According to its banner, the version of Apache 2.4.x installed on the remote host is prior to 2.4.16. It is, therefore, affected by the following vulnerabilities :', ""- A flaw exists in the lua_websocket_read() function in the 'mod_lua' module due to incorrect handling of WebSocket PING frames. A remote attacker can exploit this, by sending a crafted WebSocket PING frame after a Lua script has called the wsupgrade() function, to crash a child process, resulting in a denial of service condition. (CVE-2015-0228)"", '- A NULL pointer dereference flaw exists in the read_request_line() function due to a failure to initialize the protocol structure member. A remote attacker can exploit this flaw, on installations that enable the INCLUDES filter and has an ErrorDocument 400 directive specifying a local URI, by sending a request that lacks a method, to cause a denial of service condition. (CVE-2015-0253)', '- A flaw exists in the chunked transfer coding implementation due to a failure to properly parse chunk headers. A remote attacker can exploit this to conduct HTTP request smuggling attacks. (CVE-2015-3183)', '- A flaw exists in the ap_some_auth_required() function due to a failure to consider that a Require directive may be associated with an authorization setting rather than an authentication setting. A remote attacker can exploit this, if a module that relies on the 2.2 API behavior exists, to bypass intended access restrictions. (CVE-2015-3185)', '- A flaw exists in the RC4 algorithm due to an initial double-byte bias in the keystream generation. An attacker can exploit this, via Bayesian analysis that combines an a priori plaintext distribution with keystream distribution statistics, to conduct a plaintext recovery of the ciphertext. Note that RC4 cipher suites are prohibited per RFC 7465. This issue was fixed in Apache version 2.4.13; however, 2.4.13, 2.4.14, and 2.4.15 were never publicly released.', ""Note that the scanner has not tested for these issues but has instead relied only on the application's self-reported version number.""]</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>['According to its banner, the version of Apache 2.4.x installed on the remote host is prior to 2.4.16. It is, therefore, affected by the following vulnerabilities :', ""- A flaw exists in the lua_websocket_read() function in the 'mod_lua' module due to incorrect handling of WebSocket PING frames. A remote attacker can exploit this, by sending a crafted WebSocket PING frame after a Lua script has called the wsupgrade() function, to crash a child process, resulting in a denial of service condition. (CVE-2015-0228)"", '- A NULL pointer dereference flaw exists in the read_request_line() function due to a failure to initialize the protocol structure member. A remote attacker can exploit this flaw, on installations that enable the INCLUDES filter and has an ErrorDocument 400 directive specifying a local URI, by sending a request that lacks a method, to cause a denial of service condition. (CVE-2015-0253)', '- A flaw exists in the chunked transfer coding implementation due to a failure to properly parse chunk headers. A remote attacker can exploit this to conduct HTTP request smuggling attacks. (CVE-2015-3183)', '- A flaw exists in the ap_some_auth_required() function due to a failure to consider that a Require directive may be associated with an authorization setting rather than an authentication setting. A remote attacker can exploit this, if a module that relies on the 2.2 API behavior exists, to bypass intended access restrictions. (CVE-2015-3185)', '- A flaw exists in the RC4 algorithm due to an initial double-byte bias in the keystream generation. An attacker can exploit this, via Bayesian analysis that combines an a priori plaintext distribution with keystream distribution statistics, to conduct a plaintext recovery of the ciphertext. Note that RC4 cipher suites are prohibited per RFC 7465. This issue was fixed in Apache version 2.4.13; however, 2.4.13, 2.4.14, and 2.4.15 were never publicly released.', ""Note that the scanner has not tested for these issues but has instead relied only on the application's self-reported version number.""]</t>
+          <t>['Upgrade to Apache version 2.4.16 or later. Alternatively, ensure that the affected modules are not in use.']</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2114,67 +2120,68 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['CWE 20', 'CWE 476', 'CWE 264', 'CWE 172', 'CWE 287', 'WASC Improper Input Handling', 'WASC Improper Output Handling', 'WASC Insufficient Authentication', 'WASC Insufficient Authorization', 'OWASP 2010-A8', 'OWASP 2013-A7', 'OWASP 2010-A4', 'OWASP 2021-A3', 'OWASP 2021-A1', 'OWASP 2013-A4', 'OWASP 2010-A3', 'OWASP 2021-A7', 'OWASP 2017-A9', 'OWASP 2017-A5', 'OWASP 2013-A2', 'OWASP 2021-A6', 'OWASP 2017A2', 'OWASP 2013-A9', 'OWASP 2019-API7', 'OWASP 2019-API8', 'OWASP 2023-API8', 'CVE-2015-0228', 'CVE-2015-0253', 'CVE-2015-3183', 'CVE-2015-3185', 'BID 73041', 'BID 75963', 'BID 75964', 'BID 75965']</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr"/>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>['CVSSV3 BASE SCORE 7.5', 'CVSSV3 VECTOR CVSS:3.0/AV:N/AC:L/PR:N/UI:N/S:U/C:N/I:N/A:H', 'CVSS BASE SCORE 5.0', 'CVSS VECTOR CVSS2#AV:N/AC:L/Au:N/C:N/I:N/A:P']</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
+        <v>98908</v>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"publication_date": "2019-01-09T00:00:00+00:00",
+"modification_date": "2023-03-14T00:00:00+00:00",
+"family": "Component Vulnerability",
+"severity": "High",
+"plugin_id": 98908}
+</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>['CWE 20, 476, 264, 172, 287', 'WASC Improper Input Handling, Improper Output Handling, Insufficient Authentication, Insufficient Authorization', 'OWASP 2010-A8, 2013-A7, 2010-A4, 2021-A3, 2021-A1, 2013-A4, 2010-A3, 2021-A7, 2017-A9, 2017-A5, 2013-A2, 2021-A6, 2017-A2, 2013-A9, 2019-API7, 2019-API8, 2023-API8', 'CVE CVE-2015-0228, CVE-2015-0253, CVE-2015-3183, CVE-2015-3185', 'BID 73041, 75963, 75964, 75965']</t>
+          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Current Version: 2.4.7 Fixed Version: 2.4.16 Detected technology URL: https://juice-shop-388277804329.us-west1.run.app/apps/', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="P20" t="n">
-        <v>98908</v>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>['Upgrade to Apache version 2.4.16 or later. Alternatively, ensure that the affected modules are not in use.']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/', 'input_type': 'link', 'input_name': None, 'payload': None, 'proof': 'Current Version: 2.4.7', 'output': 'Fixed Version: 2.4.16', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -2186,12 +2193,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>['8.1', 'CVSS:3.0/AV:N/AC:H/PR:N/UI:N/S:U/C:H/I:H/A:H', '6.8', 'CVSS2#AV:N/AC:M/Au:N/C:P/I:P/A:P']</t>
+          <t>['According to its banner, the version of Apache running on the remote host is 2.4.x prior to 2.4.25. It is, therefore, affected by the following vulnerabilities :', '- A flaw exists in the mod_session_crypto module due to encryption for data and cookies using the configured ciphers with possibly either CBC or ECB modes of operation (AES256-CBC by default). An unauthenticated, remote attacker can exploit this, via a padding oracle attack, to decrypt information without knowledge of the encryption key, resulting in the disclosure of potentially sensitive information. (CVE-2016-0736)', '- A denial of service vulnerability exists in the mod_auth_digest module during client entry allocation. An unauthenticated, remote attacker can exploit this, via specially crafted input, to exhaust shared memory resources, resulting in a server crash. (CVE-2016-2161)', ""- The Apache HTTP Server is affected by a man-in-the-middle vulnerability known as 'httpoxy' due to a failure to properly resolve namespace conflicts in accordance with RFC 3875 section 4.1.18."", ""The HTTP_PROXY environment variable is set based on untrusted user data in the 'Proxy' header of HTTP requests. The HTTP_PROXY environment variable is used by some web client libraries to specify a remote proxy server. An unauthenticated, remote attacker can exploit this, via a crafted 'Proxy' header in an HTTP request, to redirect an application's internal HTTP traffic to an arbitrary proxy server where it may be observed or manipulated. (CVE-2016-5387)"", 'A denial of service vulnerability exists in the mod_http2 module due to improper handling of the LimitRequestFields directive. An unauthenticated, remote attacker can exploit this, via specially crafted CONTINUATION frames in an HTTP/2 request, to inject unlimited request headers into the server, resulting in the exhaustion of memory resources. (CVE-2016-8740)', 'A flaw exists due to improper handling of whitespace patterns in user-agent headers. An unauthenticated, remote attacker can exploit this, via a specially crafted user-agent header, to cause the program to incorrectly process sequences of requests, resulting in interpreting responses incorrectly, polluting the cache, or disclosing the content from one request to a second downstream user-agent. (CVE-2016-8743)', 'A CRLF vulnerability exists in the mod_userdir module. An unauthenticated, remote attacker can exploit this, allowing HTTP response splitting attacks. (CVE-2016-4975)', ""Note that the scanner has not tested for these issues but has instead relied only on the application's self-reported version number.""]</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>['According to its banner, the version of Apache running on the remote host is 2.4.x prior to 2.4.25. It is, therefore, affected by the following vulnerabilities :', '- A flaw exists in the mod_session_crypto module due to encryption for data and cookies using the configured ciphers with possibly either CBC or ECB modes of operation (AES256-CBC by default). An unauthenticated, remote attacker can exploit this, via a padding oracle attack, to decrypt information without knowledge of the encryption key, resulting in the disclosure of potentially sensitive information. (CVE-2016-0736)', '- A denial of service vulnerability exists in the mod_auth_digest module during client entry allocation. An unauthenticated, remote attacker can exploit this, via specially crafted input, to exhaust shared memory resources, resulting in a server crash. (CVE-2016-2161)', ""- The Apache HTTP Server is affected by a man-in-the-middle vulnerability known as 'httpoxy' due to a failure to properly resolve namespace conflicts in accordance with RFC 3875 section 4.1.18."", ""The HTTP_PROXY environment variable is set based on untrusted user data in the 'Proxy' header of HTTP requests. The HTTP_PROXY environment variable is used by some web client libraries to specify a remote proxy server. An unauthenticated, remote attacker can exploit this, via a crafted 'Proxy' header in an HTTP request, to redirect an application's internal HTTP traffic to an arbitrary proxy server where it may be observed or manipulated. (CVE-2016-5387)"", 'A denial of service vulnerability exists in the mod_http2 module due to improper handling of the LimitRequestFields directive. An unauthenticated, remote attacker can exploit this, via specially crafted CONTINUATION frames in an HTTP/2 request, to inject unlimited request headers into the server, resulting in the exhaustion of memory resources. (CVE-2016-8740)', 'A flaw exists due to improper handling of whitespace patterns in user-agent headers. An unauthenticated, remote attacker can exploit this, via a specially crafted user-agent header, to cause the program to incorrectly process sequences of requests, resulting in interpreting responses incorrectly, polluting the cache, or disclosing the content from one request to a second downstream user-agent. (CVE-2016-8743)', 'A CRLF vulnerability exists in the mod_userdir module. An unauthenticated, remote attacker can exploit this, allowing HTTP response splitting attacks. (CVE-2016-4975)', ""Note that the scanner has not tested for these issues but has instead relied only on the application's self-reported version number.""]</t>
+          <t>[""Upgrade to Apache version 2.4.25 or later. Note that the 'httpoxy' vulnerability can be mitigated by applying the workarounds or patches as referenced in the vendor advisory asf-httpoxy-response.txt. Furthermore, to mitigate the other vulnerabilities, ensure that the affected modules (mod_session_crypto, mod_auth_digest, and mod_http2) are not in use.""]</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2201,67 +2208,68 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['CWE 113', 'CWE 399', 'CWE 823', 'CWE 310', 'CWE 287', 'CWE 19', 'CWE 20', 'CWE 93', 'CWE 284', 'CWE 770', 'WASC Insufficient Authentication', 'WASC Denial of Service', 'WASC HTTP Response Splitting', 'WASC Improper Input Handling', 'WASC Insufficient Authorization', 'OWASP 2013-A7', 'OWASP 2010-A4', 'OWASP 2021-A3', 'OWASP 2021-A1', 'OWASP 2017-A1', 'OWASP 2021-A2', 'OWASP 2013-A4', 'OWASP 2010-A8', 'OWASP 2013-A1', 'OWASP 2010-A3', 'OWASP 2021-A7', 'OWASP 2017-A9', 'OWASP 2017A5', 'OWASP 2013-A2', 'OWASP 2021-A6', 'OWASP 2010-A1', 'OWASP 2017-A2', 'OWASP 2013-A9', 'OWASP 2019-API8', 'OWASP 2023-API8', 'OWASP 2019-API7', 'CVE-2016-5387', 'CVE-2016-2161', 'CVE-2016-0736', 'CVE-2016-8740', 'CVE-2016-4975', 'CVE-2016-8743', 'BID 94650', 'BID 95076', 'BID 105093', 'BID 95078', 'BID 91816', 'BID 95077']</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr"/>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>['CVSSV3 BASE SCORE 8.1', 'CVSSV3 VECTOR CVSS:3.0/AV:N/AC:H/PR:N/UI:N/S:U/C:H/I:H/A:H', 'CVSS BASE SCORE 6.8', 'CVSS VECTOR CVSS2#AV:N/AC:M/Au:N/C:P/I:P/A:P']</t>
+        </is>
+      </c>
+      <c r="L21" t="n">
+        <v>98910</v>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"publication_date": "2019-01-09T00:00:00+00:00",
+"modification_date": "2023-03-14T00:00:00+00:00",
+"family": "Component Vulnerability",
+"severity": "High",
+"plugin_id": 98910}
+</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>['CWE 113, 399, 823, 310, 287, 19, 20, 93, 284, 770', 'WASC Insufficient Authentication, Denial of Service, HTTP Response Splitting, Improper Input Handling, Insufficient Authorization', 'OWASP 2013-A7, 2010-A4, 2021-A3, 2021-A1, 2017-A1, 2021-A2, 2013-A4, 2010-A8, 2013-A1, 2010-A3, 2021-A7, 2017-A9, 2017-A5, 2013-A2, 2021-A6, 2010-A1, 2017-A2, 2013-A9, 2019-API8, 2023-API8, 2019-API7', 'CVE CVE-2016-5387, CVE-2016-2161, CVE-2016-0736, CVE-2016-8740, CVE-2016-4975, CVE-2016-8743', 'BID 94650, 95076, 105093, 95078, 91816, 95077']</t>
+          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Current Version: 2.4.7 Fixed Version: 2.4.25 Detected technology URL: https://juice-shop-388277804329.us-west1.run.app/apps/', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="P21" t="n">
-        <v>98910</v>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>[""Upgrade to Apache version 2.4.25 or later. Note that the 'httpoxy' vulnerability can be mitigated by applying the workarounds or patches as referenced in the vendor advisory asf-httpoxy-response.txt. Furthermore, to mitigate the other vulnerabilities, ensure that the affected modules (mod_session_crypto, mod_auth_digest, and mod_http2) are not in use.""]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/', 'input_type': 'link', 'input_name': None, 'payload': None, 'proof': 'Current Version: 2.4.7', 'output': 'Fixed Version: 2.4.25', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -2273,12 +2281,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>['7.5', 'CVSS:3.0/AV:N/AC:L/PR:N/UI:N/S:U/C:H/I:N/A:N', '5.0', 'CVSS2#AV:N/AC:L/Au:N/C:P/I:N/A:N']</t>
+          <t>['According to its banner, the version of Apache running on the remote host is 2.4.x prior to 2.4.28. It is, therefore, affected by an HTTP vulnerability related to the &lt;Limit {method}&gt; directive in an .htaccess file.', ""Note that the scanner has not tested for these issues but has instead relied only on the application's self-reported version number.""]</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>['According to its banner, the version of Apache running on the remote host is 2.4.x prior to 2.4.28. It is, therefore, affected by an HTTP vulnerability related to the &lt;Limit {method}&gt; directive in an .htaccess file.', ""Note that the scanner has not tested for these issues but has instead relied only on the application's self-reported version number.""]</t>
+          <t>['Upgrade to Apache version 2.4.28 or later.']</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2288,67 +2296,68 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['CWE 416', 'OWASP 2021-A6', 'OWASP 2013-A9', 'OWASP 2017-A9', 'OWASP 2019-API7', 'OWASP 2023-API8', 'CVE-2017-9798', 'BID 100872', 'BID 105598']</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr"/>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>['CVSSV3 BASE SCORE 7.5', 'CVSSV3 VECTOR CVSS:3.0/AV:N/AC:L/PR:N/UI:N/S:U/C:H/I:N/A:N', 'CVSS BASE SCORE 5.0', 'CVSS VECTOR CVSS2#AV:N/AC:L/Au:N/C:P/I:N/A:N']</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
+        <v>98913</v>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"publication_date": "2019-01-09T00:00:00+00:00",
+"modification_date": "2023-03-14T00:00:00+00:00",
+"family": "Component Vulnerability",
+"severity": "High",
+"plugin_id": 98913}
+</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>['CWE 416', 'OWASP 2021-A6, 2013-A9, 2017-A9, 2019-API7, 2023-API8', 'CVE CVE-2017-9798', 'BID 100872, 105598']</t>
+          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Current Version: 2.4.7 Fixed Version: 2.4.28 Detected technology URL: https://juice-shop-388277804329.us-west1.run.app/apps/', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="P22" t="n">
-        <v>98913</v>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>['Upgrade to Apache version 2.4.28 or later.']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/', 'input_type': 'link', 'input_name': None, 'payload': None, 'proof': 'Current Version: 2.4.7', 'output': 'Fixed Version: 2.4.28', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -2360,12 +2369,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>['7.5', 'CVSS:3.0/AV:N/AC:L/PR:N/UI:N/S:U/C:N/I:N/A:H', '5.0', 'CVSS2#AV:N/AC:L/Au:N/C:N/I:N/A:P']</t>
+          <t>['According to its banner, the version of Apache running on the remote host is 2.4.x prior to 2.4.34. It is, therefore, affected by the following vulnerabilities:', 'By specially crafting HTTP/2 requests, workers would be allocated 60 seconds longer than necessary, leading to worker exhaustion and a denial of service. (CVE-2018-1333)', 'By specially crafting HTTP requests, the mod_md challenge handler would dereference a NULL pointer and cause the child process to segfault. This could be used to DoS the server. (CVE-2018-8011)', ""Note that the scanner has not tested for these issues but has instead relied only on the application's self-reported version number.""]</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>['According to its banner, the version of Apache running on the remote host is 2.4.x prior to 2.4.34. It is, therefore, affected by the following vulnerabilities:', 'By specially crafting HTTP/2 requests, workers would be allocated 60 seconds longer than necessary, leading to worker exhaustion and a denial of service. (CVE-2018-1333)', 'By specially crafting HTTP requests, the mod_md challenge handler would dereference a NULL pointer and cause the child process to segfault. This could be used to DoS the server. (CVE-2018-8011)', ""Note that the scanner has not tested for these issues but has instead relied only on the application's self-reported version number.""]</t>
+          <t>['Upgrade to Apache version 2.4.34 or later.']</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2375,67 +2384,68 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['CWE 400', 'CWE 476', 'WASC Denial of Service', 'OWASP 2021-A6', 'OWASP 2013-A9', 'OWASP 2017-A9', 'OWASP 2019-API7', 'OWASP 2023-API8', 'CVE-2018-1333', 'CVE-2018-8011']</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr"/>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>['CVSSV3 BASE SCORE 7.5', 'CVSSV3 VECTOR CVSS:3.0/AV:N/AC:L/PR:N/UI:N/S:U/C:N/I:N/A:H', 'CVSS BASE SCORE 5.0', 'CVSS VECTOR CVSS2#AV:N/AC:L/Au:N/C:N/I:N/A:P']</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>98915</v>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"publication_date": "2019-01-31T00:00:00+00:00",
+"modification_date": "2023-03-14T00:00:00+00:00",
+"family": "Component Vulnerability",
+"severity": "High",
+"plugin_id": 98915}
+</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>['CWE 400, 476', 'WASC Denial of Service', 'OWASP 2021-A6, 2013-A9, 2017-A9, 2019-API7, 2023-API8', 'CVE CVE-2018-1333, CVE-2018-8011', 'BID -']</t>
+          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Current Version: 2.4.7 Fixed Version: 2.4.34 Detected technology URL: https://juice-shop-388277804329.us-west1.run.app/apps/', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="P23" t="n">
-        <v>98915</v>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>['Upgrade to Apache version 2.4.34 or later.']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/', 'input_type': 'link', 'input_name': None, 'payload': None, 'proof': 'Current Version: 2.4.7', 'output': 'Fixed Version: 2.4.34', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -2447,12 +2457,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>['7.5', 'CVSS:3.0/AV:N/AC:L/PR:N/UI:N/S:U/C:N/I:N/A:H', '7.8', 'CVSS2#AV:N/AC:L/Au:N/C:N/I:N/A:C']</t>
+          <t>['According to its banner, the version of Apache running on the remote host is 2.4.x prior to 2.4.58. It is, therefore, affected by multiple vulnerabilities:', 'Out-of-bounds read vulnerability in mod_macro of Apache HTTP Server. (CVE-2023-31122)', 'An attacker, opening a HTTP/2 connection with an initial window size of 0, was able to block handling of that connection indefinitely in Apache HTTP Server. This could be used to exhaust worker resources in the server, similar to the well known slow loris attack pattern. (CVE-2023-43622)', ""A client could send new requests and resets, keeping the connection busy and open and causing the memory footprint to keep on growing. On connection close, all resources were reclaimed, but the process might run out of memory before that. (CVE-2023-45802) Note that the scanner has not tested for these issues but has instead relied only on the application's self-reported version number.""]</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>['According to its banner, the version of Apache running on the remote host is 2.4.x prior to 2.4.58. It is, therefore, affected by multiple vulnerabilities:', 'Out-of-bounds read vulnerability in mod_macro of Apache HTTP Server. (CVE-2023-31122)', 'An attacker, opening a HTTP/2 connection with an initial window size of 0, was able to block handling of that connection indefinitely in Apache HTTP Server. This could be used to exhaust worker resources in the server, similar to the well known slow loris attack pattern. (CVE-2023-43622)', ""A client could send new requests and resets, keeping the connection busy and open and causing the memory footprint to keep on growing. On connection close, all resources were reclaimed, but the process might run out of memory before that. (CVE-2023-45802) Note that the scanner has not tested for these issues but has instead relied only on the application's self-reported version number.""]</t>
+          <t>['Upgrade to Apache version 2.4.58 or later.']</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2462,67 +2472,68 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['CWE 125', 'CWE 400', 'WASC Denial of Service', 'OWASP 2021-A6', 'OWASP 2013-A9', 'OWASP 2017-A9', 'OWASP 2019-API7', 'OWASP 2023-API8', 'CVE-2023-31122', 'CVE-2023-43622', 'CVE-2023-45802']</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr"/>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>['CVSSV3 BASE SCORE 7.5', 'CVSSV3 VECTOR CVSS:3.0/AV:N/AC:L/PR:N/UI:N/S:U/C:N/I:N/A:H', 'CVSS BASE SCORE 7.8', 'CVSS VECTOR CVSS2#AV:N/AC:L/Au:N/C:N/I:N/A:C']</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
+        <v>114090</v>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"publication_date": "2023-10-20T00:00:00+00:00",
+"modification_date": "2023-11-15T00:00:00+00:00",
+"family": "Component Vulnerability",
+"severity": "High",
+"plugin_id": 114090}
+</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>['CWE 125, 400', 'WASC Denial of Service', 'OWASP 2021-A6, 2013-A9, 2017-A9, 2019-API7, 2023-API8', 'CVE CVE-2023-31122, CVE-2023-43622, CVE-2023-45802', 'BID -']</t>
+          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Current Version: 2.4.7 Fixed Version: 2.4.58 Detected technology URL: https://juice-shop-388277804329.us-west1.run.app/apps/', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="P24" t="n">
-        <v>114090</v>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>['Upgrade to Apache version 2.4.58 or later.']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/', 'input_type': 'link', 'input_name': None, 'payload': None, 'proof': 'Current Version: 2.4.7', 'output': 'Fixed Version: 2.4.58', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -2534,12 +2545,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>['7.5', 'CVSS:3.0/AV:N/AC:L/PR:N/UI:N/S:U/C:N/I:N/A:H', '7.8', 'CVSS2#AV:N/AC:L/Au:N/C:N/I:N/A:C']</t>
+          <t>['According to its banner, the version of Apache running on the remote host is 2.4.x prior to 2.4.59. It is, therefore, affected by multiple vulnerabilities:', 'Faulty input validation in the core of Apache allows malicious or exploitable backend/content generators to split HTTP responses. (CVE-2023-38709)', 'HTTP Response splitting in multiple modules in Apache HTTP Server allows an attacker that can inject malicious response headers into backend applications to cause an HTTP desynchronization attack. (CVE-2024-24795)', 'HTTP/2 incoming headers exceeding the limit are temporarily buffered in nghttp2 in order to generate an informative HTTP 413 response. If a client does not stop sending headers, this leads to memory exhaustion. (CVE-2024-27316)', ""Note that the scanner has not tested for these issues but has instead relied only on the application's self-reported version number.""]</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>['According to its banner, the version of Apache running on the remote host is 2.4.x prior to 2.4.59. It is, therefore, affected by multiple vulnerabilities:', 'Faulty input validation in the core of Apache allows malicious or exploitable backend/content generators to split HTTP responses. (CVE-2023-38709)', 'HTTP Response splitting in multiple modules in Apache HTTP Server allows an attacker that can inject malicious response headers into backend applications to cause an HTTP desynchronization attack. (CVE-2024-24795)', 'HTTP/2 incoming headers exceeding the limit are temporarily buffered in nghttp2 in order to generate an informative HTTP 413 response. If a client does not stop sending headers, this leads to memory exhaustion. (CVE-2024-27316)', ""Note that the scanner has not tested for these issues but has instead relied only on the application's self-reported version number.""]</t>
+          <t>['Upgrade to Apache version 2.4.59 or later.']</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2549,67 +2560,68 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['CWE 113', 'CWE 400', 'CWE 770', 'WASC Denial of Service', 'WASC HTTP Response Splitting', 'OWASP 2013-A1', 'OWASP 2021-A3', 'OWASP 2021-A6', 'OWASP 2017-A1', 'OWASP 2013-A9', 'OWASP 2017-A9', 'OWASP 2010-A1', 'OWASP 2019-API8', 'OWASP 2023-API8', 'OWASP 2019-API7', 'CVE-2023-38709', 'CVE-2024-24795', 'CVE-2024-27316']</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr"/>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>['CVSSV3 BASE SCORE 7.5', 'CVSSV3 VECTOR CVSS:3.0/AV:N/AC:L/PR:N/UI:N/S:U/C:N/I:N/A:H', 'CVSS BASE SCORE 7.8', 'CVSS VECTOR CVSS2#AV:N/AC:L/Au:N/C:N/I:N/A:C']</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>114249</v>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"publication_date": "2024-04-09T00:00:00+00:00",
+"modification_date": "2024-04-09T00:00:00+00:00",
+"family": "Component Vulnerability",
+"severity": "High",
+"plugin_id": 114249}
+</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>['CWE 113, 400, 770', 'WASC Denial of Service, HTTP Response Splitting', 'OWASP 2013-A1, 2021-A3, 2021-A6, 2017-A1, 2013-A9, 2017-A9, 2010-A1, 2019-API8, 2023-API8, 2019-API7', 'CVE CVE-2023-38709, CVE-2024-24795, CVE-2024-27316', 'BID -']</t>
+          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Current Version: 2.4.7 Fixed Version: 2.4.59 Detected technology URL: https://juice-shop-388277804329.us-west1.run.app/apps/', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="P25" t="n">
-        <v>114249</v>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>['Upgrade to Apache version 2.4.59 or later.']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/', 'input_type': 'link', 'input_name': None, 'payload': None, 'proof': 'Current Version: 2.4.7', 'output': 'Fixed Version: 2.4.59', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -2621,12 +2633,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>['7.5', 'CVSS:3.0/AV:N/AC:L/PR:N/UI:N/S:U/C:H/I:N/A:N', '7.8', 'CVSS2#AV:N/AC:L/Au:N/C:C/I:N/A:N']</t>
+          <t>[""Server on Windows with mod_rewrite in server/vhost context, allows to potentially leak NTLM hashes to a malicious server via SSRF and malicious requests. (CVE-2024-40898) Note that the scanner has not tested for these issues but has instead relied only on the application's self-reported version number.""]</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>[""Server on Windows with mod_rewrite in server/vhost context, allows to potentially leak NTLM hashes to a malicious server via SSRF and malicious requests. (CVE-2024-40898) Note that the scanner has not tested for these issues but has instead relied only on the application's self-reported version number.""]</t>
+          <t>['Upgrade to Apache version 2.4.62 or later.']</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2636,67 +2648,68 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['CWE 668', 'CWE 918', 'WASC Application Misconfiguration', 'WASC Insufficient Authorization', 'OWASP 2010-A8', 'OWASP 2013-A7', 'OWASP 2021-A1', 'OWASP 2021-A10', 'OWASP 2013-A5', 'OWASP 2013-A9', 'OWASP 2017-A9', 'OWASP 2017-A5', 'OWASP 2017-A6', 'OWASP 2021-A6', 'OWASP 2010-A6', 'OWASP 2023-API7', 'OWASP 2023-API8', 'OWASP 2019-API7', 'CVE-2024-40725', 'CVE-2024-40898']</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr"/>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>['CVSSV3 BASE SCORE 7.5', 'CVSSV3 VECTOR CVSS:3.0/AV:N/AC:L/PR:N/UI:N/S:U/C:H/I:N/A:N', 'CVSS BASE SCORE 7.8', 'CVSS VECTOR CVSS2#AV:N/AC:L/Au:N/C:C/I:N/A:N']</t>
+        </is>
+      </c>
+      <c r="L26" t="n">
+        <v>114385</v>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"publication_date": "2024-07-22T00:00:00+00:00",
+"modification_date": "2024-07-22T00:00:00+00:00",
+"family": "Component Vulnerability",
+"severity": "High",
+"plugin_id": 114385}
+</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>['CWE 668, 918', 'WASC Application Misconfiguration, Insufficient Authorization', 'OWASP 2010-A8, 2013-A7, 2021-A1, 2021-A10, 2013-A5, 2013-A9, 2017-A9, 2017-A5, 2017-A6, 2021-A6, 2010-A6, 2023-API7,', '2023-API8, 2019-API7', 'CVE CVE-2024-40725, CVE-2024-40898', 'BID -']</t>
+          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Current Version: 2.4.7 Fixed Version: 2.4.62 Detected technology URL: https://juice-shop-388277804329.us-west1.run.app/apps/', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="P26" t="n">
-        <v>114385</v>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>['Upgrade to Apache version 2.4.62 or later.']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/', 'input_type': 'link', 'input_name': None, 'payload': None, 'proof': 'Current Version: 2.4.7', 'output': 'Fixed Version: 2.4.62', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -2708,12 +2721,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>['6.5', 'CVSS:3.0/AV:N/AC:L/PR:N/UI:N/S:U/C:L/I:L/A:N', '5.8', 'CVSS2#AV:N/AC:M/Au:N/C:P/I:P/A:N']</t>
+          <t>['The HTTP protocol by itself is clear text, meaning that any data that is transmitted via HTTP can be captured and the contents viewed. To keep data private and prevent it from being intercepted, HTTP is often tunnelled through either Secure Sockets Layer (SSL) or Transport Layer Security (TLS). When either of these encryption standards are used, it is referred to as HTTPS. HTTP Strict Transport Security (HSTS) is an optional response header that can be configured on the server to instruct the browser to only communicate via HTTPS. This will be enforced by the browser even if the user requests a HTTP resource on the same server.', 'Cyber-criminals will often attempt to compromise sensitive information passed from the client to the server using HTTP. This can be conducted via various Man-in-The-Middle (MiTM) attacks or through network packet captures.', 'Scanner discovered that the affected application is using HTTPS however does not use the HSTS header.']</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>['The HTTP protocol by itself is clear text, meaning that any data that is transmitted via HTTP can be captured and the contents viewed. To keep data private and prevent it from being intercepted, HTTP is often tunnelled through either Secure Sockets Layer (SSL) or Transport Layer Security (TLS). When either of these encryption standards are used, it is referred to as HTTPS. HTTP Strict Transport Security (HSTS) is an optional response header that can be configured on the server to instruct the browser to only communicate via HTTPS. This will be enforced by the browser even if the user requests a HTTP resource on the same server.', 'Cyber-criminals will often attempt to compromise sensitive information passed from the client to the server using HTTP. This can be conducted via various Man-in-The-Middle (MiTM) attacks or through network packet captures.', 'Scanner discovered that the affected application is using HTTPS however does not use the HSTS header.']</t>
+          <t>['Depending on the framework being used the implementation methods will vary, however it is advised that the `Strict-Transport-Security` header be configured on the server.', ""One of the options for this header is `max-age`, which is a representation (in milliseconds) determining the time in which the client's browser will adhere to the header policy."", 'Depending on the environment and the application this time period could be from as low as minutes to as long as days.']</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2723,63 +2736,68 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['CWE 319', 'CWE 523', 'WASC Insufficient Transport Layer Protection', 'OWASP 2010-A9', 'OWASP 2013-A6', 'OWASP 2017-A3', 'OWASP 2021-A2', 'OWASP 2023-API8', 'OWASP 2019-API7']</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr"/>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>['CVSSV3 BASE SCORE 6.5', 'CVSSV3 VECTOR CVSS:3.0/AV:N/AC:L/PR:N/UI:N/S:U/C:L/I:L/A:N', 'CVSS BASE SCORE 5.8', 'CVSS VECTOR CVSS2#AV:N/AC:M/Au:N/C:P/I:P/A:N']</t>
+        </is>
+      </c>
+      <c r="L27" t="n">
+        <v>98056</v>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"publication_date": "2017-03-31T00:00:00+00:00",
+"modification_date": "2024-03-18T00:00:00+00:00",
+"family": "HTTP Security Header",
+"severity": "Medium",
+"plugin_id": 98056}
+</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>['CWE 319, 523', 'WASC Insufficient Transport Layer Protection', 'OWASP 2010-A9, 2013-A6, 2017-A3, 2021-A2, 2023-API8, 2019-API7', 'CVE -', 'BID -']</t>
+          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner did not find any Strict-Transport-Security header in the response returned by the target when querying URL https://juice-shop-388277804329.us-west1.run.app/apps/.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/stylesheets/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner did not find any Strict-Transport-Security header in the response returned by the target when querying URL https://juice-shop-388277804329.us-west1.run.app/stylesheets/.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/documents/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner did not find any Strict-Transport-Security header in the response returned by the target when querying URL https://juice-shop-388277804329.us-west1.run.app/documents/.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/passwords/web.config.bak', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner did not find any Strict-Transport-Security header in the response returned by the target when querying URL https://juice-shop-388277804329.us-west1.run.app/passwords/web.config.bak.', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'application/x-trash'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/soap/nusoap.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner did not find any Strict-Transport-Security header in the response returned by the target when querying URL https://juice-shop-388277804329.us-west1.run.app/soap/nusoap.php.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/images/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner did not find any Strict-Transport-Security header in the response returned by the target when querying URL https://juice-shop-388277804329.us-west1.run.app/images/.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/phpinfo.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner did not find any Strict-Transport-Security header in the response returned by the target when querying URL https://juice-shop-388277804329.us-west1.run.app/phpinfo.php.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/db/bwapp.sqlite', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner did not find any Strict-Transport-Security header in the response returned by the target when querying URL https://juice-shop-388277804329.us-west1.run.app/db/bwapp.sqlite.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/js/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner did not find any Strict-Transport-Security header in the response returned by the target when querying URL https://juice-shop-388277804329.us-west1.run.app/js/.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/soap/class.soap_fault.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner did not find any Strict-Transport-Security header in the response returned by the target when querying URL https://juice-shop-388277804329.us-west1.run.app/soap/class.soap_fault.php.', 'request_method': 'GET', 'http_status_code': 500, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner did not find any Strict-Transport-Security header in the response returned by the target when querying URL https://juice-shop-388277804329.us-west1.run.app/.', 'request_method': 'GET', 'http_status_code': 302, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/login.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner did not find any Strict-Transport-Security header in the response returned by the target when querying URL https://juice-shop-388277804329.us-west1.run.app/login.php.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/training_install.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner did not find any Strict-Transport-Security header in the response returned by the target when querying URL https://juice-shop-388277804329.us-west1.run.app/training_install.php.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/soap/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner did not find any Strict-Transport-Security header in the response returned by the target when querying URL https://juice-shop-388277804329.us-west1.run.app/soap/.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/db/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner did not find any Strict-Transport-Security header in the response returned by the target when querying URL https://juice-shop-388277804329.us-west1.run.app/db/.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/passwords/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner did not find any Strict-Transport-Security header in the response returned by the target when querying URL https://juice-shop-388277804329.us-west1.run.app/passwords/.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/soap/class.nusoap_base.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner did not find any Strict-Transport-Security header in the response returned by the target when querying URL https://juice-shop-388277804329.us-west1.run.app/soap/class.nusoap_base.php.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/soap/class.wsdlcache.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner did not find any Strict-Transport-Security header in the response returned by the target when querying URL https://juice-shop-388277804329.us-west1.run.app/soap/class.wsdlcache.php.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/install.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner did not find any Strict-Transport-Security header in the response returned by the target when querying URL https://juice-shop-388277804329.us-west1.run.app/install.php.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/passwords/wp-config.bak', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner did not find any Strict-Transport-Security header in the response returned by the target when querying URL https://juice-shop-388277804329.us-west1.run.app/passwords/wp-config.bak.', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'application/x-trash'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/passwords/heroes.xml', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner did not find any Strict-Transport-Security header in the response returned by the target when querying URL https://juice-shop-388277804329.us-west1.run.app/passwords/heroes.xml.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/info_install.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner did not find any Strict-Transport-Security header in the response returned by the target when querying URL https://juice-shop-388277804329.us-west1.run.app/info_install.php.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/#/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner did not find any Strict-Transport-Security header in the response returned by the target when querying URL https://juice-shop-388277804329.us-west1.run.app/#/.', 'request_method': 'GET', 'http_status_code': 302, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/portal.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner did not find any Strict-Transport-Security header in the response returned by the target when querying URL https://juice-shop-388277804329.us-west1.run.app/portal.php.', 'request_method': 'GET', 'http_status_code': 302, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/movie_search', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner did not find any Strict-Transport-Security header in the response returned by the target when querying URL https://juice-shop-388277804329.us-west1.run.app/apps/movie_search.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="P27" t="n">
-        <v>98056</v>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>['Depending on the framework being used the implementation methods will vary, however it is advised that the `Strict-Transport-Security` header be configured on the server.', ""One of the options for this header is `max-age`, which is a representation (in milliseconds) determining the time in which the client's browser will adhere to the header policy."", 'Depending on the environment and the application this time period could be from as low as minutes to as long as days.']</t>
-        </is>
-      </c>
-      <c r="R27" t="inlineStr"/>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2809,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>['6.9', 'CVSS:4.0/AV:N/AC:L/AT:N/PR:N/UI:N/VC:L/VI:N/VA:N/SC:N/SI:N/SA:N', '5.3', 'CVSS:3.0/AV:N/AC:L/PR:N/UI:N/S:U/C:L/I:N/A:N', '5.0', 'CVSS2#AV:N/AC:L/Au:N/C:P/I:N/A:N']</t>
+          <t>['Web servers permitting directory listing are typically used for sharing files.', 'Directory listing allows the client to view a simple list of all the files and folders hosted on the web server. The client is then able to traverse each directory and download the files.', 'Cyber-criminals will utilise the presence of directory listing to discover sensitive files, download protected content, or even just learn how the web application is strurctured.', 'Scanner discovered that the affected page permits directory listing.']</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>['Web servers permitting directory listing are typically used for sharing files.', 'Directory listing allows the client to view a simple list of all the files and folders hosted on the web server. The client is then able to traverse each directory and download the files.', 'Cyber-criminals will utilise the presence of directory listing to discover sensitive files, download protected content, or even just learn how the web application is strurctured.', 'Scanner discovered that the affected page permits directory listing.']</t>
+          <t>['Unless the web server is being utilised to share static and non-sensitive files, enabling directory listing is considered a poor security practice', 'This can typically be done with a simple configuration change on the server. The steps to disable the directory listing will differ depending on the type of server being used (IIS, Apache, etc.). If directory listing is required, and permitted, then steps should be taken to ensure that the risk of such a configuration is reduced.', 'These can include:', '1. Requiring authentication to access affected pages. 2. Adding the affected path to the `robots.txt` file to prevent the directory contents being searchable via search engines. 3. Ensuring that sensitive files are not stored within the web or document root. 4. Removing any files that are not required for the application to function.']</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2806,67 +2824,68 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['CWE 548', 'WASC Directory Indexing', 'OWASP 2017-A6', 'OWASP 2021-A1', 'OWASP 2013-A5', 'OWASP 2010-A6', 'OWASP 2023-API8', 'OWASP 2019-API7']</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr"/>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>['CVSSV4 BASE SCORE 6.9', 'CVSSV4 VECTOR CVSS:4.0/AV:N/AC:L/AT:N/PR:N/UI:N/VC:L/VI:N/VA:N/SC:N/SI:N/SA:N', 'CVSSV3 BASE SCORE 5.3', 'CVSSV3 VECTOR CVSS:3.0/AV:N/AC:L/PR:N/UI:N/S:U/C:L/I:N/A:N', 'CVSS BASE SCORE 5.0', 'CVSS VECTOR CVSS2#AV:N/AC:L/Au:N/C:P/I:N/A:N']</t>
+        </is>
+      </c>
+      <c r="L28" t="n">
+        <v>98084</v>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"publication_date": "2019-02-04T00:00:00+00:00",
+"modification_date": "2024-08-12T00:00:00+00:00",
+"family": "Web Servers",
+"severity": "Medium",
+"plugin_id": 98084}
+</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>['CWE 548', 'WASC Directory Indexing', 'OWASP 2017-A6, 2021-A1, 2013-A5, 2010-A6, 2023-API8, 2019-API7', 'CVE -', 'BID -']</t>
+          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/passwords/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'WAS Scanner has enumerated the following Directory Listings: - https://juice-shop-388277804329.us-west1.run.app/passwords/', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/documents/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'WAS Scanner has enumerated the following Directory Listings: - https://juice-shop-388277804329.us-west1.run.app/documents/', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/db/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'WAS Scanner has enumerated the following Directory Listings: - https://juice-shop-388277804329.us-west1.run.app/db/', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/stylesheets/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'WAS Scanner has enumerated the following Directory Listings: - https://juice-shop-388277804329.us-west1.run.app/stylesheets/', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/js/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'WAS Scanner has enumerated the following Directory Listings: - https://juice-shop-388277804329.us-west1.run.app/js/', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/soap/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'WAS Scanner has enumerated the following Directory Listings: - https://juice-shop-388277804329.us-west1.run.app/soap/', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/images/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'WAS Scanner has enumerated the following Directory Listings: - https://juice-shop-388277804329.us-west1.run.app/images/', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'WAS Scanner has enumerated the following Directory Listings: - https://juice-shop-388277804329.us-west1.run.app/apps/', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}]</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="P28" t="n">
-        <v>98084</v>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>['Unless the web server is being utilised to share static and non-sensitive files, enabling directory listing is considered a poor security practice', 'This can typically be done with a simple configuration change on the server. The steps to disable the directory listing will differ depending on the type of server being used (IIS, Apache, etc.). If directory listing is required, and permitted, then steps should be taken to ensure that the risk of such a configuration is reduced.', 'These can include:', '1. Requiring authentication to access affected pages. 2. Adding the affected path to the `robots.txt` file to prevent the directory contents being searchable via search engines. 3. Ensuring that sensitive files are not stored within the web or document root. 4. Removing any files that are not required for the application to function.']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/passwords/', 'input_type': 'link', 'input_name': None, 'payload': None, 'proof': 'WAS Scanner has enumerated the following Directory Listings: - https://juice-shop-388277804329.us-west1.run.app/passwords/', 'output': 'Directory Listing Detected', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html;charset=UTF-8'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/documents/', 'input_type': 'link', 'input_name': None, 'payload': None, 'proof': 'WAS Scanner has enumerated the following Directory Listings: - https://juice-shop-388277804329.us-west1.run.app/documents/', 'output': 'Directory Listing Detected', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html;charset=UTF-8'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/db/', 'input_type': 'link', 'input_name': None, 'payload': None, 'proof': 'WAS Scanner has enumerated the following Directory Listings: - https://juice-shop-388277804329.us-west1.run.app/db/', 'output': 'Directory Listing Detected', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html;charset=UTF-8'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/stylesheets/', 'input_type': 'link', 'input_name': None, 'payload': None, 'proof': 'WAS Scanner has enumerated the following Directory Listings: - https://juice-shop-388277804329.us-west1.run.app/stylesheets/', 'output': 'Directory Listing Detected', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html;charset=UTF-8'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/js/', 'input_type': 'link', 'input_name': None, 'payload': None, 'proof': 'WAS Scanner has enumerated the following Directory Listings: - https://juice-shop-388277804329.us-west1.run.app/js/', 'output': 'Directory Listing Detected', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html;charset=UTF-8'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/soap/', 'input_type': 'link', 'input_name': None, 'payload': None, 'proof': 'WAS Scanner has enumerated the following Directory Listings: - https://juice-shop-388277804329.us-west1.run.app/soap/', 'output': 'Directory Listing Detected', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html;charset=UTF-8'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/images/', 'input_type': 'link', 'input_name': None, 'payload': None, 'proof': 'WAS Scanner has enumerated the following Directory Listings: - https://juice-shop-388277804329.us-west1.run.app/images/', 'output': 'Directory Listing Detected', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html;charset=UTF-8'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/', 'input_type': 'link', 'input_name': None, 'payload': None, 'proof': 'WAS Scanner has enumerated the following Directory Listings: - https://juice-shop-388277804329.us-west1.run.app/apps/', 'output': 'Directory Listing Detected', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html;charset=UTF-8'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -2878,12 +2897,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>['6.9', 'CVSS:4.0/AV:N/AC:L/AT:N/PR:N/UI:N/VC:L/VI:N/VA:N/SC:N/SI:N/SA:N', '5.8', 'CVSS:3.0/AV:N/AC:L/PR:N/UI:N/S:C/C:L/I:N/A:N', '5.0', 'CVSS2#AV:N/AC:L/Au:N/C:P/I:N/A:N']</t>
+          <t>[""Many PHP installation tutorials instruct the user to create a PHP file that calls the PHP function 'phpinfo()' for debugging purposes, and various PHP applications may also include such a file by default. By accessing it, a remote attacker can discover a large amount of information about the remote web server configuration to help conduct further attacks, including :"", '- Versions of the web server, operating system and PHP components', '- Details of the PHP configuration', '- Loaded PHP extensions with their configurations', '- Server environment variables.']</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>[""Many PHP installation tutorials instruct the user to create a PHP file that calls the PHP function 'phpinfo()' for debugging purposes, and various PHP applications may also include such a file by default. By accessing it, a remote attacker can discover a large amount of information about the remote web server configuration to help conduct further attacks, including :"", '- Versions of the web server, operating system and PHP components', '- Details of the PHP configuration', '- Loaded PHP extensions with their configurations', '- Server environment variables.']</t>
+          <t>['Remove the affected file(s).']</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2893,67 +2912,68 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['CWE 200', 'WASC Information Leakage', 'OWASP 2017-A6', 'OWASP 2021-A1', 'OWASP 2013-A5', 'OWASP 2010-A6', 'OWASP 2023-API8', 'OWASP 2019-API7']</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr"/>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>['CVSSV4 BASE SCORE 6.9', 'CVSSV4 VECTOR CVSS:4.0/AV:N/AC:L/AT:N/PR:N/UI:N/VC:L/VI:N/VA:N/SC:N/SI:N/SA:N', 'CVSSV3 BASE SCORE 5.8', 'CVSSV3 VECTOR CVSS:3.0/AV:N/AC:L/PR:N/UI:N/S:C/C:L/I:N/A:N', 'CVSS BASE SCORE 5.0', 'CVSS VECTOR CVSS2#AV:N/AC:L/Au:N/C:P/I:N/A:N']</t>
+        </is>
+      </c>
+      <c r="L29" t="n">
+        <v>98223</v>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"publication_date": "2018-06-27T00:00:00+00:00",
+"modification_date": "2022-06-28T00:00:00+00:00",
+"family": "Web Applications",
+"severity": "Medium",
+"plugin_id": 98223}
+</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>['CWE 200', 'WASC Information Leakage', 'OWASP 2017-A6, 2021-A1, 2013-A5, 2010-A6, 2023-API8, 2019-API7', 'CVE -', 'BID -']</t>
+          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/phpinfo.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '&lt;!DOCTYPE html PUBLIC "-//W3C//DTD XHTML 1.0 Transitional//EN" "DTD/xhtml1-transitional.dtd"&gt; &lt;html xmlns="http://www.w3.org/1999/xhtml"&gt;&lt;head&gt; &lt;style type="text/css"&gt; body {background-color: #ffffff; color: #000000;}', 'output': 'The scanner detected the presence of the `phpinfo.php` file on https://juice-shop-388277804329.us-west1.run.app/phpinfo. php', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}]</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="P29" t="n">
-        <v>98223</v>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>['Remove the affected file(s).']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/phpinfo.php', 'input_type': 'link', 'input_name': None, 'payload': None, 'proof': '&lt;!DOCTYPE html PUBLIC "-//W3C//DTD XHTML 1.0 Transitional//EN" "DTD/xhtml1-transitional.dtd"&gt;&lt;html xmlns="http://www.w3.org/1999/xhtml"&gt;&lt;head&gt;&lt;style type="text/css"&gt;body {background-color: #ffffff; color: #000000;}', 'output': 'The scanner detected the presence of the phpinfo.php file on https://juice-shop-388277804329.us-west1.run.app/phpinfo.php', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -2965,12 +2985,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>['6.9', 'CVSS:4.0/AV:N/AC:L/AT:N/PR:N/UI:N/VC:L/VI:N/VA:N/SC:N/SI:N/SA:N', '5.3', 'CVSS:3.0/AV:N/AC:L/PR:N/UI:N/S:U/C:L/I:N/A:N', '5.0', 'CVSS2#AV:N/AC:L/Au:N/C:P/I:N/A:N']</t>
+          <t>['An information disclosure vulnerability exists in the remote web server due to the disclosure of the web.config file. An unauthenticated, remote attacker can exploit this, via a simple GET request, to disclose potentially sensitive configuration information.', 'The scanner detected the presence of the `web.config` file on https://juice-shop-388277804329.us-west1.run.app/passwords/web.config']</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>['An information disclosure vulnerability exists in the remote web server due to the disclosure of the web.config file. An unauthenticated, remote attacker can exploit this, via a simple GET request, to disclose potentially sensitive configuration information.', 'The scanner detected the presence of the `web.config` file on https://juice-shop-388277804329.us-west1.run.app/passwords/web.config']</t>
+          <t>['Ensure proper restrictions are in place, or remove the file if the file is not required.']</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2980,67 +3000,68 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['CWE 425', 'WASC Predictable Resource Location', 'OWASP 2010-A4', 'OWASP 2021-A1', 'OWASP 2013-A4', 'OWASP 2017-A5', 'OWASP 2019-API7', 'OWASP 2023-API3', 'OWASP 2019-API3', 'OWASP 2023-API8']</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr"/>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>['CVSSV4 BASE SCORE 6.9', 'CVSSV4 VECTOR CVSS:4.0/AV:N/AC:L/AT:N/PR:N/UI:N/VC:L/VI:N/VA:N/SC:N/SI:N/SA:N', 'CVSSV3 BASE SCORE 5.3', 'CVSSV3 VECTOR CVSS:3.0/AV:N/AC:L/PR:N/UI:N/S:U/C:L/I:N/A:N', 'CVSS BASE SCORE 5.0', 'CVSS VECTOR CVSS2#AV:N/AC:L/Au:N/C:P/I:N/A:N']</t>
+        </is>
+      </c>
+      <c r="L30" t="n">
+        <v>98594</v>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"publication_date": "2019-05-14T00:00:00+00:00",
+"modification_date": "2022-05-16T00:00:00+00:00",
+"family": "Data Exposure",
+"severity": "Medium",
+"plugin_id": 98594}
+</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>['CWE 425', 'WASC Predictable Resource Location', 'OWASP 2010-A4, 2021-A1, 2013-A4, 2017-A5, 2019-API7, 2023-API3, 2019-API3, 2023-API8', 'CVE -', 'BID -', 'CWE 538', 'OWASP 2017-A6, 2021-A1, 2013-A5, 2010-A6, 2023-API8, 2023-API3, 2019-API3, 2019-API7']</t>
+          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/passwords/web.config', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '&lt;?xml version="1.0"?&gt; &lt;configuration&gt; &lt;configSections&gt; &lt;sectionGroup name="system.web.extensions" type="System.Web.Configuration.SystemWebExtensionsSectionGroup, System.Web. Extensions, Version=3.5.0.0, Culture=neutral, PublicKeyToken=31BF3856AD364E35"&gt;', 'output': 'The scanner detected the presence of the `web.config` file on https://juice-shop-388277804329.us-west1.run.app/passwords /web.config', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'application/x-trash'}]</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="P30" t="n">
-        <v>98594</v>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>['Ensure proper restrictions are in place, or remove the file if the file is not required.']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/passwords/web.config', 'input_type': 'link', 'input_name': None, 'payload': None, 'proof': '&lt;?xml version="1.0"?&gt;&lt;configuration&gt;&lt;configSections&gt;&lt;sectionGroup name="system.web.extensions" type="System.Web.Configuration.SystemWebExtensionsSectionGroup, System.Web.Extensions, Version=3.5.0.0, Culture=neutral, PublicKeyToken=31BF3856AD364E35"&gt;', 'output': 'The scanner detected the presence of the web.config file on https://juice-shop-388277804329.us-west1.run.app/passwords/web.config', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'application/x-trash'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -3052,12 +3073,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>['6.5', 'CVSS:3.0/AV:N/AC:H/PR:N/UI:N/S:U/C:H/I:L/A:N', '5.8', 'CVSS2#AV:N/AC:M/Au:N/C:P/I:P/A:N']</t>
+          <t>[""The remote host use at least one SSL/TLS ciphers that does not offer forward secrecy (FS) also known as perfect forward secrecy (PFS). It's a feature that provides assurances the session keys will not be compromised even if the server's private key is compromised.""]</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>[""The remote host use at least one SSL/TLS ciphers that does not offer forward secrecy (FS) also known as perfect forward secrecy (PFS). It's a feature that provides assurances the session keys will not be compromised even if the server's private key is compromised.""]</t>
+          <t>['Reconfigure the server to disable cipher suites without forward secrecy and retain only cipher suites that provide forward secrecy (ECDHE or DHE based cipher suites).']</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -3067,67 +3088,68 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['CWE 327', 'WASC Insufficient Transport Layer Protection', 'OWASP 2010-A9', 'OWASP 2013-A6', 'OWASP 2017-A3', 'OWASP 2021-A2', 'OWASP 2023-API8', 'OWASP 2019-API7']</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr"/>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>['CVSSV3 BASE SCORE 6.5', 'CVSSV3 VECTOR CVSS:3.0/AV:N/AC:H/PR:N/UI:N/S:U/C:H/I:L/A:N', 'CVSS BASE SCORE 5.8', 'CVSS VECTOR CVSS2#AV:N/AC:M/Au:N/C:P/I:P/A:N']</t>
+        </is>
+      </c>
+      <c r="L31" t="n">
+        <v>98617</v>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"publication_date": "2019-06-12T00:00:00+00:00",
+"modification_date": "2022-11-10T00:00:00+00:00",
+"family": "SSL/TLS",
+"severity": "Medium",
+"plugin_id": 98617}
+</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>['CWE 327', 'WASC Insufficient Transport Layer Protection', 'OWASP 2010-A9, 2013-A6, 2017-A3, 2021-A2, 2023-API8, 2019-API7']</t>
+          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/#/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Protocol Cipher Suite Name (RFC) Key Exchange Strength -------------------------------------------------------------------- TLS1.2 TLS_RSA_WITH_AES_128_GCM_SHA256 RSA 4096 TLS1.2 TLS_RSA_WITH_AES_256_GCM_SHA384 RSA 4096 TLS1.2 TLS_RSA_WITH_AES_128_CBC_SHA RSA 4096 TLS1.2 TLS_RSA_WITH_AES_256_CBC_SHA RSA 4096', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="P31" t="n">
-        <v>98617</v>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>['Reconfigure the server to disable cipher suites without forward secrecy and retain only cipher suites that provide forward secrecy (ECDHE or DHE based cipher suites).']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/#/', 'input_type': 'link', 'input_name': None, 'payload': None, 'proof': 'TLS1.2 TLS_RSA_WITH_AES_128_GCM_SHA256 RSA 4096\nTLS1.2 TLS_RSA_WITH_AES_256_GCM_SHA384 RSA 4096\nTLS1.2 TLS_RSA_WITH_AES_128_CBC_SHA RSA 4096\nTLS1.2 TLS_RSA_WITH_AES_256_CBC_SHA RSA 4096', 'output': 'The scanner detected supported TLS cipher suites with RSA 4096-bit key exchange on https://juice-shop-388277804329.us-west1.run.app/#/', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -3139,12 +3161,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>['6.9', 'CVSS:4.0/AV:N/AC:L/AT:N/PR:N/UI:N/VC:L/VI:N/VA:N/SC:N/SI:N/SA:N', '5.3', 'CVSS:3.0/AV:N/AC:L/PR:N/UI:N/S:U/C:L/I:N/A:N', '5.0', 'CVSS2#AV:N/AC:L/Au:N/C:P/I:N/A:N']</t>
+          <t>[""Scanner has detected server-side source code within the server's response."", 'A modern web application will be reliant on several different programming languages. These languages can be broken up in two flavours. These are client-side languages (such as those that run in the browser -- like JavaScript) and server-side languages (which are executed by the server -- like ASP, PHP, JSP, etc.) to form the dynamic pages (client-side code) that are then sent to the client. Because all server side code should be executed by the server, it should never be seen by the client, however in some scenarios it is possible that the server has a misconfiguration or the server side code has syntax errors, and therefore is not executed by the server but is instead sent to the client. As the server-side source code often contains sensitive information, such as database connection strings or details into the application workflow, this can be extremely risky.', 'Cyber-criminals will attempt to discover pages that either accidentally or forcefully allow the server-side source code to be disclosed, to assist in discovering further vulnerabilities or sensitive information.']</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>[""Scanner has detected server-side source code within the server's response."", 'A modern web application will be reliant on several different programming languages. These languages can be broken up in two flavours. These are client-side languages (such as those that run in the browser -- like JavaScript) and server-side languages (which are executed by the server -- like ASP, PHP, JSP, etc.) to form the dynamic pages (client-side code) that are then sent to the client. Because all server side code should be executed by the server, it should never be seen by the client, however in some scenarios it is possible that the server has a misconfiguration or the server side code has syntax errors, and therefore is not executed by the server but is instead sent to the client. As the server-side source code often contains sensitive information, such as database connection strings or details into the application workflow, this can be extremely risky.', 'Cyber-criminals will attempt to discover pages that either accidentally or forcefully allow the server-side source code to be disclosed, to assist in discovering further vulnerabilities or sensitive information.']</t>
+          <t>['It is important that the server does not deliver server side code to the client, and the server misconfiguration or server code should be changed to prevent this.']</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -3154,67 +3176,68 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['CWE 540', 'WASC Information Leakage', 'OWASP 2017-A6', 'OWASP 2021-A1', 'OWASP 2010-A6', 'OWASP 2013-A5', 'OWASP 2023-API3', 'OWASP 2019-API3']</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr"/>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>['CVSSV4 BASE SCORE 6.9', 'CVSSV4 VECTOR CVSS:4.0/AV:N/AC:L/AT:N/PR:N/UI:N/VC:L/VI:N/VA:N/SC:N/SI:N/SA:N', 'CVSSV3 BASE SCORE 5.3', 'CVSSV3 VECTOR CVSS:3.0/AV:N/AC:L/PR:N/UI:N/S:U/C:L/I:N/A:N', 'CVSS BASE SCORE 5.0', 'CVSS VECTOR CVSS2#AV:N/AC:L/Au:N/C:P/I:N/A:N']</t>
+        </is>
+      </c>
+      <c r="L32" t="n">
+        <v>98779</v>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"publication_date": "2019-12-19T00:00:00+00:00",
+"modification_date": "2024-01-03T00:00:00+00:00",
+"family": "Data Exposure",
+"severity": "Medium",
+"plugin_id": 98779}
+</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>['CWE 540', 'WASC Information Leakage', 'OWASP 2017-A6, 2021-A1, 2010-A6, 2013-A5, 2023-API3, 2019-API3']</t>
+          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/passwords/wp-config.bak', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'The following patterns were detected in the HTTP response body : - &lt;?php', 'output': "The scanner detected the presence of a 'PHP' source code in the web application response.", 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'application/x-trash'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/db/bwapp.sqlite', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'The following patterns were detected in the HTTP response body : - &lt;?', 'output': "The scanner detected the presence of a 'PHP' source code in the web application response.", 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}]</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="P32" t="n">
-        <v>98779</v>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>['It is important that the server does not deliver server side code to the client, and the server misconfiguration or server code should be changed to prevent this.']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/passwords/wp-config.bak', 'input_type': 'link', 'input_name': None, 'payload': None, 'proof': 'The following patterns were detected in the HTTP response body : - &lt;?php', 'output': "The scanner detected the presence of a 'PHP' source code in the web application response.", 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'application/x-trash'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/db/bwapp.sqlite', 'input_type': 'link', 'input_name': None, 'payload': None, 'proof': 'The following patterns were detected in the HTTP response body : - &lt;?', 'output': "The scanner detected the presence of a 'PHP' source code in the web application response.", 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -3225,11 +3248,6 @@
         </is>
       </c>
       <c r="B33" t="inlineStr">
-        <is>
-          <t>['None,None, 5.9,  CVSS:3.0/AV:N/AC:H/PR:N/UI:N/S:U/C:N/I:N/A:H, 4.3, CVSS2#AV:N/AC:M/Au:N/C:N/I:N/A:P']</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
         <is>
           <t>['According to its banner, the version of Apache running on the remote host is 2.4.x prior to 2.4.35. By sending continuous
 SETTINGS frames of maximum size an ongoing HTTP/2 connection could be kept busy and would never time out. This can be
@@ -3238,6 +3256,11 @@
 number.']</t>
         </is>
       </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>['Upgrade to Apache version 2.4.35 or later.']</t>
+        </is>
+      </c>
       <c r="D33" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3245,64 +3268,64 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+          <t>['CWE 20', 'CWE 400', 'WASC Denial of Service', 'WASC Improper Input Handling', 'OWASP 2010-A4', 'OWASP 2021-A3', 'OWASP 2021-A6', 'OWASP 2013-A9', 'OWASP 2013-A4', 'OWASP 2017-A9', 'OWASP 2017-A5', 'OWASP 2019-API7', 'OWASP 2023-API8', 'CVE-2018-11763', 'BID 105414']</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr"/>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>['CVSSV3 BASE SCORE 5.9', 'CVSSV3 VECTOR CVSS:3.0/AV:N/AC:H/PR:N/UI:N/S:U/C:N/I:N/A:H', 'CVSS BASE SCORE 4.3', 'CVSS VECTOR CVSS2#AV:N/AC:M/Au:N/C:N/I:N/A:P']</t>
+        </is>
+      </c>
+      <c r="L33" t="n">
+        <v>98916</v>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"publication_date": "2019-01-31T00:00:00+00:00",
+"modification_date": "2023-03-14T00:00:00+00:00",
+"family": "Component Vulnerability",
+"severity": "Medium",
+"plugin_id": 98916}
+</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>['CWE 20, 400, WASC Denial of Service, Improper Input Handling, OWASP 2010-A4, 2021-A3, 2021-A6, 2013-A9, 2013-A4, 2017-A9, 2017-A5, 2019-API7, 2023-API8, CVE CVE-2018-11763
-BID 105414']</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="n">
-        <v>98916</v>
+          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Current Version: 2.4.7 Fixed Version: 2.4.35 Detected technology URL: https://juice-shop-388277804329.us-west1.run.app/apps/', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>['Upgrade to Apache version 2.4.35 or later.']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/', 'input_type': 'link', 'input_name': None, 'payload': None, 'proof': 'Current Version: 2.4.7', 'output': 'Fixed Version: 2.4.35', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -3314,12 +3337,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>['2.1', '3.1', '2.6', 'CVSS:4.0/AV:N/AC:H/AT:N/PR:N/UI:A/VC:L/VI:N/VA:N/SC:N/SI:N/SA:N', 'CVSS:3.0/AV:N/AC:H/PR:N/UI:R/S:U/C:L/I:N/A:N', 'CVSS2#AV:N/AC:H/Au:N/C:P/I:N/A:N']</t>
+          <t>['The HttpOnly flag assists in the prevention of client side-scripts (such as JavaScript) from accessing and using the cookie.', ""This can help prevent XSS attacks from targeting the cookies holding the client's session token (setting the HttpOnly flag does not prevent, nor safeguard against XSS vulnerabilities themselves).""]</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>['The HttpOnly flag assists in the prevention of client side-scripts (such as JavaScript) from accessing and using the cookie.', ""This can help prevent XSS attacks from targeting the cookies holding the client's session token (setting the HttpOnly flag does not prevent, nor safeguard against XSS vulnerabilities themselves).""]</t>
+          <t>['The initial step to remedy this would be to determine whether any client-side scripts (such as JavaScript) need to access the cookie and if not, set the HttpOnly flag.', 'It should be noted that some older browsers are not compatible with the HttpOnly flag; therefore, setting this flag will not protect those clients against this form of attack.']</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -3329,67 +3352,68 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['CWE 456', 'CWE 601', 'CWE 908', 'WASC URL Redirector Abuse', 'OWASP 2021-A6', 'OWASP 2021-A1', 'OWASP 2013-A10', 'OWASP 2010-A10', 'OWASP 2013-A9', 'OWASP 2017-A9', 'OWASP 2019-API7', 'OWASP 2023-API8', 'CVE-2020-1927', 'CVE-2020-1934']</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr"/>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>['CVSSV3 BASE SCORE 6.1', 'CVSSV3 VECTOR CVSS:3.0/AV:N/AC:L/PR:N/UI:R/S:C/C:L/I:L/A:N', 'CVSS BASE SCORE 5.8', 'CVSS VECTOR CVSS2#AV:N/AC:M/Au:N/C:P/I:P/A:N']</t>
+        </is>
+      </c>
+      <c r="L34" t="n">
+        <v>98998</v>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"publication_date": "2020-04-10T00:00:00+00:00",
+"modification_date": "2023-03-14T00:00:00+00:00",
+"family": "Component Vulnerability",
+"severity": "Medium",
+"plugin_id": 98998}
+</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>['CWE 1004', 'WASC Application Misconfiguration', 'OWASP 2010-A9, 2013-A6, 2017-A3, 2021-A5', 'CVE -', 'BID -']</t>
+          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Current Version: 2.4.7 Fixed Version: 2.4.43 Detected technology URL: https://juice-shop-388277804329.us-west1.run.app/apps/', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="P34" t="n">
-        <v>98998</v>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>['The initial step to remedy this would be to determine whether any client-side scripts (such as JavaScript) need to access the cookie and if not, set the HttpOnly flag.', 'It should be noted that some older browsers are not compatible with the HttpOnly flag; therefore, setting this flag will not protect those clients against this form of attack.']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/', 'input_type': 'link', 'input_name': None, 'payload': None, 'proof': 'Current Version: 2.4.7', 'output': 'Fixed Version: 2.4.43', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -3401,15 +3425,15 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>['6.9, CVSS:4.0/AV:N/AC:L/AT:N/PR:N/UI:N/VC:L/VI:N/VA:N/SC:N/SI:N/SA:N, 5.3, CVSS:3.0/AV:N/AC:L/PR:N/UI:N/S:U/C:L/I:N/A:N, 5.0, CVSS2#AV:N/AC:L/Au:N/C:P/I:N/A:N']</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
           <t>['A web server configuration file has been detected on the target host. This may expose privileged information or configurations
 to a malicious actor.']</t>
         </is>
       </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>['Restrict access to the web server file or remove it.']</t>
+        </is>
+      </c>
       <c r="D35" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3417,67 +3441,68 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['CWE 538', 'WASC Predictable Resource Location', 'OWASP 2017-A6', 'OWASP 2021-A1', 'OWASP 2013-A5', 'OWASP 2010-A6', 'OWASP 2023-API8', 'OWASP 2023-API3', 'OWASP 2019-API3', 'OWASP 2019-API7']</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr"/>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>['CVSSV4 BASE SCORE 6.9', 'CVSSV4 VECTOR CVSS:4.0/AV:N/AC:L/AT:N/PR:N/UI:N/VC:L/VI:N/VA:N/SC:N/SI:N/SA:N', 'CVSSV3 BASE SCORE 5.3', 'CVSSV3 VECTOR CVSS:3.0/AV:N/AC:L/PR:N/UI:N/S:U/C:L/I:N/A:N', 'CVSS BASE SCORE 5.0', 'CVSS VECTOR CVSS2#AV:N/AC:L/Au:N/C:P/I:N/A:N']</t>
+        </is>
+      </c>
+      <c r="L35" t="n">
+        <v>114195</v>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"publication_date": "2024-02-02T00:00:00+00:00",
+"modification_date": "2024-02-02T00:00:00+00:00",
+"family": "Data Exposure",
+"severity": "Medium",
+"plugin_id": 114195}
+</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>['CWE 538',
-'WASC Predictable Resource Location',
-'OWASP 2017-A6, 2021-A1, 2013-A5, 2010-A6, 2023-API8, 2023-API3, 2019-API3, 2019-API7',
-CVE -,
-BID -']</t>
+          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/passwords/web.config', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '&lt;?xml version="1.0"?&gt; &lt;configuration&gt; &lt;configSections&gt; &lt;sectionGroup name="system.web.extensions" type="System.Web.Configuration.SystemWebExtensionsSectionGroup, System.Web. Extensions, Version=3.5.0.0, Culture=neutral, PublicKeyToken=31BF3856AD364E35"&gt;', 'output': 'The scanner detected the presence of the `web.config` file on https://juice-shop-388277804329.us-west1.run.app/passwords /web.config', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'application/x-trash'}]</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="P35" t="n">
-        <v>114195</v>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>['Restrict access to the web server file or remove it.']</t>
-        </is>
-      </c>
-      <c r="R35" t="inlineStr"/>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -3488,11 +3513,6 @@
         </is>
       </c>
       <c r="B36" t="inlineStr">
-        <is>
-          <t>['None, None, 3.1, CVSS:3.0/AV:N/AC:H/PR:N/UI:R/S:U/C:N/I:L/A:N, 2.6, CVSS2#AV:N/AC:H/Au:N/C:N/I:P/A:N']</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
         <is>
           <t>['Clickjacking (User Interface redress attack, UI redress attack, UI redressing) is a malicious technique of tricking a Web user into
 clicking on something different from what the user perceives they are clicking on, thus potentially revealing confidential
@@ -3503,6 +3523,11 @@
 into other sites.']</t>
         </is>
       </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>['Configure your web server to include an `X-Frame-Options` header.']</t>
+        </is>
+      </c>
       <c r="D36" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3510,67 +3535,68 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['CWE 1021', 'CWE 346', 'WASC Application Misconfiguration', 'OWASP 2021-A7', 'OWASP 2017-A6', 'OWASP 2021-A4', 'OWASP 2013-A5', 'OWASP 2010-A6', 'OWASP 2023-API8', 'OWASP 2019-API7']</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr"/>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>['CVSSV3 BASE SCORE 3.1', 'CVSSV3 VECTOR CVSS:3.0/AV:N/AC:H/PR:N/UI:R/S:U/C:N/I:L/A:N', 'CVSS BASE SCORE 2.6', 'CVSS VECTOR CVSS2#AV:N/AC:H/Au:N/C:N/I:P/A:N']</t>
+        </is>
+      </c>
+      <c r="L36" t="n">
+        <v>98060</v>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"publication_date": "2017-03-31T00:00:00+00:00",
+"modification_date": "2024-03-25T00:00:00+00:00",
+"family": "HTTP Security Header",
+"severity": "Low",
+"plugin_id": 98060}
+</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>['CWE 1021, 346',
-'WASC Application Misconfiguration',
-'OWASP 2021-A7, 2017-A6, 2021-A4, 2013-A5, 2010-A6, 2023-API8, 2019-API7',
-'CVE -',
-'BID -']</t>
+          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/stylesheets/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Page https://juice-shop-388277804329.us-west1.run.app/stylesheets/ has no X-Frame-Options header defined', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/passwords/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Page https://juice-shop-388277804329.us-west1.run.app/passwords/ has no X-Frame-Options header defined', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/passwords/wp-config.bak', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Page https://juice-shop-388277804329.us-west1.run.app/passwords/wp-config.bak has no X-Frame-Options header defined', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'application/x-trash'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/passwords/web.config.bak', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Page https://juice-shop-388277804329.us-west1.run.app/passwords/web.config.bak has no X-Frame-Options header defined', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'application/x-trash'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/soap/nusoap.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Page https://juice-shop-388277804329.us-west1.run.app/soap/nusoap.php has no X-Frame-Options header defined', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/images/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Page https://juice-shop-388277804329.us-west1.run.app/images/ has no X-Frame-Options header defined', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/install.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Page https://juice-shop-388277804329.us-west1.run.app/install.php has no X-Frame-Options header defined', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/db/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Page https://juice-shop-388277804329.us-west1.run.app/db/ has no X-Frame-Options header defined', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/js/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Page https://juice-shop-388277804329.us-west1.run.app/js/ has no X-Frame-Options header defined', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/info_install.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Page https://juice-shop-388277804329.us-west1.run.app/info_install.php has no X-Frame-Options header defined', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/user_new.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Page https://juice-shop-388277804329.us-west1.run.app/user_new.php has no X-Frame-Options header defined', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/db/bwapp.sqlite', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Page https://juice-shop-388277804329.us-west1.run.app/db/bwapp.sqlite has no X-Frame-Options header defined', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/training_install.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Page https://juice-shop-388277804329.us-west1.run.app/training_install.php has no X-Frame-Options header defined', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/info.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Page https://juice-shop-388277804329.us-west1.run.app/info.php has no X-Frame-Options header defined', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/soap/class.soap_fault.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Page https://juice-shop-388277804329.us-west1.run.app/soap/class.soap_fault.php has no X-Frame-Options header defined', 'request_method': 'GET', 'http_status_code': 500, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/movie_search', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Page https://juice-shop-388277804329.us-west1.run.app/apps/movie_search has no X-Frame-Options header defined', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/soap/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Page https://juice-shop-388277804329.us-west1.run.app/soap/ has no X-Frame-Options header defined', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/phpinfo.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Page https://juice-shop-388277804329.us-west1.run.app/phpinfo.php has no X-Frame-Options header defined', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/training.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Page https://juice-shop-388277804329.us-west1.run.app/training.php has no X-Frame-Options header defined', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/passwords/heroes.xml', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Page https://juice-shop-388277804329.us-west1.run.app/passwords/heroes.xml has no X-Frame-Options header defined', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/login.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Page https://juice-shop-388277804329.us-west1.run.app/login.php has no X-Frame-Options header defined', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/soap/class.nusoap_base.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Page https://juice-shop-388277804329.us-west1.run.app/soap/class.nusoap_base.php has no X-Frame-Options header defined', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/soap/class.wsdlcache.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Page https://juice-shop-388277804329.us-west1.run.app/soap/class.wsdlcache.php has no X-Frame-Options header defined', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/documents/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Page https://juice-shop-388277804329.us-west1.run.app/documents/ has no X-Frame-Options header defined', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Page https://juice-shop-388277804329.us-west1.run.app/apps/ has no X-Frame-Options header defined', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="P36" t="n">
-        <v>98060</v>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>['Configure your web server to include an `X-Frame-Options` header.']</t>
-        </is>
-      </c>
-      <c r="R36" t="inlineStr"/>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -3581,77 +3607,13 @@
         </is>
       </c>
       <c r="B37" t="inlineStr">
-        <is>
-          <t>['2.1, CVSS:4.0/AV:N/AC:H/AT:N/PR:N/UI:A/VC:L/VI:N/VA:N/SC:N/SI:N/SA:N, 3.1,CVSS:3.0/AV:N/AC:H/PR:N/UI:R/S:U/C:L/I:N/A:N, 2.6, CVSS2#AV:N/AC:H/Au:N/C:P/I:N/A:N']</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
         <is>
           <t>['The HttpOnly flag assists in the prevention of client side-scripts (such as JavaScript) from accessing and using the cookie.
 This can help prevent XSS attacks from targeting the cookies holding the client's session token (setting the HttpOnly flag does
 not prevent, nor safeguard against XSS vulnerabilities themselves).']</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>['CWE 1004',
-'WASC Application Misconfiguration',
-'OWASP 2010-A9, 2013-A6, 2017-A3, 2021-A5',
-'CVE -',
-BID -']</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="P37" t="n">
-        <v>98063</v>
-      </c>
-      <c r="Q37" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>['The initial step to remedy this would be to determine whether any client-side scripts (such as JavaScript) need to access the
 cookie and if not, set the HttpOnly flag.
@@ -3659,14 +3621,75 @@
 protect those clients against this form of attack.']</t>
         </is>
       </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>['CWE 1004', 'WASC Application Misconfiguration', 'OWASP 2010-A9', 'OWASP 2013-A6', 'OWASP 2017-A3', 'OWASP 2021-A5']</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>['CVSSV4 BASE SCORE 2.1', 'CVSSV4 VECTOR CVSS:4.0/AV:N/AC:H/AT:N/PR:N/UI:A/VC:L/VI:N/VA:N/SC:N/SI:N/SA:N', 'CVSSV3 BASE SCORE 3.1', 'CVSSV3 VECTOR CVSS:3.0/AV:N/AC:H/PR:N/UI:R/S:U/C:L/I:N/A:N', 'CVSS BASE SCORE 2.6', 'CVSS VECTOR CVSS2#AV:N/AC:H/Au:N/C:P/I:N/A:N']</t>
+        </is>
+      </c>
+      <c r="L37" t="n">
+        <v>98063</v>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"publication_date": "2017-03-31T00:00:00+00:00",
+"modification_date": "2023-12-11T00:00:00+00:00",
+"family": "HTTP Security Header",
+"severity": "Low",
+"plugin_id": 98063}
+</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/', 'input_type': 'cookie', 'input_name': 'PHPSESSID', 'payload': '', 'proof': 'PHPSESSID=711vt1tpgrucudl1kaq9t074f5; Path=/', 'output': "The scanner detected a cookie named 'PHPSESSID' set with JavaScript which prevents the HTTPOnly attribute from being used. If the cookie is set to handle sensitive information (for example session-based information), it should be set via the HTTP method.", 'request_method': 'GET', 'http_status_code': 302, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}]</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/', 'input_type': 'cookie', 'input_name': 'PHPSESSID', 'payload': None, 'proof': 'PHPSESSID=711vt1tpgrucudl1kaq9t074f5; Path=/', 'output': "The scanner detected a cookie named 'PHPSESSID' set with JavaScript which prevents the HTTPOnly attribute from being used. If the cookie is set to handle sensitive information (for example session-based information), it should be set via the HTTP method.", 'request_method': 'GET', 'http_status_code': 302, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -3677,11 +3700,6 @@
         </is>
       </c>
       <c r="B38" t="inlineStr">
-        <is>
-          <t>['2.1,CVSS:4.0/AV:N/AC:H/AT:N/PR:N/UI:A/VC:L/VI:N/VA:N/SC:N/SI:N/SA:N, 3.1, CVSS:3.0/AV:N/AC:H/PR:N/UI:R/S:U/C:L/I:N/A:N,2.6, CVSS2#AV:N/AC:H/Au:N/C:P/I:N/A:N']</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
         <is>
           <t>['When the `secure` flag is set on a cookie, the browser will prevent it from being sent over a clear text channel (HTTP) and only
 allow it to be sent when an encrypted channel is used (HTTPS).
@@ -3690,6 +3708,11 @@
 Note that if the cookie does not contain sensitive information, the risk of this vulnerability is mitigated.']</t>
         </is>
       </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>['If the cookie contains sensitive information, then the server should ensure that the cookie has the `secure` flag set.']</t>
+        </is>
+      </c>
       <c r="D38" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3697,71 +3720,68 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['CWE 614', 'WASC Insufficient Transport Layer Protection', 'OWASP 2010-A9', 'OWASP 2013-A6', 'OWASP 2017-A3', 'OWASP 2021-A5']</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr"/>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>['CVSSV4 BASE SCORE 2.1', 'CVSSV4 VECTOR CVSS:4.0/AV:N/AC:H/AT:N/PR:N/UI:A/VC:L/VI:N/VA:N/SC:N/SI:N/SA:N', 'CVSSV3 BASE SCORE 3.1', 'CVSSV3 VECTOR CVSS:3.0/AV:N/AC:H/PR:N/UI:R/S:U/C:L/I:N/A:N', 'CVSS BASE SCORE 2.6', 'CVSS VECTOR CVSS2#AV:N/AC:H/Au:N/C:P/I:N/A:N']</t>
+        </is>
+      </c>
+      <c r="L38" t="n">
+        <v>98064</v>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"publication_date": "2017-03-31T00:00:00+00:00",
+"modification_date": "2023-12-11T00:00:00+00:00",
+"family": "HTTP Security Header",
+"severity": "Low",
+"plugin_id": 98064}
+</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>['CWE 614',
-'WASC Insufficient Transport Layer Protection',
-'OWASP 2010-A9, 2013-A6, 2017-A3, 2021-A5',
-'CVE -',
-BID -']</t>
+          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/', 'input_type': 'cookie', 'input_name': 'PHPSESSID', 'payload': '', 'proof': 'PHPSESSID=711vt1tpgrucudl1kaq9t074f5; Path=/', 'output': "The scanner detected a cookie named 'PHPSESSID' set with JavaScript without the Secure flag set.", 'request_method': 'GET', 'http_status_code': 302, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}]</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="P38" t="n">
-        <v>98064</v>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>['If the cookie contains sensitive information, then the server should ensure that the cookie has the `secure` flag set.']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/', 'input_type': 'cookie', 'input_name': 'PHPSESSID', 'payload': None, 'proof': 'PHPSESSID=711vt1tpgrucudl1kaq9t074f5; Path=/', 'output': "The scanner detected a cookie named 'PHPSESSID' set with JavaScript without the Secure flag set.", 'request_method': 'GET', 'http_status_code': 302, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -3773,12 +3793,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>['2.3', '3.1', '2.6']</t>
+          <t>['In typical form-based web applications, it is common practice for developers to allow `autocomplete` within the HTML form to improve the usability of the page. With `autocomplete` enabled (default), the browser is allowed to cache previously entered form values.', 'For legitimate purposes, this allows the user to quickly re-enter the same data when completing the form multiple times.', ""When `autocomplete` is enabled on either/both the username and password fields, this could allow a cyber-criminal with access to the victim's computer the ability to have the victim's credentials automatically entered as the cyber-criminal visits the affected page."", 'Scanner has discovered that the affected page contains a form containing a password field that has not disabled `autocomplete`.']</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>['In typical form-based web applications, it is common practice for developers to allow `autocomplete` within the HTML form to improve the usability of the page. With `autocomplete` enabled (default), the browser is allowed to cache previously entered form values.', 'For legitimate purposes, this allows the user to quickly re-enter the same data when completing the form multiple times.', ""When `autocomplete` is enabled on either/both the username and password fields, this could allow a cyber-criminal with access to the victim's computer the ability to have the victim's credentials automatically entered as the cyber-criminal visits the affected page."", 'Scanner has discovered that the affected page contains a form containing a password field that has not disabled `autocomplete`.']</t>
+          <t>['The `autocomplete` value can be configured in two different locations.', 'The first and most secure location is to disable the `autocomplete` attribute on the `&lt;form&gt;` HTML tag. This will disable `autocomplete` for all inputs within that form. An example of disabling `autocomplete` within the form tag is `&lt;form autocomplete=off&gt;`.', 'The second slightly less desirable option is to disable the `autocomplete` attribute for a specific `&lt;input&gt;` HTML tag. While this may be the less desired solution from a security perspective, it may be preferred method for usability reasons, depending on size of the form. An example of disabling the `autocomplete` attribute within a password input tag is `&lt;input type=password autocomplete=off&gt;`.']</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -3788,67 +3808,68 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['CWE 16', 'WASC Application Misconfiguration', 'OWASP 2021-A5', 'OWASP 2017-A6', 'OWASP 2013-A5', 'OWASP 2010-A6', 'OWASP 2023-API8', 'OWASP 2019-API7']</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr"/>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>['CVSSV4 BASE SCORE 2.3', 'CVSSV4 VECTOR CVSS:4.0/AV:N/AC:H/AT:N/PR:N/UI:P/VC:L/VI:N/VA:N/SC:N/SI:L/SA:N', 'CVSSV3 BASE SCORE 3.1', 'CVSSV3 VECTOR CVSS:3.0/AV:N/AC:H/PR:N/UI:R/S:U/C:L/I:N/A:N', 'CVSS BASE SCORE 2.6', 'CVSS VECTOR CVSS2#AV:N/AC:H/Au:N/C:P/I:N/A:N']</t>
+        </is>
+      </c>
+      <c r="L39" t="n">
+        <v>98081</v>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"publication_date": "2017-03-31T00:00:00+00:00",
+"modification_date": "2022-03-03T00:00:00+00:00",
+"family": "Authentication &amp; Session",
+"severity": "Low",
+"plugin_id": 98081}
+</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>['CWE 16', 'WASC Application Misconfiguration', 'OWASP 2021-A5, 2017-A6, 2013-A5, 2010-A6, 2023-API8, 2019-API7', 'CVE -', 'BID -']</t>
+          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/user_new.php', 'input_type': 'form', 'input_name': 'combined:post::https://juice-shop-388277804329.us-west1.run.app/user_new.php', 'payload': '', 'proof': '', 'output': 'The following form has been found to have not restricted \'password auto complete\' attribute : &lt;form action="/user_new.php" method="POST"&gt; &lt;input type="text" id="login" name="login"&gt; &lt;/input&gt; &lt;input type="text" id="email" name="email" size="30"&gt; &lt;/input&gt; &lt;input type="password" id="password" name="password"&gt; &lt;/input&gt; &lt;input type="password" id="password_conf" name="password_conf"&gt; &lt;/input&gt; &lt;input type="text" id="secret" name="secret" size="40"&gt; &lt;/input&gt; &lt;input type="checkbox" id="mail_activation" name="mail_activation" value=""&gt; &lt;/input&gt; &lt;button type="submit" name="action" value="create"&gt; Create &lt;/button&gt; &lt;/form&gt;', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="P39" t="n">
-        <v>98081</v>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>['The `autocomplete` value can be configured in two different locations.', 'The first and most secure location is to disable the `autocomplete` attribute on the `&lt;form&gt;` HTML tag. This will disable `autocomplete` for all inputs within that form. An example of disabling `autocomplete` within the form tag is `&lt;form autocomplete=off&gt;`.', 'The second slightly less desirable option is to disable the `autocomplete` attribute for a specific `&lt;input&gt;` HTML tag. While this may be the less desired solution from a security perspective, it may be preferred method for usability reasons, depending on size of the form. An example of disabling the `autocomplete` attribute within a password input tag is `&lt;input type=password autocomplete=off&gt;`.']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/user_new.php', 'input_type': 'form', 'input_name': 'combined:post::https://juice-shop-388277804329.us-west1.run.app/user_new.php', 'payload': None, 'proof': '&lt;form action="/user_new.php" method="POST"&gt;&lt;input type="text" id="login" name="login"&gt;&lt;/input&gt;&lt;input type="text" id="email" name="email" size="30"&gt;&lt;/input&gt;&lt;input type="password" id="password" name="password"&gt;&lt;/input&gt;&lt;input type="password" id="password_conf" name="password_conf"&gt;&lt;/input&gt;&lt;input type="text" id="secret" name="secret" size="40"&gt;&lt;/input&gt;&lt;input type="checkbox" id="mail_activation" name="mail_activation" value=""&gt;&lt;/input&gt;&lt;button type="submit" name="action" value="create"&gt;Create&lt;/button&gt;&lt;/form&gt;', 'output': "The following form has been found to have not restricted 'password auto complete' attribute.", 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/1.1', 'response_content_type': 'text/html'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -3860,12 +3881,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>['2.1', '3.1', '2.6']</t>
+          <t>['The HTTP headers sent by the remote web server disclose information that can aid an attacker, such as the server version and technologies used by the web server.']</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>['The HTTP headers sent by the remote web server disclose information that can aid an attacker, such as the server version and technologies used by the web server.']</t>
+          <t>['Modify the HTTP headers of the web server to not disclose detailed information about the underlying web server.']</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -3875,63 +3896,68 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['CWE 200', 'WASC Information Leakage', 'OWASP 2017-A6', 'OWASP 2021-A1', 'OWASP 2013-A5', 'OWASP 2010-A6', 'OWASP 2023-API8', 'OWASP 2019-API7']</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr"/>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>['CVSSV4 BASE SCORE 2.1', 'CVSSV4 VECTOR CVSS:4.0/AV:N/AC:H/AT:N/PR:N/UI:A/VC:L/VI:N/VA:N/SC:N/SI:N/SA:N', 'CVSSV3 BASE SCORE 3.1', 'CVSSV3 VECTOR CVSS:3.0/AV:N/AC:H/PR:N/UI:R/S:U/C:L/I:N/A:N', 'CVSS BASE SCORE 2.6', 'CVSS VECTOR CVSS2#AV:N/AC:H/Au:N/C:P/I:N/A:N']</t>
+        </is>
+      </c>
+      <c r="L40" t="n">
+        <v>98618</v>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"publication_date": "2019-06-12T00:00:00+00:00",
+"modification_date": "2024-03-25T00:00:00+00:00",
+"family": "HTTP Security Header",
+"severity": "Low",
+"plugin_id": 98618}
+</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>['CWE 200', 'WASC Information Leakage', 'OWASP 2017-A6, 2021-A1, 2013-A5, 2010-A6, 2023-API8, 2019-API7', 'CVE -', 'BID -']</t>
+          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/stylesheets/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The following header information disclosures have been detected on https://juice-shop-388277804329.us-west1.run.app /stylesheets/: - Server: Google Frontend', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/movie_search', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The following header information disclosures have been detected on https://juice-shop-388277804329.us-west1.run.app/apps /movie_search: - Server: Google Frontend', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/soap/class.nusoap_base.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The following header information disclosures have been detected on https://juice-shop-388277804329.us-west1.run.app/soap /class.nusoap_base.php: - X-Powered-By: PHP/5.5.9-1ubuntu4.14 - Server: Google Frontend', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/passwords/web.config.bak', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The following header information disclosures have been detected on https://juice-shop-388277804329.us-west1.run.app /passwords/web.config.bak: - Server: Google Frontend', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'application/x-trash'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/soap/class.soap_fault.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The following header information disclosures have been detected on https://juice-shop-388277804329.us-west1.run.app/soap /class.soap_fault.php: - X-Powered-By: PHP/5.5.9-1ubuntu4.14 - Server: Google Frontend', 'request_method': 'GET', 'http_status_code': 500, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/db/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The following header information disclosures have been detected on https://juice-shop-388277804329.us-west1.run.app/db/: - Server: Google Frontend', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/install.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The following header information disclosures have been detected on https://juice-shop-388277804329.us-west1.run.app /install.php: - X-Powered-By: PHP/5.5.9-1ubuntu4.14 - Server: Google Frontend', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/images/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The following header information disclosures have been detected on https://juice-shop-388277804329.us-west1.run.app /images/: - Server: Google Frontend', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/#/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The following header information disclosures have been detected on https://juice-shop-388277804329.us-west1.run.app/#/: - X-Powered-By: PHP/5.5.9-1ubuntu4.14 - Server: Google Frontend', 'request_method': 'GET', 'http_status_code': 302, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/info_install.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The following header information disclosures have been detected on https://juice-shop-388277804329.us-west1.run.app /info_install.php: - X-Powered-By: PHP/5.5.9-1ubuntu4.14 - Server: Google Frontend', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/phpinfo.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The following header information disclosures have been detected on https://juice-shop-388277804329.us-west1.run.app /phpinfo.php: - X-Powered-By: PHP/5.5.9-1ubuntu4.14 - Server: Google Frontend', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/portal.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The following header information disclosures have been detected on https://juice-shop-388277804329.us-west1.run.app /portal.php: - X-Powered-By: PHP/5.5.9-1ubuntu4.14 - Server: Google Frontend', 'request_method': 'GET', 'http_status_code': 302, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/documents/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The following header information disclosures have been detected on https://juice-shop-388277804329.us-west1.run.app /documents/: - Server: Google Frontend', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/soap/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The following header information disclosures have been detected on https://juice-shop-388277804329.us-west1.run.app /soap/: - Server: Google Frontend', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/soap/nusoap.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The following header information disclosures have been detected on https://juice-shop-388277804329.us-west1.run.app/soap /nusoap.php: - X-Powered-By: PHP/5.5.9-1ubuntu4.14 - Server: Google Frontend', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The following header information disclosures have been detected on https://juice-shop-388277804329.us-west1.run.app /apps/: - Server: Google Frontend', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/training_install.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The following header information disclosures have been detected on https://juice-shop-388277804329.us-west1.run.app /training_install.php: - X-Powered-By: PHP/5.5.9-1ubuntu4.14 - Server: Google Frontend', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The following header information disclosures have been detected on https://juice-shop-388277804329.us-west1.run.app/: - X-Powered-By: PHP/5.5.9-1ubuntu4.14 - Server: Google Frontend', 'request_method': 'GET', 'http_status_code': 302, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/soap/class.wsdlcache.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The following header information disclosures have been detected on https://juice-shop-388277804329.us-west1.run.app/soap /class.wsdlcache.php: - X-Powered-By: PHP/5.5.9-1ubuntu4.14 - Server: Google Frontend', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/passwords/heroes.xml', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The following header information disclosures have been detected on https://juice-shop-388277804329.us-west1.run.app /passwords/heroes.xml: - Server: Google Frontend', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/db/bwapp.sqlite', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The following header information disclosures have been detected on https://juice-shop-388277804329.us-west1.run.app/db /bwapp.sqlite: - Server: Google Frontend', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/js/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The following header information disclosures have been detected on https://juice-shop-388277804329.us-west1.run.app/js/: - Server: Google Frontend', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/passwords/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The following header information disclosures have been detected on https://juice-shop-388277804329.us-west1.run.app /passwords/: - Server: Google Frontend', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/login.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The following header information disclosures have been detected on https://juice-shop-388277804329.us-west1.run.app /login.php: - X-Powered-By: PHP/5.5.9-1ubuntu4.14 - Server: Google Frontend', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/passwords/wp-config.bak', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The following header information disclosures have been detected on https://juice-shop-388277804329.us-west1.run.app /passwords/wp-config.bak: - Server: Google Frontend', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'application/x-trash'}]</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="P40" t="n">
-        <v>98618</v>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>['Modify the HTTP headers of the web server to not disclose detailed information about the underlying web server.']</t>
-        </is>
-      </c>
-      <c r="R40" t="inlineStr"/>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -3943,12 +3969,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>['3.1', 'CVSS:3.0/AV:N/AC:H/PR:N/UI:R/S:U/C:L/I:N/A:N', '2.6', 'CVSS2#AV:N/AC:H/Au:N/C:P/I:N/A:N']</t>
+          <t>[""The HTTP 'X-Content-Type-Options' response header prevents the browser from MIME-sniffing a response away from the declared content-type."", ""The server did not return a correct 'X-Content-Type-Options' header, which means that this website could be at risk of a Cross-Site Scripting (XSS) attack.""]</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>[""The HTTP 'X-Content-Type-Options' response header prevents the browser from MIME-sniffing a response away from the declared content-type."", ""The server did not return a correct 'X-Content-Type-Options' header, which means that this website could be at risk of a Cross-Site Scripting (XSS) attack.""]</t>
+          <t>[""Configure your web server to include an 'X-Content-Type-Options' header with a value of 'nosniff'.""]</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -3958,63 +3984,68 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['CWE 693', 'WASC Application Misconfiguration', 'OWASP 2017-A6', 'OWASP 2013-A5', 'OWASP 2010-A6', 'OWASP 2023-API8', 'OWASP 2019-API7']</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr"/>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>['CVSSV3 BASE SCORE 3.1', 'CVSSV3 VECTOR CVSS:3.0/AV:N/AC:H/PR:N/UI:R/S:U/C:L/I:N/A:N', 'CVSS BASE SCORE 2.6', 'CVSS VECTOR CVSS2#AV:N/AC:H/Au:N/C:P/I:N/A:N']</t>
+        </is>
+      </c>
+      <c r="L41" t="n">
+        <v>112529</v>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"publication_date": "2018-11-28T00:00:00+00:00",
+"modification_date": "2024-03-25T00:00:00+00:00",
+"family": "HTTP Security Header",
+"severity": "Low",
+"plugin_id": 112529}
+</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>['CWE 693', 'WASC Application Misconfiguration', 'OWASP 2017-A6, 2013-A5, 2010-A6, 2023-API8, 2019-API7', 'CVE -', 'BID -']</t>
+          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/training_install.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner detected the lack of a correct X-Content-Type-Options header configuration in the target application response', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/images/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner detected the lack of a correct X-Content-Type-Options header configuration in the target application response', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/passwords/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner detected the lack of a correct X-Content-Type-Options header configuration in the target application response', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/info.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner detected the lack of a correct X-Content-Type-Options header configuration in the target application response', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/documents/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner detected the lack of a correct X-Content-Type-Options header configuration in the target application response', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/info_install.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner detected the lack of a correct X-Content-Type-Options header configuration in the target application response', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/login.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner detected the lack of a correct X-Content-Type-Options header configuration in the target application response', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/phpinfo.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner detected the lack of a correct X-Content-Type-Options header configuration in the target application response', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/movie_search', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner detected the lack of a correct X-Content-Type-Options header configuration in the target application response', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/soap/class.nusoap_base.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner detected the lack of a correct X-Content-Type-Options header configuration in the target application response', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/soap/class.wsdlcache.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner detected the lack of a correct X-Content-Type-Options header configuration in the target application response', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/stylesheets/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner detected the lack of a correct X-Content-Type-Options header configuration in the target application response', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/db/bwapp.sqlite', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner detected the lack of a correct X-Content-Type-Options header configuration in the target application response', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner detected the lack of a correct X-Content-Type-Options header configuration in the target application response', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/training.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner detected the lack of a correct X-Content-Type-Options header configuration in the target application response', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/soap/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner detected the lack of a correct X-Content-Type-Options header configuration in the target application response', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/soap/class.soap_fault.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner detected the lack of a correct X-Content-Type-Options header configuration in the target application response', 'request_method': 'GET', 'http_status_code': 500, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/passwords/wp-config.bak', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner detected the lack of a correct X-Content-Type-Options header configuration in the target application response', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'application/x-trash'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/soap/nusoap.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner detected the lack of a correct X-Content-Type-Options header configuration in the target application response', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/db/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner detected the lack of a correct X-Content-Type-Options header configuration in the target application response', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/install.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner detected the lack of a correct X-Content-Type-Options header configuration in the target application response', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/passwords/web.config.bak', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner detected the lack of a correct X-Content-Type-Options header configuration in the target application response', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'application/x-trash'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/user_new.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner detected the lack of a correct X-Content-Type-Options header configuration in the target application response', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/passwords/heroes.xml', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner detected the lack of a correct X-Content-Type-Options header configuration in the target application response', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/js/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner detected the lack of a correct X-Content-Type-Options header configuration in the target application response', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="P41" t="n">
-        <v>112529</v>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>[""Configure your web server to include an 'X-Content-Type-Options' header with a value of 'nosniff'.""]</t>
-        </is>
-      </c>
-      <c r="R41" t="inlineStr"/>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -4026,12 +4057,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>['2.3', '3.7', '2.6', 'CVSS:4.0/AV:N/AC:H/AT:N/PR:N/UI:P/VC:L/VI:N/VA:N/SC:N/SI:N/SA:N', 'CVSS:3.0/AV:N/AC:H/PR:N/UI:N/S:U/C:L/I:N/A:N', 'CVSS2#AV:N/AC:H/Au:N/C:P/I:N/A:N']</t>
+          <t>['The remote host supports the use of SSL/TLS ciphers that offer weak encryption (including RC4 and 3DES encryption).']</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>['The remote host supports the use of SSL/TLS ciphers that offer weak encryption (including RC4 and 3DES encryption).']</t>
+          <t>['Reconfigure the affected application, if possible to avoid the use of weak ciphers.']</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -4041,67 +4072,68 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['CWE 326', 'WASC Application Misconfiguration', 'OWASP 2010-A7', 'OWASP 2013-A6', 'OWASP 2017-A3', 'OWASP 2021-A2', 'OWASP 2023-API8', 'OWASP 2019-API7']</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr"/>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>['CVSSV4 BASE SCORE 2.3', 'CVSSV4 VECTOR CVSS:4.0/AV:N/AC:H/AT:N/PR:N/UI:P/VC:L/VI:N/VA:N/SC:N/SI:N/SA:N', 'CVSSV3 BASE SCORE 3.7', 'CVSSV3 VECTOR CVSS:3.0/AV:N/AC:H/PR:N/UI:N/S:U/C:L/I:N/A:N', 'CVSS BASE SCORE 2.6', 'CVSS VECTOR CVSS2#AV:N/AC:H/Au:N/C:P/I:N/A:N']</t>
+        </is>
+      </c>
+      <c r="L42" t="n">
+        <v>112539</v>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"publication_date": "2019-01-21T00:00:00+00:00",
+"modification_date": "2022-10-07T00:00:00+00:00",
+"family": "SSL/TLS",
+"severity": "Low",
+"plugin_id": 112539}
+</t>
+        </is>
+      </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>['CWE 326', 'WASC Application Misconfiguration', 'OWASP 2010-A7, 2013-A6, 2017-A3, 2021-A2, 2023-API8, 2019-API7', 'CVE -', 'BID -']</t>
+          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/#/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Protocol Cipher Suite Name (RFC) Key Exchange Strength ------------------------------------------------------------------------- TLS1.2 TLS_ECDHE_ECDSA_WITH_AES_128_CBC_SHA x25519 256 TLS1.2 TLS_ECDHE_ECDSA_WITH_AES_256_CBC_SHA x25519 256 TLS1.2 TLS_ECDHE_RSA_WITH_AES_128_CBC_SHA x25519 256 TLS1.2 TLS_ECDHE_RSA_WITH_AES_256_CBC_SHA x25519 256 TLS1.2 TLS_RSA_WITH_AES_128_GCM_SHA256 RSA 4096 TLS1.2 TLS_RSA_WITH_AES_256_GCM_SHA384 RSA 4096 TLS1.2 TLS_RSA_WITH_AES_128_CBC_SHA RSA 4096 TLS1.2 TLS_RSA_WITH_AES_256_CBC_SHA RSA 4096', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="P42" t="n">
-        <v>112539</v>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>['Reconfigure the affected application, if possible to avoid the use of weak ciphers.']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/#/', 'input_type': 'link', 'input_name': None, 'payload': None, 'proof': 'TLS1.2 TLS_ECDHE_ECDSA_WITH_AES_128_CBC_SHA x25519 256\nTLS1.2 TLS_ECDHE_ECDSA_WITH_AES_256_CBC_SHA x25519 256\nTLS1.2 TLS_ECDHE_RSA_WITH_AES_128_CBC_SHA x25519 256\nTLS1.2 TLS_ECDHE_RSA_WITH_AES_256_CBC_SHA x25519 256\nTLS1.2 TLS_RSA_WITH_AES_128_GCM_SHA256 RSA 4096\nTLS1.2 TLS_RSA_WITH_AES_256_GCM_SHA384 RSA 4096\nTLS1.2 TLS_RSA_WITH_AES_128_CBC_SHA RSA 4096\nTLS1.2 TLS_RSA_WITH_AES_256_CBC_SHA RSA 4096', 'output': 'The scanner detected supported TLS cipher suites including ECDHE with x25519 (256-bit) and RSA 4096-bit key exchange on https://juice-shop-388277804329.us-west1.run.app/#/', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -4113,12 +4145,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>['3.1', '2.6', 'CVSS:3.0/AV:N/AC:H/PR:N/UI:R/S:U/C:L/I:N/A:N', 'CVSS2#AV:N/AC:H/Au:N/C:P/I:N/A:N']</t>
+          <t>['Content Security Policy (CSP) is a web security standard that helps to mitigate attacks like cross-site scripting (XSS), clickjacking or mixed content issues. CSP provides mechanisms to websites to restrict content that browsers will be allowed to load. No CSP header has been detected on this host. This URL is flagged as a specific example.']</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>['Content Security Policy (CSP) is a web security standard that helps to mitigate attacks like cross-site scripting (XSS), clickjacking or mixed content issues. CSP provides mechanisms to websites to restrict content that browsers will be allowed to load. No CSP header has been detected on this host. This URL is flagged as a specific example.']</t>
+          <t>[""Configure Content Security Policy on your website by adding 'Content-Security-Policy' HTTP header or meta tag http-equiv='Content-Security-Policy'.""]</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -4128,63 +4160,68 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['CWE 1021', 'WASC Application Misconfiguration', 'OWASP 2017-A6', 'OWASP 2021-A4', 'OWASP 2013-A5', 'OWASP 2010-A6', 'OWASP 2023-API8', 'OWASP 2019-API7']</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr"/>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>['CVSSV3 BASE SCORE 3.1', 'CVSSV3 VECTOR CVSS:3.0/AV:N/AC:H/PR:N/UI:R/S:U/C:L/I:N/A:N', 'CVSS BASE SCORE 2.6', 'CVSS VECTOR CVSS2#AV:N/AC:H/Au:N/C:P/I:N/A:N']</t>
+        </is>
+      </c>
+      <c r="L43" t="n">
+        <v>112551</v>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"publication_date": "2019-02-14T00:00:00+00:00",
+"modification_date": "2024-03-25T00:00:00+00:00",
+"family": "HTTP Security Header",
+"severity": "Low",
+"plugin_id": 112551}
+</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>['CWE 1021', 'WASC Application Misconfiguration', 'OWASP 2017-A6, 2021-A4, 2013-A5, 2010-A6, 2023-API8, 2019-API7', 'CVE -', 'BID -']</t>
+          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/info.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-388277804329.us-west1.run.app/info.php has no Content Security Policy defined.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/passwords/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-388277804329.us-west1.run.app/passwords/ has no Content Security Policy defined.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/phpinfo.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-388277804329.us-west1.run.app/phpinfo.php has no Content Security Policy defined.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/stylesheets/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-388277804329.us-west1.run.app/stylesheets/ has no Content Security Policy defined.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/db/bwapp.sqlite', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-388277804329.us-west1.run.app/db/bwapp.sqlite has no Content Security Policy defined.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/images/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-388277804329.us-west1.run.app/images/ has no Content Security Policy defined.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/soap/class.nusoap_base.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-388277804329.us-west1.run.app/soap/class.nusoap_base.php has no Content Security Policy defined.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/soap/class.soap_fault.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-388277804329.us-west1.run.app/soap/class.soap_fault.php has no Content Security Policy defined.', 'request_method': 'GET', 'http_status_code': 500, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-388277804329.us-west1.run.app/apps/ has no Content Security Policy defined.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/user_new.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-388277804329.us-west1.run.app/user_new.php has no Content Security Policy defined.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/install.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-388277804329.us-west1.run.app/install.php has no Content Security Policy defined.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/documents/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-388277804329.us-west1.run.app/documents/ has no Content Security Policy defined.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/login.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-388277804329.us-west1.run.app/login.php has no Content Security Policy defined.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/soap/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-388277804329.us-west1.run.app/soap/ has no Content Security Policy defined.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/soap/nusoap.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-388277804329.us-west1.run.app/soap/nusoap.php has no Content Security Policy defined.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/js/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-388277804329.us-west1.run.app/js/ has no Content Security Policy defined.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/movie_search', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-388277804329.us-west1.run.app/apps/movie_search has no Content Security Policy defined.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/db/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-388277804329.us-west1.run.app/db/ has no Content Security Policy defined.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/soap/class.wsdlcache.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-388277804329.us-west1.run.app/soap/class.wsdlcache.php has no Content Security Policy defined.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/training.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-388277804329.us-west1.run.app/training.php has no Content Security Policy defined.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/info_install.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-388277804329.us-west1.run.app/info_install.php has no Content Security Policy defined.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/training_install.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-388277804329.us-west1.run.app/training_install.php has no Content Security Policy defined.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="P43" t="n">
-        <v>112551</v>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>[""Configure Content Security Policy on your website by adding 'Content-Security-Policy' HTTP header or meta tag http-equiv='Content-Security-Policy'.""]</t>
-        </is>
-      </c>
-      <c r="R43" t="inlineStr"/>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -4196,12 +4233,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>['2.1', '3.7', '2.6', 'CVSS:4.0/AV:N/AC:H/AT:N/PR:N/UI:A/VC:L/VI:N/VA:N/SC:N/SI:N/SA:N', 'CVSS:3.0/AV:N/AC:H/PR:N/UI:N/S:U/C:L/I:N/A:N', 'CVSS2#AV:N/AC:H/Au:N/C:P/I:N/A:N']</t>
+          <t>[""The HTTP 'Cache-Control' header is used to specify directives for caching mechanisms."", ""The server did not return or returned an invalid 'Cache-Control' header which means page containing sensitive information (password, credit card, personal data, social security number, etc) could be stored on client side disk and then be exposed to unauthorised persons. This URL is flagged as a specific example.""]</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>[""The HTTP 'Cache-Control' header is used to specify directives for caching mechanisms."", ""The server did not return or returned an invalid 'Cache-Control' header which means page containing sensitive information (password, credit card, personal data, social security number, etc) could be stored on client side disk and then be exposed to unauthorised persons. This URL is flagged as a specific example.""]</t>
+          <t>[""Configure your web server to include a 'Cache-Control' header with appropriate directives. If page contains sensitive information 'Cache-Control' value should be 'no-store' and 'Pragma' header value should be 'no-cache'.""]</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -4211,63 +4248,68 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['CWE 525', 'WASC Application Misconfiguration', 'OWASP 2017-A6', 'OWASP 2021-A4', 'OWASP 2013-A5', 'OWASP 2010-A6', 'OWASP 2023-API8', 'OWASP 2019-API7']</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr"/>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>['CVSSV4 BASE SCORE 2.1', 'CVSSV4 VECTOR CVSS:4.0/AV:N/AC:H/AT:N/PR:N/UI:A/VC:L/VI:N/VA:N/SC:N/SI:N/SA:N', 'CVSSV3 BASE SCORE 3.7', 'CVSSV3 VECTOR CVSS:3.0/AV:N/AC:H/PR:N/UI:N/S:U/C:L/I:N/A:N', 'CVSS BASE SCORE 2.6', 'CVSS VECTOR CVSS2#AV:N/AC:H/Au:N/C:P/I:N/A:N']</t>
+        </is>
+      </c>
+      <c r="L44" t="n">
+        <v>112553</v>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"publication_date": "2019-02-15T00:00:00+00:00",
+"modification_date": "2024-03-25T00:00:00+00:00",
+"family": "HTTP Security Header",
+"severity": "Low",
+"plugin_id": 112553}
+</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>['CWE 525', 'WASC Application Misconfiguration', 'OWASP 2017-A6, 2021-A4, 2013-A5, 2010-A6, 2023-API8, 2019-API7', 'CVE -', 'BID -']</t>
+          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-388277804329.us-west1.run.app/apps/ has no Cache Control header defined.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/passwords/heroes.xml', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-388277804329.us-west1.run.app/passwords/heroes.xml has no Cache Control header defined.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/login.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-388277804329.us-west1.run.app/login.php has invalid directive found : - post-check=0 https://juice-shop-388277804329.us-west1.run.app/login.php has invalid directive found : - pre-check=0', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/soap/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-388277804329.us-west1.run.app/soap/ has no Cache Control header defined.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/passwords/web.config.bak', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-388277804329.us-west1.run.app/passwords/web.config.bak has no Cache Control header defined.', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'application/x-trash'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/db/bwapp.sqlite', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-388277804329.us-west1.run.app/db/bwapp.sqlite has no Cache Control header defined.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/soap/nusoap.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-388277804329.us-west1.run.app/soap/nusoap.php has no Cache Control header defined.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/documents/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-388277804329.us-west1.run.app/documents/ has no Cache Control header defined.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/install.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-388277804329.us-west1.run.app/install.php has no Cache Control header defined.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/soap/class.nusoap_base.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-388277804329.us-west1.run.app/soap/class.nusoap_base.php has no Cache Control header defined.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/images/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-388277804329.us-west1.run.app/images/ has no Cache Control header defined.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/passwords/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-388277804329.us-west1.run.app/passwords/ has no Cache Control header defined.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/info.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-388277804329.us-west1.run.app/info.php has no Cache Control header defined.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/training_install.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-388277804329.us-west1.run.app/training_install.php has no Cache Control header defined.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/phpinfo.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-388277804329.us-west1.run.app/phpinfo.php has no Cache Control header defined.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/user_new.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-388277804329.us-west1.run.app/user_new.php has no Cache Control header defined.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/movie_search', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-388277804329.us-west1.run.app/apps/movie_search has no Cache Control header defined.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/js/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-388277804329.us-west1.run.app/js/ has no Cache Control header defined.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/soap/class.soap_fault.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-388277804329.us-west1.run.app/soap/class.soap_fault.php has no Cache Control header defined.', 'request_method': 'GET', 'http_status_code': 500, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/stylesheets/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-388277804329.us-west1.run.app/stylesheets/ has no Cache Control header defined.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/db/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-388277804329.us-west1.run.app/db/ has no Cache Control header defined.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/info_install.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-388277804329.us-west1.run.app/info_install.php has no Cache Control header defined.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/passwords/wp-config.bak', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-388277804329.us-west1.run.app/passwords/wp-config.bak has no Cache Control header defined.', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'application/x-trash'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/training.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-388277804329.us-west1.run.app/training.php has no Cache Control header defined.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/soap/class.wsdlcache.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-388277804329.us-west1.run.app/soap/class.wsdlcache.php has no Cache Control header defined.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="P44" t="n">
-        <v>112553</v>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>[""Configure your web server to include a 'Cache-Control' header with appropriate directives. If page contains sensitive information 'Cache-Control' value should be 'no-store' and 'Pragma' header value should be 'no-cache'.""]</t>
-        </is>
-      </c>
-      <c r="R44" t="inlineStr"/>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -4279,12 +4321,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>['2.1', 'CVSS:4.0/AV:N/AC:H/AT:N/PR:N/UI:A/VC:N/VI:L/VA:N/SC:N/SI:N/SA:N', '3.1', 'CVSS:3.0/AV:N/AC:H/PR:N/UI:R/S:U/C:N/I:L/A:N', '2.6', 'CVSS2#AV:N/AC:H/Au:N/C:N/I:P/A:N']</t>
+          <t>[""Cross Site Request Forgery (CSRF) occurs when an user is tricked into clicking on a link which would automatically submit a request without the user's consent."", 'This can be made possible when the request does not include an anti-CSRF token, generated each time the request is visited and passed when the request is submitted, and which can be used by the web application backend to verify that the request originates from a legitimate user.', 'Exploiting requests vulnerable to Cross-Site Request Forgery requires different factors:', '- The request must perform a sensitive action.', '- The attacker must make the victim click on a link to send the request without their consent.', 'The exploitation of this vulnerability will in most cases have a very limited impact. However, it is possible to create complex scenarios in case the application is also vulnerable to Cross-Site Scripting.']</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>[""Cross Site Request Forgery (CSRF) occurs when an user is tricked into clicking on a link which would automatically submit a request without the user's consent."", 'This can be made possible when the request does not include an anti-CSRF token, generated each time the request is visited and passed when the request is submitted, and which can be used by the web application backend to verify that the request originates from a legitimate user.', 'Exploiting requests vulnerable to Cross-Site Request Forgery requires different factors:', '- The request must perform a sensitive action.', '- The attacker must make the victim click on a link to send the request without their consent.', 'The exploitation of this vulnerability will in most cases have a very limited impact. However, it is possible to create complex scenarios in case the application is also vulnerable to Cross-Site Scripting.']</t>
+          <t>['Update the application by adding support of anti-CSRF tokens on this login form.', 'Most web frameworks provide either built-in solutions or have plugins that can be used to easily add these tokens to any form.', 'Check the references for possible solutions provided for the most known frameworks.']</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -4294,67 +4336,68 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['CWE 352', 'WASC Cross-Site Request Forgery', 'OWASP 2013-A8', 'OWASP 2010-A5', 'OWASP 2021-A1', 'OWASP 2023-API8', 'OWASP 2019-API7']</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr"/>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>['CVSSV4 BASE SCORE 2.1', 'CVSSV4 VECTOR CVSS:4.0/AV:N/AC:H/AT:N/PR:N/UI:A/VC:N/VI:L/VA:N/SC:N/SI:N/SA:N', 'CVSSV3 BASE SCORE 3.1', 'CVSSV3 VECTOR CVSS:3.0/AV:N/AC:H/PR:N/UI:R/S:U/C:N/I:L/A:N', 'CVSS BASE SCORE 2.6', 'CVSS VECTOR CVSS2#AV:N/AC:H/Au:N/C:N/I:P/A:N']</t>
+        </is>
+      </c>
+      <c r="L45" t="n">
+        <v>113332</v>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"publication_date": "2022-08-08T00:00:00+00:00",
+"modification_date": "2023-01-17T00:00:00+00:00",
+"family": "Cross Site Request Forgery",
+"severity": "Low",
+"plugin_id": 113332}
+</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>['CWE 352', 'WASC Cross-Site Request Forgery', 'OWASP 2013-A8, 2010-A5, 2021-A1, 2023-API8, 2019-API7', 'CVE -', 'BID -']</t>
+          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/login.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '&lt;form action="/login.php" method="POST"&gt; &lt;input type="text" id="login" name="login" size="20" autocomplete="off"&gt; &lt;/input&gt; &lt;input type="password" id="password" name="password" size="20" autocomplete="off"&gt; &lt;/input&gt; &lt;select name="security_level"&gt; &lt;option value="0"&gt; low &lt;/option&gt; &lt;option value="1"&gt; medium &lt;/option&gt; &lt;option value="2"&gt; high &lt;/option&gt; &lt;/select&gt; &lt;button type="submit" name="form" value="submit"&gt; Login &lt;/button&gt; &lt;/form&gt;', 'output': 'No anti-CSRF token could have been found in the login form attached in proof. By requesting it several times, the scanner could not find any dynamic input field that would generate a token used by the application to confirm the user intention to submit this form.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="P45" t="n">
-        <v>113332</v>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>['Update the application by adding support of anti-CSRF tokens on this login form.', 'Most web frameworks provide either built-in solutions or have plugins that can be used to easily add these tokens to any form.', 'Check the references for possible solutions provided for the most known frameworks.']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/login.php', 'input_type': 'form', 'input_name': 'login', 'payload': None, 'proof': 'No anti-CSRF token found in login form', 'output': 'Form vulnerable to CSRF: no dynamic token detected', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/1.1', 'response_content_type': 'text/html', 'server': 'Google Frontend', 'x_powered_by': 'PHP/5.5.9-1ubuntu4.14'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -4366,12 +4409,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>['2.1', 'CVSS:4.0/AV:N/AC:H/AT:N/PR:N/UI:A/VC:L/VI:N/VA:N/SC:N/SI:N/SA:N', '3.1', 'CVSS:3.0/AV:N/AC:H/PR:N/UI:R/S:U/C:L/I:N/A:N', '2.6', 'CVSS2#AV:N/AC:H/Au:N/C:P/I:N/A:N']</t>
+          <t>['SameSite is an attribute which can be set on a cookie to instruct the web browser if this cookie can be sent along with cross-site requests to help prevent Cross-Site Request Forgery (CSRF) attacks.', 'The attribute has three possible values :', '- Strict : the cookie will only be sent in a first-party context, thus preventing cross-site requests initiated from third-party websites to include it.', '- Lax : the cookie is allowed to be sent in GET cross-site requests initiated by the top-level navigation from third-party websites. For example, following an hypertext link from the external website will make the request include the cookie.', '- None : the cookie is explicitly set to be sent by the browser in any context.', 'The scanner identified the lack of SameSite attribute on cookies set by the application or a misconfiguration.']</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>['SameSite is an attribute which can be set on a cookie to instruct the web browser if this cookie can be sent along with cross-site requests to help prevent Cross-Site Request Forgery (CSRF) attacks.', 'The attribute has three possible values :', '- Strict : the cookie will only be sent in a first-party context, thus preventing cross-site requests initiated from third-party websites to include it.', '- Lax : the cookie is allowed to be sent in GET cross-site requests initiated by the top-level navigation from third-party websites. For example, following an hypertext link from the external website will make the request include the cookie.', '- None : the cookie is explicitly set to be sent by the browser in any context.', 'The scanner identified the lack of SameSite attribute on cookies set by the application or a misconfiguration.']</t>
+          <t>[""Web browsers default behavior may differ when processing cookies in a cross-site context, making the final decision to send the cookie in this context unpredictable. The SameSite attribute should be set in every cookie to enforce the expected result by developers. When using the 'None' attribute value, ensure that the cookie is also set with the 'Secure' flag.""]</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -4381,67 +4424,68 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['CWE 352', 'WASC Cross-Site Request Forgery', 'OWASP 2013-A8', 'OWASP 2010-A5', 'OWASP 2021-A1', 'OWASP 2023-API8', 'OWASP 2019-API7']</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr"/>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>['CVSSV4 BASE SCORE 2.1', 'CVSSV4 VECTOR CVSS:4.0/AV:N/AC:H/AT:N/PR:N/UI:A/VC:L/VI:N/VA:N/SC:N/SI:N/SA:N', 'CVSSV3 BASE SCORE 3.1', 'CVSSV3 VECTOR CVSS:3.0/AV:N/AC:H/PR:N/UI:R/S:U/C:L/I:N/A:N', 'CVSS BASE SCORE 2.6', 'CVSS VECTOR CVSS2#AV:N/AC:H/Au:N/C:P/I:N/A:N']</t>
+        </is>
+      </c>
+      <c r="L46" t="n">
+        <v>115540</v>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"publication_date": "2018-12-14T00:00:00+00:00",
+"modification_date": "2023-12-11T00:00:00+00:00",
+"family": "HTTP Security Header",
+"severity": "Low",
+"plugin_id": 115540}
+</t>
+        </is>
+      </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>['CWE 352', 'WASC Cross-Site Request Forgery', 'OWASP 2013-A8, 2010-A5, 2021-A1, 2023-API8, 2019-API7', 'CVE -', 'BID -']</t>
+          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/', 'input_type': 'cookie', 'input_name': 'PHPSESSID', 'payload': '', 'proof': 'PHPSESSID=711vt1tpgrucudl1kaq9t074f5; Path=/', 'output': "The scanner detected a cookie named 'PHPSESSID' set with JavaScript which does not have the 'SameSite' attribute set.", 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="P46" t="n">
-        <v>115540</v>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>[""Web browsers default behavior may differ when processing cookies in a cross-site context, making the final decision to send the cookie in this context unpredictable. The SameSite attribute should be set in every cookie to enforce the expected result by developers. When using the 'None' attribute value, ensure that the cookie is also set with the 'Secure' flag.""]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/', 'input_type': 'cookie', 'input_name': 'PHPSESSID', 'payload': None, 'proof': 'PHPSESSID=711vt1tpgrucudl1kaq9t074f5; Path=/', 'output': "Cookie 'PHPSESSID' set without SameSite attribute", 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/1.1', 'response_content_type': 'text/html'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -4453,12 +4497,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Provides scan information and statistics of plugins run.']</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>['Provides scan information and statistics of plugins run.']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -4466,55 +4510,52 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr"/>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L47" t="n">
+        <v>98000</v>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"publication_date": "2017-03-31T00:00:00+00:00",
+"modification_date": "2023-11-17T00:00:00+00:00",
+"family": "General",
+"severity": "Info",
+"plugin_id": 98000}
+</t>
+        </is>
+      </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/#/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': "Engine Version 2.26.10-1603 Plugins Version 202411140727 Scan ID 45c6aad7-0097-4f4e-a4bc-4623af2d119b Start Time 2024-11-19 00:10:32 +0000 Duration 09:35:35 Requests 706972 Crawler Requests 92 Requests/s 24.7968 Mean Response Time 0.1317s Bandwidth Usage - Data to Target 274 MB - Data from Target 2.24 GB Timeouts Encountered Network Timeouts 7 Browser Timeouts 0 Browser Respawns 0 HTTP Protocols Detected - HTTPs Authentication Identified - None Plugins - 729 have been included per scan policy - 792 have been started based on target information collected List of plugins is available in 'plugins.csv' attachment. Settings used to conduct this scan are available in 'configuration.csv' attachment.", 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="P47" t="n">
-        <v>98000</v>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
@@ -4523,12 +4564,12 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/#/', 'input_type': 'scan_metadata', 'input_name': None, 'payload': None, 'proof': 'Engine Version 2.26.10-1603; Plugins Version 202411140727; Scan ID 45c6aad7-0097-4f4e-a4bc-4623af2d119b', 'output': 'Scan completed with 706972 requests, duration 09:35:35, mean response time 0.1317s, bandwidth usage 274 MB to target / 2.24 GB from target. No authentication identified.', 'request_method': None, 'http_status_code': None, 'http_protocol': 'HTTPS', 'response_content_type': None, 'scan_start_time': '2024-11-19 00:10:32 +0000', 'scan_duration': '09:35:35', 'requests_total': 706972, 'crawler_requests': 92, 'requests_per_second': 24.7968, 'mean_response_time': '0.1317s', 'bandwidth_to_target': '274 MB', 'bandwidth_from_target': '2.24 GB', 'timeouts_network': 7, 'timeouts_browser': 0, 'timeouts_respawns': 0, 'protocols_detected': ['HTTPS'], 'authentication': 'None', 'plugins_included': 729, 'plugins_started': 792, 'attachments': ['plugins.csv', 'configuration.csv']}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -4539,11 +4580,6 @@
         </is>
       </c>
       <c r="B48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
         <is>
           <t>['Publishes the sitemap of the web application as seen by the scan.
 The list of all URLs that have been detected during the scan are available as an attachment. For each URL in the sitemap, the
@@ -4567,60 +4603,62 @@
 user_abort: The user stopped the scan before the URL could be audited']</t>
         </is>
       </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="D48" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr"/>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L48" t="n">
+        <v>98009</v>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"publication_date": "2017-03-31T00:00:00+00:00",
+"modification_date": "2023-11-17T00:00:00+00:00",
+"family": "General",
+"severity": "Info",
+"plugin_id": 98009}
+</t>
+        </is>
+      </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/#/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scan has discovered 173 distinct URLs. The following is a breakdown of which URLs were audited: - 69 effectively audited - 8 not audited due to the page was too similar to another page already audited - 42 not queued due to file extension exclusions - 29 not queued due to the URL not being in the target domain - 24 not queued due to the URL being considered redundant with other processed URLs - 1 not queued due to the URL containing a fragment which is a feature of browsers and not included in HTTP requests. The page being referred to by the fragment shall still be audited by the scanner. For URLs we received responses for, here is a distribution of the content type headers: - 1 application/javascript - 2 application/x-trash - 1 application/xml - 7 image/gif - 4 image/jpeg - 11 image/png - 1 text/css - 26 text/html - 48 text/html;charset=utf-8 Response times ranged between 0.020808s and 0.281579s. You can access the complete list of URLs with the information collected by the scan as an attachment to this plugin.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="P48" t="n">
-        <v>98009</v>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
@@ -4629,12 +4667,12 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/#/', 'input_type': 'scan_urls', 'input_name': None, 'payload': None, 'proof': 'Scan discovered 173 distinct URLs', 'output': '69 audited, 8 skipped (similar pages), 42 excluded (file extension), 29 excluded (outside domain), 24 excluded (redundant), 1 excluded (fragment only). Content types: 1 application/javascript, 2 application/x-trash, 1 application/xml, 7 image/gif, 4 image/jpeg, 11 image/png, 1 text/css, 26 text/html, 48 text/html;charset=utf-8. Response times ranged between 0.020808s and 0.281579s.', 'request_method': None, 'http_status_code': None, 'http_protocol': 'HTTPS', 'response_content_type': None}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -4646,12 +4684,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Provides a report of network timeouts encountered during the scan, showing URLs and the number of timeouts for each URL.', 'Note that assessment will stop on any URLs in timeout state, and timeouts may increase significantly the overall duration of the scan.']</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>['Provides a report of network timeouts encountered during the scan, showing URLs and the number of timeouts for each URL.', 'Note that assessment will stop on any URLs in timeout state, and timeouts may increase significantly the overall duration of the scan.']</t>
+          <t>['Check your web application logs and verify that it is functioning as expected and can handle significant amounts of traffic generated by the scanner.', 'Additionally, the scan policy may be edited to optimize the performance settings.']</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -4659,69 +4697,66 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr"/>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L49" t="n">
+        <v>98019</v>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"publication_date": "2017-09-25T00:00:00+00:00",
+"modification_date": "2023-11-17T00:00:00+00:00",
+"family": "General",
+"severity": "Info",
+"plugin_id": 98019}
+</t>
+        </is>
+      </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/#/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner encountered 7 network timeouts during the scan. See the attachment for more details', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="P49" t="n">
-        <v>98019</v>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>['Check your web application logs and verify that it is functioning as expected and can handle significant amounts of traffic generated by the scanner.', 'Additionally, the scan policy may be edited to optimize the performance settings.']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/#/', 'input_type': 'scan_timeouts', 'input_name': None, 'payload': None, 'proof': 'The scanner encountered 7 network timeouts during the scan', 'output': 'Scan reported 7 network timeouts. See attachment for details.', 'request_method': None, 'http_status_code': None, 'http_protocol': 'HTTPS', 'response_content_type': None}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -4733,12 +4768,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['This is an informational notice that the scanner identified a potential login form that could be used by the scanner to authenticate and have access to additional pages for extending its coverage.']</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>['This is an informational notice that the scanner identified a potential login form that could be used by the scanner to authenticate and have access to additional pages for extending its coverage.']</t>
+          <t>['Edit scan policy and add login form authentication credentials to allow scanner to authenticate to the web application.']</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -4746,69 +4781,66 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr"/>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L50" t="n">
+        <v>98033</v>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"publication_date": "2018-02-08T00:00:00+00:00",
+"modification_date": "2018-02-08T00:00:00+00:00",
+"family": "Authentication &amp; Session",
+"severity": "Info",
+"plugin_id": 98033}
+</t>
+        </is>
+      </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/login.php', 'input_type': 'form', 'input_name': 'combined:post::https://juice-shop-388277804329.us-west1.run.app/login.php', 'payload': '', 'proof': '', 'output': "Potential login form has been identified in URL 'https://juice-shop-388277804329.us-west1.run.app/login.php' with following fields: - login (TEXT) - password (PASSWORD) - No name or id (SELECT) - form (SUBMIT) To perform authenticated scan, configure your scan and add 'Login Form' authentication, with the URL associated to this plugin and as login parameters values for the above non-hidden fields.", 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="P50" t="n">
-        <v>98033</v>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>['Edit scan policy and add login form authentication credentials to allow scanner to authenticate to the web application.']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/login.php', 'input_type': 'form', 'input_name': 'combined:post::https://juice-shop-388277804329.us-west1.run.app/login.php', 'payload': None, 'proof': 'Potential login form identified with fields: login (TEXT), password (PASSWORD), no name/id (SELECT), form (SUBMIT)', 'output': "Login form detected. To perform authenticated scan, configure 'Login Form' authentication with these parameters.", 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/1.1', 'response_content_type': 'text/html'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -4820,12 +4852,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['There are a number of HTTP methods that can be used on a webserver (`OPTIONS`, `HEAD`, `GET`, `POST`, `PUT`, `DELETE` etc.). Each of these methods perform a different function and each have an associated level of risk when their use is permitted on the webserver. By sending an HTTP OPTIONS request and a direct HTTP request for each method, the scanner discovered the methods that are allowed by the server.']</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>['There are a number of HTTP methods that can be used on a webserver (`OPTIONS`, `HEAD`, `GET`, `POST`, `PUT`, `DELETE` etc.). Each of these methods perform a different function and each have an associated level of risk when their use is permitted on the webserver. By sending an HTTP OPTIONS request and a direct HTTP request for each method, the scanner discovered the methods that are allowed by the server.']</t>
+          <t>['It is recommended that a whitelisting approach be taken to explicitly permit only the HTTP methods required by the application and block all others.']</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -4833,69 +4865,66 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr"/>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L51" t="n">
+        <v>98047</v>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"publication_date": "2017-03-31T00:00:00+00:00",
+"modification_date": "2024-02-27T00:00:00+00:00",
+"family": "Web Applications",
+"severity": "Info",
+"plugin_id": 98047}
+</t>
+        </is>
+      </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>['http://httpd.apache.org/docs/2.2/mod/core.html#limitexcept']</t>
+          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/#/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner was able to identify several HTTP methods that can be used for one or several URLs. The results are available as attachments.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="P51" t="n">
-        <v>98047</v>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>['It is recommended that a whitelisting approach be taken to explicitly permit only the HTTP methods required by the application and block all others.']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/#/', 'input_type': 'http_methods', 'input_name': None, 'payload': None, 'proof': 'The scanner was able to identify several HTTP methods usable for one or more URLs', 'output': 'HTTP methods discovered. Full details are available in attachments.', 'request_method': None, 'http_status_code': None, 'http_protocol': 'HTTPS', 'response_content_type': None}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -4907,12 +4936,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[""A response has been received with a response code '403' which may require further investigation to verify if this response is due to an abnormal behavior of the target."", ""A response has been received with a response code '406' which may require further investigation to verify if this response is due to an abnormal behavior of the target."", ""A response has been received with a response code '405' which may require further investigation to verify if this response is due to an abnormal behavior of the target."", ""A response has been received with a response code '502' which may require further investigation to verify if this response is due to an abnormal behavior of the target.""]</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>[""A response has been received with a response code '403' which may require further investigation to verify if this response is due to an abnormal behavior of the target."", ""A response has been received with a response code '406' which may require further investigation to verify if this response is due to an abnormal behavior of the target."", ""A response has been received with a response code '405' which may require further investigation to verify if this response is due to an abnormal behavior of the target."", ""A response has been received with a response code '502' which may require further investigation to verify if this response is due to an abnormal behavior of the target.""]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -4920,65 +4949,66 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
-          <t>['PROOF', 'HTTP/2 403', 'OUTPUT', ""A response has been received with a response code '403' which may require further investigation to verify if this response is due to an abnormal behavior of the target. The response has been triggered by an HTTP GET request made on the URL 'https://juice-shop-388277804329.us-west1.run.app/passwords/.htaccess'."", 'REQUEST MADE', 'GET /passwords/.htaccess HTTP/2', 'REQUEST HEADERS', 'Host: juice-shop-388277804329.us-west1.run.app', 'Accept-Encoding: gzip, deflate, br', 'User-Agent: Mozilla/5.0 (X11; Linux x86_64) AppleWebKit/537.36 (KHTML, like Gecko) Chrome/124.0.6367.207 Safari/537.36', 'Accept: */*', 'Accept-Language: en-US,en;q=0.5', 'Cookie: PHPSESSID=711vt1tpgrucudl1kaq9t074f5', 'RESPONSE HEADERS', 'content-type: text/html; charset=iso-8859-1', 'x-cloud-trace-context: 97fa1398a1575190b59c247660f91cf8', 'date: Tue, 19 Nov 2024 01:23:11 GMT', 'server: Google Frontend', 'content-length: 326', 'alt-svc: h3="":443""; ma=2592000,h3-29="":443""; ma=2592000', ""A response has been received with a response code '403' which may require further investigation to verify if this response is due to an abnormal behavior of the target. The response has been triggered by an HTTP GET request made on the URL 'https://juice-shop-388277804329.us-west1.run.app/js/.htaccess'."", 'GET /js/.htaccess HTTP/2', 'x-cloud-trace-context: db7087aec6c9bf70fa45ff01dea3de87', 'date: Tue, 19 Nov 2024 01:14:09 GMT', 'content-length: 319', 'HTTP/2 400', ""A response has been received with a response code '400' which may require further investigation to verify if this response is due to an abnormal behavior of the target. The response has been triggered by an HTTP GET request made on the URL 'https://juice-shop-388277804329.us-west1.run.app/apps/setup/setup-s/%u002e%u002e/%u002e%u002e/log.jsp'."", 'GET /apps/setup/setup-s/%u002e%u002e/%u002e%u002e/log.jsp HTTP/2', 'x-cloud-trace-context: faa05836554e60e828b617206200884c', 'date: Tue, 19 Nov 2024 00:30:20 GMT', 'content-length: 331', 'HTTP/2 405', ""A response has been received with a response code '405' which may require further investigation to verify if this response is due to an abnormal behavior of the target. The response has been triggered by an HTTP TRACE request made on the URL 'https://juice-shop-388277804329.us-west1.run.app/#/'."", 'TRACE / HTTP/2', 'Accept-Language: en-US,en']</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>['https://juice-shop-388277804329.us-west1.run.app/passwords/.htaccess', 'https://juice-shop-388277804329.us-west1.run.app/js/.htaccess', 'https%3A%2F%2Fjuice-shop-388277804329.us-west1.run.app%2Fapps%2Fsetup%2Fsetup-s%2F%25u002e%25u002e%2F%25u002e%25u002e%2Flog.jsp', 'https://juice-shop-388277804329.us-west1.run.app/#/']</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr"/>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L52" t="n">
+        <v>98050</v>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"publication_date": "2017-03-31T00:00:00+00:00",
+"modification_date": "2021-06-14T00:00:00+00:00",
+"family": "Web Applications",
+"severity": "Info",
+"plugin_id": 98050}
+</t>
+        </is>
+      </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/passwords/.htaccess', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'HTTP/2 403', 'output': "A response has been received with a response code '403' which may require further investigation to verify if this response is due to an abnormal behavior of the target. The response has been triggered by an HTTP GET request made on the URL 'https://juice-shop-388277804329.us-west1.run.app /passwords/.htaccess'.", 'request_method': 'GET', 'http_status_code': 403, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/js/.htaccess', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'HTTP/2 403', 'output': "A response has been received with a response code '403' which may require further investigation to verify if this response is due to an abnormal behavior of the target. The response has been triggered by an HTTP GET request made on the URL 'https://juice-shop-388277804329.us-west1.run.app /js/.htaccess'.", 'request_method': 'GET', 'http_status_code': 403, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https%3A%2F%2Fjuice-shop-388277804329.us-west1.run.app%2Fapps%2Fsetup%2Fsetup-s%2F%25u002e%25u002e%', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'HTTP/2 400', 'output': "A response has been received with a response code '400' which may require further investigation to verify if this response is due to an abnormal behavior of the target. The response has been triggered by an HTTP GET request made on the URL 'https://juice-shop-388277804329.us-west1.run.app /apps/setup/setup-s/%u002e%u002e/%u002e%u002e/log.jsp'.", 'request_method': 'GET', 'http_status_code': 400, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/#/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'HTTP/2 405', 'output': "A response has been received with a response code '405' which may require further investigation to verify if this response is due to an abnormal behavior of the target. The response has been triggered by an HTTP TRACE request made on the URL 'https://juice-shop-388277804329.us-west1.run. app/#/'.", 'request_method': 'TRACE', 'http_status_code': 405, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/passwords/.htpasswd', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'HTTP/2 403', 'output': "A response has been received with a response code '403' which may require further investigation to verify if this response is due to an abnormal behavior of the target. The response has been triggered by an HTTP GET request made on the URL 'https://juice-shop-388277804329.us-west1.run.app /passwords/.htpasswd'.", 'request_method': 'GET', 'http_status_code': 403, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/db/.htpasswd', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'HTTP/2 403', 'output': "A response has been received with a response code '403' which may require further investigation to verify if this response is due to an abnormal behavior of the target. The response has been triggered by an HTTP GET request made on the URL 'https://juice-shop-388277804329.us-west1.run.app /db/.htpasswd'.", 'request_method': 'GET', 'http_status_code': 403, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/stylesheets/.htpasswd', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'HTTP/2 403', 'output': "A response has been received with a response code '403' which may require further investigation to verify if this response is due to an abnormal behavior of the target. The response has been triggered by an HTTP GET request made on the URL 'https://juice-shop-388277804329.us-west1.run.app /stylesheets/.htpasswd'.", 'request_method': 'GET', 'http_status_code': 403, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/passwords/heroes', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'HTTP/2 406', 'output': "A response has been received with a response code '406' which may require further investigation to verify if this response is due to an abnormal behavior of the target. The response has been triggered by an HTTP GET request made on the URL 'https://juice-shop-388277804329.us-west1.run.app /passwords/heroes'.", 'request_method': 'GET', 'http_status_code': 406, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/images/.htaccess', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'HTTP/2 403', 'output': "A response has been received with a response code '403' which may require further investigation to verify if this response is due to an abnormal behavior of the target. The response has been triggered by an HTTP GET request made on the URL 'https://juice-shop-388277804329.us-west1.run.app /images/.htaccess'.", 'request_method': 'GET', 'http_status_code': 403, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/soap/.htpasswd', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'HTTP/2 403', 'output': "A response has been received with a response code '403' which may require further investigation to verify if this response is due to an abnormal behavior of the target. The response has been triggered by an HTTP GET request made on the URL 'https://juice-shop-388277804329.us-west1.run.app /soap/.htpasswd'.", 'request_method': 'GET', 'http_status_code': 403, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/documents/.htaccess', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'HTTP/2 403', 'output': "A response has been received with a response code '403' which may require further investigation to verify if this response is due to an abnormal behavior of the target. The response has been triggered by an HTTP GET request made on the URL 'https://juice-shop-388277804329.us-west1.run.app /documents/.htaccess'.", 'request_method': 'GET', 'http_status_code': 403, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/.htaccess', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'HTTP/2 403', 'output': "A response has been received with a response code '403' which may require further investigation to verify if this response is due to an abnormal behavior of the target. The response has been triggered by an HTTP GET request made on the URL 'https://juice-shop-388277804329.us-west1.run.app /apps/.htaccess'.", 'request_method': 'GET', 'http_status_code': 403, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/was-tnb.aspx', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'HTTP/2 502', 'output': "A response has been received with a response code '502' which may require further investigation to verify if this response is due to an abnormal behavior of the target. The response has been triggered by an HTTP DEBUG request made on the URL 'https://juice-shop-388277804329.us-west1.run. app/apps/was-tnb.aspx'.", 'request_method': 'DEBUG', 'http_status_code': 502, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/documents/.htpasswd', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'HTTP/2 403', 'output': "A response has been received with a response code '403' which may require further investigation to verify if this response is due to an abnormal behavior of the target. The response has been triggered by an HTTP GET request made on the URL 'https://juice-shop-388277804329.us-west1.run.app /documents/.htpasswd'.", 'request_method': 'GET', 'http_status_code': 403, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/.htaccess', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'HTTP/2 403', 'output': "A response has been received with a response code '403' which may require further investigation to verify if this response is due to an abnormal behavior of the target. The response has been triggered by an HTTP GET request made on the URL 'https://juice-shop-388277804329.us-west1.run. app/.htaccess'.", 'request_method': 'GET', 'http_status_code': 403, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/stylesheets/.htaccess', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'HTTP/2 403', 'output': "A response has been received with a response code '403' which may require further investigation to verify if this response is due to an abnormal behavior of the target. The response has been triggered by an HTTP GET request made on the URL 'https://juice-shop-388277804329.us-west1.run.app /stylesheets/.htaccess'.", 'request_method': 'GET', 'http_status_code': 403, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/passwords/web.config', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'HTTP/2 406', 'output': "A response has been received with a response code '406' which may require further investigation to verify if this response is due to an abnormal behavior of the target. The response has been triggered by an HTTP GET request made on the URL 'https://juice-shop-388277804329.us-west1.run.app /passwords/web.config'.", 'request_method': 'GET', 'http_status_code': 406, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/.htpasswd', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'HTTP/2 403', 'output': "A response has been received with a response code '403' which may require further investigation to verify if this response is due to an abnormal behavior of the target. The response has been triggered by an HTTP GET request made on the URL 'https://juice-shop-388277804329.us-west1.run.app /apps/.htpasswd'.", 'request_method': 'GET', 'http_status_code': 403, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/images/.htpasswd', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'HTTP/2 403', 'output': "A response has been received with a response code '403' which may require further investigation to verify if this response is due to an abnormal behavior of the target. The response has been triggered by an HTTP GET request made on the URL 'https://juice-shop-388277804329.us-west1.run.app /images/.htpasswd'.", 'request_method': 'GET', 'http_status_code': 403, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/soap/.htaccess', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'HTTP/2 403', 'output': "A response has been received with a response code '403' which may require further investigation to verify if this response is due to an abnormal behavior of the target. The response has been triggered by an HTTP GET request made on the URL 'https://juice-shop-388277804329.us-west1.run.app /soap/.htaccess'.", 'request_method': 'GET', 'http_status_code': 403, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/js/.htpasswd', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'HTTP/2 403', 'output': "A response has been received with a response code '403' which may require further investigation to verify if this response is due to an abnormal behavior of the target. The response has been triggered by an HTTP GET request made on the URL 'https://juice-shop-388277804329.us-west1.run.app /js/.htpasswd'.", 'request_method': 'GET', 'http_status_code': 403, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/db/.htaccess', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'HTTP/2 403', 'output': "A response has been received with a response code '403' which may require further investigation to verify if this response is due to an abnormal behavior of the target. The response has been triggered by an HTTP GET request made on the URL 'https://juice-shop-388277804329.us-west1.run.app /db/.htaccess'.", 'request_method': 'GET', 'http_status_code': 403, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/server-status', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'HTTP/2 403', 'output': "A response has been received with a response code '403' which may require further investigation to verify if this response is due to an abnormal behavior of the target. The response has been triggered by an HTTP GET request made on the URL 'https://juice-shop-388277804329.us-west1.run.app /server-status'.", 'request_method': 'GET', 'http_status_code': 403, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/.htpasswd', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'HTTP/2 403', 'output': "A response has been received with a response code '403' which may require further investigation to verify if this response is due to an abnormal behavior of the target. The response has been triggered by an HTTP GET request made on the URL 'https://juice-shop-388277804329.us-west1.run. app/.htpasswd'.", 'request_method': 'GET', 'http_status_code': 403, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/install.php?cb=was_302_ebiu', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'HTTP/2 400', 'output': "A response has been received with a response code '400' which may require further investigation to verify if this response is due to an abnormal behavior of the target. The response has been triggered by an HTTP GET request made on the URL 'https://juice-shop-388277804329.us-west1.run.app /install.php'.", 'request_method': 'GET', 'http_status_code': 400, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}]</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="P52" t="n">
-        <v>98050</v>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="R52" t="inlineStr"/>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -4990,12 +5020,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['This is an informational plugin to inform the user what technologies the framework has detected on the target application, which can then be examined and checked for known vulnerable software versions']</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>['This is an informational plugin to inform the user what technologies the framework has detected on the target application, which can then be examined and checked for known vulnerable software versions']</t>
+          <t>['Only use components that do not have known vulnerabilities, only use components that when combined to not introduce a security vulnerability, and ensure that a misconfiguration does not cause any vulnerabilities']</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -5003,69 +5033,66 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr"/>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L53" t="n">
+        <v>98059</v>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"publication_date": "2017-12-06T00:00:00+00:00",
+"modification_date": "2023-11-17T00:00:00+00:00",
+"family": "Web Applications",
+"severity": "Info",
+"plugin_id": 98059}
+</t>
+        </is>
+      </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/#/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The framework has detected the following technologies in the target application: - PHP (v5.5.9) - Apache (v2.4.7)', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="P53" t="n">
-        <v>98059</v>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>['Only use components that do not have known vulnerabilities, only use components that when combined to not introduce a security vulnerability, and ensure that a misconfiguration does not cause any vulnerabilities']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/#/', 'input_type': 'technology', 'input_name': None, 'payload': None, 'proof': 'Detected technologies: PHP v5.5.9, Apache v2.4.7', 'output': 'The framework identified PHP (v5.5.9) and Apache (v2.4.7) in the target application.', 'request_method': None, 'http_status_code': None, 'http_protocol': 'HTTPS', 'response_content_type': None}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -5077,12 +5104,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['The scanner collected the cookies returned by the application during the scan. The list includes the following information for each cookie:', '- Name: name of the cookie', '- Value: value of the cookie', '- Domain: hosts to which the cookie will be sent', '- Path: URL path which must exist in the requested resource before sending the cookie', '- Expires: maximum lifetime of the cookie as an HTTP-date timestamp', '- Max-Age: number of seconds until the cookie expires', '- HttpOnly: cookie is set to be not accessible via JavaScript, XMLHttpRequest and Request APIs', '- Secure: cookie will be sent to the server only when a request is made using HTTPS', '- SameSite: cookie will be sent along with cross-site request according the defined policy', '- URL: first URL discovered which set the cookie in its response', '- Set-Method: method used by the application to set the cookie (Set-Cookie or JavaScript)', '- Audited: cookie will be audited by plugins during the scan', '- Reason Not Audited: reason given for the cookie not being audited during the scan']</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>['The scanner collected the cookies returned by the application during the scan. The list includes the following information for each cookie:', '- Name: name of the cookie', '- Value: value of the cookie', '- Domain: hosts to which the cookie will be sent', '- Path: URL path which must exist in the requested resource before sending the cookie', '- Expires: maximum lifetime of the cookie as an HTTP-date timestamp', '- Max-Age: number of seconds until the cookie expires', '- HttpOnly: cookie is set to be not accessible via JavaScript, XMLHttpRequest and Request APIs', '- Secure: cookie will be sent to the server only when a request is made using HTTPS', '- SameSite: cookie will be sent along with cross-site request according the defined policy', '- URL: first URL discovered which set the cookie in its response', '- Set-Method: method used by the application to set the cookie (Set-Cookie or JavaScript)', '- Audited: cookie will be audited by plugins during the scan', '- Reason Not Audited: reason given for the cookie not being audited during the scan']</t>
+          <t>['-']</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -5090,69 +5117,66 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr"/>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L54" t="n">
+        <v>98061</v>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"publication_date": "2020-09-01T00:00:00+00:00",
+"modification_date": "2023-11-17T00:00:00+00:00",
+"family": "Web Applications",
+"severity": "Info",
+"plugin_id": 98061}
+</t>
+        </is>
+      </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/#/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The following cookies have been collected during the scan of the target: - 0 cookie(s) specified via Set-Cookie - 1 cookie(s) set via JavaScript code The complete list of the cookies is available in attachment.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="P54" t="n">
-        <v>98061</v>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>['-']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/#/', 'input_type': 'cookie_collection', 'input_name': None, 'payload': None, 'proof': '0 cookie(s) via Set-Cookie; 1 cookie(s) set via JavaScript', 'output': 'The scanner collected cookies: none via Set-Cookie, one via JavaScript. Full list available in attachment.', 'request_method': None, 'http_status_code': None, 'http_protocol': 'HTTPS', 'response_content_type': None}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -5164,12 +5188,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Scanner has detected common sensitive files on the remote web server.', 'Web applications are often made up of multiple files and directories. It is possible that over time some files may become unreferenced (unused) by the web application and forgotten about by the administrator or developer. Because web applications are built using common frameworks, they contain common files that can be discovered (independent of server).', 'During the initial reconnaissance stages of an attack, cyber-criminals will attempt to locate unreferenced files in the hope that the file will assist in further compromise of the web application. To achieve this, they will make thousands of requests using word lists containing common filenames. The response headers from the server will then indicate if the file exists.']</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>['Scanner has detected common sensitive files on the remote web server.', 'Web applications are often made up of multiple files and directories. It is possible that over time some files may become unreferenced (unused) by the web application and forgotten about by the administrator or developer. Because web applications are built using common frameworks, they contain common files that can be discovered (independent of server).', 'During the initial reconnaissance stages of an attack, cyber-criminals will attempt to locate unreferenced files in the hope that the file will assist in further compromise of the web application. To achieve this, they will make thousands of requests using word lists containing common filenames. The response headers from the server will then indicate if the file exists.']</t>
+          <t>['If files are unreferenced, then they should be removed from the web root and/or the application directory.', 'Preventing access without authentication may also be an option and can stop a client from being able to view the contents of a file; however, it is still likely that the directory structure will be able to be discovered.', ""Using obscure file names is implementing 'security through obscurity' and is not a recommended option.""]</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -5177,69 +5201,66 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="M55" t="inlineStr"/>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L55" t="n">
+        <v>98071</v>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"publication_date": "2017-03-31T00:00:00+00:00",
+"modification_date": "2024-01-08T00:00:00+00:00",
+"family": "Web Servers",
+"severity": "Info",
+"plugin_id": 98071}
+</t>
+        </is>
+      </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>['http://httpd.apache.org/docs/2.0/mod/mod_access.html', 'http://projects.webappsec.org/w/page/13246953/Predictable%20Resource%20Location', 'http://nginx.org/en/docs/http/ngx_http_access_module.html', 'https://www.nginx.com/resources/admin-guide/restricting-access-auth-basic/', 'https://www.owasp.org/index.php/Forced_browsing']</t>
+          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/install.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': "The common file 'install.php' was identified by the scanner.", 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}]</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="P55" t="n">
-        <v>98071</v>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>['If files are unreferenced, then they should be removed from the web root and/or the application directory.', 'Preventing access without authentication may also be an option and can stop a client from being able to view the contents of a file; however, it is still likely that the directory structure will be able to be discovered.', ""Using obscure file names is implementing 'security through obscurity' and is not a recommended option.""]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/install.php', 'input_type': 'file', 'input_name': 'install.php', 'payload': None, 'proof': "The common file 'install.php' was identified by the scanner", 'output': "File 'install.php' accessible on target application", 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -5251,12 +5272,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Scanner has detected a common directory on the remote web server.', 'Web applications are often made up of multiple files and directories. It is possible that over time some directories may become unreferenced (unused) by the web application and forgotten about by the administrator or developer. Because web applications are built using common frameworks, they contain common directories that can be discovered (independent of server).', 'During the initial reconnaissance stages of an attack, cyber-criminals will attempt to locate unreferenced directories in the hope that the directory will assist in further compromise of the web application. To achieve this, they will make thousands of requests using word lists containing common names. The response headers from the server will then indicate if the directory exists.']</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>['Scanner has detected a common directory on the remote web server.', 'Web applications are often made up of multiple files and directories. It is possible that over time some directories may become unreferenced (unused) by the web application and forgotten about by the administrator or developer. Because web applications are built using common frameworks, they contain common directories that can be discovered (independent of server).', 'During the initial reconnaissance stages of an attack, cyber-criminals will attempt to locate unreferenced directories in the hope that the directory will assist in further compromise of the web application. To achieve this, they will make thousands of requests using word lists containing common names. The response headers from the server will then indicate if the directory exists.']</t>
+          <t>['If directories are unreferenced, then they should be removed from the web root and/or the application directory.', 'Preventing access without authentication may also be an option and can stop a client from being able to view the contents of a file; however, it is still likely that the directory structure will be able to be discovered.', ""Using obscure directory names is implementing 'security through obscurity' and is not a recommended option.""]</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -5264,65 +5285,66 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="M56" t="inlineStr"/>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L56" t="n">
+        <v>98072</v>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"publication_date": "2017-03-31T00:00:00+00:00",
+"modification_date": "2024-01-03T00:00:00+00:00",
+"family": "Web Servers",
+"severity": "Info",
+"plugin_id": 98072}
+</t>
+        </is>
+      </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>['http://httpd.apache.org/docs/2.0/mod/mod_access.html', 'http://projects.webappsec.org/w/page/13246953/Predictable%20Resource%20Location', 'https://www.nginx.com/resources/admin-guide/restricting-access-auth-basic/', 'https://www.owasp.org/index.php/Forced_browsing']</t>
+          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/db/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': "The common directory 'db' was identified by the scanner.", 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/documents/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': "The common directory 'documents' was identified by the scanner.", 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/images/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': "The common directory 'images' was identified by the scanner.", 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/stylesheets/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': "The common directory 'stylesheets' was identified by the scanner.", 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': "The common directory 'apps' was identified by the scanner.", 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/soap/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': "The common directory 'soap' was identified by the scanner.", 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/js/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': "The common directory 'js' was identified by the scanner.", 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/passwords/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': "The common directory 'passwords' was identified by the scanner.", 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}]</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="P56" t="n">
-        <v>98072</v>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>['If directories are unreferenced, then they should be removed from the web root and/or the application directory.', 'Preventing access without authentication may also be an option and can stop a client from being able to view the contents of a file; however, it is still likely that the directory structure will be able to be discovered.', ""Using obscure directory names is implementing 'security through obscurity' and is not a recommended option.""]</t>
-        </is>
-      </c>
-      <c r="R56" t="inlineStr"/>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -5334,12 +5356,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Private, or non-routable, IP addresses are generally used within a home or company network and are typically unknown to anyone outside of that network.', 'Cyber-criminals will attempt to identify the private IP address range being used by their victim, to aid in collecting further information that could then lead to a possible compromise.', 'Scanner discovered that the affected page returned a RFC 1918 compliant private IP address and therefore could be revealing sensitive information.', 'This finding typically requires manual verification to ensure the context is correct, as any private IP address within the HTML body will trigger it.']</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>['Private, or non-routable, IP addresses are generally used within a home or company network and are typically unknown to anyone outside of that network.', 'Cyber-criminals will attempt to identify the private IP address range being used by their victim, to aid in collecting further information that could then lead to a possible compromise.', 'Scanner discovered that the affected page returned a RFC 1918 compliant private IP address and therefore could be revealing sensitive information.', 'This finding typically requires manual verification to ensure the context is correct, as any private IP address within the HTML body will trigger it.']</t>
+          <t>['Identifying the context in which the affected page displays a Private IP address is necessary.', 'If the page is publicly accessible and displays the Private IP of the affected server (or supporting infrastructure), then measures should be put in place to ensure that the IP address is removed from any response.']</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -5347,69 +5369,66 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>['https://juice-shop-388277804329.us-west1.run.app/#/', '169.254.169.1 found on 1 URL', '169.254.169.126 found on 1 URL', '127.0.0.1 found on 1 URL']</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="M57" t="inlineStr"/>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L57" t="n">
+        <v>98077</v>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"publication_date": "2017-03-31T00:00:00+00:00",
+"modification_date": "2023-11-17T00:00:00+00:00",
+"family": "Data Exposure",
+"severity": "Info",
+"plugin_id": 98077}
+</t>
+        </is>
+      </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>['http://projects.webappsec.org/w/page/13246936/Information%20Leakage', 'CWE -', 'WASC -', 'OWASP -', 'CVE -', 'BID -']</t>
+          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/#/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Number of Private IP Addresses Collected: 3 Listed below are each private ip address: 169.254.169.1 found on 1 URL 169.254.169.126 found on 1 URL 127.0.0.1 found on 1 URL', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="P57" t="n">
-        <v>98077</v>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>['Identifying the context in which the affected page displays a Private IP address is necessary.', 'If the page is publicly accessible and displays the Private IP of the affected server (or supporting infrastructure), then measures should be put in place to ensure that the IP address is removed from any response.']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/#/', 'input_type': 'private_ip', 'input_name': None, 'payload': None, 'proof': 'Number of Private IP Addresses Collected: 3 (169.254.169.1, 169.254.169.126, 127.0.0.1)', 'output': 'The scanner identified 3 private IP addresses exposed in the application.', 'request_method': None, 'http_status_code': None, 'http_protocol': 'HTTPS', 'response_content_type': None}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -5421,12 +5440,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Email addresses are typically found on ""Contact us"" pages, however, they can also be found within scripts or code comments of the application. They are used to provide a legitimate means of contacting an organisation.', 'As one of the initial steps in information gathering, cyber-criminals will spider a website and using automated methods collect as many email addresses as possible, that they may then use in a social engineering attack.', 'Using the same automated methods, scanner was able to detect one or more email addresses that were stored within the affected page.']</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>['Email addresses are typically found on ""Contact us"" pages, however, they can also be found within scripts or code comments of the application. They are used to provide a legitimate means of contacting an organisation.', 'As one of the initial steps in information gathering, cyber-criminals will spider a website and using automated methods collect as many email addresses as possible, that they may then use in a social engineering attack.', 'Using the same automated methods, scanner was able to detect one or more email addresses that were stored within the affected page.']</t>
+          <t>['E-mail addresses should be presented in such a way that it is hard to process them automatically.']</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -5434,69 +5453,66 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>['https://juice-shop-388277804329.us-west1.run.app/#/', 'license@php.net found on 1 URL', 'bee6885858486f31043e5839c735d99457f045affd0bwapp-bee@mailinator.comA found on 1 URL', 'A.I.M.6885858486f31043e5839c735d99457f045affd0bwapp-aim@mailinator.comA found on 1 URL']</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr"/>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L58" t="n">
+        <v>98078</v>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"publication_date": "2017-03-31T00:00:00+00:00",
+"modification_date": "2023-11-17T00:00:00+00:00",
+"family": "Data Exposure",
+"severity": "Info",
+"plugin_id": 98078}
+</t>
+        </is>
+      </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>['CWE -', 'WASC -', 'OWASP -', 'CVE -', 'BID -']</t>
+          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/#/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Number of Email Addresses Collected: 3 Listed below are each email address and the number of URLs where the email address has been found: license@php.net found on 1 URL bee6885858486f31043e5839c735d99457f045affd0bwapp-bee@mailinator.comA found on 1 URL A.I.M.6885858486f31043e5839c735d99457f045affd0bwapp-aim@mailinator.comA found on 1 URL', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="P58" t="n">
-        <v>98078</v>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>['E-mail addresses should be presented in such a way that it is hard to process them automatically.']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/#/', 'input_type': 'email_collection', 'input_name': None, 'payload': None, 'proof': 'Number of Email Addresses Collected: 3 (license@php.net, bee6885858486f31043e5839c735d99457f045affd0bwapp-bee@mailinator.comA, A.I.M.6885858486f31043e5839c735d99457f045affd0bwapp-aim@mailinator.comA)', 'output': 'The scanner identified 3 email addresses exposed in the application.', 'request_method': None, 'http_status_code': None, 'http_protocol': 'HTTPS', 'response_content_type': None}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5524,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Publishes the target information of the starting url as evaluated by the scan.']</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>['Publishes the target information of the starting url as evaluated by the scan.']</t>
+          <t>['-']</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -5521,69 +5537,66 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
-          <t>['Status Code : 302', 'Return Code : ok', 'Return Message: No error', 'Response Time : 0.078037s', 'Response Size : 294 bytes', 'Content-Type : text/html', 'DEBUG INFORMATION', 'HTTP Network Timeout : 30s', 'REQUEST MADE', 'GET / HTTP/2', 'REQUEST HEADERS', 'Host: juice-shop-388277804329.us-west1.run.app', 'Accept-Encoding: gzip, deflate, br', 'User-Agent: Mozilla/5.0 (X11; Linux x86_64) AppleWebKit/537.36 (KHTML, like Gecko) Chrome/124.0.6367.207 Safari/537.36', 'Accept: */*', 'Accept-Language: en-US,en;q=0.5', 'RESPONSE HEADERS', 'HTTP/2 302', 'x-powered-by: PHP/5.5.9-1ubuntu4.14', 'location: portal.php', 'content-type: text/html', 'x-cloud-trace-context: 1af46a284798e67769151ba2877d7ea6', 'date: Tue, 19 Nov 2024 00:10:34 GMT', 'server: Google Frontend', 'content-length: 0', 'alt-svc: h3="":443""; ma=2592000,h3-29="":443""; ma=2592000']</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>['https://juice-shop-388277804329.us-west1.run.app/#/', 'Domain Name : juice-shop-388277804329.us-west1.run.app', 'IP Address : 216.239.32.53']</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="M59" t="inlineStr"/>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L59" t="n">
+        <v>98136</v>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"publication_date": "2017-07-27T00:00:00+00:00",
+"modification_date": "2024-04-26T00:00:00+00:00",
+"family": "General",
+"severity": "Info",
+"plugin_id": 98136}
+</t>
+        </is>
+      </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>['CWE -', 'WASC -', 'OWASP -', 'CVE -', 'BID -']</t>
+          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/#/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': "Access to URL 'https://juice-shop-388277804329.us-west1.run.app/#/' has been confirmed. Target Information ------------------------ Domain Name : juice-shop-388277804329.us-west1.run.app IP Address : 216.239.32.53 Response Information --------------------------- Status Code : 302 Return Code : ok Return Message: No error Response Time : 0.078037s Response Size : 294 bytes Content-Type : text/html DEBUG INFORMATION ----------------------- HTTP Network Timeout : 30s", 'request_method': 'GET', 'http_status_code': 302, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}]</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="P59" t="n">
-        <v>98136</v>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>['-']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/#/', 'input_type': 'access', 'input_name': None, 'payload': None, 'proof': 'Access confirmed to target. Domain: juice-shop-388277804329.us-west1.run.app, IP: 216.239.32.53', 'output': 'Access to target URL confirmed with status code 302 and redirection to portal.php.', 'request_method': 'GET', 'http_status_code': 302, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -5595,12 +5608,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Screenshot of the target web page, see attached image. This screenshot should show you the target page we are launching the scan against. If the image is not of the intended target page, please check the provided url in the scan configuration.']</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>['Screenshot of the target web page, see attached image. This screenshot should show you the target page we are launching the scan against. If the image is not of the intended target page, please check the provided url in the scan configuration.']</t>
+          <t>['-']</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -5608,69 +5621,66 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>['https://juice-shop-388277804329.us-west1.run.app/#/', ""WAS Scanner has taken a screenshot of the page at url 'https://juice-shop-388277804329.us-west1.run.app/#/' with dimensions 1600x1200.""]</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="M60" t="inlineStr"/>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L60" t="n">
+        <v>98138</v>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"publication_date": "2018-01-23T00:00:00+00:00",
+"modification_date": "2018-02-14T00:00:00+00:00",
+"family": "General",
+"severity": "Info",
+"plugin_id": 98138}
+</t>
+        </is>
+      </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>['CWE -', 'WASC -', 'OWASP -', 'CVE -', 'BID -']</t>
+          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/#/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': "WAS Scanner has taken a screenshot of the page at url 'https://juice-shop-388277804329.us-west1.run.app/#/' with dimensions 1600x1200. Please see the attachment for the screenshot image.", 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="P60" t="n">
-        <v>98138</v>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>['-']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/#/', 'input_type': 'screenshot', 'input_name': None, 'payload': None, 'proof': 'WAS Scanner captured screenshot at 1600x1200 resolution', 'output': 'Scanner successfully took a screenshot of the target page. Image available in attachment.', 'request_method': None, 'http_status_code': None, 'http_protocol': 'HTTPS', 'response_content_type': None}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -5682,12 +5692,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['The scanner has detected the presence of a form during the crawling of the target web application. Details about the form are provided in the plugin output.']</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>['The scanner has detected the presence of a form during the crawling of the target web application. Details about the form are provided in the plugin output.']</t>
+          <t>['-']</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -5695,69 +5705,66 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="M61" t="inlineStr"/>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L61" t="n">
+        <v>98148</v>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"publication_date": "2021-10-21T00:00:00+00:00",
+"modification_date": "2021-10-21T00:00:00+00:00",
+"family": "Web Applications",
+"severity": "Info",
+"plugin_id": 98148}
+</t>
+        </is>
+      </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>['CWE -', 'WASC -', 'OWASP -', 'CVE -', 'BID -']</t>
+          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/login.php', 'input_type': 'form', 'input_name': 'combined:post::https://juice-shop-388277804329.us-west1.run.app/login.php', 'payload': '', 'proof': '', 'output': 'A form with no identifier has been detected on the following URL https://juice-shop-388277804329.us-west1.run.app/login. php with input fields : - login (text) - password (password) - No name or id (select) - form (submit) This form is submitted by using the following action : https://juice-shop-388277804329.us-west1.run.app/login.php', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/user_new.php', 'input_type': 'form', 'input_name': 'combined:post::https://juice-shop-388277804329.us-west1.run.app/user_new.php', 'payload': '', 'proof': '', 'output': 'A form with no identifier has been detected on the following URL https://juice-shop-388277804329.us-west1.run.app /user_new.php with input fields : - login (text) - email (text) - password (password) - password_conf (password) - secret (text) - mail_activation (checkbox) - action (submit) This form is submitted by using the following action : https://juice-shop-388277804329.us-west1.run.app/user_new.php', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="P61" t="n">
-        <v>98148</v>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>['-']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/login.php', 'input_type': 'form', 'input_name': 'combined:post::https://juice-shop-388277804329.us-west1.run.app/login.php', 'payload': None, 'proof': 'Form detected with fields: login (text), password (password), no name/id (select), form (submit)', 'output': 'Form with no identifier detected. Submitted via action https://juice-shop-388277804329.us-west1.run.app/login.php', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/1.1', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/user_new.php', 'input_type': 'form', 'input_name': 'combined:post::https://juice-shop-388277804329.us-west1.run.app/user_new.php', 'payload': None, 'proof': 'Form detected with fields: login (text), email (text), password (password), password_conf (password), secret (text), mail_activation (checkbox), action (submit)', 'output': 'Form with no identifier detected. Submitted via action https://juice-shop-388277804329.us-west1.run.app/user_new.php', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/1.1', 'response_content_type': 'text/html'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5776,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['An external URL is an URL for which the Fully Qualified Domain Name (FQDN) is not the same as the web target URL one. The scanner detected the presence of external URLs on the target web application and have listed them based on two types : URLs with a domain name in common with the web target URL and all the other external URLs.']</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>['An external URL is an URL for which the Fully Qualified Domain Name (FQDN) is not the same as the web target URL one. The scanner detected the presence of external URLs on the target web application and have listed them based on two types : URLs with a domain name in common with the web target URL and all the other external URLs.']</t>
+          <t>['-']</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -5782,69 +5789,66 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>['https://juice-shop-388277804329.us-west1.run.app/#/']</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="M62" t="inlineStr"/>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L62" t="n">
+        <v>98154</v>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"publication_date": "2022-11-30T00:00:00+00:00",
+"modification_date": "2022-12-12T00:00:00+00:00",
+"family": "General",
+"severity": "Info",
+"plugin_id": 98154}
+</t>
+        </is>
+      </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/#/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner detected the presence of 24 URLs on the target application: - 0 URLs which use a hostname related to the target hostname - 24 URLs which use a third party hostname The list of the detected URLs is provided in attachment.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="P62" t="n">
-        <v>98154</v>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>['-']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/#/', 'input_type': 'url_collection', 'input_name': None, 'payload': None, 'proof': 'Scanner detected 24 URLs: 0 related to target hostname, 24 using third-party hostnames', 'output': 'The scanner identified 24 URLs in the application, all pointing to third-party hostnames. Full list available in attachment.', 'request_method': None, 'http_status_code': None, 'http_protocol': 'HTTPS', 'response_content_type': None}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -5856,12 +5860,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Permissions Policy provides mechanisms to websites to restrict the use of browser features in its own frame and in iframes that it embeds.']</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>['Permissions Policy provides mechanisms to websites to restrict the use of browser features in its own frame and in iframes that it embeds.']</t>
+          <t>[""Configure Permissions Policy on your website by adding 'Permissions-Policy' HTTP header.""]</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -5869,65 +5873,66 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
-          <t>['No Permissions-Policy headers were found on https://juice-shop-388277804329.us-west1.run.app/soap/class.nusoap_base.php', 'No Permissions-Policy headers were found on https://juice-shop-388277804329.us-west1.run.app/info_install.php', 'No Permissions-Policy headers were found on https://juice-shop-388277804329.us-west1.run.app/db/', 'No Permissions-Policy headers were found on https://juice-shop-388277804329.us-west1.run.app/documents/', 'No Permissions-Policy headers were found on https://juice-shop-388277804329.us-west1.run.app/js/', 'No Permissions-Policy headers were found on https://juice-shop-388277804329.us-west1.run.app/training_install.php']</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>['https://juice-shop-388277804329.us-west1.run.app/soap/class.nusoap_base.php', 'https://juice-shop-388277804329.us-west1.run.app/info_install.php', 'https://juice-shop-388277804329.us-west1.run.app/db/', 'https://juice-shop-388277804329.us-west1.run.app/documents/', 'https://juice-shop-388277804329.us-west1.run.app/js/', 'https://juice-shop-388277804329.us-west1.run.app/training_install.php']</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="M63" t="inlineStr"/>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L63" t="n">
+        <v>98526</v>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"publication_date": "2019-03-27T00:00:00+00:00",
+"modification_date": "2024-03-25T00:00:00+00:00",
+"family": "HTTP Security Header",
+"severity": "Info",
+"plugin_id": 98526}
+</t>
+        </is>
+      </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>['CWE -', 'WASC -', 'OWASP -', 'CVE -', 'BID -']</t>
+          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/soap/class.nusoap_base.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Permissions-Policy headers were found on https://juice-shop-388277804329.us-west1.run.app/soap/class.nusoap_base.php', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/info_install.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Permissions-Policy headers were found on https://juice-shop-388277804329.us-west1.run.app/info_install.php', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/db/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Permissions-Policy headers were found on https://juice-shop-388277804329.us-west1.run.app/db/', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/documents/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Permissions-Policy headers were found on https://juice-shop-388277804329.us-west1.run.app/documents/', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/js/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Permissions-Policy headers were found on https://juice-shop-388277804329.us-west1.run.app/js/', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/training_install.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Permissions-Policy headers were found on https://juice-shop-388277804329.us-west1.run.app/training_install.php', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/install.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Permissions-Policy headers were found on https://juice-shop-388277804329.us-west1.run.app/install.php', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/stylesheets/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Permissions-Policy headers were found on https://juice-shop-388277804329.us-west1.run.app/stylesheets/', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/info.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Permissions-Policy headers were found on https://juice-shop-388277804329.us-west1.run.app/info.php', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/images/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Permissions-Policy headers were found on https://juice-shop-388277804329.us-west1.run.app/images/', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/soap/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Permissions-Policy headers were found on https://juice-shop-388277804329.us-west1.run.app/soap/', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/passwords/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Permissions-Policy headers were found on https://juice-shop-388277804329.us-west1.run.app/passwords/', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/soap/class.wsdlcache.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Permissions-Policy headers were found on https://juice-shop-388277804329.us-west1.run.app/soap/class.wsdlcache.php', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/passwords/wp-config.bak', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Permissions-Policy headers were found on https://juice-shop-388277804329.us-west1.run.app/passwords/wp-config.bak', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'application/x-trash'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/soap/class.soap_fault.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Permissions-Policy headers were found on https://juice-shop-388277804329.us-west1.run.app/soap/class.soap_fault.php', 'request_method': 'GET', 'http_status_code': 500, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/phpinfo.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Permissions-Policy headers were found on https://juice-shop-388277804329.us-west1.run.app/phpinfo.php', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/movie_search', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Permissions-Policy headers were found on https://juice-shop-388277804329.us-west1.run.app/apps/movie_search', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/db/bwapp.sqlite', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Permissions-Policy headers were found on https://juice-shop-388277804329.us-west1.run.app/db/bwapp.sqlite', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/passwords/heroes.xml', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Permissions-Policy headers were found on https://juice-shop-388277804329.us-west1.run.app/passwords/heroes.xml', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/soap/nusoap.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Permissions-Policy headers were found on https://juice-shop-388277804329.us-west1.run.app/soap/nusoap.php', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Permissions-Policy headers were found on https://juice-shop-388277804329.us-west1.run.app/apps/', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/login.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Permissions-Policy headers were found on https://juice-shop-388277804329.us-west1.run.app/login.php', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/user_new.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Permissions-Policy headers were found on https://juice-shop-388277804329.us-west1.run.app/user_new.php', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/passwords/web.config.bak', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Permissions-Policy headers were found on https://juice-shop-388277804329.us-west1.run.app/passwords/web.config.bak', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'application/x-trash'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/training.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Permissions-Policy headers were found on https://juice-shop-388277804329.us-west1.run.app/training.php', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="P63" t="n">
-        <v>98526</v>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>[""Configure Permissions Policy on your website by adding 'Permissions-Policy' HTTP header.""]</t>
-        </is>
-      </c>
-      <c r="R63" t="inlineStr"/>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -5939,12 +5944,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Referrer Policy provides mechanisms to websites to restrict referrer information (sent in the referer header) that browsers will be allowed to add.', 'No Referrer Policy header or metatag configuration has been detected.']</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>['Referrer Policy provides mechanisms to websites to restrict referrer information (sent in the referer header) that browsers will be allowed to add.', 'No Referrer Policy header or metatag configuration has been detected.']</t>
+          <t>[""Configure Referrer Policy on your website by adding 'Referrer-Policy' HTTP header or meta tag referrer in HTML.""]</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -5952,65 +5957,66 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
-          <t>['No Referrer-Policy headers or body meta tags were found on https://juice-shop-388277804329.us-west1.run.app/passwords/wp-config.bak\nREQUEST MADE\nGET /passwords/wp-config.bak HTTP/2\nREQUEST HEADERS\nHost: juice-shop-388277804329.us-west1.run.app\nAccept-Encoding: gzip, deflate, br\nUser-Agent: Mozilla/5.0 (X11; Linux x86_64) AppleWebKit/537.36 (KHTML, like Gecko) Chrome/124.0.6367.207 Safari/537.36\nAccept: */*\nAccept-Language: en-US,en;q=0.5\nCookie: PHPSESSID=711vt1tpgrucudl1kaq9t074f5\nRESPONSE HEADERS\nHTTP/2 200\nlast-modified: Wed, 13 Nov 2024 02:15:28 GMT\netag: ""603-626c1e84a7000""\naccept-ranges: bytes\ncontent-type: application/x-trash\nx-cloud-trace-context: bccbdb7c061d2d5009d67b2ae3eb5bac\ndate: Tue, 19 Nov 2024 06:12:37 GMT\nserver: Google Frontend\ncontent-length: 1539\nalt-svc: h3="":443""; ma=2592000,h3-29="":443""; ma=2592000', 'No Referrer-Policy headers or body meta tags were found on https://juice-shop-388277804329.us-west1.run.app/user_new.php\nREQUEST MADE\nGET https://juice-shop-388277804329.us-west1.run.app/user_new.php\nREQUEST HEADERS\nAccept=*/*\nAccept-Encoding=gzip, deflate, br\nAccept-Language=en-US,en;q=0.5\nCookie=PHPSESSID=711vt1tpgrucudl1kaq9t074f5\nPriority=u=0, i\nSec-Ch-Ua=""Chromium"";v=""124"", ""HeadlessChrome"";v=""124"", ""Not-A.Brand"";v=""99""\nSec-Ch-Ua-Mobile=?0\nSec-Ch-Ua-Platform=""Linux""\nSec-Fetch-Dest=document\nSec-Fetch-Mode=navigate\nSec-Fetch-Site=none\nSec-Fetch-User=?1\nUpgrade-Insecure-Requests=1\nUser-Agent=Mozilla/5.0 (X11; Linux x86_64) AppleWebKit/537.36 (KHTML, like Gecko) Chrome/124.0.6367.207 Safari/537.36\nRESPONSE HEADERS\nHTTP/1.1 200 OK\nAlt-Svc=h3="":443""; ma=2592000,h3-29="":443""; ma=2592000\nContent-Encoding=gzip\nContent-Type=text/html\nDate=Tue, 19 Nov 2024 07:45:52 GMT\nServer=Google Frontend\nVary=Accept-Encoding\nX-Cloud-Trace-Context=1de28a3c31c89c397b35ab9cf352eeaf\nX-Powered-By=PHP/5.5.9-1ubuntu4.14\nContent-Length=4224', 'No Referrer-Policy headers or body meta tags were found on https://juice-shop-388277804329.us-west1.run.app/soap/class.nusoap_base.php\nREQUEST MADE\nGET https://juice-shop-388277804329.us-west1.run.app/soap/class.nusoap_base.php\nREQUEST HEADERS\nAccept=*/*\nAccept-Encoding=gzip, deflate, br\nAccept-Language=en-US,en;q=0.5\nCookie=PHPSESSID=711vt1tpgrucudl1kaq9t074f5\nPriority=u=0, i\nSec-Ch-Ua=""Chromium"";v=""124"", ""HeadlessChrome"";v=""124"", ""Not-A.Brand"";v=""99""\nSec-Ch-Ua-Mobile=?0\nSec-Ch-Ua-Platform=""Linux""\nSec-Fetch-Dest=document\nSec-Fetch-Mode=navigate\nSec-Fetch-Site=none\nSec-Fetch-User=?1\nUpgrade-Insecure-Requests=1\nUser-Agent=Mozilla/5.0 (X11; Linux x86_64) AppleWebKit/537.36 (KHTML, like Gecko) Chrome/124.0.6367.207 Safari/537.36\nRESPONSE HEADERS\nHTTP/1.1 200 OK\nAlt-Svc=h3="":443""; ma=2592000,h3-29="":443""; ma=2592000\nContent-Type=text/html\nDate=Tue, 19 Nov 2024 06:46:36 GMT\nServer=Google Frontend\nX-Cloud-Trace-Context=c53cd0b0ef8c298766ed3c1bd61168b7\nX-Powered-By=PHP/5.5.9-1ubuntu4.14\nContent-Length=811', 'No Referrer-Policy headers or body meta tags were found on https://juice-shop-388277804329.us-west1.run.app/soap/class.wsdlcache.php\nREQUEST MADE\nGET https://juice-shop-388277804329.us-west1.run.app/soap/class.wsdlcache.php\nREQUEST HEADERS\nAccept=*/*\nAccept-Encoding=gzip, deflate, br\nAccept-Language=en-US,en;q=0.5\nCookie=PHPSESSID=711vt1tpgrucudl1kaq9t074f5\nPriority=u=0, i\nSec-Ch-Ua=""Chromium"";v=""124"", ""HeadlessChrome"";v=""124"", ""Not-A.Brand"";v=""99""\nSec-Ch-Ua-Mobile=?0\nSec-Ch-Ua-Platform=""Linux""\nSec-Fetch-Dest=document\nSec-Fetch-Mode=navigate\nSec-Fetch-Site=none\nSec-Fetch-User=?1\nUpgrade-Insecure-Requests=1\nUser-Agent=Mozilla/5.0 (X11; Linux x86_64) AppleWebKit/537.36 (KHTML, like Gecko) Chrome/124.0.6367.207 Safari/537.36\nRESPONSE HEADERS\nHTTP/1.1 200 OK\nAlt-Svc=h3="":443""; ma=2592000,h3-29="":443""; ma=2592000\nContent-Type=text/html\nDate=Tue, 19 Nov 2024 06:59:07 GMT\nServer=Google Frontend\nX-Cloud-Trace-Context=7cb98e8601bf9fb1d2977a54ea93f5f7\nX-Powered-By=PHP/5.5.9-1ubuntu4.14\nContent-Length=811', 'No Referrer-Policy headers or body meta tags were found on https://juice-shop-388277804329.us-west1.run.app/passwords/web.config.bak\nREQUEST MADE\nGET /passwords/web.config.bak HTTP/2\nREQUEST HEADERS\nHost: juice-shop-388277804329.us-west1.run.app\nAccept-Encoding: gzip, deflate, br\nUser-Agent: Mozilla/5.0 (X11; Linux x86_64) AppleWebKit/537.36 (KHTML, like Gecko) Chrome/124.0.6367.207 Safari/537.36\nAccept: */*\nAccept-Language: en-US,en;q=0.5\nCookie: PHPSESSID=711vt1tpgrucudl1kaq9t074f5\nRESPONSE HEADERS\nHTTP/2 200\nlast-modified: Wed, 13 Nov 2024 02:15:28 GMT\netag: ""1d84-626c1e84a7000""\naccept-ranges: bytes\ncontent-type: application/x-trash\nx-cloud-trace-context: dd8a0753fe21b8d0d381c2313f0202d5\ndate: Tue, 19 Nov 2024 06:08:24 GMT\nserver: Google Frontend\ncontent-length: 7556\nalt-svc: h3="":443""; ma=2592000,h3-29="":443""; ma=2592000', 'No Referrer-Policy headers or body meta tags were found on https://juice-shop-388277804329.us-west1.run.app/soap/\nREQUEST MADE\nGET https://juice-shop-388277804329.us-west1.run.app/soap/\nREQUEST HEADERS\nAccept=*/*\nAccept-Encoding=gzip, deflate, br\nAccept-Language=en-US,en;q=0.5\nCookie=PHPSESSID=711vt1tpgrucudl1kaq9t074f5\nPriority=u=0, i\nSec-Ch-Ua=""Chromium"";v=""124"", ""HeadlessChrome"";v=""124"", ""Not-A.Brand"";v=""99""\nSec-Ch-Ua-Mobile=?0\nSec-Ch-Ua-Platform=""Linux""\nSec-Fetch-Dest=document\nSec-Fetch-Mode=navigate\nSec-Fetch-Site=none\nSec-Fetch-User=?1\nUpgrade-Insecure-Requests=1\nUser-Agent=Mozilla/5.0 (X11; Linux x86_64) AppleWebKit/537.36 (KHTML, like Gecko) Chrome/124.0.6367.207 Safari/537.36\nRESPONSE HEADERS\nHTTP/1.1 200 OK\nAlt-Svc=h3="":443""; ma=2592000,h3-29="":443""; ma=2592000\nContent-Encoding=gzip\nContent-Type=text/html;charset=UTF-8\nDate=Tue, 19 Nov 2024 01:24:49 GMT\nServer=Google Frontend\nVary=Accept-Encoding\nX-Cloud-Trace-Context=00c8cab83d92eca2ba95785b966a73c5\nContent-Length=4201', 'No Referrer-Policy headers or body meta tags were found on https://juice-shop-388277804329.us-west1.run.app/passwords/\nREQUEST MADE\nGET https://juice-shop-388277804329.us-west1.run.app/passwords/\nREQUEST HEADERS\nAccept=*/*\nAccept-Encoding=gzip, deflate, br\nAccept-Language=en-US,en;q=0.5\nCookie=PHPSESSID=711vt1tpgrucudl1kaq9t074f5\nPriority=u=0, i\nSec-Ch-Ua=""Chromium"";v=""124"", ""HeadlessChrome"";v=""124"", ""Not-A.Brand"";v=""99""\nSec-Ch-Ua-Mobile=?0\nSec-Ch-Ua-Platform=""Linux""\nSec-Fetch-Dest=document\nSec-Fetch-Mode=navigate\nSec-Fetch-Site=none\nSec-Fetch-User=?1\nUpgrade-Insecure-Requests=1\nUser-Agent=Mozilla/5.0 (X11; Linux x86_64) AppleWebKit/537.36 (KHTML, like Gecko) Chrome/124.0.6367.207 Safari/537.36\nRESPONSE HEADERS\nHTTP/1.1 200 OK\nAlt-Svc=h3="":443""; ma=2592000,h3-29="":443""; ma=2592000\nContent-Encoding=gzip\nContent-Type=text/html;charset=UTF-8\nDate=Tue, 19 Nov 2024 01:15:47 GMT\nServer=Google Frontend\nVary=Accept-Encoding\nX-Cloud-Trace-Context=23cbd446a1bfac87a66163e22db42b14\nContent-Length=2204', 'No Referrer-Policy headers or body meta tags were found on https://juice-shop-388277804329.us-west1.run.app/db/\nREQUEST MADE\nGET https://juice-shop-388277804329.us-west1.run.app/db/\nREQUEST HEADERS\nAccept=*/*\nAccept-Encoding=gzip, deflate, br\nAccept-Language=en-US,en;q=0.5\nCookie=PHPSESSID=711vt1tpgrucudl1kaq9t074f5\nPriority=u=0, i\nSec-Ch-Ua=""Chromium"";v=""124"", ""HeadlessChrome"";v=""124"", ""Not-A.Brand"";v=""99""\nSec-Ch-Ua-Mobile=?0\nSec-Ch-Ua-Platform=""Linux""\nSec-Fetch-Dest=document\nSec-Fetch-Mode=navigate\nSec-Fetch-Site=none\nSec-Fetch-User=?1\nUpgrade-Insecure-Requests=1\nUser-Agent=Mozilla/5.0 (X11; Linux x86_64) AppleWebKit/537.36 (KHTML, like Gecko) Chrome/124.0.6367.207 Safari/537.36\nRESPONSE HEADERS\nHTTP/1.1 200 OK\nAlt-Svc=h3="":443""; ma=2592000,h3-29="":443""; ma=2592000\nContent-Encoding=gzip\nContent-Type=text/html;charset=UTF-8\nDate=Tue, 19 Nov 2024 00:39:25 GMT\nServer=Google Frontend\nVary=Accept-Encoding\nX-Cloud-Trace-Context=7330f8397d6d6ed7b0975d370f2d06ee\nContent-Length=1778', 'No Referrer-Policy headers or body meta tags were found on https://juice-shop-388277804329.us-west1.run.app/info_install.php\nREQUEST MADE\nGET https://juice-shop-388277804329.us-west1.run.app/info_install.php\nREQUEST HEADERS\nAccept=*/*\nAccept-Encoding=gzip, deflate, br\nAccept-Language=en-US,en;q=0.5\nCookie=PHPSESSID=711vt1tpgrucudl1kaq9t074f5\nPriority=u=0, i\nSec-Ch-Ua=""Chromium"";v=""124"", ""HeadlessChrome"";v=""124"", ""Not-A.Brand"";v=""99""\nSec-Ch-Ua-Arch=""""\nSec-Ch-Ua-Bitness=""""\nSec-Ch-Ua-Full-Version-List=""Chromium"", ""HeadlessChrome"", ""Not-A.Brand"";v=""99.0.0.0""\nSec-Ch-Ua-Mobile=?0\nSec-Ch-Ua-Model=""""\nSec-Ch-Ua-Platform=""Linux""\nSec-Ch-Ua-Platform-Version=""""\nSec-Ch-Ua-Wow64=?0\nSec-Fetch-Dest=document\nSec-Fetch-Mode=navigate\nSec-Fetch-Site=none\nSec-Fetch-User=?1\nUpgrade-Insecure-Requests=1\nUser-Agent=Mozilla/5.0 (X11; Linux x86_64) AppleWebKit/537.36 (KHTML, like Gecko) Chrome/124.0.6367.207 Safari/537.36\nRESPONSE HEADERS\nHTTP/1.1 200 OK\nAlt-Svc=h3="":443""; ma=2592000,h3-29="":443""; ma=2592000\nContent-Encoding=gzip\nContent-Type=text/html\nDate=Tue, 19 Nov 2024 02:21:07 GMT\nServer=Google Frontend\nVary=Accept-Encoding\nX-Cloud-Trace-Context=3305fabc85563bee1adce5fca1986cef\nX-Powered-By=PHP/5.5.9-1ubuntu4.14\nContent-Length=4188']</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>['https://juice-shop-388277804329.us-west1.run.app/passwords/wp-config.bak', 'https://juice-shop-388277804329.us-west1.run.app/user_new.php', 'https://juice-shop-388277804329.us-west1.run.app/soap/class.nusoap_base.php', 'https://juice-shop-388277804329.us-west1.run.app/soap/class.wsdlcache.php', 'https://juice-shop-388277804329.us-west1.run.app/passwords/web.config.bak', 'https://juice-shop-388277804329.us-west1.run.app/soap/', 'https://juice-shop-388277804329.us-west1.run.app/passwords/', 'https://juice-shop-388277804329.us-west1.run.app/db/', 'https://juice-shop-388277804329.us-west1.run.app/info_install.php']</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="M64" t="inlineStr"/>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L64" t="n">
+        <v>98527</v>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"publication_date": "2019-04-02T00:00:00+00:00",
+"modification_date": "2024-03-25T00:00:00+00:00",
+"family": "HTTP Security Header",
+"severity": "Info",
+"plugin_id": 98527}
+</t>
+        </is>
+      </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>['CWE -', 'WASC -', 'OWASP -', 'CVE -', 'BID -']</t>
+          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/passwords/wp-config.bak', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Referrer-Policy headers or body meta tags were found on https://juice-shop-388277804329.us-west1.run.app/passwords /wp-config.bak', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'application/x-trash'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/user_new.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Referrer-Policy headers or body meta tags were found on https://juice-shop-388277804329.us-west1.run.app/user_new.php', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/soap/class.nusoap_base.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Referrer-Policy headers or body meta tags were found on https://juice-shop-388277804329.us-west1.run.app/soap/class. nusoap_base.php', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/soap/class.wsdlcache.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Referrer-Policy headers or body meta tags were found on https://juice-shop-388277804329.us-west1.run.app/soap/class. wsdlcache.php', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/passwords/web.config.bak', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Referrer-Policy headers or body meta tags were found on https://juice-shop-388277804329.us-west1.run.app/passwords /web.config.bak', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'application/x-trash'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/soap/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Referrer-Policy headers or body meta tags were found on https://juice-shop-388277804329.us-west1.run.app/soap/', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/passwords/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Referrer-Policy headers or body meta tags were found on https://juice-shop-388277804329.us-west1.run.app/passwords/', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/db/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Referrer-Policy headers or body meta tags were found on https://juice-shop-388277804329.us-west1.run.app/db/', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/info_install.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Referrer-Policy headers or body meta tags were found on https://juice-shop-388277804329.us-west1.run.app /info_install.php', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/soap/class.soap_fault.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Referrer-Policy headers or body meta tags were found on https://juice-shop-388277804329.us-west1.run.app/soap/class. soap_fault.php', 'request_method': 'GET', 'http_status_code': 500, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/training_install.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Referrer-Policy headers or body meta tags were found on https://juice-shop-388277804329.us-west1.run.app /training_install.php', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/soap/nusoap.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Referrer-Policy headers or body meta tags were found on https://juice-shop-388277804329.us-west1.run.app/soap/nusoap. php', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/passwords/heroes.xml', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Referrer-Policy headers or body meta tags were found on https://juice-shop-388277804329.us-west1.run.app/passwords /heroes.xml', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/images/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Referrer-Policy headers or body meta tags were found on https://juice-shop-388277804329.us-west1.run.app/images/', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/login.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Referrer-Policy headers or body meta tags were found on https://juice-shop-388277804329.us-west1.run.app/login.php', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/training.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Referrer-Policy headers or body meta tags were found on https://juice-shop-388277804329.us-west1.run.app/training.php', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/js/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Referrer-Policy headers or body meta tags were found on https://juice-shop-388277804329.us-west1.run.app/js/', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/info.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Referrer-Policy headers or body meta tags were found on https://juice-shop-388277804329.us-west1.run.app/info.php', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/phpinfo.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Referrer-Policy headers or body meta tags were found on https://juice-shop-388277804329.us-west1.run.app/phpinfo.php', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/db/bwapp.sqlite', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Referrer-Policy headers or body meta tags were found on https://juice-shop-388277804329.us-west1.run.app/db/bwapp. sqlite', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/documents/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Referrer-Policy headers or body meta tags were found on https://juice-shop-388277804329.us-west1.run.app/documents/', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Referrer-Policy headers or body meta tags were found on https://juice-shop-388277804329.us-west1.run.app/apps/', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/install.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Referrer-Policy headers or body meta tags were found on https://juice-shop-388277804329.us-west1.run.app/install.php', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/movie_search', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Referrer-Policy headers or body meta tags were found on https://juice-shop-388277804329.us-west1.run.app/apps /movie_search', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/stylesheets/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Referrer-Policy headers or body meta tags were found on https://juice-shop-388277804329.us-west1.run.app/stylesheets/', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="P64" t="n">
-        <v>98527</v>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>[""Configure Referrer Policy on your website by adding 'Referrer-Policy' HTTP header or meta tag referrer in HTML.""]</t>
-        </is>
-      </c>
-      <c r="R64" t="inlineStr"/>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -6022,12 +6028,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[""The remote host contains a file named 'robots.txt' that is intended to prevent web 'robots' from visiting certain directories in a website for maintenance or indexing purposes. A malicious user may also be able to use the contents of this file to learn of sensitive documents or directories on the affected site and either retrieve them directly or target them for other attacks.""]</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>[""The remote host contains a file named 'robots.txt' that is intended to prevent web 'robots' from visiting certain directories in a website for maintenance or indexing purposes. A malicious user may also be able to use the contents of this file to learn of sensitive documents or directories on the affected site and either retrieve them directly or target them for other attacks.""]</t>
+          <t>[""Review the contents of the site's robots.txt file, use Robots META tags instead of entries in the robots.txt file, and/or adjust the web server's access controls to limit access to sensitive material.""]</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -6035,69 +6041,66 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
-          <t>['REQUEST MADE\nGET /robots.txt HTTP/2\nREQUEST HEADERS\nHost: juice-shop-388277804329.us-west1.run.app\nAccept-Encoding: gzip, deflate, br\nUser-Agent: Mozilla/5.0 (X11; Linux x86_64) AppleWebKit/537.36 (KHTML, like Gecko) Chrome/124.0.6367.207 Safari/537.36\nAccept: */*\nAccept-Language: en-US,en;q=0.5\nRESPONSE HEADERS\nHTTP/2 200\nlast-modified: Wed, 13 Nov 2024 02:15:28 GMT\netag: ""a7-626c1e84a7000-gzip""\naccept-ranges: bytes\nvary: Accept-Encoding\ncontent-type: text/plain\ncontent-encoding: gzip\nx-cloud-trace-context: 254908cf9b3dd329fb06f688b5d60e42\ndate: Tue, 19 Nov 2024 00:11:23 GMT\nserver: Google Frontend\ncontent-length: 102\nalt-svc: h3="":443""; ma=2592000,h3-29="":443""; ma=2592000']</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>['https://juice-shop-388277804329.us-west1.run.app/robots.txt']</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="M65" t="inlineStr"/>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L65" t="n">
+        <v>98705</v>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"publication_date": "2019-09-19T00:00:00+00:00",
+"modification_date": "2020-12-17T00:00:00+00:00",
+"family": "Web Servers",
+"severity": "Info",
+"plugin_id": 98705}
+</t>
+        </is>
+      </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>['CWE -', 'WASC -', 'OWASP -', 'CVE -', 'BID -']</t>
+          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/robots.txt', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': "A robots.txt file was detected at 'https://juice-shop-388277804329.us-west1.run.app/robots.txt'.", 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/plain'}]</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="P65" t="n">
-        <v>98705</v>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>[""Review the contents of the site's robots.txt file, use Robots META tags instead of entries in the robots.txt file, and/or adjust the web server's access controls to limit access to sensitive material.""]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/robots.txt', 'input_type': 'file', 'input_name': 'robots.txt', 'payload': None, 'proof': 'A robots.txt file was detected at https://juice-shop-388277804329.us-west1.run.app/robots.txt', 'output': 'Robots.txt file accessible on target application', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/plain'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -6109,12 +6112,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['This plugin displays information about the X.509 certificate extracted from the HTTPS connection.']</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>['This plugin displays information about the X.509 certificate extracted from the HTTPS connection.']</t>
+          <t>['-']</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -6122,69 +6125,66 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
-          <t>['Certificate 1\n--------------\nCommon Name: *.a.run.app\nAlternative Names: *.a.run.app run.app *.africa-south1.run.app *.asia-east1.run.app *.asia-east2.run.app *.asia-northeast1.run.app *.asia-northeast2.run.app *.asia-northeast3.run.app *.asia-south1.run.app *.asia-south2.run.app *.asia-southeast1.run.app *.asia-southeast2.run.app *.australia-southeast1.run.app *.australia-southeast2.run.app *.europe-central2.run.app *.europe-north1.run.app *.europe-north2.run.app *.europe-southwest1.run.app *.europe-west1.run.app *.europe-west10.run.app *.europe-west12.run.app *.europe-west2.run.app *.europe-west3.run.app *.europe-west4.run.app *.europe-west5.run.app *.europe-west6.run.app *.europe-west8.run.app *.europe-west9.run.app *.me-central1.run.app *.me-central2.run.app *.me-west1.run.app *.northamerica-northeast1.run.app *.northamerica-northeast2.run.app *.northamerica-south1.run.app *.southamerica-east1.run.app *.southamerica-west1.run.app *.us-central1.run.app *.us-central2.run.app *.us-east1.run.app *.us-east4.run.app *.us-east5.run.app *.us-east7.run.app *.us-south1.run.app *.us-west1.run.app *.us-west2.run.app *.us-west3.run.app *.us-west4.run.app *.us-west8.run.app\nIssuer: Google Trust Services\nValid from: 2024-10-21 08:']</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>['https://juice-shop-388277804329.us-west1.run.app/#/']</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="M66" t="inlineStr"/>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L66" t="n">
+        <v>112491</v>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"publication_date": "2018-10-03T00:00:00+00:00",
+"modification_date": "2023-05-05T00:00:00+00:00",
+"family": "SSL/TLS",
+"severity": "Info",
+"plugin_id": 112491}
+</t>
+        </is>
+      </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>['CWE -', 'WASC -', 'OWASP -', 'CVE -', 'BID -']</t>
+          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/#/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Certificate 1 -------------- Common Name: *.a.run.app Alternative Names: *.a.run.app run.app *.africa-south1.run.app *.asia-east1.run.app *.asia-east2.run.app *.asia\ufffenortheast1.run.app *.asia-northeast2.run.app *.asia-northeast3.run.app *.asia-south1.run.app *.asia-south2.run.app *. asia-southeast1.run.app *.asia-southeast2.run.app *.australia-southeast1.run.app *.australia-southeast2.run.app *. europe-central2.run.app *.europe-north1.run.app *.europe-north2.run.app *.europe-southwest1.run.app *.europe-west1.run. app *.europe-west10.run.app *.europe-west12.run.app *.europe-west2.run.app *.europe-west3.run.app *.europe-west4.run. app *.europe-west5.run.app *.europe-west6.run.app *.europe-west8.run.app *.europe-west9.run.app *.me-central1.run.app *. me-central2.run.app *.me-west1.run.app *.northamerica-northeast1.run.app *.northamerica-northeast2.run.app *. northamerica-south1.run.app *.southamerica-east1.run.app *.southamerica-west1.run.app *.us-central1.run.app *.us\ufffecentral2.run.app *.us-east1.run.app *.us-east4.run.app *.us-east5.run.app *.us-east7.run.app *.us-south1.run.app *.us\ufffewest1.run.app *.us-west2.run.app *.us-west3.run.app *.us-west4.run.app *.us-west8.run.app Issuer: Google Trust Services Valid from: 2024-10-21 08:36:39 UTC Valid until: 2025-01-13 08:36:38 UTC (expires in 1 month, 3 weeks, 3 days) Validity Period: 83 days Key: RSA 256-bit Signature: sha256WithRSAEncryption Certificate 2 -------------- Common Name: wr Issuer: Google Trust Services LLC Valid from: 2023-12-13 09:00:00 UTC Valid until: 2029-02-20 14:00:00 UTC (expires in 4 years, 3 months, 2 days) Validity Period: 1896 days Key: RSA 2048-bit Signature: sha256WithRSAEncryption Certificate 3 -------------- Common Name: gts root r Issuer: GlobalSign nv Valid from: 2020-06-19 00:00:42 UTC Valid until: 2028-01-28 00:00:42 UTC (expires in 3 years, 2 months, 1 week, 1 day) Validity Period: 2779 days Key: RSA 4096-bit Signature: sha256WithRSAEncryption', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="P66" t="n">
-        <v>112491</v>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>['-']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/#/', 'input_type': 'certificate', 'input_name': None, 'payload': None, 'proof': 'Certificate 1: CN=*.a.run.app, Issuer=Google Trust Services, Valid 2024-10-21 to 2025-01-13; Certificate 2: CN=wr, Issuer=Google Trust Services LLC, Valid 2023-12-13 to 2029-02-20; Certificate 3: CN=gts root r, Issuer=GlobalSign nv, Valid 2020-06-19 to 2028-01-28', 'output': 'Scanner identified 3 SSL/TLS certificates in use by the target application.', 'request_method': None, 'http_status_code': None, 'http_protocol': 'HTTPS', 'response_content_type': None}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -6196,12 +6196,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[""The HTTP 'X-XSS-Protection' response header is a feature of old browsers that allows websites to control their XSS auditors.\n\nThe server is not configured to return a 'X-XSS-Protection' header which means that any pages on this website could be at risk of a Cross-Site Scripting (XSS) attack. This URL is flagged as a specific example.\n\nHowever, this header is deprecated by modern browsers, if legacy browsers support is not needed, it is recommended to use Content-Security-Policy without allowing unsafe-inline scripts instead.""]</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>[""The HTTP 'X-XSS-Protection' response header is a feature of old browsers that allows websites to control their XSS auditors.\n\nThe server is not configured to return a 'X-XSS-Protection' header which means that any pages on this website could be at risk of a Cross-Site Scripting (XSS) attack. This URL is flagged as a specific example.\n\nHowever, this header is deprecated by modern browsers, if legacy browsers support is not needed, it is recommended to use Content-Security-Policy without allowing unsafe-inline scripts instead.""]</t>
+          <t>[""Configure your web server to include an 'X-XSS-Protection' header with a value of '1; mode=block' on all pages.""]</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -6209,65 +6209,66 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
-          <t>['GET https://juice-shop-388277804329.us-west1.run.app/documents/ | RESPONSE HEADERS: HTTP/1.1 200 OK ...', 'GET https://juice-shop-388277804329.us-west1.run.app/phpinfo.php | RESPONSE HEADERS: HTTP/1.1 200 OK ...', 'GET /soap/class.soap_fault.php HTTP/2 | RESPONSE HEADERS: HTTP/2 500 ...', 'GET https://juice-shop-388277804329.us-west1.run.app/soap/class.wsdlcache.php | RESPONSE HEADERS: HTTP/1.1 200 OK ...', 'GET https://juice-shop-388277804329.us-west1.run.app/images/ | RESPONSE HEADERS: HTTP/1.1 200 OK ...', 'GET /passwords/wp-config.bak HTTP/2 | RESPONSE HEADERS: HTTP/2 200 ...', 'GET https://juice-shop-388277804329.us-west1.run.app/db/ | RESPONSE HEADERS: HTTP/1.1 200 OK ...', 'GET https://juice-shop-388277804329.us-west1.run.app/apps/ | RESPONSE HEADERS: HTTP/1.1 200 OK ...', 'GET /passwords/web.config.bak HTTP/2 | RESPONSE HEADERS: HTTP/2 200 ...']</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>['https://juice-shop-388277804329.us-west1.run.app/documents/', 'https://juice-shop-388277804329.us-west1.run.app/phpinfo.php', 'https://juice-shop-388277804329.us-west1.run.app/soap/class.soap_fault.php', 'https://juice-shop-388277804329.us-west1.run.app/soap/class.wsdlcache.php', 'https://juice-shop-388277804329.us-west1.run.app/images/', 'https://juice-shop-388277804329.us-west1.run.app/passwords/wp-config.bak', 'https://juice-shop-388277804329.us-west1.run.app/db/', 'https://juice-shop-388277804329.us-west1.run.app/apps/', 'https://juice-shop-388277804329.us-west1.run.app/passwords/web.config.bak']</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="M67" t="inlineStr"/>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L67" t="n">
+        <v>112526</v>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"publication_date": "2018-11-27T00:00:00+00:00",
+"modification_date": "2024-03-25T00:00:00+00:00",
+"family": "HTTP Security Header",
+"severity": "Info",
+"plugin_id": 112526}
+</t>
+        </is>
+      </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>['CWE -', 'WASC -', 'OWASP -', 'CVE -', 'BID -']</t>
+          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/documents/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner detected the lack of X-XSS-Protection header in the target application response.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/phpinfo.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner detected the lack of X-XSS-Protection header in the target application response.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/soap/class.soap_fault.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner detected the lack of X-XSS-Protection header in the target application response.', 'request_method': 'GET', 'http_status_code': 500, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/soap/class.wsdlcache.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner detected the lack of X-XSS-Protection header in the target application response.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/images/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner detected the lack of X-XSS-Protection header in the target application response.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/passwords/wp-config.bak', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner detected the lack of X-XSS-Protection header in the target application response.', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'application/x-trash'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/db/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner detected the lack of X-XSS-Protection header in the target application response.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner detected the lack of X-XSS-Protection header in the target application response.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/passwords/web.config.bak', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner detected the lack of X-XSS-Protection header in the target application response.', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'application/x-trash'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/stylesheets/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner detected the lack of X-XSS-Protection header in the target application response.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/db/bwapp.sqlite', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner detected the lack of X-XSS-Protection header in the target application response.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/training.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner detected the lack of X-XSS-Protection header in the target application response.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/soap/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner detected the lack of X-XSS-Protection header in the target application response.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/passwords/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner detected the lack of X-XSS-Protection header in the target application response.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/js/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner detected the lack of X-XSS-Protection header in the target application response.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/login.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner detected the lack of X-XSS-Protection header in the target application response.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/user_new.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner detected the lack of X-XSS-Protection header in the target application response.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/soap/nusoap.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner detected the lack of X-XSS-Protection header in the target application response.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/soap/class.nusoap_base.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner detected the lack of X-XSS-Protection header in the target application response.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/movie_search', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner detected the lack of X-XSS-Protection header in the target application response.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/training_install.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner detected the lack of X-XSS-Protection header in the target application response.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/info_install.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner detected the lack of X-XSS-Protection header in the target application response.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/info.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner detected the lack of X-XSS-Protection header in the target application response.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/install.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner detected the lack of X-XSS-Protection header in the target application response.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/passwords/heroes.xml', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner detected the lack of X-XSS-Protection header in the target application response.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="P67" t="n">
-        <v>112526</v>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>[""Configure your web server to include an 'X-XSS-Protection' header with a value of '1; mode=block' on all pages.""]</t>
-        </is>
-      </c>
-      <c r="R67" t="inlineStr"/>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -6279,12 +6280,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['This plugin displays information about the SSL/TLS versions supported by remote server for HTTPS connection.']</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>['This plugin displays information about the SSL/TLS versions supported by remote server for HTTPS connection.']</t>
+          <t>['-']</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -6292,59 +6293,56 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
-          <t>['Protocol Supported\n---------------------\nSSL 2.0 No\nSSL 3.0 No\nTLS 1.0 No\nTLS 1.1 No\nTLS 1.2 Yes\nTLS 1.3 Yes']</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>['https://juice-shop-388277804329.us-west1.run.app/#/']</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="M68" t="inlineStr"/>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L68" t="n">
+        <v>112530</v>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"publication_date": "2018-10-03T00:00:00+00:00",
+"modification_date": "2020-10-02T00:00:00+00:00",
+"family": "SSL/TLS",
+"severity": "Info",
+"plugin_id": 112530}
+</t>
+        </is>
+      </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>['CWE -', 'WASC -', 'OWASP -', 'CVE -', 'BID -']</t>
+          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/#/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Protocol Supported --------------------- SSL 2.0 No SSL 3.0 No TLS 1.0 No TLS 1.1 No TLS 1.2 Yes TLS 1.3 Yes', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="P68" t="n">
-        <v>112530</v>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>['-']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
@@ -6354,7 +6352,7 @@
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -6366,12 +6364,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['The remote server is not configured with a SSL/TLS cipher suite preference list, making the cipher suite selection during the \nnegotiation use the ordered list from the client.']</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>['The remote server is not configured with a SSL/TLS cipher suite preference list, making the cipher suite selection during the \nnegotiation use the ordered list from the client.']</t>
+          <t>['-']</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -6379,69 +6377,66 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
-          <t>['The scanner detected that the remote host is not configured with a cipher suite preference for the following protocol\n(s) : TLS v1.2, TLS v1.3']</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>['https://juice-shop-388277804329.us-west1.run.app/#/']</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="M69" t="inlineStr"/>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L69" t="n">
+        <v>112599</v>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"publication_date": "2020-09-24T00:00:00+00:00",
+"modification_date": "2021-08-25T00:00:00+00:00",
+"family": "SSL/TLS",
+"severity": "Info",
+"plugin_id": 112599}
+</t>
+        </is>
+      </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>['CWE -', 'WASC -', 'OWASP -', 'CVE -', 'BID -']</t>
+          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/#/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner detected that the remote host is not configured with a cipher suite preference for the following protocol (s) : TLS v1.2, TLS v1.3', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="P69" t="n">
-        <v>112599</v>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>['-']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/#/', 'input_type': 'cipher_suite', 'input_name': None, 'payload': None, 'proof': 'Scanner detected no cipher suite preference configured for TLS v1.2 and TLS v1.3', 'output': 'The remote host does not enforce a cipher suite preference for TLS 1.2 and TLS 1.3.', 'request_method': None, 'http_status_code': None, 'http_protocol': 'HTTPS', 'response_content_type': None}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -6453,12 +6448,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['The Hypertext Transfer Protocol (HTTP) is the underlying protocol of the World Wide Web. Since its first release, HTTP has \nevolved to support modern web usages and currently exists in three versions: \n- HTTP/1.0 \n- HTTP/1.1 \n- HTTP/2 \nThe scanner identified the supported versions of the HTTP protocol on the target web application.']</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>['The Hypertext Transfer Protocol (HTTP) is the underlying protocol of the World Wide Web. Since its first release, HTTP has \nevolved to support modern web usages and currently exists in three versions: \n- HTTP/1.0 \n- HTTP/1.1 \n- HTTP/2 \nThe scanner identified the supported versions of the HTTP protocol on the target web application.']</t>
+          <t>['-']</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -6466,69 +6461,66 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
-          <t>['The scanner detected the following HTTP versions on the target application : \n- HTTP/1.0 \n- HTTP/1.1 \n- HTTP/2 \nThe list of requests and responses observed is provided in attachment.']</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>['https://juice-shop-388277804329.us-west1.run.app/#/']</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="M70" t="inlineStr"/>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L70" t="n">
+        <v>112613</v>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"publication_date": "2020-10-13T00:00:00+00:00",
+"modification_date": "2023-01-17T00:00:00+00:00",
+"family": "Web Applications",
+"severity": "Info",
+"plugin_id": 112613}
+</t>
+        </is>
+      </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>['CWE -', 'WASC -', 'OWASP -', 'CVE -', 'BID -']</t>
+          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/#/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner detected the following HTTP versions on the target application : - HTTP/1.0 - HTTP/1.1 - HTTP/2 The list of requests and responses observed is provided in attachment.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="P70" t="n">
-        <v>112613</v>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>['-']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/#/', 'input_type': 'http_version', 'input_name': None, 'payload': None, 'proof': 'Scanner detected HTTP/1.0, HTTP/1.1, and HTTP/2 supported by the target application', 'output': 'The target application supports multiple HTTP versions: 1.0, 1.1, and 2.0. Full request/response details are available in attachment.', 'request_method': None, 'http_status_code': None, 'http_protocol': 'HTTPS', 'response_content_type': None}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -6540,12 +6532,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['A Security.txt file has not been detected on the target. \n\nWhen security risks in web services are discovered by independent security researchers, this file defines the channels to \ndisclose them properly &amp; enables 3rd party researchers to disclose issues securely in a manner defined by the organization.\nOrganizations should consider creating a security.txt file containing contact and other information in the defined format and \nplace it under the .well-known directory of the server.', ""No or a malformed security.txt was found at 'https://juice-shop-388277804329.us-west1.run.app/.well-known/security.txt'.""]</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>['A Security.txt file has not been detected on the target. \n\nWhen security risks in web services are discovered by independent security researchers, this file defines the channels to \ndisclose them properly &amp; enables 3rd party researchers to disclose issues securely in a manner defined by the organization.\nOrganizations should consider creating a security.txt file containing contact and other information in the defined format and \nplace it under the .well-known directory of the server.', ""No or a malformed security.txt was found at 'https://juice-shop-388277804329.us-west1.run.app/.well-known/security.txt'.""]</t>
+          <t>['-']</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -6553,69 +6545,66 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
-          <t>['REQUEST MADE\nGET /.well-known/security.txt HTTP/2\nREQUEST HEADERS\nHost: juice-shop-388277804329.us-west1.run.app\nAccept-Encoding: gzip, deflate, br\nUser-Agent: Mozilla/5.0 (X11; Linux x86_64) AppleWebKit/537.36 (KHTML, like Gecko) Chrome/124.0.6367.207 Safari/537.36\nAccept: */*\nAccept-Language: en-US,en;q=0.5\nRESPONSE HEADERS\nHTTP/2 404\ncontent-type: text/html; charset=iso-8859-1\nx-cloud-trace-context: 38b4de5541ac2e0d3c96ad261354853f\ndate: Tue, 19 Nov 2024 00:11:23 GMT\nserver: Google Frontend\ncontent-length: 327\nalt-svc: h3="":443""; ma=2592000,h3-29="":443""; ma=2592000']</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>['https://juice-shop-388277804329.us-west1.run.app/.well-known/security.txt']</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="M71" t="inlineStr"/>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L71" t="n">
+        <v>112723</v>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"publication_date": "2021-03-17T00:00:00+00:00",
+"modification_date": "2021-03-17T00:00:00+00:00",
+"family": "Web Servers",
+"severity": "Info",
+"plugin_id": 112723}
+</t>
+        </is>
+      </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>['CWE -', 'WASC -', 'OWASP -', 'CVE -', 'BID -']</t>
+          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/.well-known/security.txt', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': "No or a malformed security.txt was found at 'https://juice-shop-388277804329.us-west1.run.app/.well-known/security.txt'.", 'request_method': 'GET', 'http_status_code': 404, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}]</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="P71" t="n">
-        <v>112723</v>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>['-']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/.well-known/security.txt', 'input_type': 'file', 'input_name': 'security.txt', 'payload': None, 'proof': 'No or malformed security.txt file detected at https://juice-shop-388277804329.us-west1.run.app/.well-known/security.txt', 'output': 'The scanner did not find a valid security.txt file on the target application.', 'request_method': 'GET', 'http_status_code': 404, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html; charset=iso-8859-1'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -6627,12 +6616,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['The remote server presents an SSL/TLS certificate with wildcard entries. The use of a wildcard character in a entry permits a certificate to cover a number of subdomains of a domain.']</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>['The remote server presents an SSL/TLS certificate with wildcard entries. The use of a wildcard character in a entry permits a certificate to cover a number of subdomains of a domain.']</t>
+          <t>['-']</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -6640,69 +6629,66 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
-          <t>['A wildcard symbol (*) has been detected in the following certificate entries:\nCertificate Common Name: *.a.run.app\nCertificate Subject Alternative Names:\n- *.a.run.app\n- *.africa-south1.run.app\n- *.asia-east1.run.app\n- *.asia-east2.run.app\n- *.asia-northeast1.run.app\n- *.asia-northeast2.run.app\n- *.asia-northeast3.run.app\n- *.asia-south1.run.app\n- *.asia-south2.run.app\n- *.asia-southeast1.run.app\n- *.asia-southeast2.run.app\n- *.australia-southeast1.run.app\n- *.australia-southeast2.run.app\n- *.europe-central2.run.app\n- *.europe-north1.run.app\n- *.europe-north2.run.app\n- *.europe-southwest1.run.app\n- *.europe-west1.run.app\n- *.europe-west10.run.app\n- *.europe-west12.run.app\n- *.europe-west2.run.app\n- *.europe-west3.run.app\n- *.europe-west4.run.app\n- *.europe-west5.run.app\n- *.europe-west6.run.app\n- *.europe-west8.run.app\n- *.europe-west9.run.app\n- *.me-central1.run.app\n- *.me-central2.run.app\n- *.me-west1.run.app\n- *.northamerica-northeast1.run.app\n- *.northamerica-northeast2.run.app\n- *.northamerica-south1.run.app\n- *.southamerica-east1.run.app\n- *.southamerica-west1.run.app\n- *.us-central1.run.app\n- *.us-central2.run.app\n- *.us-east1.run.app\n- *.us-east4.run.app\n- *.us-east5.run.app\n- *.us-east7.run.app\n- *.us-south1.run.app\n- *.us-west1.run.app\n- *.us-west2.run.app\n- *.us-west3.run.app\n- *.us-west4.run.app\n- *.us-west8.run.app']</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>['https://juice-shop-388277804329.us-west1.run.app/#/']</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="M72" t="inlineStr"/>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L72" t="n">
+        <v>113045</v>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"publication_date": "2021-11-10T00:00:00+00:00",
+"modification_date": "2021-11-10T00:00:00+00:00",
+"family": "SSL/TLS",
+"severity": "Info",
+"plugin_id": 113045}
+</t>
+        </is>
+      </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/#/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'A wildcard symbol (*) has been detected in the following certificate entries: Certificate Common Name: *.a.run.app Certificate Subject Alternative Names: - *.a.run.app - *.africa-south1.run.app - *.asia-east1.run.app - *.asia-east2.run.app - *.asia-northeast1.run.app - *.asia-northeast2.run.app - *.asia-northeast3.run.app - *.asia-south1.run.app - *.asia-south2.run.app - *.asia-southeast1.run.app - *.asia-southeast2.run.app - *.australia-southeast1.run.app - *.australia-southeast2.run.app - *.europe-central2.run.app - *.europe-north1.run.app - *.europe-north2.run.app - *.europe-southwest1.run.app - *.europe-west1.run.app - *.europe-west10.run.app - *.europe-west12.run.app - *.europe-west2.run.app - *.europe-west3.run.app - *.europe-west4.run.app - *.europe-west5.run.app - *.europe-west6.run.app - *.europe-west8.run.app - *.europe-west9.run.app - *.me-central1.run.app - *.me-central2.run.app - *.me-west1.run.app - *.northamerica-northeast1.run.app - *.northamerica-northeast2.run.app - *.northamerica-south1.run.app - *.southamerica-east1.run.app - *.southamerica-west1.run.app - *.us-central1.run.app - *.us-central2.run.app - *.us-east1.run.app - *.us-east4.run.app - *.us-east5.run.app - *.us-east7.run.app - *.us-south1.run.app - *.us-west1.run.app - *.us-west2.run.app - *.us-west3.run.app - *.us-west4.run.app - *.us-west8.run.app', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="P72" t="n">
-        <v>113045</v>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>['-']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/#/', 'input_type': 'certificate_wildcard', 'input_name': None, 'payload': None, 'proof': 'Wildcard symbol (*) detected in certificate entries: CN=*.a.run.app and multiple SAN entries (*.region.run.app)', 'output': 'The scanner identified wildcard usage in the SSL/TLS certificate Common Name and Subject Alternative Names.', 'request_method': None, 'http_status_code': None, 'http_protocol': 'HTTPS', 'response_content_type': None}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -6714,12 +6700,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['This finding provides information to assist in scan performance tuning.']</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>['This finding provides information to assist in scan performance tuning.']</t>
+          <t>['-']</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -6727,69 +6713,66 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
-          <t>['Three attachments are included in this finding to assist in performance tuning of your scan:\n-pages_telemetry.csv: Scan statistics organized by page\n-plugins_telemetry.csv: Scan statistics organized by plugin\n-time_telemetry.csv: Chronological scan statistics']</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>['https://juice-shop-388277804329.us-west1.run.app/#/']</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="M73" t="inlineStr"/>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L73" t="n">
+        <v>113393</v>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"publication_date": "2022-10-17T00:00:00+00:00",
+"modification_date": "2024-10-03T00:00:00+00:00",
+"family": "General",
+"severity": "Info",
+"plugin_id": 113393}
+</t>
+        </is>
+      </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/#/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Three attachments are included in this finding to assist in performance tuning of your scan: -pages_telemetry.csv: Scan statistics organized by page -plugins_telemetry.csv: Scan statistics organized by plugin -time_telemetry.csv: Chronological scan statistics', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="P73" t="n">
-        <v>113393</v>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>['-']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/#/', 'input_type': 'telemetry', 'input_name': None, 'payload': None, 'proof': 'Three attachments included: pages_telemetry.csv, plugins_telemetry.csv, time_telemetry.csv', 'output': 'Scanner provided telemetry attachments to assist in performance tuning of the scan.', 'request_method': None, 'http_status_code': None, 'http_protocol': 'HTTPS', 'response_content_type': None}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -6801,12 +6784,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['HTML comments are often used by developers to include information related to the application inline, which are ignored by a clients browser during rendering. These comments may include sensitive information such as SQL queries, credentials or internal IP for example.']</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>['HTML comments are often used by developers to include information related to the application inline, which are ignored by a clients browser during rendering. These comments may include sensitive information such as SQL queries, credentials or internal IP for example.']</t>
+          <t>['Review the HTML comments identified on the page for any information leakage, and remove any sensitive information identified.']</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -6814,65 +6797,66 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
-          <t>['2 HTML comments have been detected in the application HTTP response. Please see the attachment for further details.\nREQUEST MADE\nGET https://juice-shop-388277804329.us-west1.run.app/install.php?install=yes\nREQUEST HEADERS\nAccept=*/*\nAccept-Encoding=gzip, deflate, br\nAccept-Language=en-US,en;q=0.5\nCookie=PHPSESSID=711vt1tpgrucudl1kaq9t074f5\nPriority=u=0, i\nSec-Ch-Ua=""Chromium"";v=""124"", ""HeadlessChrome"";v=""124"", ""Not-A.Brand"";v=""99""\nSec-Ch-Ua-Mobile=?0\nSec-Ch-Ua-Platform=""Linux""\nSec-Fetch-Dest=document\nSec-Fetch-Mode=navigate\nSec-Fetch-Site=none\nSec-Fetch-User=?1\nUpgrade-Insecure-Requests=1\nUser-Agent=Mozilla/5.0 (X11; Linux x86_64) AppleWebKit/537.36 (KHTML, like Gecko) Chrome/124.0.6367.207 Safari/537.36\nRESPONSE HEADERS\nHTTP/1.1 200 OK\nAlt-Svc=h3="":443""; ma=2592000,h3-29="":443""; ma=2592000\nContent-Encoding=gzip\nContent-Type=text/html\nDate=Tue, 19 Nov 2024 02:39:05 GMT\nServer=Google Frontend\nVary=Accept-Encoding\nX-Cloud-Trace-Context=b8eba21cccffcc35373450a248516ba1\nX-Powered-By=PHP/5.5.9-1ubuntu4.14\nContent-Length=3085', '2 HTML comments have been detected in the application HTTP response. Please see the attachment for further details.\nREQUEST MADE\nGET https://juice-shop-388277804329.us-west1.run.app/db/bwapp.sqlite\nREQUEST HEADERS\nAccept=*/*\nAccept-Encoding=gzip, deflate, br\nAccept-Language=en-US,en;q=0.5\nCookie=PHPSESSID=711vt1tpgrucudl1kaq9t074f5\nPriority=u=0, i\nSec-Ch-Ua=""Chromium"";v=""124"", ""HeadlessChrome"";v=""124"", ""Not-A.Brand"";v=""99""\nSec-Ch-Ua-Mobile=?0\nSec-Ch-Ua-Platform=""Linux""\nSec-Fetch-Dest=document\nSec-Fetch-Mode=navigate\nSec-Fetch-Site=none\nSec-Fetch-User=?1\nUpgrade-Insecure-Requests=1\nUser-Agent=Mozilla/5.0 (X11; Linux x86_64) AppleWebKit/537.36 (KHTML, like Gecko) Chrome/124.0.6367.207 Safari/537.36\nRESPONSE HEADERS\nHTTP/1.1 200 OK\nAccept-Ranges=bytes\nAlt-Svc=h3="":443""; ma=2592000,h3-29="":443""; ma=2592000\nContent-Type=text/html\nDate=Tue, 19 Nov 2024 03:57:01 GMT\nEtag=""3000-626c1e84a7000""\nLast-Modified=Wed, 13 Nov 2024 02:15:28 GMT\nServer=Google Frontend\nX-Cloud-Trace-Context=2a74d2d814c14512fd8fac93e4bfc679\nContent-Length=12288', '2 HTML comments have been detected in the application HTTP response. Please see the attachment for further details.\nREQUEST MADE\nGET https://juice-shop-388277804329.us-west1.run.app/training_install.php\nREQUEST HEADERS\nAccept=*/*\nAccept-Encoding=gzip, deflate, br\nAccept-Language=en-US,en;q=0.5\nCookie=PHPSESSID=711vt1tpgrucudl1kaq9t074f5\nPriority=u=0, i\nSec-Ch-Ua=""Chromium"";v=""124"", ""HeadlessChrome"";v=""124"", ""Not-A.Brand"";v=""99""\nSec-Ch-Ua-Mobile=?0\nSec-Ch-Ua-Platform=""Linux""\nSec-Fetch-Dest=document\nSec-Fetch-Mode=navigate\nSec-Fetch-Site=none\nSec-Fetch-User=?1\nUpgrade-Insecure-Requests=1\nUser-Agent=Mozilla/5.0 (X11; Linux x86_64) AppleWebKit/537.36 (KHTML, like Gecko) Chrome/124.0.6367.207 Safari/537.36\nRESPONSE HEADERS\nHTTP/1.1 200 OK\nAlt-Svc=h3="":443""; ma=2592000,h3-29="":443""; ma=2592000\nContent-Encoding=gzip\nContent-Type=text/html\nDate=Tue, 19 Nov 2024 02:31:16 GMT\nServer=Google Frontend\nVary=Accept-Encoding\nX-Cloud-Trace-Context=dc248926d66de31d4ae1d4212ab637d0\nX-Powered-By=PHP/5.5.9-1ubuntu4.14\nContent-Length=4629', '2 HTML comments have been detected in the application HTTP response. Please see the attachment for further details.\nREQUEST MADE\nGET https://juice-shop-388277804329.us-west1.run.app/info_install.php\nREQUEST HEADERS\nAccept=*/*\nAccept-Encoding=gzip, deflate, br\nAccept-Language=en-US,en;q=0.5\nCookie=PHPSESSID=711vt1tpgrucudl1kaq9t074f5\nPriority=u=0, i\nSec-Ch-Ua=""Chromium"";v=""124"", ""HeadlessChrome"";v=""124"", ""Not-A.Brand"";v=""99""\nSec-Ch-Ua-Arch=""""\nSec-Ch-Ua-Bitness=""""\nSec-Ch-Ua-Full-Version-List=""Chromium"", ""HeadlessChrome"", ""Not-A.Brand"";v=""99.0.0.0""\nSec-Ch-Ua-Mobile=?0\nSec-Ch-Ua-Model=""""\nSec-Ch-Ua-Platform=""Linux""\nSec-Ch-Ua-Platform-Version=""""\nSec-Ch-Ua-Wow64=?0\nSec-Fetch-Dest=document\nSec-Fetch-Mode=navigate\nSec-Fetch-Site=none\nSec-Fetch-User=?1\nUpgrade-Insecure-Requests=1\nUser-Agent=Mozilla/5.0 (X11; Linux x86_64) AppleWebKit/537.36 (KHTML, like Gecko) Chrome/124.0.6367.207 Safari/537.36\nRESPONSE HEADERS\nHTTP/1.1 200 OK\nAlt-Svc=h3="":443""; ma=2592000,h3-29="":443""; ma=2592000\nContent-Encoding=gzip\nContent-Type=text/html\nDate=Tue, 19 Nov 2024 02:21:07 GMT\nServer=Google Frontend\nVary=Accept-Encoding\nX-Cloud-Trace-Context=3305fabc85563bee1adce5fca1986cef\nX-Powered-By=PHP/5.5.9-1ubuntu4.14\nContent-Length=4188', '2 HTML comments have been detected in the application HTTP response. Please see the attachment for further details.\nREQUEST MADE\nGET https://juice-shop-388277804329.us-west1.run.app/install.php\nREQUEST HEADERS\nAccept=*/*\nAccept-Encoding=gzip, deflate, br\nAccept-Language=en-US,en;q=0.5\nCookie=PHPSESSID=711vt1tpgrucudl1kaq9t074f5\nPriority=u=0, i\nSec-Ch-Ua=""Chromium"";v=""124"", ""HeadlessChrome"";v=""124"", ""Not-A.Brand"";v=""99""\nSec-Ch-Ua-Arch=""""\nSec-Ch-Ua-Bitness=""""\nSec-Ch-Ua-Full-Version-List=""Chromium"", ""HeadlessChrome"", ""Not-A.Brand"";v=""99.0.0.0""\nSec-Ch-Ua-Mobile=?0\nSec-Ch-Ua-Model=""""\nSec-Ch-Ua-Platform=""Linux""\nSec-Ch-Ua-Platform-Version=""""\nSec-Ch-Ua-Wow64=?0\nSec-Fetch-Dest=document\nSec-Fetch-Mode=navigate\nSec-Fetch-Site=none\nSec-Fetch-User=?1\nUpgrade-Insecure-Requests=1\nUser-Agent=Mozilla/5.0 (X11; Linux x86_64) AppleWebKit/537.36 (KHTML, like Gecko) Chrome/124.0.6367.207 Safari/537.36\nRESPONSE HEADERS\nHTTP/1.1 200 OK\nAlt-Svc=h3="":443""; ma=2592000,h3-29="":443""; ma=2592000\nContent-Encoding=gzip\nContent-Type=text/html\nDate=Tue, 19 Nov 2024 00:19:04 GMT\nServer=']</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>['https://juice-shop-388277804329.us-west1.run.app/install.php?install=yes', 'https://juice-shop-388277804329.us-west1.run.app/db/bwapp.sqlite', 'https://juice-shop-388277804329.us-west1.run.app/training_install.php', 'https://juice-shop-388277804329.us-west1.run.app/info_install.php', 'https://juice-shop-388277804329.us-west1.run.app/install.php']</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="M74" t="inlineStr"/>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L74" t="n">
+        <v>113897</v>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"publication_date": "2023-06-09T00:00:00+00:00",
+"modification_date": "2024-11-08T00:00:00+00:00",
+"family": "Data Exposure",
+"severity": "Info",
+"plugin_id": 113897}
+</t>
+        </is>
+      </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>['https://owasp.org/www-project-web-security-testing-guide/v42/4-Web_Application_Security_Testing/01-Information_Gathering/05-Review_Webpage_Content_for_Information_Leakage']</t>
+          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/install.php?install=yes', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': '2 HTML comments have been detected in the application HTTP response. Please see the attachment for further details.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/db/bwapp.sqlite', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': '2 HTML comments have been detected in the application HTTP response. Please see the attachment for further details.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/training_install.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': '2 HTML comments have been detected in the application HTTP response. Please see the attachment for further details.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/info_install.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': '2 HTML comments have been detected in the application HTTP response. Please see the attachment for further details.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/install.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': '2 HTML comments have been detected in the application HTTP response. Please see the attachment for further details.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/login.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': '2 HTML comments have been detected in the application HTTP response. Please see the attachment for further details.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/info.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': '2 HTML comments have been detected in the application HTTP response. Please see the attachment for further details.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/training.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': '2 HTML comments have been detected in the application HTTP response. Please see the attachment for further details.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/user_new.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': '2 HTML comments have been detected in the application HTTP response. Please see the attachment for further details.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="P74" t="n">
-        <v>113897</v>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>['Review the HTML comments identified on the page for any information leakage, and remove any sensitive information identified.']</t>
-        </is>
-      </c>
-      <c r="R74" t="inlineStr"/>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -6884,12 +6868,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['This is an informational plugin to inform that user data controlled input is reflected in the response.']</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>['This is an informational plugin to inform that user data controlled input is reflected in the response.']</t>
+          <t>['-']</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -6897,65 +6881,66 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="M75" t="inlineStr"/>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L75" t="n">
+        <v>114135</v>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"publication_date": "2023-12-18T00:00:00+00:00",
+"modification_date": "2023-12-18T00:00:00+00:00",
+"family": "Injection",
+"severity": "Info",
+"plugin_id": 114135}
+</t>
+        </is>
+      </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>['https://cheatsheetseries.owasp.org/cheatsheets/Input_Validation_Cheat_Sheet.html', 'CWE -', 'WASC -', 'OWASP -', 'CVE -', 'BID -']</t>
+          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/phpinfo.php', 'input_type': 'cookie', 'input_name': 'PHPSESSID', 'payload': 'was-tnb-hsv', 'proof': "Input reflected in the response body : 'was-tnb-hsv'.", 'output': 'The scanner was able to detect an input reflected in the response body.', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/phpinfo.php', 'input_type': 'header', 'input_name': 'Sec-Fetch-User', 'payload': 'was-tnb-hsv', 'proof': "Input reflected in the response body : 'was-tnb-hsv'.", 'output': 'The scanner was able to detect an input reflected in the response body.', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/phpinfo.php', 'input_type': 'header', 'input_name': 'Accept-Charset', 'payload': 'was-tnb-hsv', 'proof': "Input reflected in the response body : 'was-tnb-hsv'.", 'output': 'The scanner was able to detect an input reflected in the response body.', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/phpinfo.php', 'input_type': 'header', 'input_name': 'Sec-Ch-Ua', 'payload': 'was-tnb-hsv', 'proof': "Input reflected in the response body : 'was-tnb-hsv'.", 'output': 'The scanner was able to detect an input reflected in the response body.', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/phpinfo.php', 'input_type': 'header', 'input_name': 'Sec-Ch-Ua-Platform', 'payload': 'was-tnb-hsv', 'proof': "Input reflected in the response body : 'was-tnb-hsv'.", 'output': 'The scanner was able to detect an input reflected in the response body.', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/phpinfo.php', 'input_type': 'header', 'input_name': 'Accept-Encoding', 'payload': 'was-tnb-hsv', 'proof': "Input reflected in the response body : 'was-tnb-hsv'.", 'output': 'The scanner was able to detect an input reflected in the response body.', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/phpinfo.php', 'input_type': 'header', 'input_name': 'Sec-Fetch-Mode', 'payload': 'was-tnb-hsv', 'proof': "Input reflected in the response body : 'was-tnb-hsv'.", 'output': 'The scanner was able to detect an input reflected in the response body.', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/phpinfo.php', 'input_type': 'cookie', 'input_name': 'was-tnb-hsv', 'payload': 'was-tnb-hsv', 'proof': "Input reflected in the response body : 'was-tnb-hsv'.", 'output': 'The scanner was able to detect an input reflected in the response body.', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/phpinfo.php', 'input_type': 'header', 'input_name': 'Priority', 'payload': 'was-tnb-hsv', 'proof': "Input reflected in the response body : 'was-tnb-hsv'.", 'output': 'The scanner was able to detect an input reflected in the response body.', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/phpinfo.php', 'input_type': 'header', 'input_name': 'Sec-Fetch-Site', 'payload': 'was-tnb-hsv', 'proof': "Input reflected in the response body : 'was-tnb-hsv'.", 'output': 'The scanner was able to detect an input reflected in the response body.', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/phpinfo.php', 'input_type': 'header', 'input_name': 'Parameter name fuzzing', 'payload': 'was-tnb-hsv', 'proof': "Input reflected in the response body : 'was-tnb-hsv'.", 'output': 'The scanner was able to detect an input reflected in the response body.', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/phpinfo.php', 'input_type': 'header', 'input_name': 'Upgrade-Insecure-Requests', 'payload': 'was-tnb-hsv', 'proof': "Input reflected in the response body : 'was-tnb-hsv'.", 'output': 'The scanner was able to detect an input reflected in the response body.', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/phpinfo.php', 'input_type': 'header', 'input_name': 'Cookie', 'payload': 'was-tnb-hsv', 'proof': "Input reflected in the response body : 'was-tnb-hsv'.", 'output': 'The scanner was able to detect an input reflected in the response body.', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/phpinfo.php', 'input_type': 'header', 'input_name': 'Accept-Language', 'payload': 'was-tnb-hsv', 'proof': "Input reflected in the response body : 'was-tnb-hsv'.", 'output': 'The scanner was able to detect an input reflected in the response body.', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/phpinfo.php', 'input_type': 'header', 'input_name': 'Pragma', 'payload': 'was-tnb-hsv', 'proof': "Input reflected in the response body : 'was-tnb-hsv'.", 'output': 'The scanner was able to detect an input reflected in the response body.', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/phpinfo.php', 'input_type': 'header', 'input_name': 'Sec-Fetch-Dest', 'payload': 'was-tnb-hsv', 'proof': "Input reflected in the response body : 'was-tnb-hsv'.", 'output': 'The scanner was able to detect an input reflected in the response body.', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/phpinfo.php', 'input_type': 'header', 'input_name': 'Accept', 'payload': 'was-tnb-hsv', 'proof': "Input reflected in the response body : 'was-tnb-hsv'.", 'output': 'The scanner was able to detect an input reflected in the response body.', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/phpinfo.php', 'input_type': 'header', 'input_name': 'User-Agent', 'payload': 'was-tnb-hsv', 'proof': "Input reflected in the response body : 'was-tnb-hsv'.", 'output': 'The scanner was able to detect an input reflected in the response body.', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/phpinfo.php', 'input_type': 'header', 'input_name': 'Sec-Ch-Ua-Mobile', 'payload': 'was-tnb-hsv', 'proof': "Input reflected in the response body : 'was-tnb-hsv'.", 'output': 'The scanner was able to detect an input reflected in the response body.', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}]</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="P75" t="n">
-        <v>114135</v>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>['-']</t>
-        </is>
-      </c>
-      <c r="R75" t="inlineStr"/>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -6967,12 +6952,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['A Path Relative Style Sheet Import occurs when the application imports a style sheet via a relative URL and uses user input in the file name. This vulnerability mainly affects older browsers such as Internet Explorer and allows an attacker to exploit the way the browser handles stylesheet imports in order to perform CSS Injection.']</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>['A Path Relative Style Sheet Import occurs when the application imports a style sheet via a relative URL and uses user input in the file name. This vulnerability mainly affects older browsers such as Internet Explorer and allows an attacker to exploit the way the browser handles stylesheet imports in order to perform CSS Injection.']</t>
+          <t>[""It is preferable not to use path-related URLs in stylesheet imports, and also to use the 'X-Content-Type-Options: nosnif' and 'X-Frame-Options: deny' headers.""]</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -6980,65 +6965,66 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="M76" t="inlineStr"/>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L76" t="n">
+        <v>114466</v>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"publication_date": "2024-10-30T00:00:00+00:00",
+"modification_date": "2024-11-08T00:00:00+00:00",
+"family": "Injection",
+"severity": "Info",
+"plugin_id": 114466}
+</t>
+        </is>
+      </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>['CWE -', 'WASC -', 'OWASP -', 'CVE -', 'BID -']</t>
+          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/login.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': "The following value is extracted from a &lt;link&gt; tag that imports a style sheet with a 'href' that does not begin with a / : * stylesheets/stylesheet.css", 'output': 'The scanner was able to detect a Path Relative Stylesheet Import.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/install.php?install=yes', 'input_type': '', 'input_name': '', 'payload': '', 'proof': "The following value is extracted from a &lt;link&gt; tag that imports a style sheet with a 'href' that does not begin with a / : * stylesheets/stylesheet.css", 'output': 'The scanner was able to detect a Path Relative Stylesheet Import.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/info_install.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': "The following value is extracted from a &lt;link&gt; tag that imports a style sheet with a 'href' that does not begin with a / : * stylesheets/stylesheet.css", 'output': 'The scanner was able to detect a Path Relative Stylesheet Import.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/training_install.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': "The following value is extracted from a &lt;link&gt; tag that imports a style sheet with a 'href' that does not begin with a / : * stylesheets/stylesheet.css", 'output': 'The scanner was able to detect a Path Relative Stylesheet Import.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/install.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': "The following value is extracted from a &lt;link&gt; tag that imports a style sheet with a 'href' that does not begin with a / : * stylesheets/stylesheet.css", 'output': 'The scanner was able to detect a Path Relative Stylesheet Import.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/training.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': "The following value is extracted from a &lt;link&gt; tag that imports a style sheet with a 'href' that does not begin with a / : * stylesheets/stylesheet.css", 'output': 'The scanner was able to detect a Path Relative Stylesheet Import.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/info.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': "The following value is extracted from a &lt;link&gt; tag that imports a style sheet with a 'href' that does not begin with a / : * stylesheets/stylesheet.css", 'output': 'The scanner was able to detect a Path Relative Stylesheet Import.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/user_new.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': "The following value is extracted from a &lt;link&gt; tag that imports a style sheet with a 'href' that does not begin with a / : * stylesheets/stylesheet.css", 'output': 'The scanner was able to detect a Path Relative Stylesheet Import.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>Info</t>
-        </is>
-      </c>
-      <c r="P76" t="n">
-        <v>114466</v>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>[""It is preferable not to use path-related URLs in stylesheet imports, and also to use the 'X-Content-Type-Options: nosnif' and 'X-Frame-Options: deny' headers.""]</t>
-        </is>
-      </c>
-      <c r="R76" t="inlineStr"/>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -7050,12 +7036,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['This plugin displays supported SSL/TLS cipher suites.']</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>['This plugin displays supported SSL/TLS cipher suites.']</t>
+          <t>['-']</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -7063,69 +7049,66 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="M77" t="inlineStr"/>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L77" t="n">
+        <v>115491</v>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"publication_date": "2019-01-09T00:00:00+00:00",
+"modification_date": "2022-10-07T00:00:00+00:00",
+"family": "SSL/TLS",
+"severity": "Info",
+"plugin_id": 115491}
+</t>
+        </is>
+      </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>['https://www.iana.org/assignments/tls-parameters/tls-parameters.xhtml', 'CWE -', 'WASC -', 'OWASP -', 'CVE -', 'BID -']</t>
+          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/#/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Protocol Cipher Suite Name (RFC) Key Exchange Strength ---------------------------------------------------------------------------- TLS1.2 TLS_ECDHE_ECDSA_WITH_AES_128_GCM_SHA256 x25519 256 TLS1.2 TLS_ECDHE_ECDSA_WITH_CHACHA20_POLY1305 x25519 256 TLS1.2 TLS_ECDHE_ECDSA_WITH_AES_256_GCM_SHA384 x25519 256 TLS1.2 TLS_ECDHE_ECDSA_WITH_AES_128_CBC_SHA x25519 256 TLS1.2 TLS_ECDHE_ECDSA_WITH_AES_256_CBC_SHA x25519 256 TLS1.2 TLS_ECDHE_RSA_WITH_AES_128_GCM_SHA256 x25519 256 TLS1.2 TLS_ECDHE_RSA_WITH_AES_256_GCM_SHA384 x25519 256 TLS1.2 TLS_ECDHE_RSA_WITH_AES_128_CBC_SHA x25519 256 TLS1.2 TLS_ECDHE_RSA_WITH_AES_256_CBC_SHA x25519 256 TLS1.2 TLS_RSA_WITH_AES_128_GCM_SHA256 RSA 4096 TLS1.2 TLS_RSA_WITH_AES_256_GCM_SHA384 RSA 4096 TLS1.2 TLS_RSA_WITH_AES_128_CBC_SHA RSA 4096 TLS1.2 TLS_RSA_WITH_AES_256_CBC_SHA RSA 4096 TLS1.3 TLS_AES_128_GCM_SHA256 x25519 256 TLS1.3 TLS_AES_256_GCM_SHA384 x25519 256 TLS1.3 TLS_CHACHA20_POLY1305_SHA256 x25519 256', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="P77" t="n">
-        <v>115491</v>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>['-']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/#/', 'input_type': 'cipher_suite_list', 'input_name': None, 'payload': None, 'proof': 'Scanner detected supported cipher suites for TLS 1.2 and TLS 1.3, including AES-GCM, AES-CBC, and CHACHA20-POLY1305 variants with key exchange x25519 (256-bit) and RSA (4096-bit).', 'output': 'The target application supports multiple cipher suites under TLS 1.2 and TLS 1.3, with strong key exchange mechanisms (x25519 and RSA 4096).', 'request_method': None, 'http_status_code': None, 'http_protocol': 'HTTPS', 'response_content_type': None}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
         </is>
       </c>
     </row>

--- a/resources/tenable/TenableWAS_JuiceShop.xlsx
+++ b/resources/tenable/TenableWAS_JuiceShop.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S65"/>
+  <dimension ref="A1:N65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,31 +487,6 @@
           <t>instances</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>detection_method</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>detection_result</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>insight</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>log_method</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>product_detection_result</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -544,9 +519,6 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -575,31 +547,6 @@
           <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/products/search', 'input_type': 'link', 'input_name': 'q', 'payload': '"\'`--', 'proof': 'SQLITE_ERROR: near &amp;quot;`--%&amp;#39; OR description LIKE &amp;#39;%nessus_was_textjvihbcaq&amp;quot;&amp;#39;`&amp;quot;: syntax error', 'output': "The scanner was able to detect a possible SQL injection. The detected database engine used is 'sqlite'.", 'request_method': 'GET', 'http_status_code': 500, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}]</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -632,9 +579,6 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -663,31 +607,6 @@
           <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/products/search', 'input_type': 'link', 'input_name': 'q', 'payload': "10002'+(select '1')+'1", 'proof': "10002'+(select '1','2')+'1 for TRUE statement and 10002'+(select '1')+'1 for FALSE statement", 'output': 'A differential based SQL Injection has been identified by the scanner.', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'application/json'}]</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -720,9 +639,6 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -751,31 +667,6 @@
           <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/memories/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'The following patterns were detected in the HTTP response body : - "password":"9283f1b2e9669749081963be0462e466" - "password":"6edd9d726cbdc873c539e41ae8757b8c" - "password":"2c17c6393771ee3048ae34d6b380c5ec" - "password":"00479e957b6b42c459ee5746478e4d45" - "password":"402f1c4a75e316afec5a6ea63147f739"', 'output': 'The scanner identified one or more `Generic Password` secret(s) on the target page.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}]</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -808,9 +699,6 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -839,31 +727,6 @@
           <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/redirect', 'input_type': 'link', 'input_name': 'to', 'payload': 'https://98147a45-d7d1-4fb3-a532-d4d4b2db551e.com?x=https://github.com/juice-shop/juice-shop', 'proof': 'The issue was raised because the scanner was redirected to https://98147a45-d7d1-4fb3-a532-d4d4b2db551e.com? x=https://github.com/juice-shop/juice-shop', 'output': "An unvalidated redirect was found on https://juice-shop-16-0-1-178712031365.us-west1.run.app/redirect?to=https%3A%2F% 2F98147a45-d7d1-4fb3-a532-d4d4b2db551e.com%3Fx%3Dhttps%3A%2F%2Fgithub.com%2Fjuice-shop%2Fjuice-shop by injecting https://98147a45-d7d1-4fb3-a532-d4d4b2db551e.com?x=https://github.com/juice-shop/juice-shop into the query parameter 'to' to create the url 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/redirect?to=https%3A%2F%2F98147a45-d7d14fb3-a532-d4d4b2db551e.com%3Fx%3Dhttps%3A%2F%2Fgithub.com%2Fjuice-shop%2Fjuice-shop'.", 'request_method': '', 'http_status_code': 302, 'http_protocol': '', 'response_content_type': 'text/plain'}]</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -896,9 +759,6 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -927,31 +787,6 @@
           <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/de_DE.json', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner did not find any Strict-Transport-Security header in the response returned by the target when querying URL https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/de_DE.json.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/api/Feedbacks/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner did not find any Strict-Transport-Security header in the response returned by the target when querying URL https://juice-shop-16-0-1-178712031365.us-west1.run.app/api/Feedbacks/.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/user/whoami', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner did not find any Strict-Transport-Security header in the response returned by the target when querying URL https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/user/whoami.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/api/Quantitys/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner did not find any Strict-Transport-Security header in the response returned by the target when querying URL https://juice-shop-16-0-1-178712031365.us-west1.run.app/api/Quantitys/.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/memories/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner did not find any Strict-Transport-Security header in the response returned by the target when querying URL https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/memories/.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/languages', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner did not find any Strict-Transport-Security header in the response returned by the target when querying URL https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/languages.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/cs_CZ.json', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner did not find any Strict-Transport-Security header in the response returned by the target when querying URL https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/cs_CZ.json.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/products/1/reviews', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner did not find any Strict-Transport-Security header in the response returned by the target when querying URL https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/products/1/reviews.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/captcha/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner did not find any Strict-Transport-Security header in the response returned by the target when querying URL https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/captcha/.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/socket.io/?EIO=4&amp;transport=polling&amp;t=PPlDpDO', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner did not find any Strict-Transport-Security header in the response returned by the target when querying URL https://juice-shop-16-0-1-178712031365.us-west1.run.app/socket.io/?EIO=4&amp;transport=polling&amp;t=PPlDpDO.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'text/plain'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/id_ID.json', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner did not find any Strict-Transport-Security header in the response returned by the target when querying URL https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/id_ID.json.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/da_DK.json', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner did not find any Strict-Transport-Security header in the response returned by the target when querying URL https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/da_DK.json.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/admin/application-configuration', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner did not find any Strict-Transport-Security header in the response returned by the target when querying URL https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/admin/application-configuration.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner did not find any Strict-Transport-Security header in the response returned by the target when querying URL https://juice-shop-16-0-1-178712031365.us-west1.run.app/.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/products/search?q=', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner did not find any Strict-Transport-Security header in the response returned by the target when querying URL https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/products/search?q=.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/en.json', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner did not find any Strict-Transport-Security header in the response returned by the target when querying URL https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/en.json.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/az_AZ.json', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner did not find any Strict-Transport-Security header in the response returned by the target when querying URL https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/az_AZ.json.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/fr_FR.json', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner did not find any Strict-Transport-Security header in the response returned by the target when querying URL https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/fr_FR.json.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/api/Challenges/?name=Score%20Board', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner did not find any Strict-Transport-Security header in the response returned by the target when querying URL https://juice-shop-16-0-1-178712031365.us-west1.run.app/api/Challenges/?name=Score%20Board.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/et_EE.json', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner did not find any Strict-Transport-Security header in the response returned by the target when querying URL https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/et_EE.json.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/ca_ES.json', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner did not find any Strict-Transport-Security header in the response returned by the target when querying URL https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/ca_ES.json.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/es_ES.json', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner did not find any Strict-Transport-Security header in the response returned by the target when querying URL https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/es_ES.json.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/ftp/legal.md', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner did not find any Strict-Transport-Security header in the response returned by the target when querying URL https://juice-shop-16-0-1-178712031365.us-west1.run.app/ftp/legal.md.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'text/markdown'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/admin/application-version', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner did not find any Strict-Transport-Security header in the response returned by the target when querying URL https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/admin/application-version.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/continue-code', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner did not find any Strict-Transport-Security header in the response returned by the target when querying URL https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/continue-code.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}]</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -984,9 +819,6 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -1015,31 +847,6 @@
           <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/ftp/legal.md', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'WAS Scanner has enumerated the following Directory Listings: - https://juice-shop-16-0-1-178712031365.us-west1.run.app/ftp/', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/ftp/quarantine/juicy_malware_linux_amd_64.url', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'WAS Scanner has enumerated the following Directory Listings: - https://juice-shop-16-0-1-178712031365.us-west1.run.app/ftp/quarantine/', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}]</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1072,9 +879,6 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -1103,31 +907,6 @@
           <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/', 'input_type': 'ui_input_dom', 'input_name': 'mat-input-0', 'payload': 'javascript:window.top._tenable_wasscan_js_namespace_taint_tracer.log_execution_flow_sink()//"//`//\'//"//--&gt;&lt;/style&gt;&lt;', 'proof': '', 'output': 'Vulnerability has been detected on URL \'https://juice-shop-16-0-1-178712031365.us-west1.run.app/\' by exploiting \'ui_input_dom\' element named \'mat-input-0\' and injecting following payload: | javascript:window.top._tenable_wasscan_js_namespace_taint_tracer.log_execution_flow_sink()//"//`//\'//"//--&gt;&lt;/style&gt;&lt; /select&gt;&lt;/noscript&gt;&lt;/noembed&gt;&lt;/template&gt;&lt;/title&gt;&lt;/textarea&gt;&lt;/script&gt;&lt;iframe/srcdoc="&lt;svg/onload=window.top. _tenable_wasscan_js_namespace_taint_tracer.log_execution_flow_sink()&gt;"&gt;&lt;frame/onload=window.top. _tenable_wasscan_js_namespace_taint_tracer.log_execution_flow_sink()&gt;*/ window.top. _tenable_wasscan_js_namespace_taint_tracer.log_execution_flow_sink()//', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1160,9 +939,6 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -1191,31 +967,6 @@
           <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Current Version: 2.2.4 Fixed Version: 3.4.0 Detected technology URL: https://juice-shop-16-0-1-178712031365.us-west1.run.app/', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1248,9 +999,6 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -1279,31 +1027,6 @@
           <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Protocol Cipher Suite Name (RFC) Key Exchange Strength -------------------------------------------------------------------- TLS1.2 TLS_RSA_WITH_AES_128_GCM_SHA256 RSA 4096 TLS1.2 TLS_RSA_WITH_AES_256_GCM_SHA384 RSA 4096 TLS1.2 TLS_RSA_WITH_AES_128_CBC_SHA RSA 4096 TLS1.2 TLS_RSA_WITH_AES_256_CBC_SHA RSA 4096', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1336,9 +1059,6 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -1367,31 +1087,6 @@
           <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/api-docs/swagger-ui-bundle.js', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'The following patterns were detected in the HTTP response body : - &lt;?php', 'output': "The scanner detected the presence of a 'PHP' source code in the web application response.", 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1427,9 +1122,6 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -1458,31 +1150,6 @@
           <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Current Version: 2.2.4 Fixed Version: 3.5.0 Detected technology URL: https://juice-shop-16-0-1-178712031365.us-west1.run.app/', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1515,9 +1182,6 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -1546,31 +1210,6 @@
           <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Current Version: 2.2.4 Fixed Version: 3.0.0 Detected technology URL: https://juice-shop-16-0-1-178712031365.us-west1.run.app/', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1603,9 +1242,6 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -1634,31 +1270,6 @@
           <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/api-docs/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': "The scanner detected the presence of permissive input(s) in the API host(s) used in the detected OpenAPI file on the following URL https://juice-shop-16-0-1-178712031365.us-west1.run.app/api-docs/. The following components have parameter with permissive inputs : - Component 'Order' has parameter 'cid' (String) without the 'format' property declared - Component 'Order' has parameter 'cid' (String) without the 'maxLength' property declared - Component 'Order' has parameter 'cid' (String) without the 'pattern' property declared - Component 'OrderConfirmation' has parameter 'cid' (String) without the 'format' property declared - Component 'OrderConfirmation' has parameter 'cid' (String) without the 'maxLength' property declared - Component 'OrderConfirmation' has parameter 'cid' (String) without the 'pattern' property declared - Component 'OrderConfirmation' has parameter 'orderNo' (String) without the 'format' property declared - Component 'OrderConfirmation' has parameter 'orderNo' (String) without the 'maxLength' property declared - Component 'OrderConfirmation' has parameter 'orderNo' (String) without the 'pattern' property declared - Component 'OrderConfirmation' has parameter 'paymentDue' (String) without the 'maxLength' property declared - Component 'OrderConfirmation' has parameter 'paymentDue' (String) without the 'pattern' property declared - Component 'OrderLine' has parameter 'productId' (Integer) without the 'format' property declared - Component 'OrderLine' has parameter 'productId' (Integer) without the 'maximum' property declared - Component 'OrderLine' has parameter 'productId' (Integer) without the 'minimum' property declared - Component 'OrderLine' has parameter 'quantity' (Integer) without the 'format' property declared - Component 'OrderLine' has parameter 'quantity' (Integer) without the 'maximum' property declared - Component 'OrderLine' has parameter 'customerReference' (String) without the 'format' property declared - Component 'OrderLine' has parameter 'customerReference' (String) without the 'maxLength' property declared - Component 'OrderLine' has parameter 'customerReference' (String) without the 'pattern' property declared", 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1691,9 +1302,6 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -1722,31 +1330,6 @@
           <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/metrics', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '# HELP file_uploads_count Total number of successful file uploads grouped by file type. # TYPE file_uploads_count counter # HELP file_upload_errors Total number of failed file uploads grouped by file type.', 'output': 'The scanner was able to detect the exposure of a sensitive Prometheus endpoint at the following URL : https://juice\ufffeshop-16-0-1-178712031365.us-west1.run.app/metrics', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/plain'}]</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1779,9 +1362,6 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -1810,31 +1390,6 @@
           <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/es_ES.json', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'Access-Control-Allow-Origin: *', 'output': "Vulnerability has been detected on URL 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/es_ES.json' To confirm the presence of the vulnerability, this proof has been identified in the target response: | Access-Control-Allow-Origin: * The information used to check the vulnerability have been provided in attachment.", 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/continue-code', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'Access-Control-Allow-Origin: *', 'output': "Vulnerability has been detected on URL 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/continue-code' To confirm the presence of the vulnerability, this proof has been identified in the target response: | Access-Control-Allow-Origin: * The information used to check the vulnerability have been provided in attachment.", 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/products/search?q=', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'Access-Control-Allow-Origin: *', 'output': "Vulnerability has been detected on URL 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/products/search?q=' To confirm the presence of the vulnerability, this proof has been identified in the target response: | Access-Control-Allow-Origin: * The information used to check the vulnerability have been provided in attachment.", 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'Access-Control-Allow-Origin: *', 'output': "Vulnerability has been detected on URL 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/' To confirm the presence of the vulnerability, this proof has been identified in the target response: | Access-Control-Allow-Origin: * The information used to check the vulnerability have been provided in attachment.", 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/admin/application-version', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'Access-Control-Allow-Origin: *', 'output': "Vulnerability has been detected on URL 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/admin/application\ufffeversion' To confirm the presence of the vulnerability, this proof has been identified in the target response: | Access-Control-Allow-Origin: * The information used to check the vulnerability have been provided in attachment.", 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/cs_CZ.json', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'Access-Control-Allow-Origin: *', 'output': "Vulnerability has been detected on URL 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/cs_CZ.json' To confirm the presence of the vulnerability, this proof has been identified in the target response: | Access-Control-Allow-Origin: * The information used to check the vulnerability have been provided in attachment.", 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/en.json', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'Access-Control-Allow-Origin: *', 'output': "Vulnerability has been detected on URL 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/en.json' To confirm the presence of the vulnerability, this proof has been identified in the target response: | Access-Control-Allow-Origin: * The information used to check the vulnerability have been provided in attachment.", 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/captcha/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'Access-Control-Allow-Origin: *', 'output': "Vulnerability has been detected on URL 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/captcha/' To confirm the presence of the vulnerability, this proof has been identified in the target response: | Access-Control-Allow-Origin: * The information used to check the vulnerability have been provided in attachment.", 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/user/whoami', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'Access-Control-Allow-Origin: *', 'output': "Vulnerability has been detected on URL 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/user/whoami' To confirm the presence of the vulnerability, this proof has been identified in the target response: | Access-Control-Allow-Origin: * The information used to check the vulnerability have been provided in attachment.", 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/api/Quantitys/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'Access-Control-Allow-Origin: *', 'output': "Vulnerability has been detected on URL 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/api/Quantitys/' To confirm the presence of the vulnerability, this proof has been identified in the target response: | Access-Control-Allow-Origin: * The information used to check the vulnerability have been provided in attachment.", 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/et_EE.json', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'Access-Control-Allow-Origin: *', 'output': "Vulnerability has been detected on URL 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/et_EE.json' To confirm the presence of the vulnerability, this proof has been identified in the target response: | Access-Control-Allow-Origin: * The information used to check the vulnerability have been provided in attachment.", 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/api/Challenges/?name=Score%20Board', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'Access-Control-Allow-Origin: *', 'output': "Vulnerability has been detected on URL 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/api/Challenges/? name=Score%20Board' To confirm the presence of the vulnerability, this proof has been identified in the target response: | Access-Control-Allow-Origin: * The information used to check the vulnerability have been provided in attachment.", 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/de_DE.json', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'Access-Control-Allow-Origin: *', 'output': "Vulnerability has been detected on URL 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/de_DE.json' To confirm the presence of the vulnerability, this proof has been identified in the target response: | Access-Control-Allow-Origin: * The information used to check the vulnerability have been provided in attachment.", 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/admin/application-configuration', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'Access-Control-Allow-Origin: *', 'output': "Vulnerability has been detected on URL 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/admin/application\ufffeconfiguration' To confirm the presence of the vulnerability, this proof has been identified in the target response: | Access-Control-Allow-Origin: * The information used to check the vulnerability have been provided in attachment.", 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/ftp/legal.md', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'Access-Control-Allow-Origin: *', 'output': "Vulnerability has been detected on URL 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/ftp/legal.md' To confirm the presence of the vulnerability, this proof has been identified in the target response: | Access-Control-Allow-Origin: * The information used to check the vulnerability have been provided in attachment.", 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'text/markdown'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/api/Feedbacks/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'Access-Control-Allow-Origin: *', 'output': "Vulnerability has been detected on URL 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/api/Feedbacks/' To confirm the presence of the vulnerability, this proof has been identified in the target response: | Access-Control-Allow-Origin: * The information used to check the vulnerability have been provided in attachment.", 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/languages', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'Access-Control-Allow-Origin: *', 'output': "Vulnerability has been detected on URL 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/languages' To confirm the presence of the vulnerability, this proof has been identified in the target response: | Access-Control-Allow-Origin: * The information used to check the vulnerability have been provided in attachment.", 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/products/1/reviews', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'Access-Control-Allow-Origin: *', 'output': "Vulnerability has been detected on URL 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/products/1/reviews' To confirm the presence of the vulnerability, this proof has been identified in the target response: | Access-Control-Allow-Origin: * The information used to check the vulnerability have been provided in attachment.", 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/fr_FR.json', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'Access-Control-Allow-Origin: *', 'output': "Vulnerability has been detected on URL 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/fr_FR.json' To confirm the presence of the vulnerability, this proof has been identified in the target response: | Access-Control-Allow-Origin: * The information used to check the vulnerability have been provided in attachment.", 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/az_AZ.json', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'Access-Control-Allow-Origin: *', 'output': "Vulnerability has been detected on URL 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/az_AZ.json' To confirm the presence of the vulnerability, this proof has been identified in the target response: | Access-Control-Allow-Origin: * The information used to check the vulnerability have been provided in attachment.", 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/id_ID.json', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'Access-Control-Allow-Origin: *', 'output': "Vulnerability has been detected on URL 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/id_ID.json' To confirm the presence of the vulnerability, this proof has been identified in the target response: | Access-Control-Allow-Origin: * The information used to check the vulnerability have been provided in attachment.", 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/memories/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'Access-Control-Allow-Origin: *', 'output': "Vulnerability has been detected on URL 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/memories/' To confirm the presence of the vulnerability, this proof has been identified in the target response: | Access-Control-Allow-Origin: * The information used to check the vulnerability have been provided in attachment.", 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/ca_ES.json', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'Access-Control-Allow-Origin: *', 'output': "Vulnerability has been detected on URL 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/ca_ES.json' To confirm the presence of the vulnerability, this proof has been identified in the target response: | Access-Control-Allow-Origin: * The information used to check the vulnerability have been provided in attachment.", 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/redirect?to=https://github.com/juice-shop/juice-shop', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'Access-Control-Allow-Origin: *', 'output': "Vulnerability has been detected on URL 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/redirect? to=https://github.com/juice-shop/juice-shop' To confirm the presence of the vulnerability, this proof has been identified in the target response: | Access-Control-Allow-Origin: * The information used to check the vulnerability have been provided in attachment.", 'request_method': 'GET', 'http_status_code': 302, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/plain'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/da_DK.json', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'Access-Control-Allow-Origin: *', 'output': "Vulnerability has been detected on URL 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/da_DK.json' To confirm the presence of the vulnerability, this proof has been identified in the target response: | Access-Control-Allow-Origin: * The information used to check the vulnerability have been provided in attachment.", 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}]</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1867,9 +1422,6 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -1898,31 +1450,6 @@
           <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/socket.io/?EIO=4&amp;transport=polling&amp;t=PPlDpDO', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Page https://juice-shop-16-0-1-178712031365.us-west1.run.app/socket.io/?EIO=4&amp;transport=polling&amp;t=PPlDpDO has no X\ufffeFrame-Options header defined', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'text/plain'}]</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1955,9 +1482,6 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -1986,31 +1510,6 @@
           <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/', 'input_type': 'cookie', 'input_name': 'cookieconsent_status', 'payload': '', 'proof': 'cookieconsent_status=dismiss; Path=/; Expires=2026-04-25 23:10:31 +0000', 'output': "The scanner detected a cookie named 'cookieconsent_status' set with JavaScript which prevents the HTTPOnly attribute from being used. If the cookie is set to handle sensitive information (for example session-based information), it should be set via the HTTP method.", 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/', 'input_type': 'cookie', 'input_name': 'language', 'payload': '', 'proof': 'language=en; Path=/; Expires=2026-04-25 23:10:11 +0000', 'output': "The scanner detected a cookie named 'language' set with JavaScript which prevents the HTTPOnly attribute from being used. If the cookie is set to handle sensitive information (for example session-based information), it should be set via the HTTP method.", 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/', 'input_type': 'cookie', 'input_name': 'continueCode', 'payload': '', 'proof': 'continueCode=z67RBJkpxgOw1qjLrbzDM95EnABVfXDUb9A3Y2aePl4VXZvQ8mW7yKo6NXeE; Path=/; Expires=2026-04-25 23:16:47 +0000', 'output': "The scanner detected a cookie named 'continueCode' set with JavaScript which prevents the HTTPOnly attribute from being used. If the cookie is set to handle sensitive information (for example session-based information), it should be set via the HTTP method.", 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/', 'input_type': 'cookie', 'input_name': 'welcomebanner_status', 'payload': '', 'proof': 'welcomebanner_status=dismiss; Path=/; Expires=2026-04-25 23:13:45 +0000', 'output': "The scanner detected a cookie named 'welcomebanner_status' set with JavaScript which prevents the HTTPOnly attribute from being used. If the cookie is set to handle sensitive information (for example session-based information), it should be set via the HTTP method.", 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': 'text/html'}]</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2043,9 +1542,6 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -2074,31 +1570,6 @@
           <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/', 'input_type': 'cookie', 'input_name': 'continueCode', 'payload': '', 'proof': 'continueCode=z67RBJkpxgOw1qjLrbzDM95EnABVfXDUb9A3Y2aePl4VXZvQ8mW7yKo6NXeE; Path=/; Expires=2026-04-25 23:16:47 +0000', 'output': "The scanner detected a cookie named 'continueCode' set with JavaScript without the Secure flag set.", 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/', 'input_type': 'cookie', 'input_name': 'cookieconsent_status', 'payload': '', 'proof': 'cookieconsent_status=dismiss; Path=/; Expires=2026-04-25 23:10:31 +0000', 'output': "The scanner detected a cookie named 'cookieconsent_status' set with JavaScript without the Secure flag set.", 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/', 'input_type': 'cookie', 'input_name': 'welcomebanner_status', 'payload': '', 'proof': 'welcomebanner_status=dismiss; Path=/; Expires=2026-04-25 23:13:45 +0000', 'output': "The scanner detected a cookie named 'welcomebanner_status' set with JavaScript without the Secure flag set.", 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/', 'input_type': 'cookie', 'input_name': 'language', 'payload': '', 'proof': 'language=en; Path=/; Expires=2026-04-25 23:10:11 +0000', 'output': "The scanner detected a cookie named 'language' set with JavaScript without the Secure flag set.", 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': 'text/html'}]</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2131,9 +1602,6 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -2162,31 +1630,6 @@
           <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/fr_FR.json', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The following header information disclosures have been detected on https://juice-shop-16-0-1-178712031365.us-west1.run. app/assets/i18n/fr_FR.json: - Server: Google Frontend', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/api/Feedbacks/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The following header information disclosures have been detected on https://juice-shop-16-0-1-178712031365.us-west1.run. app/api/Feedbacks/: - Server: Google Frontend', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/de_DE.json', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The following header information disclosures have been detected on https://juice-shop-16-0-1-178712031365.us-west1.run. app/assets/i18n/de_DE.json: - Server: Google Frontend', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/az_AZ.json', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The following header information disclosures have been detected on https://juice-shop-16-0-1-178712031365.us-west1.run. app/assets/i18n/az_AZ.json: - Server: Google Frontend', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/admin/application-configuration', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The following header information disclosures have been detected on https://juice-shop-16-0-1-178712031365.us-west1.run. app/rest/admin/application-configuration: - Server: Google Frontend', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/en.json', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The following header information disclosures have been detected on https://juice-shop-16-0-1-178712031365.us-west1.run. app/assets/i18n/en.json: - Server: Google Frontend', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/products/search?q=', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The following header information disclosures have been detected on https://juice-shop-16-0-1-178712031365.us-west1.run. app/rest/products/search?q=: - Server: Google Frontend', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/et_EE.json', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The following header information disclosures have been detected on https://juice-shop-16-0-1-178712031365.us-west1.run. app/assets/i18n/et_EE.json: - Server: Google Frontend', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/continue-code', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The following header information disclosures have been detected on https://juice-shop-16-0-1-178712031365.us-west1.run. app/rest/continue-code: - Server: Google Frontend', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/cs_CZ.json', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The following header information disclosures have been detected on https://juice-shop-16-0-1-178712031365.us-west1.run. app/assets/i18n/cs_CZ.json: - Server: Google Frontend', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/admin/application-version', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The following header information disclosures have been detected on https://juice-shop-16-0-1-178712031365.us-west1.run. app/rest/admin/application-version: - Server: Google Frontend', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/products/1/reviews', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The following header information disclosures have been detected on https://juice-shop-16-0-1-178712031365.us-west1.run. app/rest/products/1/reviews: - Server: Google Frontend', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/id_ID.json', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The following header information disclosures have been detected on https://juice-shop-16-0-1-178712031365.us-west1.run. app/assets/i18n/id_ID.json: - Server: Google Frontend', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/api/Challenges/?name=Score%20Board', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The following header information disclosures have been detected on https://juice-shop-16-0-1-178712031365.us-west1.run. app/api/Challenges/?name=Score%20Board: - Server: Google Frontend', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/socket.io/?EIO=4&amp;transport=polling&amp;t=PPlDpDO', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The following header information disclosures have been detected on https://juice-shop-16-0-1-178712031365.us-west1.run. app/socket.io/?EIO=4&amp;transport=polling&amp;t=PPlDpDO: - Server: Google Frontend', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'text/plain'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/da_DK.json', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The following header information disclosures have been detected on https://juice-shop-16-0-1-178712031365.us-west1.run. app/assets/i18n/da_DK.json: - Server: Google Frontend', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/languages', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The following header information disclosures have been detected on https://juice-shop-16-0-1-178712031365.us-west1.run. app/rest/languages: - Server: Google Frontend', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/es_ES.json', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The following header information disclosures have been detected on https://juice-shop-16-0-1-178712031365.us-west1.run. app/assets/i18n/es_ES.json: - Server: Google Frontend', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/user/whoami', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The following header information disclosures have been detected on https://juice-shop-16-0-1-178712031365.us-west1.run. app/rest/user/whoami: - Server: Google Frontend', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/captcha/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The following header information disclosures have been detected on https://juice-shop-16-0-1-178712031365.us-west1.run. app/rest/captcha/: - Server: Google Frontend', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/api/Quantitys/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The following header information disclosures have been detected on https://juice-shop-16-0-1-178712031365.us-west1.run. app/api/Quantitys/: - Server: Google Frontend', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/ftp/legal.md', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The following header information disclosures have been detected on https://juice-shop-16-0-1-178712031365.us-west1.run. app/ftp/legal.md: - Server: Google Frontend', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'text/markdown'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/ca_ES.json', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The following header information disclosures have been detected on https://juice-shop-16-0-1-178712031365.us-west1.run. app/assets/i18n/ca_ES.json: - Server: Google Frontend', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The following header information disclosures have been detected on https://juice-shop-16-0-1-178712031365.us-west1.run. app/: - Server: Google Frontend', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/memories/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The following header information disclosures have been detected on https://juice-shop-16-0-1-178712031365.us-west1.run. app/rest/memories/: - Server: Google Frontend', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}]</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2219,9 +1662,6 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -2249,31 +1689,6 @@
           <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/socket.io/?EIO=4&amp;transport=polling&amp;t=PPlDpDO', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner detected the lack of a correct X-Content-Type-Options header configuration in the target application response', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'text/plain'}]</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2306,9 +1721,6 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -2336,31 +1748,6 @@
           <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Protocol Cipher Suite Name (RFC) Key Exchange Strength ------------------------------------------------------------------------- TLS1.2 TLS_ECDHE_ECDSA_WITH_AES_128_CBC_SHA x25519 256 TLS1.2 TLS_ECDHE_ECDSA_WITH_AES_256_CBC_SHA x25519 256 TLS1.2 TLS_ECDHE_RSA_WITH_AES_128_CBC_SHA x25519 256 TLS1.2 TLS_ECDHE_RSA_WITH_AES_256_CBC_SHA x25519 256 TLS1.2 TLS_RSA_WITH_AES_128_GCM_SHA256 RSA 4096 TLS1.2 TLS_RSA_WITH_AES_256_GCM_SHA384 RSA 4096 TLS1.2 TLS_RSA_WITH_AES_128_CBC_SHA RSA 4096 TLS1.2 TLS_RSA_WITH_AES_256_CBC_SHA RSA 4096', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2393,9 +1780,6 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -2424,31 +1808,6 @@
           <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/ftp/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/ftp/ has no Content Security Policy defined.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/ftp/quarantine', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/ftp/quarantine has no Content Security Policy defined.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/b2b/v2/orders', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/b2b/v2/orders has no Content Security Policy defined.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/ has no Content Security Policy defined.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/api-docs/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/api-docs/ has no Content Security Policy defined.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/ftp/quarantine/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/ftp/quarantine/ has no Content Security Policy defined.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/ftp/coupons_2013.md.bak', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/ftp/coupons_2013.md.bak has no Content Security Policy defined.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/public/images/uploads/%F0%9F%98%BC\ufffeIdentification', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/public/images/uploads/%F0%9F%98%BC- has no Content Security Policy defined.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': 'text/html'}]</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2481,9 +1840,6 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -2512,31 +1868,6 @@
           <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/api-docs/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/api-docs/ has no Cache Control header defined.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/captcha/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/captcha/ has no Cache Control header defined.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/products/1/reviews', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/products/1/reviews has no Cache Control header defined.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/socket.io/?EIO=4&amp;transport=polling&amp;t=PPlDpDO', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/socket.io/?EIO=4&amp;transport=polling&amp;t=PPlDpDO has no Cache Control header defined.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'text/plain'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/api/Quantitys/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/api/Quantitys/ has no Cache Control header defined.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/api/Feedbacks/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/api/Feedbacks/ has no Cache Control header defined.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/ftp/quarantine', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/ftp/quarantine has no Cache Control header defined.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/user/whoami', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/user/whoami has no Cache Control header defined.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/products/search?q=', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/products/search?q= has no Cache Control header defined.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/memories/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/memories/ has no Cache Control header defined.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/admin/application-version', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/admin/application-version has no Cache Control header defined.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/continue-code', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/continue-code has no Cache Control header defined.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/api/Challenges/?name=Score%20Board', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/api/Challenges/?name=Score%20Board has no Cache Control header defined.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/products/1/reviews/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/products/1/reviews/ has no Cache Control header defined.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/ftp/quarantine/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/ftp/quarantine/ has no Cache Control header defined.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/ftp/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/ftp/ has no Cache Control header defined.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/admin/application-configuration', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/admin/application-configuration has no Cache Control header defined.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/products/search/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/products/search/ has no Cache Control header defined.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/ftp/coupons_2013.md.bak', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/ftp/coupons_2013.md.bak has no Cache Control header defined.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/languages', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/languages has no Cache Control header defined.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/b2b/v2/orders', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/b2b/v2/orders has no Cache Control header defined.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'text/html'}]</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2569,9 +1900,6 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -2599,31 +1927,6 @@
           <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/admin/application-configuration/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'The following patterns were detected in the HTTP response body : - "user":"bjoernGoogle"', 'output': 'The scanner identified one or more `Generic` username(s) on the target page.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/memories/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'The following patterns were detected in the HTTP response body : - "username":"bkimminich" - "username":"evmrox"', 'output': 'The scanner identified one or more `Generic` username(s) on the target page.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/admin/application-configuration', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'The following patterns were detected in the HTTP response body : - "user":"bjoernGoogle"', 'output': 'The scanner identified one or more `Generic` username(s) on the target page.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}]</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2656,9 +1959,6 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -2686,31 +1986,6 @@
           <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/', 'input_type': 'cookie', 'input_name': 'cookieconsent_status', 'payload': '', 'proof': 'cookieconsent_status=dismiss; Path=/; Expires=2026-04-25 23:10:31 +0000', 'output': "The scanner detected a cookie named 'cookieconsent_status' set with JavaScript which does not have the 'SameSite' attribute set.", 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/', 'input_type': 'cookie', 'input_name': 'continueCode', 'payload': '', 'proof': 'continueCode=z67RBJkpxgOw1qjLrbzDM95EnABVfXDUb9A3Y2aePl4VXZvQ8mW7yKo6NXeE; Path=/; Expires=2026-04-25 23:16:47 +0000', 'output': "The scanner detected a cookie named 'continueCode' set with JavaScript which does not have the 'SameSite' attribute set.", 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/', 'input_type': 'cookie', 'input_name': 'welcomebanner_status', 'payload': '', 'proof': 'welcomebanner_status=dismiss; Path=/; Expires=2026-04-25 23:13:45 +0000', 'output': "The scanner detected a cookie named 'welcomebanner_status' set with JavaScript which does not have the 'SameSite' attribute set.", 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/', 'input_type': 'cookie', 'input_name': 'language', 'payload': '', 'proof': 'language=en; Path=/; Expires=2026-04-25 23:10:11 +0000', 'output': "The scanner detected a cookie named 'language' set with JavaScript which does not have the 'SameSite' attribute set.", 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2733,15 +2008,11 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -2767,31 +2038,6 @@
       <c r="N27" t="inlineStr">
         <is>
           <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/#/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': "Engine Version 2.32.4-1790 Plugins Version 202504170639 Scan ID 98147a45-d7d1-4fb3-a532-d4d4b2db551e Start Time 2025-04-25 23:10:05 +0000 Duration 09:02:14 Requests 541973 Crawler Requests 98 Requests/s 20.8353 Mean Response Time 0.1956s Bandwidth Usage - Data to Target 356 MB - Data from Target 6.4 GB Timeouts Encountered Network Timeouts 3 Browser Timeouts 0 Browser Respawns 0 HTTP Protocols Detected - HTTPs Authentication Identified - None Plugins - 811 have been included per scan policy - 612 have been started based on target information collected List of plugins is available in 'plugins.csv' attachment. Settings used to conduct this scan are available in 'configuration.csv' attachment.", 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>[]</t>
         </is>
       </c>
     </row>
@@ -2825,21 +2071,16 @@
 user_abort: The user stopped the scan before the URL could be audited']</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -2867,31 +2108,6 @@
           <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/#/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scan has discovered 5122 distinct URLs. The following is a breakdown of which URLs were audited: - 43 effectively audited - 5 not audited due to the page was too similar to another page already audited - 1 not audited due to not being within the bounds of the user defined scan scope - 4973 not queued due to the URL being considered redundant with other processed URLs - 49 not queued due to file extension exclusions - 31 not queued due to the URL not being in the target domain - 17 not queued due to the URL containing a fragment which is a feature of browsers and not included in HTTP requests. The page being referred to by the fragment shall still be audited by the scanner. For URLs we received responses for, here is a distribution of the content type headers: - 126 application/json - 24 application/json; charset=utf-8 - 5 application/octet-stream - 36 image/jpeg - 6 image/png - 2 text/css; charset=utf-8 - 1454 text/html - 24 text/html; charset=utf-8 - 3 text/markdown; charset=utf-8 - 3400 text/plain; charset=utf-8 Response times ranged between 0.061378s and 0.281365s. You can access the complete list of URLs with the information collected by the scan as an attachment to this plugin.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2914,15 +2130,11 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -2950,31 +2162,6 @@
           <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/#/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner encountered 3 network timeouts during the scan. See the attachment for more details', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2997,15 +2184,11 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -3033,31 +2216,6 @@
           <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/#/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner was able to identify several HTTP methods that can be used for one or several URLs. The results are available as attachments.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3080,15 +2238,11 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -3116,31 +2270,6 @@
           <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'HTTP/2 405', 'output': "A response has been received with a response code '405' which may require further investigation to verify if this response is due to an abnormal behavior of the target. The response has been triggered by an HTTP TRACE request made on the URL 'https://juice-shop-16-0-1-178712031365.us\ufffewest1.run.app/'.", 'request_method': 'TRACE', 'http_status_code': 405, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/api/content/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'HTTP/2 500', 'output': "A response has been received with a response code '500' which may require further investigation to verify if this response is due to an abnormal behavior of the target. The response has been triggered by an HTTP POST request made on the URL 'https://juice-shop-16-0-1-178712031365.us\ufffewest1.run.app/api/content/'.", 'request_method': 'POST', 'http_status_code': 500, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/api/?wsdl', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'HTTP/2 500', 'output': "A response has been received with a response code '500' which may require further investigation to verify if this response is due to an abnormal behavior of the target. The response has been triggered by an HTTP GET request made on the URL 'https://juice-shop-16-0-1-178712031365.us-west1. run.app/api/?wsdl'.", 'request_method': 'GET', 'http_status_code': 500, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/api/v1/swagger.yaml', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'HTTP/2 500', 'output': "A response has been received with a response code '500' which may require further investigation to verify if this response is due to an abnormal behavior of the target. The response has been triggered by an HTTP GET request made on the URL 'https://juice-shop-16-0-1-178712031365.us-west1. run.app/api/v1/swagger.yaml'.", 'request_method': 'GET', 'http_status_code': 500, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/api/docs/v2/swagger.yaml', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'HTTP/2 500', 'output': "A response has been received with a response code '500' which may require further investigation to verify if this response is due to an abnormal behavior of the target. The response has been triggered by an HTTP GET request made on the URL 'https://juice-shop-16-0-1-178712031365.us-west1. run.app/api/docs/v2/swagger.yaml'.", 'request_method': 'GET', 'http_status_code': 500, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/api/swagger.json', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'HTTP/2 500', 'output': "A response has been received with a response code '500' which may require further investigation to verify if this response is due to an abnormal behavior of the target. The response has been triggered by an HTTP GET request made on the URL 'https://juice-shop-16-0-1-178712031365.us-west1. run.app/api/swagger.json'.", 'request_method': 'GET', 'http_status_code': 500, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/api/swagger.yaml', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'HTTP/2 500', 'output': "A response has been received with a response code '500' which may require further investigation to verify if this response is due to an abnormal behavior of the target. The response has been triggered by an HTTP GET request made on the URL 'https://juice-shop-16-0-1-178712031365.us-west1. run.app/api/swagger.yaml'.", 'request_method': 'GET', 'http_status_code': 500, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/api/login', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'HTTP/2 500', 'output': "A response has been received with a response code '500' which may require further investigation to verify if this response is due to an abnormal behavior of the target. The response has been triggered by an HTTP POST request made on the URL 'https://juice-shop-16-0-1-178712031365.us\ufffewest1.run.app/api/login'.", 'request_method': 'POST', 'http_status_code': 500, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/api/v2/swagger.json', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'HTTP/2 500', 'output': "A response has been received with a response code '500' which may require further investigation to verify if this response is due to an abnormal behavior of the target. The response has been triggered by an HTTP GET request made on the URL 'https://juice-shop-16-0-1-178712031365.us-west1. run.app/api/v2/swagger.json'.", 'request_method': 'GET', 'http_status_code': 500, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https%3A%2F%2Fjuice-shop-16-0-1-178712031365.us-west1.run.app%2Fsetup%2Fsetup-s%2F%25u002e%25u002e%2F%', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'HTTP/2 400', 'output': "A response has been received with a response code '400' which may require further investigation to verify if this response is due to an abnormal behavior of the target. The response has been triggered by an HTTP GET request made on the URL 'https://juice-shop-16-0-1-178712031365.us-west1. run.app/setup/setup-s/%u002e%u002e/%u002e%u002e/log.jsp'.", 'request_method': 'GET', 'http_status_code': 400, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/api/v1/swagger.json', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'HTTP/2 500', 'output': "A response has been received with a response code '500' which may require further investigation to verify if this response is due to an abnormal behavior of the target. The response has been triggered by an HTTP GET request made on the URL 'https://juice-shop-16-0-1-178712031365.us-west1. run.app/api/v1/swagger.json'.", 'request_method': 'GET', 'http_status_code': 500, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/was-tnb.aspx', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'HTTP/2 502', 'output': "A response has been received with a response code '502' which may require further investigation to verify if this response is due to an abnormal behavior of the target. The response has been triggered by an HTTP DEBUG request made on the URL 'https://juice-shop-16-0-1-178712031365.us\ufffewest1.run.app/was-tnb.aspx'.", 'request_method': 'DEBUG', 'http_status_code': 502, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/plain'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/api/docs/v2/swagger.json', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'HTTP/2 500', 'output': "A response has been received with a response code '500' which may require further investigation to verify if this response is due to an abnormal behavior of the target. The response has been triggered by an HTTP GET request made on the URL 'https://juice-shop-16-0-1-178712031365.us-west1. run.app/api/docs/v2/swagger.json'.", 'request_method': 'GET', 'http_status_code': 500, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/api/api-docs/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'HTTP/2 500', 'output': "A response has been received with a response code '500' which may require further investigation to verify if this response is due to an abnormal behavior of the target. The response has been triggered by an HTTP GET request made on the URL 'https://juice-shop-16-0-1-178712031365.us-west1. run.app/api/api-docs/'.", 'request_method': 'GET', 'http_status_code': 500, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/profile/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'HTTP/2 500', 'output': "A response has been received with a response code '500' which may require further investigation to verify if this response is due to an abnormal behavior of the target. The response has been triggered by an HTTP GET request made on the URL 'https://juice-shop-16-0-1-178712031365.us-west1. run.app/profile/'.", 'request_method': 'GET', 'http_status_code': 500, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/api/cors/https/rfi.nessus.org/rfi.txt', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'HTTP/2 500', 'output': "A response has been received with a response code '500' which may require further investigation to verify if this response is due to an abnormal behavior of the target. The response has been triggered by an HTTP GET request made on the URL 'https://juice-shop-16-0-1-178712031365.us-west1. run.app/api/cors/https/rfi.nessus.org/rfi.txt'.", 'request_method': 'GET', 'http_status_code': 500, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/api/docs/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'HTTP/2 500', 'output': "A response has been received with a response code '500' which may require further investigation to verify if this response is due to an abnormal behavior of the target. The response has been triggered by an HTTP GET request made on the URL 'https://juice-shop-16-0-1-178712031365.us-west1. run.app/api/docs/'.", 'request_method': 'GET', 'http_status_code': 500, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/redirect?to=1%29%7Bwindow.top.', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'HTTP/1.1 406 Not Acceptable', 'output': "A response has been received with a response code '406' which may require further investigation to verify if this response is due to an abnormal behavior of the target. The response has been triggered by an HTTP GET request made on the URL 'https://juice-shop-16-0-1-178712031365.us-west1. run.app/redirect?to=1%29%7Bwindow.top._tenable_wasscan_js_namespace_taint_tracer.log_execution_flow_sink%28%29%2F%2F'.", 'request_method': '', 'http_status_code': 406, 'http_protocol': '', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/api/v1/status/config', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'HTTP/2 500', 'output': "A response has been received with a response code '500' which may require further investigation to verify if this response is due to an abnormal behavior of the target. The response has been triggered by an HTTP GET request made on the URL 'https://juice-shop-16-0-1-178712031365.us-west1. run.app/api/v1/status/config'.", 'request_method': 'GET', 'http_status_code': 500, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/restricted/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'HTTP/2 500', 'output': "A response has been received with a response code '500' which may require further investigation to verify if this response is due to an abnormal behavior of the target. The response has been triggered by an HTTP GET request made on the URL 'https://juice-shop-16-0-1-178712031365.us-west1. run.app/restricted/'.", 'request_method': 'GET', 'http_status_code': 500, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/api/components/suggestions?recentlyBrowsed=', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'HTTP/2 500', 'output': "A response has been received with a response code '500' which may require further investigation to verify if this response is due to an abnormal behavior of the target. The response has been triggered by an HTTP GET request made on the URL 'https://juice-shop-16-0-1-178712031365.us-west1. run.app/api/components/suggestions?recentlyBrowsed='.", 'request_method': 'GET', 'http_status_code': 500, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/wls-wsat/CoordinatorPortType', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'HTTP/2 413', 'output': "A response has been received with a response code '413' which may require further investigation to verify if this response is due to an abnormal behavior of the target. The response has been triggered by an HTTP POST request made on the URL 'https://juice-shop-16-0-1-178712031365.us\ufffewest1.run.app/wls-wsat/CoordinatorPortType'.", 'request_method': 'POST', 'http_status_code': 413, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/api/docs/v1/swagger.json', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'HTTP/2 500', 'output': "A response has been received with a response code '500' which may require further investigation to verify if this response is due to an abnormal behavior of the target. The response has been triggered by an HTTP GET request made on the URL 'https://juice-shop-16-0-1-178712031365.us-west1. run.app/api/docs/v1/swagger.json'.", 'request_method': 'GET', 'http_status_code': 500, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/api/v1/targets', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'HTTP/2 500', 'output': "A response has been received with a response code '500' which may require further investigation to verify if this response is due to an abnormal behavior of the target. The response has been triggered by an HTTP GET request made on the URL 'https://juice-shop-16-0-1-178712031365.us-west1. run.app/api/v1/targets'.", 'request_method': 'GET', 'http_status_code': 500, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/api/docs/v1/swagger.yaml', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'HTTP/2 500', 'output': "A response has been received with a response code '500' which may require further investigation to verify if this response is due to an abnormal behavior of the target. The response has been triggered by an HTTP GET request made on the URL 'https://juice-shop-16-0-1-178712031365.us-west1. run.app/api/docs/v1/swagger.yaml'.", 'request_method': 'GET', 'http_status_code': 500, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}]</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3163,15 +2292,11 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -3199,31 +2324,6 @@
           <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/#/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The framework has detected the following technologies in the target application: - jQuery (v2.2.4) - Swagger UI (version unknown)', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3246,15 +2346,11 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -3282,31 +2378,6 @@
           <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/#/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The following cookies have been collected during the scan of the target: - 0 cookie(s) specified via Set-Cookie - 10 cookie(s) set via JavaScript code The complete list of the cookies is available in attachment.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3329,15 +2400,11 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -3365,31 +2432,6 @@
           <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/products/search/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': "The common directory 'search' was identified by the scanner.", 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/api-docs/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': "The common directory 'api-docs' was identified by the scanner.", 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/ftp/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': "The common directory 'ftp' was identified by the scanner.", 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/products/1/reviews/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': "The common directory 'reviews' was identified by the scanner.", 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'application/json'}]</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3412,15 +2454,11 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -3448,31 +2486,6 @@
           <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/#/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Number of Private IP Addresses Collected: 4 Listed below are each private ip address: 127.0.0.1 found on 1 URL 192.168.99.100 found on 1 URL 169.254.169.254 found on 1 URL 169.254.169.126 found on 1 URL', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3495,15 +2508,11 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -3531,31 +2540,6 @@
           <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/#/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Number of Email Addresses Collected: 10 Listed below are each email address and the number of URLs where the email address has been found: donotreply@owasp-juice.shop found on 1 URL admin@juice-sh.op found on 3 URLs ethereum@juice-sh.op found on 1 URL john@juice-sh.op found on 1 URL emma@juice-sh.op found on 1 URL in@juice-sh.op found on 2 URLs der@juice-sh.op found on 2 URLs ereum@juice-sh.op found on 2 URLs bjoern@owasp.org found on 1 URL bjoern.kimminich@gmail.com found on 1 URL', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3578,15 +2562,11 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -3614,31 +2594,6 @@
           <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/#/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': "Access to URL 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/#/' has been confirmed. Target Information ------------------------ Domain Name : juice-shop-16-0-1-178712031365.us-west1.run.app IP Address : 216.239.32.53 Response Information --------------------------- Status Code : 200 Return Code : ok Return Message: No error Response Time : 0.137635s Response Size : 4247 bytes Content-Type : text/html; charset=UTF-8 DEBUG INFORMATION ----------------------- HTTP Network Timeout : 30s", 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}]</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3661,15 +2616,11 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -3697,31 +2648,6 @@
           <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/#/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': "WAS Scanner has taken a screenshot of the page at url 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/#/' with dimensions 1600x1200. Please see the attachment for the screenshot image.", 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -3744,15 +2670,11 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -3780,31 +2702,6 @@
           <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/b2b/v2/orders', 'input_type': 'form', 'input_name': 'combined:post::https://juice-shop-16-0-1-178712031365.us-west1.run.app/b2b/v2/orders', 'payload': '', 'proof': '', 'output': 'A form with no identifier has been detected on the following URL https://juice-shop-16-0-1-178712031365.us-west1.run.app /b2b/v2/orders with no input fields This form is submitted by using the following action : https://juice-shop-16-0-1-178712031365.us-west1.run.app/b2b/v2 /orders', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/api-docs/', 'input_type': 'form', 'input_name': 'combined:get::https://juice-shop-16-0-1-178712031365.us-west1.run.app/api-docs/', 'payload': '', 'proof': '', 'output': 'A form with no identifier has been detected on the following URL https://juice-shop-16-0-1-178712031365.us-west1.run.app /api-docs/ with input fields : - download-url-input (text) This form is submitted by using the following action : https://juice-shop-16-0-1-178712031365.us-west1.run.app/api-docs/', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/socket.io/?', 'input_type': 'form', 'input_name': 'combined:post::https://juice-shop-16-0-1-178712031365.us-west1.run.app/socket.io/?', 'payload': '', 'proof': '', 'output': 'A form with no identifier has been detected on the following URL https://juice-shop-16-0-1-178712031365.us-west1.run.app /socket.io/?EIO=4&amp;transport=polling&amp;t=PPlDpGv&amp;sid=0N98D_jaorFN-7ioAAAK with no input fields This form is submitted by using the following action : https://juice-shop-16-0-1-178712031365.us-west1.run.app/socket. io/?EIO=4&amp;transport=polling&amp;t=PPlDpGv&amp;sid=0N98D_jaorFN-7ioAAAK', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/socket.io/?', 'input_type': 'form', 'input_name': 'combined:get::https://juice-shop-16-0-1-178712031365.us-west1.run.app/socket.io/', 'payload': '', 'proof': '', 'output': 'A form with no identifier has been detected on the following URL https://juice-shop-16-0-1-178712031365.us-west1.run.app /socket.io/?EIO=4&amp;transport=polling&amp;t=PPlDpGv&amp;sid=0N98D_jaorFN-7ioAAAK with no input fields This form is submitted by using the following action : https://juice-shop-16-0-1-178712031365.us-west1.run.app/socket. io/', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': 'text/html'}]</t>
         </is>
       </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -3827,15 +2724,11 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -3863,31 +2756,6 @@
           <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/#/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner detected the presence of 30 URLs on the target application: - 0 URLs which use a hostname related to the target hostname - 30 URLs which use a third party hostname The list of the detected URLs is provided in attachment.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -3910,15 +2778,11 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -3946,31 +2810,6 @@
           <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/api/Feedbacks/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'A Feature-Policy header was found on https://juice-shop-16-0-1-178712031365.us-west1.run.app/api/Feedbacks/ but this header must be renamed to Permissions-Policy.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/en.json', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'A Feature-Policy header was found on https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/en.json but this header must be renamed to Permissions-Policy.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/products/1/reviews', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'A Feature-Policy header was found on https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/products/1/reviews but this header must be renamed to Permissions-Policy.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/continue-code', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'A Feature-Policy header was found on https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/continue-code but this header must be renamed to Permissions-Policy.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/ftp/legal.md', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'A Feature-Policy header was found on https://juice-shop-16-0-1-178712031365.us-west1.run.app/ftp/legal.md but this header must be renamed to Permissions-Policy.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'text/markdown'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'A Feature-Policy header was found on https://juice-shop-16-0-1-178712031365.us-west1.run.app/ but this header must be renamed to Permissions-Policy.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/api/Challenges/?name=Score%20Board', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'A Feature-Policy header was found on https://juice-shop-16-0-1-178712031365.us-west1.run.app/api/Challenges/?name=Score% 20Board but this header must be renamed to Permissions-Policy.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/et_EE.json', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'A Feature-Policy header was found on https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/et_EE.json but this header must be renamed to Permissions-Policy.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/socket.io/?EIO=4&amp;transport=polling&amp;t=PPlDpDO', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Permissions-Policy headers were found on https://juice-shop-16-0-1-178712031365.us-west1.run.app/socket.io/? EIO=4&amp;transport=polling&amp;t=PPlDpDO', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'text/plain'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/api/Quantitys/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'A Feature-Policy header was found on https://juice-shop-16-0-1-178712031365.us-west1.run.app/api/Quantitys/ but this header must be renamed to Permissions-Policy.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/languages', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'A Feature-Policy header was found on https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/languages but this header must be renamed to Permissions-Policy.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/de_DE.json', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'A Feature-Policy header was found on https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/de_DE.json but this header must be renamed to Permissions-Policy.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/es_ES.json', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'A Feature-Policy header was found on https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/es_ES.json but this header must be renamed to Permissions-Policy.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/cs_CZ.json', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'A Feature-Policy header was found on https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/cs_CZ.json but this header must be renamed to Permissions-Policy.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/az_AZ.json', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'A Feature-Policy header was found on https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/az_AZ.json but this header must be renamed to Permissions-Policy.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/fr_FR.json', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'A Feature-Policy header was found on https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/fr_FR.json but this header must be renamed to Permissions-Policy.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/admin/application-configuration', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'A Feature-Policy header was found on https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/admin/application\ufffeconfiguration but this header must be renamed to Permissions-Policy.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/admin/application-version', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'A Feature-Policy header was found on https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/admin/application\ufffeversion but this header must be renamed to Permissions-Policy.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/captcha/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'A Feature-Policy header was found on https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/captcha/ but this header must be renamed to Permissions-Policy.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/ca_ES.json', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'A Feature-Policy header was found on https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/ca_ES.json but this header must be renamed to Permissions-Policy.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/id_ID.json', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'A Feature-Policy header was found on https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/id_ID.json but this header must be renamed to Permissions-Policy.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/da_DK.json', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'A Feature-Policy header was found on https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/da_DK.json but this header must be renamed to Permissions-Policy.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/products/search?q=', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'A Feature-Policy header was found on https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/products/search?q= but this header must be renamed to Permissions-Policy.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/user/whoami', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'A Feature-Policy header was found on https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/user/whoami but this header must be renamed to Permissions-Policy.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/memories/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'A Feature-Policy header was found on https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/memories/ but this header must be renamed to Permissions-Policy.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}]</t>
         </is>
       </c>
-      <c r="O41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -3993,15 +2832,11 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -4029,31 +2864,6 @@
           <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Referrer-Policy headers or body meta tags were found on https://juice-shop-16-0-1-178712031365.us-west1.run.app/', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/admin/application-configuration', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Referrer-Policy headers or body meta tags were found on https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest /admin/application-configuration', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/de_DE.json', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Referrer-Policy headers or body meta tags were found on https://juice-shop-16-0-1-178712031365.us-west1.run.app /assets/i18n/de_DE.json', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/ftp/legal.md', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Referrer-Policy headers or body meta tags were found on https://juice-shop-16-0-1-178712031365.us-west1.run.app/ftp /legal.md', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'text/markdown'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/products/1/reviews', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Referrer-Policy headers or body meta tags were found on https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest /products/1/reviews', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/continue-code', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Referrer-Policy headers or body meta tags were found on https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest /continue-code', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/user/whoami', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Referrer-Policy headers or body meta tags were found on https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest /user/whoami', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/products/search?q=', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Referrer-Policy headers or body meta tags were found on https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest /products/search?q=', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/ca_ES.json', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Referrer-Policy headers or body meta tags were found on https://juice-shop-16-0-1-178712031365.us-west1.run.app /assets/i18n/ca_ES.json', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/es_ES.json', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Referrer-Policy headers or body meta tags were found on https://juice-shop-16-0-1-178712031365.us-west1.run.app /assets/i18n/es_ES.json', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/captcha/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Referrer-Policy headers or body meta tags were found on https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest /captcha/', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/cs_CZ.json', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Referrer-Policy headers or body meta tags were found on https://juice-shop-16-0-1-178712031365.us-west1.run.app /assets/i18n/cs_CZ.json', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/api/Feedbacks/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Referrer-Policy headers or body meta tags were found on https://juice-shop-16-0-1-178712031365.us-west1.run.app/api /Feedbacks/', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/en.json', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Referrer-Policy headers or body meta tags were found on https://juice-shop-16-0-1-178712031365.us-west1.run.app /assets/i18n/en.json', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/da_DK.json', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Referrer-Policy headers or body meta tags were found on https://juice-shop-16-0-1-178712031365.us-west1.run.app /assets/i18n/da_DK.json', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/languages', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Referrer-Policy headers or body meta tags were found on https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest /languages', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/socket.io/?EIO=4&amp;transport=polling&amp;t=PPlDpDO', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Referrer-Policy headers or body meta tags were found on https://juice-shop-16-0-1-178712031365.us-west1.run.app /socket.io/?EIO=4&amp;transport=polling&amp;t=PPlDpDO', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'text/plain'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/et_EE.json', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Referrer-Policy headers or body meta tags were found on https://juice-shop-16-0-1-178712031365.us-west1.run.app /assets/i18n/et_EE.json', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/az_AZ.json', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Referrer-Policy headers or body meta tags were found on https://juice-shop-16-0-1-178712031365.us-west1.run.app /assets/i18n/az_AZ.json', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/api/Quantitys/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Referrer-Policy headers or body meta tags were found on https://juice-shop-16-0-1-178712031365.us-west1.run.app/api /Quantitys/', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/api/Challenges/?name=Score%20Board', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Referrer-Policy headers or body meta tags were found on https://juice-shop-16-0-1-178712031365.us-west1.run.app/api /Challenges/?name=Score%20Board', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/memories/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Referrer-Policy headers or body meta tags were found on https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest /memories/', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/id_ID.json', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Referrer-Policy headers or body meta tags were found on https://juice-shop-16-0-1-178712031365.us-west1.run.app /assets/i18n/id_ID.json', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/fr_FR.json', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Referrer-Policy headers or body meta tags were found on https://juice-shop-16-0-1-178712031365.us-west1.run.app /assets/i18n/fr_FR.json', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/admin/application-version', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Referrer-Policy headers or body meta tags were found on https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest /admin/application-version', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}]</t>
         </is>
       </c>
-      <c r="O42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -4076,15 +2886,11 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -4112,31 +2918,6 @@
           <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/#/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': "The scanner detected 4 resources without subresource integrity defined : - 2 URLs related to 'script' resources - 2 URLs related to 'link' resources The list of all the detected resources is provided in attachment.", 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
-      <c r="O43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -4159,15 +2940,11 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -4195,31 +2972,6 @@
           <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/robots.txt', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': "A robots.txt file was detected at 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/robots.txt'.", 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/plain'}]</t>
         </is>
       </c>
-      <c r="O44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -4242,15 +2994,11 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -4278,31 +3026,6 @@
           <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/#/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scan detected 7631 unique XMLHttpRequests. Here is the distribution of MIME types used by the detected requests: - 174 as "application/json" - 5045 as "text/plain" - 2284 as "text/html" - 5 as "application/octet-stream" - 123 with no specified or detected MIME type The scan detected 15 unique Fetch Requests. Here is the distribution of MIME types used by the detected requests: - 5 as "application/json" - 7 as "text/html" - 1 as "text/fragment+html" - 1 as "text/plain" - 1 with no specified or detected MIME type', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q45" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R45" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -4325,15 +3048,11 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -4361,31 +3080,6 @@
           <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Certificate 1 -------------- Common Name: *.a.run.app Alternative Names: *.a.run.app run.app *.africa-south1.run.app *.asia-east1.run.app *.asia-east2.run.app *.asia\ufffenortheast1.run.app *.asia-northeast2.run.app *.asia-northeast3.run.app *.asia-south1.run.app *.asia-south2.run.app *. asia-southeast1.run.app *.asia-southeast2.run.app *.asia-southeast3.run.app *.australia-southeast1.run.app *.australia\ufffesoutheast2.run.app *.europe-central2.run.app *.europe-north1.run.app *.europe-north2.run.app *.europe-southwest1.run. app *.europe-west1.run.app *.europe-west10.run.app *.europe-west12.run.app *.europe-west15.run.app *.europe-west2.run. app *.europe-west3.run.app *.europe-west4.run.app *.europe-west5.run.app *.europe-west6.run.app *.europe-west8.run.app *.europe-west9.run.app *.me-central1.run.app *.me-central2.run.app *.me-west1.run.app *.northamerica-northeast1.run.app *.northamerica-northeast2.run.app *.northamerica-south1.run.app *.southamerica-east1.run.app *.southamerica-west1.run. app *.us-central1.run.app *.us-central2.run.app *.us-east1.run.app *.us-east4.run.app *.us-east5.run.app *.us-east7.run. app *.us-south1.run.app *.us-west1.run.app *.us-west2.run.app *.us-west3.run.app *.us-west4.run.app *.us-west8.run.app Issuer: Google Trust Services Valid from: 2025-03-31 08:54:20 UTC Valid until: 2025-06-23 08:54:19 UTC (expires in 1 month, 3 weeks, 6 days) Validity Period: 83 days Key: 256-bit Signature: ecdsa-with-SHA256 Certificate 2 -------------- Common Name: we2 Issuer: Google Trust Services LLC Valid from: 2023-12-13 09:00:00 UTC Valid until: 2029-02-20 14:00:00 UTC (expires in 3 years, 9 months, 3 weeks, 5 days) Validity Period: 1896 days Key: 256-bit Signature: ecdsa-with-SHA384 Certificate 3 -------------- Common Name: gts root r4 Issuer: GlobalSign nv Valid from: 2023-11-15 03:43:21 UTC Valid until: 2028-01-28 00:00:42 UTC (expires in 2 years, 9 months, 2 days) Validity Period: 1534 days Key: RSA 384-bit Signature: sha256WithRSAEncryption', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
-      <c r="O46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -4408,15 +3102,11 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -4444,31 +3134,6 @@
           <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Protocol Supported --------------------- SSL 2.0 No SSL 3.0 No TLS 1.0 No TLS 1.1 No TLS 1.2 Yes TLS 1.3 Yes', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
-      <c r="O47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -4491,15 +3156,11 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -4527,31 +3188,6 @@
           <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/api/Challenges/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'The following patterns were detected in the HTTP response body : - C:\\\\Windows\\\\system', 'output': 'The scanner detected the disclosure of full paths in the web application response.', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'application/json'}]</t>
         </is>
       </c>
-      <c r="O48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -4574,15 +3210,11 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -4610,31 +3242,6 @@
           <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner detected that the remote host is not configured with a cipher suite preference for the following protocol (s) : TLS v1.2, TLS v1.3', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -4657,15 +3264,11 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -4693,31 +3296,6 @@
           <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/#/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner detected the following HTTP versions on the target application : - HTTP/1.0 - HTTP/1.1 - HTTP/2 The list of requests and responses observed is provided in attachment.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
-      <c r="O50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -4740,15 +3318,11 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -4776,31 +3350,6 @@
           <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/api-docs/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner was able to detect a Swagger or OpenAPI definition file on https://juice-shop-16-0-1-178712031365.us-west1. run.app/api-docs/. The file is available in attachments.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
-      <c r="O51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -4823,15 +3372,11 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -4859,31 +3404,6 @@
           <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/#/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'API endpoints have been detected for the following host(s): - https://juice-shop-16-0-1-178712031365.us-west1.run.app - https://github.com', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
-      <c r="O52" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P52" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q52" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R52" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S52" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -4906,15 +3426,11 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -4942,31 +3458,6 @@
           <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/.well-known/security.txt', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': "A security.txt file was detected at 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/.well-known/security.txt'.", 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/plain'}]</t>
         </is>
       </c>
-      <c r="O53" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P53" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q53" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R53" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S53" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -4989,15 +3480,11 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -5025,31 +3512,6 @@
           <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Technology jQuery has been detected with version 2.2.4. Latest version available is : 3.7.1', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
-      <c r="O54" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P54" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q54" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R54" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S54" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -5072,15 +3534,11 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -5108,31 +3566,6 @@
           <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'A wildcard symbol (*) has been detected in the following certificate entries: Certificate Common Name: *.a.run.app Certificate Subject Alternative Names: - *.a.run.app - *.africa-south1.run.app - *.asia-east1.run.app - *.asia-east2.run.app - *.asia-northeast1.run.app - *.asia-northeast2.run.app - *.asia-northeast3.run.app - *.asia-south1.run.app - *.asia-south2.run.app - *.asia-southeast1.run.app - *.asia-southeast2.run.app - *.asia-southeast3.run.app - *.australia-southeast1.run.app - *.australia-southeast2.run.app - *.europe-central2.run.app - *.europe-north1.run.app - *.europe-north2.run.app - *.europe-southwest1.run.app - *.europe-west1.run.app - *.europe-west10.run.app - *.europe-west12.run.app - *.europe-west15.run.app - *.europe-west2.run.app - *.europe-west3.run.app - *.europe-west4.run.app - *.europe-west5.run.app - *.europe-west6.run.app - *.europe-west8.run.app - *.europe-west9.run.app - *.me-central1.run.app - *.me-central2.run.app - *.me-west1.run.app - *.northamerica-northeast1.run.app - *.northamerica-northeast2.run.app - *.northamerica-south1.run.app - *.southamerica-east1.run.app - *.southamerica-west1.run.app - *.us-central1.run.app - *.us-central2.run.app - *.us-east1.run.app - *.us-east4.run.app - *.us-east5.run.app - *.us-east7.run.app - *.us-south1.run.app - *.us-west1.run.app - *.us-west2.run.app - *.us-west3.run.app - *.us-west4.run.app - *.us-west8.run.app', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
-      <c r="O55" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P55" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q55" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R55" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S55" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -5155,15 +3588,11 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -5191,31 +3620,6 @@
           <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/#/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Three attachments are included in this finding to assist in performance tuning of your scan: -pages_telemetry.csv: Scan statistics organized by page -plugins_telemetry.csv: Scan statistics organized by plugin -time_telemetry.csv: Chronological scan statistics', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
-      <c r="O56" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P56" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q56" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R56" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S56" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -5238,15 +3642,11 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -5274,31 +3674,6 @@
           <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner detected the presence of listeners which does not check for the message origin. The code of the JavaScript function used by the listener is available in attachment.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': 'text/html'}]</t>
         </is>
       </c>
-      <c r="O57" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P57" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q57" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R57" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S57" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -5321,15 +3696,11 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -5357,31 +3728,6 @@
           <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': '3 HTML comments have been detected in the application HTTP response. Please see the attachment for further details.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/public/images/uploads/%F0%9F%98%BCIdentification', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': '2 HTML comments have been detected in the application HTTP response. Please see the attachment for further details.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': 'text/html'}]</t>
         </is>
       </c>
-      <c r="O58" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P58" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q58" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R58" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S58" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -5404,15 +3750,11 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -5440,31 +3782,6 @@
           <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/api-docs/swagger-ui-bundle.js', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner was able to detect the presence of JavaScript source maps in the response body.The following source map files were detected : - https://juice-shop-16-0-1-178712031365.us-west1.run.app/api-docs/swagger-ui-bundle.js.map', 'request_method': 'GET', 'http_status_code': None, 'http_protocol': 'HTTP/2', 'response_content_type': ''}]</t>
         </is>
       </c>
-      <c r="O59" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P59" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q59" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R59" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S59" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -5487,15 +3804,11 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -5523,31 +3836,6 @@
           <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/redirect', 'input_type': 'link', 'input_name': 'to', 'payload': 'was-tnb-jmx', 'proof': "Input reflected in the response body : 'was-tnb-jmx'.", 'output': 'The scanner was able to detect an input reflected in the response body.', 'request_method': 'GET', 'http_status_code': 406, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}]</t>
         </is>
       </c>
-      <c r="O60" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P60" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q60" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R60" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S60" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -5570,15 +3858,11 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -5606,31 +3890,6 @@
           <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'The scanner detected a WebSocket creation to the following endpoint: wss://juice-shop-16-0-1-178712031365.us-west1.run. app/socket.io/?EIO=4&amp;transport=websocket&amp;sid=q57_qHGEncDGUU1JAABc.The WebSocket creation has been initialized by the following resource : https://juice-shop-16-0-1-178712031365.us-west1.run.app/vendor.js (script)', 'output': 'The scanner was able to identify the usage of WebSockets on the target application.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': 'text/html'}]</t>
         </is>
       </c>
-      <c r="O61" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P61" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q61" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R61" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S61" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -5653,15 +3912,11 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -5689,31 +3944,6 @@
           <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': "The following value is extracted from a &lt;link&gt; tag that imports a style sheet with a 'href' that does not begin with a / : * styles.css", 'output': 'The scanner was able to detect a Path Relative Stylesheet Import.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/public/images/uploads/%F0%9F%98%BC\ufffeIdentification', 'input_type': '', 'input_name': '', 'payload': '', 'proof': "The following value is extracted from a &lt;link&gt; tag that imports a style sheet with a 'href' that does not begin with a / : * styles.css", 'output': 'The scanner was able to detect a Path Relative Stylesheet Import.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/api-docs/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': "The following value is extracted from a &lt;link&gt; tag that imports a style sheet with a 'href' that does not begin with a / : * ./swagger-ui.css", 'output': 'The scanner was able to detect a Path Relative Stylesheet Import.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': 'text/html'}]</t>
         </is>
       </c>
-      <c r="O62" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P62" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q62" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R62" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S62" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -5736,15 +3966,11 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -5772,31 +3998,6 @@
           <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/#/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': "By crafting a request with a specific 'Host' header the scanner obtained a different response", 'output': "The scanner was able to detect the present of another virtual host on the target ip 216.239.32.53: 'admin.us-west1.run. app:443'", 'request_method': 'GET', 'http_status_code': 404, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}]</t>
         </is>
       </c>
-      <c r="O63" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P63" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q63" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R63" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S63" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -5819,15 +4020,11 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -5855,31 +4052,6 @@
           <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/api/SecurityQuestions/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner was able to identify a REST API.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/api/Quantitys/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner was able to identify a REST API.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/api/Challenges/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner was able to identify a REST API.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/api/Feedbacks/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner was able to identify a REST API.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/api-docs/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner was able to identify a REST API.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
-      <c r="O64" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P64" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q64" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R64" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S64" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -5902,15 +4074,11 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -5938,31 +4106,6 @@
           <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Protocol Cipher Suite Name (RFC) Key Exchange Strength ---------------------------------------------------------------------------- TLS1.2 TLS_ECDHE_ECDSA_WITH_AES_128_GCM_SHA256 x25519 256 TLS1.2 TLS_ECDHE_ECDSA_WITH_CHACHA20_POLY1305 x25519 256 TLS1.2 TLS_ECDHE_ECDSA_WITH_AES_256_GCM_SHA384 x25519 256 TLS1.2 TLS_ECDHE_ECDSA_WITH_AES_128_CBC_SHA x25519 256 TLS1.2 TLS_ECDHE_ECDSA_WITH_AES_256_CBC_SHA x25519 256 TLS1.2 TLS_ECDHE_RSA_WITH_AES_128_GCM_SHA256 x25519 256 TLS1.2 TLS_ECDHE_RSA_WITH_AES_256_GCM_SHA384 x25519 256 TLS1.2 TLS_ECDHE_RSA_WITH_AES_128_CBC_SHA x25519 256 TLS1.2 TLS_ECDHE_RSA_WITH_AES_256_CBC_SHA x25519 256 TLS1.2 TLS_RSA_WITH_AES_128_GCM_SHA256 RSA 4096 TLS1.2 TLS_RSA_WITH_AES_256_GCM_SHA384 RSA 4096 TLS1.2 TLS_RSA_WITH_AES_128_CBC_SHA RSA 4096 TLS1.2 TLS_RSA_WITH_AES_256_CBC_SHA RSA 4096 TLS1.3 TLS_AES_128_GCM_SHA256 x25519 256 TLS1.3 TLS_AES_256_GCM_SHA384 x25519 256 TLS1.3 TLS_CHACHA20_POLY1305_SHA256 x25519 256', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
-      <c r="O65" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P65" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q65" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R65" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S65" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/resources/tenable/TenableWAS_JuiceShop.xlsx
+++ b/resources/tenable/TenableWAS_JuiceShop.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -519,6 +519,9 @@
           <t>HIGH</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -579,6 +582,9 @@
           <t>HIGH</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -639,6 +645,9 @@
           <t>HIGH</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -699,6 +708,9 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -759,6 +771,9 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -819,6 +834,9 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -879,6 +897,9 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -939,6 +960,9 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -999,6 +1023,9 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -1059,6 +1086,9 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -1122,6 +1152,9 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -1182,6 +1215,9 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -1242,6 +1278,9 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -1302,6 +1341,9 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -1362,6 +1404,9 @@
           <t>LOW</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -1422,6 +1467,9 @@
           <t>LOW</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -1482,6 +1530,9 @@
           <t>LOW</t>
         </is>
       </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -1542,6 +1593,9 @@
           <t>LOW</t>
         </is>
       </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -1602,6 +1656,9 @@
           <t>LOW</t>
         </is>
       </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -1662,6 +1719,9 @@
           <t>LOW</t>
         </is>
       </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -1721,6 +1781,9 @@
           <t>LOW</t>
         </is>
       </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -1780,6 +1843,9 @@
           <t>LOW</t>
         </is>
       </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -1840,6 +1906,9 @@
           <t>LOW</t>
         </is>
       </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -1900,6 +1969,9 @@
           <t>LOW</t>
         </is>
       </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -1959,6 +2031,9 @@
           <t>LOW</t>
         </is>
       </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -2008,11 +2083,15 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -2071,16 +2150,21 @@
 user_abort: The user stopped the scan before the URL could be audited']</t>
         </is>
       </c>
+      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
+      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -2130,11 +2214,15 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -2184,11 +2272,15 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -2238,11 +2330,15 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -2292,11 +2388,15 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -2346,11 +2446,15 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -2400,11 +2504,15 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -2454,11 +2562,15 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -2508,11 +2620,15 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -2547,11 +2663,7 @@
           <t>Target Information</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>['Publishes the target information of the starting url as evaluated by the scan.']</t>
-        </is>
-      </c>
+      <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2562,11 +2674,15 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -2616,11 +2732,15 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -2670,11 +2790,15 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -2724,11 +2848,15 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -2778,11 +2906,15 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -2832,11 +2964,15 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -2886,11 +3022,15 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -2940,11 +3080,15 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -2994,11 +3138,15 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -3048,11 +3196,15 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -3102,11 +3254,15 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -3156,11 +3312,15 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -3210,11 +3370,15 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -3264,11 +3428,15 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -3303,11 +3471,7 @@
           <t>OpenAPI File Detected</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>['A OpenAPI configuration file has been detected and is available as an attachment below. OpenAPI is a specification that helps with documentation and consumption of REST APIs and may also be used to configure API scanning.']</t>
-        </is>
-      </c>
+      <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3318,11 +3482,15 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -3357,11 +3525,7 @@
           <t>API Detected</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>['The scan detected that some XHR requests seem to call an API. The scanner generated an OpenAPI file based on the observed requests and attached it to the plugin output. This OpenAPI file can then be used to run a scan against the API with WAS API Scanning.']</t>
-        </is>
-      </c>
+      <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3372,11 +3536,15 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -3426,11 +3594,15 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -3480,11 +3652,15 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -3534,11 +3710,15 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -3588,11 +3768,15 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -3642,11 +3826,15 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -3696,11 +3884,15 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -3750,11 +3942,15 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -3804,11 +4000,15 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -3858,11 +4058,15 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -3912,11 +4116,15 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -3966,11 +4174,15 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -4005,11 +4217,7 @@
           <t>REST API Detected</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>['This is an informational notice that the scanner was able to detect a REST API.']</t>
-        </is>
-      </c>
+      <c r="B64" t="inlineStr"/>
       <c r="C64" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4020,11 +4228,15 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -4059,11 +4271,7 @@
           <t>SSL/TLS Cipher Suites Supported</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>['This plugin displays supported SSL/TLS cipher suites.']</t>
-        </is>
-      </c>
+      <c r="B65" t="inlineStr"/>
       <c r="C65" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4074,11 +4282,15 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
